--- a/vs-x64/Running erasure.xlsx
+++ b/vs-x64/Running erasure.xlsx
@@ -5080,19 +5080,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>14.6203</v>
+        <v>14.1525</v>
       </c>
       <c r="C2" t="n">
-        <v>35.8256</v>
+        <v>14.915</v>
       </c>
       <c r="D2" t="n">
-        <v>42.0444</v>
+        <v>43.6711</v>
       </c>
       <c r="E2" t="n">
-        <v>14.1354</v>
+        <v>13.6242</v>
       </c>
       <c r="F2" t="n">
-        <v>34.602</v>
+        <v>34.344</v>
       </c>
     </row>
     <row r="3">
@@ -5100,19 +5100,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>14.2848</v>
+        <v>13.8265</v>
       </c>
       <c r="C3" t="n">
-        <v>35.692</v>
+        <v>15.0558</v>
       </c>
       <c r="D3" t="n">
-        <v>42.0165</v>
+        <v>43.4323</v>
       </c>
       <c r="E3" t="n">
-        <v>14.0956</v>
+        <v>13.5542</v>
       </c>
       <c r="F3" t="n">
-        <v>34.5307</v>
+        <v>34.3696</v>
       </c>
     </row>
     <row r="4">
@@ -5120,19 +5120,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>13.9208</v>
+        <v>13.523</v>
       </c>
       <c r="C4" t="n">
-        <v>34.8543</v>
+        <v>15.0996</v>
       </c>
       <c r="D4" t="n">
-        <v>42.1459</v>
+        <v>43.621</v>
       </c>
       <c r="E4" t="n">
-        <v>13.8489</v>
+        <v>13.3022</v>
       </c>
       <c r="F4" t="n">
-        <v>34.4057</v>
+        <v>34.0415</v>
       </c>
     </row>
     <row r="5">
@@ -5140,19 +5140,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>13.7294</v>
+        <v>13.4676</v>
       </c>
       <c r="C5" t="n">
-        <v>34.5837</v>
+        <v>15.0536</v>
       </c>
       <c r="D5" t="n">
-        <v>42.2098</v>
+        <v>43.7665</v>
       </c>
       <c r="E5" t="n">
-        <v>13.7134</v>
+        <v>13.1719</v>
       </c>
       <c r="F5" t="n">
-        <v>34.1048</v>
+        <v>34.1647</v>
       </c>
     </row>
     <row r="6">
@@ -5160,19 +5160,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>13.4119</v>
+        <v>13.159</v>
       </c>
       <c r="C6" t="n">
-        <v>33.9368</v>
+        <v>15.1504</v>
       </c>
       <c r="D6" t="n">
-        <v>42.2679</v>
+        <v>43.7939</v>
       </c>
       <c r="E6" t="n">
-        <v>13.5446</v>
+        <v>13.0123</v>
       </c>
       <c r="F6" t="n">
-        <v>34.0374</v>
+        <v>33.8867</v>
       </c>
     </row>
     <row r="7">
@@ -5180,19 +5180,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>13.0627</v>
+        <v>13.1479</v>
       </c>
       <c r="C7" t="n">
-        <v>33.6891</v>
+        <v>15.1958</v>
       </c>
       <c r="D7" t="n">
-        <v>42.6723</v>
+        <v>44.0201</v>
       </c>
       <c r="E7" t="n">
-        <v>13.2907</v>
+        <v>12.7756</v>
       </c>
       <c r="F7" t="n">
-        <v>33.738</v>
+        <v>33.4888</v>
       </c>
     </row>
     <row r="8">
@@ -5200,19 +5200,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>12.8589</v>
+        <v>12.6984</v>
       </c>
       <c r="C8" t="n">
-        <v>32.6819</v>
+        <v>16.9344</v>
       </c>
       <c r="D8" t="n">
-        <v>42.6409</v>
+        <v>43.9727</v>
       </c>
       <c r="E8" t="n">
-        <v>13.0678</v>
+        <v>12.4857</v>
       </c>
       <c r="F8" t="n">
-        <v>33.6224</v>
+        <v>33.27</v>
       </c>
     </row>
     <row r="9">
@@ -5220,19 +5220,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>12.4805</v>
+        <v>12.3138</v>
       </c>
       <c r="C9" t="n">
-        <v>32.8035</v>
+        <v>16.8945</v>
       </c>
       <c r="D9" t="n">
-        <v>42.8006</v>
+        <v>44.0559</v>
       </c>
       <c r="E9" t="n">
-        <v>16.3291</v>
+        <v>15.6713</v>
       </c>
       <c r="F9" t="n">
-        <v>37.0185</v>
+        <v>36.3985</v>
       </c>
     </row>
     <row r="10">
@@ -5240,19 +5240,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>17.2307</v>
+        <v>16.707</v>
       </c>
       <c r="C10" t="n">
-        <v>37.5644</v>
+        <v>16.7534</v>
       </c>
       <c r="D10" t="n">
-        <v>42.6398</v>
+        <v>44.0456</v>
       </c>
       <c r="E10" t="n">
-        <v>19.059</v>
+        <v>15.5998</v>
       </c>
       <c r="F10" t="n">
-        <v>36.9164</v>
+        <v>36.1627</v>
       </c>
     </row>
     <row r="11">
@@ -5260,19 +5260,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>16.9763</v>
+        <v>16.472</v>
       </c>
       <c r="C11" t="n">
-        <v>37.3858</v>
+        <v>16.7053</v>
       </c>
       <c r="D11" t="n">
-        <v>42.7557</v>
+        <v>44.0946</v>
       </c>
       <c r="E11" t="n">
-        <v>17.738</v>
+        <v>15.3608</v>
       </c>
       <c r="F11" t="n">
-        <v>36.5248</v>
+        <v>35.9909</v>
       </c>
     </row>
     <row r="12">
@@ -5280,19 +5280,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>16.7694</v>
+        <v>16.1743</v>
       </c>
       <c r="C12" t="n">
-        <v>37.0837</v>
+        <v>16.6486</v>
       </c>
       <c r="D12" t="n">
-        <v>42.8323</v>
+        <v>44.1844</v>
       </c>
       <c r="E12" t="n">
-        <v>15.978</v>
+        <v>15.2458</v>
       </c>
       <c r="F12" t="n">
-        <v>36.2129</v>
+        <v>35.6846</v>
       </c>
     </row>
     <row r="13">
@@ -5300,19 +5300,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>16.3271</v>
+        <v>15.822</v>
       </c>
       <c r="C13" t="n">
-        <v>37.1564</v>
+        <v>16.4608</v>
       </c>
       <c r="D13" t="n">
-        <v>42.8666</v>
+        <v>44.0803</v>
       </c>
       <c r="E13" t="n">
-        <v>15.7648</v>
+        <v>14.9659</v>
       </c>
       <c r="F13" t="n">
-        <v>35.9478</v>
+        <v>35.5644</v>
       </c>
     </row>
     <row r="14">
@@ -5320,19 +5320,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>16.0035</v>
+        <v>15.4923</v>
       </c>
       <c r="C14" t="n">
-        <v>36.7544</v>
+        <v>16.3643</v>
       </c>
       <c r="D14" t="n">
-        <v>42.8627</v>
+        <v>44.203</v>
       </c>
       <c r="E14" t="n">
-        <v>17.4594</v>
+        <v>14.7094</v>
       </c>
       <c r="F14" t="n">
-        <v>35.6678</v>
+        <v>35.9093</v>
       </c>
     </row>
     <row r="15">
@@ -5340,19 +5340,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>15.6107</v>
+        <v>15.2396</v>
       </c>
       <c r="C15" t="n">
-        <v>36.4583</v>
+        <v>16.3243</v>
       </c>
       <c r="D15" t="n">
-        <v>42.7696</v>
+        <v>44.1618</v>
       </c>
       <c r="E15" t="n">
-        <v>15.2151</v>
+        <v>14.5516</v>
       </c>
       <c r="F15" t="n">
-        <v>35.4409</v>
+        <v>35.1271</v>
       </c>
     </row>
     <row r="16">
@@ -5360,19 +5360,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>15.328</v>
+        <v>15.1086</v>
       </c>
       <c r="C16" t="n">
-        <v>36.0835</v>
+        <v>16.2557</v>
       </c>
       <c r="D16" t="n">
-        <v>42.804</v>
+        <v>44.3819</v>
       </c>
       <c r="E16" t="n">
-        <v>15.0335</v>
+        <v>14.374</v>
       </c>
       <c r="F16" t="n">
-        <v>35.2756</v>
+        <v>34.9785</v>
       </c>
     </row>
     <row r="17">
@@ -5380,19 +5380,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>14.9474</v>
+        <v>14.7609</v>
       </c>
       <c r="C17" t="n">
-        <v>35.7026</v>
+        <v>16.1113</v>
       </c>
       <c r="D17" t="n">
-        <v>42.8028</v>
+        <v>44.3205</v>
       </c>
       <c r="E17" t="n">
-        <v>14.8327</v>
+        <v>14.1573</v>
       </c>
       <c r="F17" t="n">
-        <v>35.0984</v>
+        <v>34.7474</v>
       </c>
     </row>
     <row r="18">
@@ -5400,19 +5400,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>14.6966</v>
+        <v>14.4808</v>
       </c>
       <c r="C18" t="n">
-        <v>35.3843</v>
+        <v>15.9766</v>
       </c>
       <c r="D18" t="n">
-        <v>42.7172</v>
+        <v>44.3682</v>
       </c>
       <c r="E18" t="n">
-        <v>14.5909</v>
+        <v>14.0174</v>
       </c>
       <c r="F18" t="n">
-        <v>34.8601</v>
+        <v>34.5544</v>
       </c>
     </row>
     <row r="19">
@@ -5420,19 +5420,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>14.2223</v>
+        <v>14.1795</v>
       </c>
       <c r="C19" t="n">
-        <v>34.889</v>
+        <v>16.0638</v>
       </c>
       <c r="D19" t="n">
-        <v>42.8514</v>
+        <v>44.4829</v>
       </c>
       <c r="E19" t="n">
-        <v>14.4052</v>
+        <v>13.716</v>
       </c>
       <c r="F19" t="n">
-        <v>34.5967</v>
+        <v>34.5133</v>
       </c>
     </row>
     <row r="20">
@@ -5440,19 +5440,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>14.0334</v>
+        <v>13.8125</v>
       </c>
       <c r="C20" t="n">
-        <v>34.4648</v>
+        <v>15.9902</v>
       </c>
       <c r="D20" t="n">
-        <v>42.7298</v>
+        <v>44.4168</v>
       </c>
       <c r="E20" t="n">
-        <v>14.1416</v>
+        <v>13.5447</v>
       </c>
       <c r="F20" t="n">
-        <v>34.4508</v>
+        <v>34.2182</v>
       </c>
     </row>
     <row r="21">
@@ -5460,19 +5460,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>13.6967</v>
+        <v>13.7059</v>
       </c>
       <c r="C21" t="n">
-        <v>34.202</v>
+        <v>15.7596</v>
       </c>
       <c r="D21" t="n">
-        <v>43.2471</v>
+        <v>44.6855</v>
       </c>
       <c r="E21" t="n">
-        <v>13.9079</v>
+        <v>13.1677</v>
       </c>
       <c r="F21" t="n">
-        <v>34.2357</v>
+        <v>33.982</v>
       </c>
     </row>
     <row r="22">
@@ -5480,19 +5480,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>13.2759</v>
+        <v>13.1152</v>
       </c>
       <c r="C22" t="n">
-        <v>33.6747</v>
+        <v>17.5631</v>
       </c>
       <c r="D22" t="n">
-        <v>43.3005</v>
+        <v>44.7908</v>
       </c>
       <c r="E22" t="n">
-        <v>13.7216</v>
+        <v>13.0193</v>
       </c>
       <c r="F22" t="n">
-        <v>33.883</v>
+        <v>33.6869</v>
       </c>
     </row>
     <row r="23">
@@ -5500,19 +5500,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.8018</v>
+        <v>12.6437</v>
       </c>
       <c r="C23" t="n">
-        <v>32.9743</v>
+        <v>17.4257</v>
       </c>
       <c r="D23" t="n">
-        <v>43.2689</v>
+        <v>44.6638</v>
       </c>
       <c r="E23" t="n">
-        <v>16.5604</v>
+        <v>15.9818</v>
       </c>
       <c r="F23" t="n">
-        <v>37.4936</v>
+        <v>36.9171</v>
       </c>
     </row>
     <row r="24">
@@ -5520,19 +5520,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>17.5348</v>
+        <v>17.3793</v>
       </c>
       <c r="C24" t="n">
-        <v>38.4425</v>
+        <v>17.2735</v>
       </c>
       <c r="D24" t="n">
-        <v>43.3142</v>
+        <v>44.7373</v>
       </c>
       <c r="E24" t="n">
-        <v>16.4202</v>
+        <v>15.7275</v>
       </c>
       <c r="F24" t="n">
-        <v>37.2224</v>
+        <v>36.7143</v>
       </c>
     </row>
     <row r="25">
@@ -5540,19 +5540,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>17.2549</v>
+        <v>17.1628</v>
       </c>
       <c r="C25" t="n">
-        <v>37.4983</v>
+        <v>17.166</v>
       </c>
       <c r="D25" t="n">
-        <v>43.3665</v>
+        <v>44.761</v>
       </c>
       <c r="E25" t="n">
-        <v>16.184</v>
+        <v>15.5364</v>
       </c>
       <c r="F25" t="n">
-        <v>37.1241</v>
+        <v>36.5094</v>
       </c>
     </row>
     <row r="26">
@@ -5560,19 +5560,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>16.9158</v>
+        <v>16.8269</v>
       </c>
       <c r="C26" t="n">
-        <v>37.4796</v>
+        <v>17.0135</v>
       </c>
       <c r="D26" t="n">
-        <v>43.3596</v>
+        <v>44.6882</v>
       </c>
       <c r="E26" t="n">
-        <v>16.0318</v>
+        <v>15.3677</v>
       </c>
       <c r="F26" t="n">
-        <v>37.1628</v>
+        <v>36.2847</v>
       </c>
     </row>
     <row r="27">
@@ -5580,19 +5580,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>16.5532</v>
+        <v>16.491</v>
       </c>
       <c r="C27" t="n">
-        <v>37.3494</v>
+        <v>16.8913</v>
       </c>
       <c r="D27" t="n">
-        <v>43.2251</v>
+        <v>44.7944</v>
       </c>
       <c r="E27" t="n">
-        <v>15.7812</v>
+        <v>15.1884</v>
       </c>
       <c r="F27" t="n">
-        <v>36.4397</v>
+        <v>36.5126</v>
       </c>
     </row>
     <row r="28">
@@ -5600,19 +5600,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>16.1838</v>
+        <v>16.1506</v>
       </c>
       <c r="C28" t="n">
-        <v>36.9974</v>
+        <v>16.8018</v>
       </c>
       <c r="D28" t="n">
-        <v>43.1213</v>
+        <v>44.8044</v>
       </c>
       <c r="E28" t="n">
-        <v>15.6322</v>
+        <v>15.0253</v>
       </c>
       <c r="F28" t="n">
-        <v>36.324</v>
+        <v>36.1392</v>
       </c>
     </row>
     <row r="29">
@@ -5620,19 +5620,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>15.815</v>
+        <v>15.8248</v>
       </c>
       <c r="C29" t="n">
-        <v>36.5864</v>
+        <v>16.7541</v>
       </c>
       <c r="D29" t="n">
-        <v>43.1407</v>
+        <v>44.8781</v>
       </c>
       <c r="E29" t="n">
-        <v>15.4764</v>
+        <v>14.8368</v>
       </c>
       <c r="F29" t="n">
-        <v>36.1033</v>
+        <v>35.9238</v>
       </c>
     </row>
     <row r="30">
@@ -5640,19 +5640,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>15.4768</v>
+        <v>15.4822</v>
       </c>
       <c r="C30" t="n">
-        <v>36.4084</v>
+        <v>16.6275</v>
       </c>
       <c r="D30" t="n">
-        <v>43.2514</v>
+        <v>44.8185</v>
       </c>
       <c r="E30" t="n">
-        <v>15.2451</v>
+        <v>14.6094</v>
       </c>
       <c r="F30" t="n">
-        <v>35.749</v>
+        <v>35.5061</v>
       </c>
     </row>
     <row r="31">
@@ -5660,19 +5660,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>15.1391</v>
+        <v>15.1593</v>
       </c>
       <c r="C31" t="n">
-        <v>36.0286</v>
+        <v>16.5381</v>
       </c>
       <c r="D31" t="n">
-        <v>43.264</v>
+        <v>44.7925</v>
       </c>
       <c r="E31" t="n">
-        <v>15.004</v>
+        <v>14.4126</v>
       </c>
       <c r="F31" t="n">
-        <v>35.4998</v>
+        <v>35.215</v>
       </c>
     </row>
     <row r="32">
@@ -5680,19 +5680,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>14.8346</v>
+        <v>14.8267</v>
       </c>
       <c r="C32" t="n">
-        <v>35.647</v>
+        <v>16.4101</v>
       </c>
       <c r="D32" t="n">
-        <v>43.199</v>
+        <v>44.724</v>
       </c>
       <c r="E32" t="n">
-        <v>14.8088</v>
+        <v>14.2064</v>
       </c>
       <c r="F32" t="n">
-        <v>35.1925</v>
+        <v>35.0581</v>
       </c>
     </row>
     <row r="33">
@@ -5700,19 +5700,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>14.5744</v>
+        <v>14.5299</v>
       </c>
       <c r="C33" t="n">
-        <v>35.5093</v>
+        <v>16.3626</v>
       </c>
       <c r="D33" t="n">
-        <v>43.2886</v>
+        <v>44.7761</v>
       </c>
       <c r="E33" t="n">
-        <v>14.6147</v>
+        <v>14.0267</v>
       </c>
       <c r="F33" t="n">
-        <v>35.0006</v>
+        <v>34.9313</v>
       </c>
     </row>
     <row r="34">
@@ -5720,19 +5720,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>14.3026</v>
+        <v>14.2063</v>
       </c>
       <c r="C34" t="n">
-        <v>34.6778</v>
+        <v>16.3312</v>
       </c>
       <c r="D34" t="n">
-        <v>43.2605</v>
+        <v>44.8176</v>
       </c>
       <c r="E34" t="n">
-        <v>14.4734</v>
+        <v>13.7855</v>
       </c>
       <c r="F34" t="n">
-        <v>34.7545</v>
+        <v>34.4943</v>
       </c>
     </row>
     <row r="35">
@@ -5740,19 +5740,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>13.9799</v>
+        <v>13.9179</v>
       </c>
       <c r="C35" t="n">
-        <v>34.3819</v>
+        <v>16.2008</v>
       </c>
       <c r="D35" t="n">
-        <v>43.8599</v>
+        <v>45.2753</v>
       </c>
       <c r="E35" t="n">
-        <v>14.1929</v>
+        <v>13.5204</v>
       </c>
       <c r="F35" t="n">
-        <v>34.5787</v>
+        <v>34.249</v>
       </c>
     </row>
     <row r="36">
@@ -5760,19 +5760,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>13.6265</v>
+        <v>13.5209</v>
       </c>
       <c r="C36" t="n">
-        <v>34.0561</v>
+        <v>16.1407</v>
       </c>
       <c r="D36" t="n">
-        <v>43.8679</v>
+        <v>45.24</v>
       </c>
       <c r="E36" t="n">
-        <v>13.8873</v>
+        <v>13.2955</v>
       </c>
       <c r="F36" t="n">
-        <v>34.224</v>
+        <v>34.4689</v>
       </c>
     </row>
     <row r="37">
@@ -5780,19 +5780,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.1932</v>
+        <v>13.1181</v>
       </c>
       <c r="C37" t="n">
-        <v>33.1729</v>
+        <v>17.7192</v>
       </c>
       <c r="D37" t="n">
-        <v>43.8045</v>
+        <v>45.1372</v>
       </c>
       <c r="E37" t="n">
-        <v>17.0291</v>
+        <v>16.4402</v>
       </c>
       <c r="F37" t="n">
-        <v>38.2542</v>
+        <v>37.5715</v>
       </c>
     </row>
     <row r="38">
@@ -5800,19 +5800,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>17.5953</v>
+        <v>17.4622</v>
       </c>
       <c r="C38" t="n">
-        <v>38.1346</v>
+        <v>17.589</v>
       </c>
       <c r="D38" t="n">
-        <v>43.8575</v>
+        <v>45.1665</v>
       </c>
       <c r="E38" t="n">
-        <v>16.7433</v>
+        <v>16.1897</v>
       </c>
       <c r="F38" t="n">
-        <v>37.7895</v>
+        <v>37.1423</v>
       </c>
     </row>
     <row r="39">
@@ -5820,19 +5820,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>17.317</v>
+        <v>17.2062</v>
       </c>
       <c r="C39" t="n">
-        <v>37.8693</v>
+        <v>17.3586</v>
       </c>
       <c r="D39" t="n">
-        <v>43.7994</v>
+        <v>45.2385</v>
       </c>
       <c r="E39" t="n">
-        <v>16.5065</v>
+        <v>15.9326</v>
       </c>
       <c r="F39" t="n">
-        <v>37.2727</v>
+        <v>36.9244</v>
       </c>
     </row>
     <row r="40">
@@ -5840,19 +5840,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>16.9875</v>
+        <v>16.9204</v>
       </c>
       <c r="C40" t="n">
-        <v>37.6447</v>
+        <v>17.2209</v>
       </c>
       <c r="D40" t="n">
-        <v>43.528</v>
+        <v>45.1382</v>
       </c>
       <c r="E40" t="n">
-        <v>16.2372</v>
+        <v>15.7315</v>
       </c>
       <c r="F40" t="n">
-        <v>36.9521</v>
+        <v>36.5939</v>
       </c>
     </row>
     <row r="41">
@@ -5860,19 +5860,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>16.6667</v>
+        <v>16.5861</v>
       </c>
       <c r="C41" t="n">
-        <v>37.5131</v>
+        <v>17.072</v>
       </c>
       <c r="D41" t="n">
-        <v>43.6337</v>
+        <v>45.1758</v>
       </c>
       <c r="E41" t="n">
-        <v>16.081</v>
+        <v>15.4253</v>
       </c>
       <c r="F41" t="n">
-        <v>36.9851</v>
+        <v>36.3569</v>
       </c>
     </row>
     <row r="42">
@@ -5880,19 +5880,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>16.3197</v>
+        <v>16.2456</v>
       </c>
       <c r="C42" t="n">
-        <v>37.3528</v>
+        <v>16.9612</v>
       </c>
       <c r="D42" t="n">
-        <v>43.7067</v>
+        <v>45.2626</v>
       </c>
       <c r="E42" t="n">
-        <v>15.8857</v>
+        <v>15.2745</v>
       </c>
       <c r="F42" t="n">
-        <v>36.76</v>
+        <v>36.1199</v>
       </c>
     </row>
     <row r="43">
@@ -5900,19 +5900,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>16.0012</v>
+        <v>15.8975</v>
       </c>
       <c r="C43" t="n">
-        <v>37.0639</v>
+        <v>16.8477</v>
       </c>
       <c r="D43" t="n">
-        <v>43.6525</v>
+        <v>45.0895</v>
       </c>
       <c r="E43" t="n">
-        <v>15.702</v>
+        <v>15.0978</v>
       </c>
       <c r="F43" t="n">
-        <v>36.2367</v>
+        <v>36.029</v>
       </c>
     </row>
     <row r="44">
@@ -5920,19 +5920,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>15.6354</v>
+        <v>15.5771</v>
       </c>
       <c r="C44" t="n">
-        <v>36.7522</v>
+        <v>16.7511</v>
       </c>
       <c r="D44" t="n">
-        <v>43.7063</v>
+        <v>45.2942</v>
       </c>
       <c r="E44" t="n">
-        <v>15.4662</v>
+        <v>14.8944</v>
       </c>
       <c r="F44" t="n">
-        <v>36.0523</v>
+        <v>35.6586</v>
       </c>
     </row>
     <row r="45">
@@ -5940,19 +5940,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>15.2942</v>
+        <v>15.2218</v>
       </c>
       <c r="C45" t="n">
-        <v>36.44</v>
+        <v>16.6122</v>
       </c>
       <c r="D45" t="n">
-        <v>43.7269</v>
+        <v>45.1719</v>
       </c>
       <c r="E45" t="n">
-        <v>15.2997</v>
+        <v>14.6829</v>
       </c>
       <c r="F45" t="n">
-        <v>35.837</v>
+        <v>35.4036</v>
       </c>
     </row>
     <row r="46">
@@ -5960,19 +5960,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>14.964</v>
+        <v>14.9134</v>
       </c>
       <c r="C46" t="n">
-        <v>36.2935</v>
+        <v>16.5289</v>
       </c>
       <c r="D46" t="n">
-        <v>43.539</v>
+        <v>45.0164</v>
       </c>
       <c r="E46" t="n">
-        <v>15.0619</v>
+        <v>14.5018</v>
       </c>
       <c r="F46" t="n">
-        <v>35.5509</v>
+        <v>35.1297</v>
       </c>
     </row>
     <row r="47">
@@ -5980,19 +5980,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>14.6665</v>
+        <v>14.6104</v>
       </c>
       <c r="C47" t="n">
-        <v>35.7101</v>
+        <v>16.4714</v>
       </c>
       <c r="D47" t="n">
-        <v>43.3845</v>
+        <v>45.1144</v>
       </c>
       <c r="E47" t="n">
-        <v>14.8846</v>
+        <v>14.2642</v>
       </c>
       <c r="F47" t="n">
-        <v>35.3088</v>
+        <v>34.9654</v>
       </c>
     </row>
     <row r="48">
@@ -6000,19 +6000,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>14.3893</v>
+        <v>14.3253</v>
       </c>
       <c r="C48" t="n">
-        <v>35.2704</v>
+        <v>16.3971</v>
       </c>
       <c r="D48" t="n">
-        <v>43.6211</v>
+        <v>45.1633</v>
       </c>
       <c r="E48" t="n">
-        <v>14.6464</v>
+        <v>14.0196</v>
       </c>
       <c r="F48" t="n">
-        <v>35.2948</v>
+        <v>34.7749</v>
       </c>
     </row>
     <row r="49">
@@ -6020,19 +6020,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>14.0625</v>
+        <v>14.0213</v>
       </c>
       <c r="C49" t="n">
-        <v>34.8792</v>
+        <v>16.3126</v>
       </c>
       <c r="D49" t="n">
-        <v>43.5102</v>
+        <v>45.2458</v>
       </c>
       <c r="E49" t="n">
-        <v>14.4297</v>
+        <v>13.8242</v>
       </c>
       <c r="F49" t="n">
-        <v>34.8125</v>
+        <v>34.5198</v>
       </c>
     </row>
     <row r="50">
@@ -6040,19 +6040,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>13.7158</v>
+        <v>13.6924</v>
       </c>
       <c r="C50" t="n">
-        <v>34.2861</v>
+        <v>16.3062</v>
       </c>
       <c r="D50" t="n">
-        <v>44.259</v>
+        <v>45.7083</v>
       </c>
       <c r="E50" t="n">
-        <v>14.1399</v>
+        <v>13.5724</v>
       </c>
       <c r="F50" t="n">
-        <v>34.7615</v>
+        <v>34.4198</v>
       </c>
     </row>
     <row r="51">
@@ -6060,19 +6060,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>13.2963</v>
+        <v>13.2762</v>
       </c>
       <c r="C51" t="n">
-        <v>33.6925</v>
+        <v>17.8066</v>
       </c>
       <c r="D51" t="n">
-        <v>44.2677</v>
+        <v>45.6727</v>
       </c>
       <c r="E51" t="n">
-        <v>17.239</v>
+        <v>16.6953</v>
       </c>
       <c r="F51" t="n">
-        <v>38.0691</v>
+        <v>37.6753</v>
       </c>
     </row>
     <row r="52">
@@ -6080,19 +6080,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>12.7907</v>
+        <v>12.7389</v>
       </c>
       <c r="C52" t="n">
-        <v>32.8377</v>
+        <v>17.6272</v>
       </c>
       <c r="D52" t="n">
-        <v>44.2441</v>
+        <v>45.6994</v>
       </c>
       <c r="E52" t="n">
-        <v>16.9878</v>
+        <v>16.402</v>
       </c>
       <c r="F52" t="n">
-        <v>38.1845</v>
+        <v>37.4115</v>
       </c>
     </row>
     <row r="53">
@@ -6100,19 +6100,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>17.4436</v>
+        <v>17.3138</v>
       </c>
       <c r="C53" t="n">
-        <v>38.6763</v>
+        <v>17.4597</v>
       </c>
       <c r="D53" t="n">
-        <v>44.0665</v>
+        <v>45.515</v>
       </c>
       <c r="E53" t="n">
-        <v>16.7422</v>
+        <v>16.1227</v>
       </c>
       <c r="F53" t="n">
-        <v>37.7003</v>
+        <v>37.6511</v>
       </c>
     </row>
     <row r="54">
@@ -6120,19 +6120,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>17.1223</v>
+        <v>17.0268</v>
       </c>
       <c r="C54" t="n">
-        <v>38.1695</v>
+        <v>17.3238</v>
       </c>
       <c r="D54" t="n">
-        <v>44.0977</v>
+        <v>45.4916</v>
       </c>
       <c r="E54" t="n">
-        <v>16.4881</v>
+        <v>15.8334</v>
       </c>
       <c r="F54" t="n">
-        <v>37.379</v>
+        <v>37.0787</v>
       </c>
     </row>
     <row r="55">
@@ -6140,19 +6140,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>16.7792</v>
+        <v>16.6952</v>
       </c>
       <c r="C55" t="n">
-        <v>38.4641</v>
+        <v>17.1634</v>
       </c>
       <c r="D55" t="n">
-        <v>44.0086</v>
+        <v>45.5716</v>
       </c>
       <c r="E55" t="n">
-        <v>16.2772</v>
+        <v>15.6371</v>
       </c>
       <c r="F55" t="n">
-        <v>37.339</v>
+        <v>37.2321</v>
       </c>
     </row>
     <row r="56">
@@ -6160,19 +6160,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>16.4377</v>
+        <v>16.3641</v>
       </c>
       <c r="C56" t="n">
-        <v>38.189</v>
+        <v>17.0121</v>
       </c>
       <c r="D56" t="n">
-        <v>44.1409</v>
+        <v>45.4878</v>
       </c>
       <c r="E56" t="n">
-        <v>16.0876</v>
+        <v>15.4089</v>
       </c>
       <c r="F56" t="n">
-        <v>37.5379</v>
+        <v>36.8835</v>
       </c>
     </row>
     <row r="57">
@@ -6180,19 +6180,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>16.0747</v>
+        <v>16.0183</v>
       </c>
       <c r="C57" t="n">
-        <v>37.9827</v>
+        <v>16.91</v>
       </c>
       <c r="D57" t="n">
-        <v>43.911</v>
+        <v>45.6032</v>
       </c>
       <c r="E57" t="n">
-        <v>15.9236</v>
+        <v>15.1866</v>
       </c>
       <c r="F57" t="n">
-        <v>36.8576</v>
+        <v>37.0299</v>
       </c>
     </row>
     <row r="58">
@@ -6200,19 +6200,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>15.7412</v>
+        <v>15.6799</v>
       </c>
       <c r="C58" t="n">
-        <v>37.9703</v>
+        <v>16.7965</v>
       </c>
       <c r="D58" t="n">
-        <v>44.0838</v>
+        <v>45.5881</v>
       </c>
       <c r="E58" t="n">
-        <v>15.693</v>
+        <v>15.0239</v>
       </c>
       <c r="F58" t="n">
-        <v>36.8533</v>
+        <v>36.6915</v>
       </c>
     </row>
     <row r="59">
@@ -6220,19 +6220,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>15.3986</v>
+        <v>15.3423</v>
       </c>
       <c r="C59" t="n">
-        <v>38.2459</v>
+        <v>16.7105</v>
       </c>
       <c r="D59" t="n">
-        <v>44.3134</v>
+        <v>45.885</v>
       </c>
       <c r="E59" t="n">
-        <v>15.4779</v>
+        <v>14.8301</v>
       </c>
       <c r="F59" t="n">
-        <v>37.3075</v>
+        <v>36.4082</v>
       </c>
     </row>
     <row r="60">
@@ -6240,19 +6240,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>15.0556</v>
+        <v>15.0461</v>
       </c>
       <c r="C60" t="n">
-        <v>38.1843</v>
+        <v>16.6051</v>
       </c>
       <c r="D60" t="n">
-        <v>44.3822</v>
+        <v>46.1056</v>
       </c>
       <c r="E60" t="n">
-        <v>15.2506</v>
+        <v>14.6411</v>
       </c>
       <c r="F60" t="n">
-        <v>37.2756</v>
+        <v>37.1899</v>
       </c>
     </row>
     <row r="61">
@@ -6260,19 +6260,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>14.7276</v>
+        <v>14.703</v>
       </c>
       <c r="C61" t="n">
-        <v>38.5091</v>
+        <v>16.5312</v>
       </c>
       <c r="D61" t="n">
-        <v>44.8965</v>
+        <v>46.1899</v>
       </c>
       <c r="E61" t="n">
-        <v>15.0191</v>
+        <v>14.3999</v>
       </c>
       <c r="F61" t="n">
-        <v>37.9396</v>
+        <v>37.5192</v>
       </c>
     </row>
     <row r="62">
@@ -6280,19 +6280,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>14.4613</v>
+        <v>14.4049</v>
       </c>
       <c r="C62" t="n">
-        <v>38.871</v>
+        <v>16.4572</v>
       </c>
       <c r="D62" t="n">
-        <v>45.1302</v>
+        <v>46.7621</v>
       </c>
       <c r="E62" t="n">
-        <v>14.7886</v>
+        <v>14.1461</v>
       </c>
       <c r="F62" t="n">
-        <v>36.6805</v>
+        <v>37.2383</v>
       </c>
     </row>
     <row r="63">
@@ -6300,19 +6300,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>14.1781</v>
+        <v>14.1173</v>
       </c>
       <c r="C63" t="n">
-        <v>38.3634</v>
+        <v>16.3741</v>
       </c>
       <c r="D63" t="n">
-        <v>45.5231</v>
+        <v>47.0952</v>
       </c>
       <c r="E63" t="n">
-        <v>14.5444</v>
+        <v>13.9113</v>
       </c>
       <c r="F63" t="n">
-        <v>37.7153</v>
+        <v>36.8215</v>
       </c>
     </row>
     <row r="64">
@@ -6320,19 +6320,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>13.8276</v>
+        <v>13.813</v>
       </c>
       <c r="C64" t="n">
-        <v>38.4647</v>
+        <v>16.2972</v>
       </c>
       <c r="D64" t="n">
-        <v>50.512</v>
+        <v>52.1594</v>
       </c>
       <c r="E64" t="n">
-        <v>14.2966</v>
+        <v>13.7092</v>
       </c>
       <c r="F64" t="n">
-        <v>39.0447</v>
+        <v>38.2435</v>
       </c>
     </row>
     <row r="65">
@@ -6340,19 +6340,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>13.4564</v>
+        <v>13.4148</v>
       </c>
       <c r="C65" t="n">
-        <v>39.4595</v>
+        <v>17.8843</v>
       </c>
       <c r="D65" t="n">
-        <v>50.7626</v>
+        <v>52.6975</v>
       </c>
       <c r="E65" t="n">
-        <v>14.0246</v>
+        <v>13.4395</v>
       </c>
       <c r="F65" t="n">
-        <v>38.2705</v>
+        <v>38.4956</v>
       </c>
     </row>
     <row r="66">
@@ -6360,19 +6360,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>13.0056</v>
+        <v>12.897</v>
       </c>
       <c r="C66" t="n">
-        <v>39.7105</v>
+        <v>17.6638</v>
       </c>
       <c r="D66" t="n">
-        <v>51.4216</v>
+        <v>53.1604</v>
       </c>
       <c r="E66" t="n">
-        <v>17.1754</v>
+        <v>16.5774</v>
       </c>
       <c r="F66" t="n">
-        <v>47.4606</v>
+        <v>46.4046</v>
       </c>
     </row>
     <row r="67">
@@ -6380,19 +6380,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>17.5536</v>
+        <v>17.4075</v>
       </c>
       <c r="C67" t="n">
-        <v>50.0644</v>
+        <v>17.4936</v>
       </c>
       <c r="D67" t="n">
-        <v>51.9266</v>
+        <v>53.8679</v>
       </c>
       <c r="E67" t="n">
-        <v>16.8752</v>
+        <v>16.2684</v>
       </c>
       <c r="F67" t="n">
-        <v>47.1338</v>
+        <v>47.1521</v>
       </c>
     </row>
     <row r="68">
@@ -6400,19 +6400,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>17.2601</v>
+        <v>17.098</v>
       </c>
       <c r="C68" t="n">
-        <v>50.369</v>
+        <v>17.3469</v>
       </c>
       <c r="D68" t="n">
-        <v>52.4296</v>
+        <v>54.2183</v>
       </c>
       <c r="E68" t="n">
-        <v>16.6536</v>
+        <v>16.0004</v>
       </c>
       <c r="F68" t="n">
-        <v>47.5806</v>
+        <v>47.0942</v>
       </c>
     </row>
     <row r="69">
@@ -6420,19 +6420,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>16.9241</v>
+        <v>16.8047</v>
       </c>
       <c r="C69" t="n">
-        <v>50.6656</v>
+        <v>17.2222</v>
       </c>
       <c r="D69" t="n">
-        <v>52.9739</v>
+        <v>54.4806</v>
       </c>
       <c r="E69" t="n">
-        <v>16.4234</v>
+        <v>15.817</v>
       </c>
       <c r="F69" t="n">
-        <v>48.169</v>
+        <v>47.3602</v>
       </c>
     </row>
     <row r="70">
@@ -6440,19 +6440,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>16.5514</v>
+        <v>16.4714</v>
       </c>
       <c r="C70" t="n">
-        <v>50.4957</v>
+        <v>17.0508</v>
       </c>
       <c r="D70" t="n">
-        <v>53.352</v>
+        <v>54.8983</v>
       </c>
       <c r="E70" t="n">
-        <v>16.2023</v>
+        <v>15.5779</v>
       </c>
       <c r="F70" t="n">
-        <v>47.6333</v>
+        <v>47.315</v>
       </c>
     </row>
     <row r="71">
@@ -6460,19 +6460,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>16.1829</v>
+        <v>16.1299</v>
       </c>
       <c r="C71" t="n">
-        <v>50.5841</v>
+        <v>16.9667</v>
       </c>
       <c r="D71" t="n">
-        <v>53.4892</v>
+        <v>55.3582</v>
       </c>
       <c r="E71" t="n">
-        <v>15.9735</v>
+        <v>15.3585</v>
       </c>
       <c r="F71" t="n">
-        <v>48.0507</v>
+        <v>47.4239</v>
       </c>
     </row>
     <row r="72">
@@ -6480,19 +6480,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>15.8481</v>
+        <v>15.7635</v>
       </c>
       <c r="C72" t="n">
-        <v>50.0795</v>
+        <v>16.8365</v>
       </c>
       <c r="D72" t="n">
-        <v>53.9419</v>
+        <v>55.4465</v>
       </c>
       <c r="E72" t="n">
-        <v>15.791</v>
+        <v>15.1499</v>
       </c>
       <c r="F72" t="n">
-        <v>47.5975</v>
+        <v>47.0302</v>
       </c>
     </row>
     <row r="73">
@@ -6500,19 +6500,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>15.4709</v>
+        <v>15.4171</v>
       </c>
       <c r="C73" t="n">
-        <v>49.9299</v>
+        <v>16.7187</v>
       </c>
       <c r="D73" t="n">
-        <v>54.2025</v>
+        <v>55.7675</v>
       </c>
       <c r="E73" t="n">
-        <v>15.5827</v>
+        <v>14.9181</v>
       </c>
       <c r="F73" t="n">
-        <v>47.223</v>
+        <v>46.9017</v>
       </c>
     </row>
     <row r="74">
@@ -6520,19 +6520,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>15.1402</v>
+        <v>15.0741</v>
       </c>
       <c r="C74" t="n">
-        <v>49.7538</v>
+        <v>16.6139</v>
       </c>
       <c r="D74" t="n">
-        <v>54.3029</v>
+        <v>55.8991</v>
       </c>
       <c r="E74" t="n">
-        <v>15.3596</v>
+        <v>14.6702</v>
       </c>
       <c r="F74" t="n">
-        <v>47.1282</v>
+        <v>46.9755</v>
       </c>
     </row>
     <row r="75">
@@ -6540,19 +6540,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>14.8412</v>
+        <v>14.775</v>
       </c>
       <c r="C75" t="n">
-        <v>49.1653</v>
+        <v>16.5443</v>
       </c>
       <c r="D75" t="n">
-        <v>54.4528</v>
+        <v>56.2563</v>
       </c>
       <c r="E75" t="n">
-        <v>15.106</v>
+        <v>14.4769</v>
       </c>
       <c r="F75" t="n">
-        <v>46.9161</v>
+        <v>46.4549</v>
       </c>
     </row>
     <row r="76">
@@ -6560,19 +6560,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>14.5276</v>
+        <v>14.4674</v>
       </c>
       <c r="C76" t="n">
-        <v>48.8427</v>
+        <v>16.462</v>
       </c>
       <c r="D76" t="n">
-        <v>54.4115</v>
+        <v>56.3968</v>
       </c>
       <c r="E76" t="n">
-        <v>14.8807</v>
+        <v>14.2479</v>
       </c>
       <c r="F76" t="n">
-        <v>46.6562</v>
+        <v>46.8079</v>
       </c>
     </row>
     <row r="77">
@@ -6580,19 +6580,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>14.2365</v>
+        <v>14.1779</v>
       </c>
       <c r="C77" t="n">
-        <v>48.2047</v>
+        <v>16.3866</v>
       </c>
       <c r="D77" t="n">
-        <v>54.6815</v>
+        <v>56.664</v>
       </c>
       <c r="E77" t="n">
-        <v>14.6324</v>
+        <v>14.0077</v>
       </c>
       <c r="F77" t="n">
-        <v>46.7903</v>
+        <v>46.1264</v>
       </c>
     </row>
     <row r="78">
@@ -6600,19 +6600,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>13.9253</v>
+        <v>13.8435</v>
       </c>
       <c r="C78" t="n">
-        <v>47.7138</v>
+        <v>16.3138</v>
       </c>
       <c r="D78" t="n">
-        <v>57.1847</v>
+        <v>59.1066</v>
       </c>
       <c r="E78" t="n">
-        <v>14.3673</v>
+        <v>13.7651</v>
       </c>
       <c r="F78" t="n">
-        <v>46.3328</v>
+        <v>45.9732</v>
       </c>
     </row>
     <row r="79">
@@ -6620,19 +6620,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>13.5426</v>
+        <v>13.4729</v>
       </c>
       <c r="C79" t="n">
-        <v>47.0927</v>
+        <v>17.9151</v>
       </c>
       <c r="D79" t="n">
-        <v>57.3703</v>
+        <v>58.7954</v>
       </c>
       <c r="E79" t="n">
-        <v>14.1332</v>
+        <v>13.5082</v>
       </c>
       <c r="F79" t="n">
-        <v>46.0351</v>
+        <v>45.7045</v>
       </c>
     </row>
     <row r="80">
@@ -6640,19 +6640,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>13.0888</v>
+        <v>12.9926</v>
       </c>
       <c r="C80" t="n">
-        <v>46.4307</v>
+        <v>17.7619</v>
       </c>
       <c r="D80" t="n">
-        <v>57.1587</v>
+        <v>58.7451</v>
       </c>
       <c r="E80" t="n">
-        <v>17.2525</v>
+        <v>16.655</v>
       </c>
       <c r="F80" t="n">
-        <v>49.9723</v>
+        <v>49.3429</v>
       </c>
     </row>
     <row r="81">
@@ -6660,19 +6660,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>17.6874</v>
+        <v>17.5139</v>
       </c>
       <c r="C81" t="n">
-        <v>52.461</v>
+        <v>17.5436</v>
       </c>
       <c r="D81" t="n">
-        <v>57.4013</v>
+        <v>58.8162</v>
       </c>
       <c r="E81" t="n">
-        <v>16.9825</v>
+        <v>16.3679</v>
       </c>
       <c r="F81" t="n">
-        <v>49.5062</v>
+        <v>48.8518</v>
       </c>
     </row>
     <row r="82">
@@ -6680,19 +6680,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>17.3817</v>
+        <v>17.2497</v>
       </c>
       <c r="C82" t="n">
-        <v>52.0862</v>
+        <v>17.3939</v>
       </c>
       <c r="D82" t="n">
-        <v>57.2556</v>
+        <v>58.8098</v>
       </c>
       <c r="E82" t="n">
-        <v>16.7364</v>
+        <v>16.139</v>
       </c>
       <c r="F82" t="n">
-        <v>48.9258</v>
+        <v>48.6154</v>
       </c>
     </row>
     <row r="83">
@@ -6700,19 +6700,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>17.0356</v>
+        <v>16.9316</v>
       </c>
       <c r="C83" t="n">
-        <v>51.7177</v>
+        <v>17.2515</v>
       </c>
       <c r="D83" t="n">
-        <v>57.0954</v>
+        <v>59.0143</v>
       </c>
       <c r="E83" t="n">
-        <v>16.5162</v>
+        <v>15.9129</v>
       </c>
       <c r="F83" t="n">
-        <v>48.4579</v>
+        <v>48.5021</v>
       </c>
     </row>
     <row r="84">
@@ -6720,19 +6720,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>16.6815</v>
+        <v>16.5766</v>
       </c>
       <c r="C84" t="n">
-        <v>54.3432</v>
+        <v>17.1126</v>
       </c>
       <c r="D84" t="n">
-        <v>61.1211</v>
+        <v>62.2108</v>
       </c>
       <c r="E84" t="n">
-        <v>16.2614</v>
+        <v>15.6657</v>
       </c>
       <c r="F84" t="n">
-        <v>52.4838</v>
+        <v>53.0153</v>
       </c>
     </row>
     <row r="85">
@@ -6740,19 +6740,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>16.3082</v>
+        <v>16.2056</v>
       </c>
       <c r="C85" t="n">
-        <v>54.1262</v>
+        <v>16.9991</v>
       </c>
       <c r="D85" t="n">
-        <v>61.1017</v>
+        <v>62.2583</v>
       </c>
       <c r="E85" t="n">
-        <v>16.0711</v>
+        <v>15.4107</v>
       </c>
       <c r="F85" t="n">
-        <v>52.3673</v>
+        <v>52.7661</v>
       </c>
     </row>
     <row r="86">
@@ -6760,19 +6760,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>15.9484</v>
+        <v>15.8603</v>
       </c>
       <c r="C86" t="n">
-        <v>53.7736</v>
+        <v>16.8941</v>
       </c>
       <c r="D86" t="n">
-        <v>61.0003</v>
+        <v>62.2481</v>
       </c>
       <c r="E86" t="n">
-        <v>15.8796</v>
+        <v>15.221</v>
       </c>
       <c r="F86" t="n">
-        <v>51.8924</v>
+        <v>52.5937</v>
       </c>
     </row>
     <row r="87">
@@ -6780,19 +6780,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>15.57</v>
+        <v>15.5052</v>
       </c>
       <c r="C87" t="n">
-        <v>53.3036</v>
+        <v>16.7768</v>
       </c>
       <c r="D87" t="n">
-        <v>61.1721</v>
+        <v>62.1549</v>
       </c>
       <c r="E87" t="n">
-        <v>15.6354</v>
+        <v>14.9985</v>
       </c>
       <c r="F87" t="n">
-        <v>51.6661</v>
+        <v>52.3441</v>
       </c>
     </row>
     <row r="88">
@@ -6800,19 +6800,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>15.2427</v>
+        <v>15.1678</v>
       </c>
       <c r="C88" t="n">
-        <v>52.818</v>
+        <v>16.675</v>
       </c>
       <c r="D88" t="n">
-        <v>61.243</v>
+        <v>62.2966</v>
       </c>
       <c r="E88" t="n">
-        <v>15.4281</v>
+        <v>14.7963</v>
       </c>
       <c r="F88" t="n">
-        <v>51.3499</v>
+        <v>52.3484</v>
       </c>
     </row>
     <row r="89">
@@ -6820,19 +6820,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>14.9258</v>
+        <v>14.8525</v>
       </c>
       <c r="C89" t="n">
-        <v>52.4794</v>
+        <v>16.5827</v>
       </c>
       <c r="D89" t="n">
-        <v>61.2001</v>
+        <v>62.2749</v>
       </c>
       <c r="E89" t="n">
-        <v>15.1893</v>
+        <v>14.5442</v>
       </c>
       <c r="F89" t="n">
-        <v>51.4726</v>
+        <v>51.7054</v>
       </c>
     </row>
     <row r="90">
@@ -6840,19 +6840,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>14.6141</v>
+        <v>14.5669</v>
       </c>
       <c r="C90" t="n">
-        <v>51.9691</v>
+        <v>16.507</v>
       </c>
       <c r="D90" t="n">
-        <v>61.1217</v>
+        <v>62.2866</v>
       </c>
       <c r="E90" t="n">
-        <v>14.9699</v>
+        <v>14.3171</v>
       </c>
       <c r="F90" t="n">
-        <v>50.7398</v>
+        <v>51.568</v>
       </c>
     </row>
     <row r="91">
@@ -6860,19 +6860,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>14.3112</v>
+        <v>14.2229</v>
       </c>
       <c r="C91" t="n">
-        <v>51.4663</v>
+        <v>16.4207</v>
       </c>
       <c r="D91" t="n">
-        <v>61.1756</v>
+        <v>62.2954</v>
       </c>
       <c r="E91" t="n">
-        <v>14.7169</v>
+        <v>14.0861</v>
       </c>
       <c r="F91" t="n">
-        <v>50.6385</v>
+        <v>51.2611</v>
       </c>
     </row>
     <row r="92">
@@ -6880,19 +6880,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>13.9834</v>
+        <v>13.9153</v>
       </c>
       <c r="C92" t="n">
-        <v>51.0842</v>
+        <v>16.3347</v>
       </c>
       <c r="D92" t="n">
-        <v>61.0062</v>
+        <v>62.0771</v>
       </c>
       <c r="E92" t="n">
-        <v>14.4735</v>
+        <v>13.8528</v>
       </c>
       <c r="F92" t="n">
-        <v>50.5239</v>
+        <v>51.1339</v>
       </c>
     </row>
     <row r="93">
@@ -6900,19 +6900,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>13.6109</v>
+        <v>13.5692</v>
       </c>
       <c r="C93" t="n">
-        <v>50.4688</v>
+        <v>16.2785</v>
       </c>
       <c r="D93" t="n">
-        <v>60.8616</v>
+        <v>62.0635</v>
       </c>
       <c r="E93" t="n">
-        <v>14.1943</v>
+        <v>13.6291</v>
       </c>
       <c r="F93" t="n">
-        <v>50.1635</v>
+        <v>51.1218</v>
       </c>
     </row>
     <row r="94">
@@ -6920,19 +6920,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>13.2125</v>
+        <v>13.1556</v>
       </c>
       <c r="C94" t="n">
-        <v>49.8437</v>
+        <v>17.7705</v>
       </c>
       <c r="D94" t="n">
-        <v>60.8024</v>
+        <v>62.0784</v>
       </c>
       <c r="E94" t="n">
-        <v>17.285</v>
+        <v>16.7463</v>
       </c>
       <c r="F94" t="n">
-        <v>53.7065</v>
+        <v>54.2098</v>
       </c>
     </row>
     <row r="95">
@@ -6940,19 +6940,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>17.7543</v>
+        <v>17.6235</v>
       </c>
       <c r="C95" t="n">
-        <v>55.0255</v>
+        <v>17.5924</v>
       </c>
       <c r="D95" t="n">
-        <v>60.8767</v>
+        <v>62.0903</v>
       </c>
       <c r="E95" t="n">
-        <v>17.044</v>
+        <v>16.4469</v>
       </c>
       <c r="F95" t="n">
-        <v>53.5743</v>
+        <v>54.0621</v>
       </c>
     </row>
     <row r="96">
@@ -6960,19 +6960,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>17.4684</v>
+        <v>17.3082</v>
       </c>
       <c r="C96" t="n">
-        <v>54.9875</v>
+        <v>17.4306</v>
       </c>
       <c r="D96" t="n">
-        <v>60.6838</v>
+        <v>61.9145</v>
       </c>
       <c r="E96" t="n">
-        <v>16.8163</v>
+        <v>16.2016</v>
       </c>
       <c r="F96" t="n">
-        <v>52.9853</v>
+        <v>53.9046</v>
       </c>
     </row>
     <row r="97">
@@ -6980,19 +6980,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>17.1127</v>
+        <v>16.9981</v>
       </c>
       <c r="C97" t="n">
-        <v>54.6099</v>
+        <v>17.2641</v>
       </c>
       <c r="D97" t="n">
-        <v>60.9188</v>
+        <v>61.9331</v>
       </c>
       <c r="E97" t="n">
-        <v>16.5319</v>
+        <v>15.9213</v>
       </c>
       <c r="F97" t="n">
-        <v>52.7082</v>
+        <v>53.4568</v>
       </c>
     </row>
     <row r="98">
@@ -7000,19 +7000,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>16.7749</v>
+        <v>16.6662</v>
       </c>
       <c r="C98" t="n">
-        <v>54.2217</v>
+        <v>17.1281</v>
       </c>
       <c r="D98" t="n">
-        <v>60.7568</v>
+        <v>61.9505</v>
       </c>
       <c r="E98" t="n">
-        <v>16.3386</v>
+        <v>15.7009</v>
       </c>
       <c r="F98" t="n">
-        <v>52.4929</v>
+        <v>53.1317</v>
       </c>
     </row>
     <row r="99">
@@ -7020,19 +7020,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>16.3836</v>
+        <v>16.287</v>
       </c>
       <c r="C99" t="n">
-        <v>54.0925</v>
+        <v>16.997</v>
       </c>
       <c r="D99" t="n">
-        <v>60.8612</v>
+        <v>61.9064</v>
       </c>
       <c r="E99" t="n">
-        <v>16.1395</v>
+        <v>15.4806</v>
       </c>
       <c r="F99" t="n">
-        <v>52.2665</v>
+        <v>53.0255</v>
       </c>
     </row>
     <row r="100">
@@ -7040,19 +7040,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>16.0283</v>
+        <v>15.9506</v>
       </c>
       <c r="C100" t="n">
-        <v>53.7173</v>
+        <v>16.9158</v>
       </c>
       <c r="D100" t="n">
-        <v>60.7752</v>
+        <v>61.9642</v>
       </c>
       <c r="E100" t="n">
-        <v>15.9336</v>
+        <v>15.2592</v>
       </c>
       <c r="F100" t="n">
-        <v>51.7649</v>
+        <v>52.753</v>
       </c>
     </row>
     <row r="101">
@@ -7060,19 +7060,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>15.6601</v>
+        <v>15.5913</v>
       </c>
       <c r="C101" t="n">
-        <v>53.3014</v>
+        <v>16.7742</v>
       </c>
       <c r="D101" t="n">
-        <v>60.6823</v>
+        <v>61.9124</v>
       </c>
       <c r="E101" t="n">
-        <v>15.7069</v>
+        <v>15.071</v>
       </c>
       <c r="F101" t="n">
-        <v>51.4832</v>
+        <v>52.5134</v>
       </c>
     </row>
     <row r="102">
@@ -7080,19 +7080,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>15.3046</v>
+        <v>15.2456</v>
       </c>
       <c r="C102" t="n">
-        <v>53.0184</v>
+        <v>16.6996</v>
       </c>
       <c r="D102" t="n">
-        <v>60.6858</v>
+        <v>61.9497</v>
       </c>
       <c r="E102" t="n">
-        <v>15.4625</v>
+        <v>14.8233</v>
       </c>
       <c r="F102" t="n">
-        <v>51.2609</v>
+        <v>52.1812</v>
       </c>
     </row>
     <row r="103">
@@ -7100,19 +7100,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>14.9803</v>
+        <v>14.9256</v>
       </c>
       <c r="C103" t="n">
-        <v>52.5809</v>
+        <v>16.5805</v>
       </c>
       <c r="D103" t="n">
-        <v>60.7133</v>
+        <v>61.9006</v>
       </c>
       <c r="E103" t="n">
-        <v>15.2257</v>
+        <v>14.576</v>
       </c>
       <c r="F103" t="n">
-        <v>51.0301</v>
+        <v>51.9209</v>
       </c>
     </row>
     <row r="104">
@@ -7120,19 +7120,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>14.6797</v>
+        <v>14.6107</v>
       </c>
       <c r="C104" t="n">
-        <v>52.204</v>
+        <v>16.511</v>
       </c>
       <c r="D104" t="n">
-        <v>60.6253</v>
+        <v>61.988</v>
       </c>
       <c r="E104" t="n">
-        <v>14.9996</v>
+        <v>14.371</v>
       </c>
       <c r="F104" t="n">
-        <v>50.8404</v>
+        <v>51.5988</v>
       </c>
     </row>
     <row r="105">
@@ -7140,19 +7140,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>14.3599</v>
+        <v>14.2864</v>
       </c>
       <c r="C105" t="n">
-        <v>51.8328</v>
+        <v>16.4238</v>
       </c>
       <c r="D105" t="n">
-        <v>60.6357</v>
+        <v>61.9234</v>
       </c>
       <c r="E105" t="n">
-        <v>14.7732</v>
+        <v>14.1488</v>
       </c>
       <c r="F105" t="n">
-        <v>50.5835</v>
+        <v>51.4633</v>
       </c>
     </row>
     <row r="106">
@@ -7160,19 +7160,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>14.0709</v>
+        <v>13.9763</v>
       </c>
       <c r="C106" t="n">
-        <v>51.5002</v>
+        <v>16.3245</v>
       </c>
       <c r="D106" t="n">
-        <v>60.6396</v>
+        <v>61.8468</v>
       </c>
       <c r="E106" t="n">
-        <v>14.5175</v>
+        <v>13.9017</v>
       </c>
       <c r="F106" t="n">
-        <v>50.3789</v>
+        <v>51.1613</v>
       </c>
     </row>
     <row r="107">
@@ -7180,19 +7180,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>13.7043</v>
+        <v>13.6278</v>
       </c>
       <c r="C107" t="n">
-        <v>50.8673</v>
+        <v>16.2711</v>
       </c>
       <c r="D107" t="n">
-        <v>59.2466</v>
+        <v>60.413</v>
       </c>
       <c r="E107" t="n">
-        <v>14.2552</v>
+        <v>13.6398</v>
       </c>
       <c r="F107" t="n">
-        <v>50.0422</v>
+        <v>50.8586</v>
       </c>
     </row>
     <row r="108">
@@ -7200,19 +7200,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>13.2543</v>
+        <v>13.2008</v>
       </c>
       <c r="C108" t="n">
-        <v>50.2699</v>
+        <v>17.7881</v>
       </c>
       <c r="D108" t="n">
-        <v>59.2851</v>
+        <v>60.7308</v>
       </c>
       <c r="E108" t="n">
-        <v>17.4217</v>
+        <v>16.9378</v>
       </c>
       <c r="F108" t="n">
-        <v>53.7038</v>
+        <v>54.4185</v>
       </c>
     </row>
     <row r="109">
@@ -7220,19 +7220,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>12.7521</v>
+        <v>12.6331</v>
       </c>
       <c r="C109" t="n">
-        <v>49.5422</v>
+        <v>17.6176</v>
       </c>
       <c r="D109" t="n">
-        <v>59.1998</v>
+        <v>60.6702</v>
       </c>
       <c r="E109" t="n">
-        <v>17.1763</v>
+        <v>16.5293</v>
       </c>
       <c r="F109" t="n">
-        <v>53.4576</v>
+        <v>54.0143</v>
       </c>
     </row>
     <row r="110">
@@ -7240,19 +7240,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>17.5125</v>
+        <v>17.3883</v>
       </c>
       <c r="C110" t="n">
-        <v>53.5814</v>
+        <v>17.4189</v>
       </c>
       <c r="D110" t="n">
-        <v>59.507</v>
+        <v>60.707</v>
       </c>
       <c r="E110" t="n">
-        <v>16.9</v>
+        <v>16.2773</v>
       </c>
       <c r="F110" t="n">
-        <v>53.0036</v>
+        <v>53.7266</v>
       </c>
     </row>
     <row r="111">
@@ -7260,19 +7260,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>17.1949</v>
+        <v>17.034</v>
       </c>
       <c r="C111" t="n">
-        <v>54.0344</v>
+        <v>17.2992</v>
       </c>
       <c r="D111" t="n">
-        <v>59.3748</v>
+        <v>60.8364</v>
       </c>
       <c r="E111" t="n">
-        <v>16.614</v>
+        <v>16.0174</v>
       </c>
       <c r="F111" t="n">
-        <v>52.7224</v>
+        <v>53.2762</v>
       </c>
     </row>
     <row r="112">
@@ -7280,19 +7280,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>16.8393</v>
+        <v>16.709</v>
       </c>
       <c r="C112" t="n">
-        <v>54.1877</v>
+        <v>17.1217</v>
       </c>
       <c r="D112" t="n">
-        <v>59.3873</v>
+        <v>60.8723</v>
       </c>
       <c r="E112" t="n">
-        <v>16.3938</v>
+        <v>15.7988</v>
       </c>
       <c r="F112" t="n">
-        <v>52.7821</v>
+        <v>53.1533</v>
       </c>
     </row>
     <row r="113">
@@ -7300,19 +7300,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>16.4699</v>
+        <v>16.3689</v>
       </c>
       <c r="C113" t="n">
-        <v>53.4085</v>
+        <v>16.9899</v>
       </c>
       <c r="D113" t="n">
-        <v>59.5261</v>
+        <v>60.9131</v>
       </c>
       <c r="E113" t="n">
-        <v>16.1726</v>
+        <v>15.5359</v>
       </c>
       <c r="F113" t="n">
-        <v>52.2383</v>
+        <v>53.0615</v>
       </c>
     </row>
     <row r="114">
@@ -7320,19 +7320,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>16.0956</v>
+        <v>15.9986</v>
       </c>
       <c r="C114" t="n">
-        <v>52.4362</v>
+        <v>16.8859</v>
       </c>
       <c r="D114" t="n">
-        <v>59.3958</v>
+        <v>60.9423</v>
       </c>
       <c r="E114" t="n">
-        <v>15.9798</v>
+        <v>15.3344</v>
       </c>
       <c r="F114" t="n">
-        <v>51.8745</v>
+        <v>52.5145</v>
       </c>
     </row>
     <row r="115">
@@ -7340,19 +7340,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>15.7244</v>
+        <v>15.6903</v>
       </c>
       <c r="C115" t="n">
-        <v>52.8868</v>
+        <v>16.7903</v>
       </c>
       <c r="D115" t="n">
-        <v>59.5572</v>
+        <v>61.0266</v>
       </c>
       <c r="E115" t="n">
-        <v>15.7546</v>
+        <v>15.1228</v>
       </c>
       <c r="F115" t="n">
-        <v>51.6181</v>
+        <v>52.3038</v>
       </c>
     </row>
     <row r="116">
@@ -7360,19 +7360,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>15.3843</v>
+        <v>15.305</v>
       </c>
       <c r="C116" t="n">
-        <v>52.5052</v>
+        <v>16.6689</v>
       </c>
       <c r="D116" t="n">
-        <v>59.5641</v>
+        <v>61.0162</v>
       </c>
       <c r="E116" t="n">
-        <v>15.5334</v>
+        <v>14.8614</v>
       </c>
       <c r="F116" t="n">
-        <v>51.3527</v>
+        <v>52.2092</v>
       </c>
     </row>
     <row r="117">
@@ -7380,19 +7380,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>15.0508</v>
+        <v>14.9875</v>
       </c>
       <c r="C117" t="n">
-        <v>51.3797</v>
+        <v>16.5937</v>
       </c>
       <c r="D117" t="n">
-        <v>59.6689</v>
+        <v>61.0443</v>
       </c>
       <c r="E117" t="n">
-        <v>15.2874</v>
+        <v>14.6471</v>
       </c>
       <c r="F117" t="n">
-        <v>51.1847</v>
+        <v>51.9332</v>
       </c>
     </row>
     <row r="118">
@@ -7400,19 +7400,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>14.7358</v>
+        <v>14.6666</v>
       </c>
       <c r="C118" t="n">
-        <v>52.7496</v>
+        <v>16.5155</v>
       </c>
       <c r="D118" t="n">
-        <v>59.6258</v>
+        <v>61.2898</v>
       </c>
       <c r="E118" t="n">
-        <v>15.0392</v>
+        <v>14.4118</v>
       </c>
       <c r="F118" t="n">
-        <v>50.9713</v>
+        <v>51.6891</v>
       </c>
     </row>
     <row r="119">
@@ -7420,19 +7420,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>14.4404</v>
+        <v>14.3594</v>
       </c>
       <c r="C119" t="n">
-        <v>52.3986</v>
+        <v>16.4039</v>
       </c>
       <c r="D119" t="n">
-        <v>59.651</v>
+        <v>61.123</v>
       </c>
       <c r="E119" t="n">
-        <v>14.8018</v>
+        <v>14.1795</v>
       </c>
       <c r="F119" t="n">
-        <v>50.432</v>
+        <v>51.4233</v>
       </c>
     </row>
     <row r="120">
@@ -7440,19 +7440,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>14.1334</v>
+        <v>14.0302</v>
       </c>
       <c r="C120" t="n">
-        <v>50.7022</v>
+        <v>16.3344</v>
       </c>
       <c r="D120" t="n">
-        <v>59.7408</v>
+        <v>61.2433</v>
       </c>
       <c r="E120" t="n">
-        <v>14.5598</v>
+        <v>13.9153</v>
       </c>
       <c r="F120" t="n">
-        <v>50.214</v>
+        <v>51.204</v>
       </c>
     </row>
     <row r="121">
@@ -7460,19 +7460,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>13.7842</v>
+        <v>13.7151</v>
       </c>
       <c r="C121" t="n">
-        <v>49.633</v>
+        <v>16.296</v>
       </c>
       <c r="D121" t="n">
-        <v>61.5523</v>
+        <v>62.6908</v>
       </c>
       <c r="E121" t="n">
-        <v>14.3075</v>
+        <v>13.6897</v>
       </c>
       <c r="F121" t="n">
-        <v>49.969</v>
+        <v>50.9748</v>
       </c>
     </row>
     <row r="122">
@@ -7480,19 +7480,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>13.3471</v>
+        <v>13.3065</v>
       </c>
       <c r="C122" t="n">
-        <v>49.9822</v>
+        <v>17.7889</v>
       </c>
       <c r="D122" t="n">
-        <v>61.3932</v>
+        <v>62.7581</v>
       </c>
       <c r="E122" t="n">
-        <v>14.045</v>
+        <v>13.4366</v>
       </c>
       <c r="F122" t="n">
-        <v>49.7656</v>
+        <v>50.5822</v>
       </c>
     </row>
     <row r="123">
@@ -7500,19 +7500,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>12.9292</v>
+        <v>12.7706</v>
       </c>
       <c r="C123" t="n">
-        <v>49.3704</v>
+        <v>17.6327</v>
       </c>
       <c r="D123" t="n">
-        <v>61.3402</v>
+        <v>62.4539</v>
       </c>
       <c r="E123" t="n">
-        <v>17.4499</v>
+        <v>16.739</v>
       </c>
       <c r="F123" t="n">
-        <v>53.5844</v>
+        <v>54.0295</v>
       </c>
     </row>
     <row r="124">
@@ -7520,19 +7520,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>17.5778</v>
+        <v>17.4054</v>
       </c>
       <c r="C124" t="n">
-        <v>53.4291</v>
+        <v>17.4471</v>
       </c>
       <c r="D124" t="n">
-        <v>61.2944</v>
+        <v>62.4273</v>
       </c>
       <c r="E124" t="n">
-        <v>17.0319</v>
+        <v>16.5321</v>
       </c>
       <c r="F124" t="n">
-        <v>53.1398</v>
+        <v>53.8254</v>
       </c>
     </row>
     <row r="125">
@@ -7540,19 +7540,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>17.2757</v>
+        <v>17.1258</v>
       </c>
       <c r="C125" t="n">
-        <v>53.8123</v>
+        <v>17.2964</v>
       </c>
       <c r="D125" t="n">
-        <v>61.3326</v>
+        <v>62.447</v>
       </c>
       <c r="E125" t="n">
-        <v>16.7561</v>
+        <v>16.1051</v>
       </c>
       <c r="F125" t="n">
-        <v>52.8796</v>
+        <v>53.3988</v>
       </c>
     </row>
     <row r="126">
@@ -7560,19 +7560,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>16.8981</v>
+        <v>16.7968</v>
       </c>
       <c r="C126" t="n">
-        <v>52.8661</v>
+        <v>17.1808</v>
       </c>
       <c r="D126" t="n">
-        <v>61.199</v>
+        <v>62.5253</v>
       </c>
       <c r="E126" t="n">
-        <v>16.5453</v>
+        <v>15.9354</v>
       </c>
       <c r="F126" t="n">
-        <v>52.3482</v>
+        <v>53.0228</v>
       </c>
     </row>
     <row r="127">
@@ -7580,19 +7580,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>16.5166</v>
+        <v>16.4463</v>
       </c>
       <c r="C127" t="n">
-        <v>52.7171</v>
+        <v>17.0298</v>
       </c>
       <c r="D127" t="n">
-        <v>61.2493</v>
+        <v>62.4305</v>
       </c>
       <c r="E127" t="n">
-        <v>16.2943</v>
+        <v>15.6178</v>
       </c>
       <c r="F127" t="n">
-        <v>52.1467</v>
+        <v>52.9502</v>
       </c>
     </row>
     <row r="128">
@@ -7600,19 +7600,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>16.1797</v>
+        <v>16.0919</v>
       </c>
       <c r="C128" t="n">
-        <v>54.1552</v>
+        <v>16.8983</v>
       </c>
       <c r="D128" t="n">
-        <v>61.1346</v>
+        <v>62.3894</v>
       </c>
       <c r="E128" t="n">
-        <v>16.0926</v>
+        <v>15.3751</v>
       </c>
       <c r="F128" t="n">
-        <v>51.8748</v>
+        <v>52.7074</v>
       </c>
     </row>
     <row r="129">
@@ -7620,19 +7620,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>15.7995</v>
+        <v>15.7115</v>
       </c>
       <c r="C129" t="n">
-        <v>52.7504</v>
+        <v>16.7766</v>
       </c>
       <c r="D129" t="n">
-        <v>61.1835</v>
+        <v>62.4152</v>
       </c>
       <c r="E129" t="n">
-        <v>15.7868</v>
+        <v>15.1288</v>
       </c>
       <c r="F129" t="n">
-        <v>51.5705</v>
+        <v>52.3868</v>
       </c>
     </row>
     <row r="130">
@@ -7640,19 +7640,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>15.4594</v>
+        <v>15.3687</v>
       </c>
       <c r="C130" t="n">
-        <v>53.2003</v>
+        <v>16.676</v>
       </c>
       <c r="D130" t="n">
-        <v>61.1025</v>
+        <v>62.2425</v>
       </c>
       <c r="E130" t="n">
-        <v>15.5848</v>
+        <v>14.9197</v>
       </c>
       <c r="F130" t="n">
-        <v>51.2845</v>
+        <v>52.1447</v>
       </c>
     </row>
     <row r="131">
@@ -7660,19 +7660,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>15.1277</v>
+        <v>15.0379</v>
       </c>
       <c r="C131" t="n">
-        <v>52.0276</v>
+        <v>16.6228</v>
       </c>
       <c r="D131" t="n">
-        <v>61.485</v>
+        <v>62.3782</v>
       </c>
       <c r="E131" t="n">
-        <v>15.3309</v>
+        <v>14.7457</v>
       </c>
       <c r="F131" t="n">
-        <v>51.1222</v>
+        <v>51.9771</v>
       </c>
     </row>
     <row r="132">
@@ -7680,19 +7680,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>14.7963</v>
+        <v>14.7183</v>
       </c>
       <c r="C132" t="n">
-        <v>51.5655</v>
+        <v>16.5033</v>
       </c>
       <c r="D132" t="n">
-        <v>60.9796</v>
+        <v>62.2736</v>
       </c>
       <c r="E132" t="n">
-        <v>15.0699</v>
+        <v>14.464</v>
       </c>
       <c r="F132" t="n">
-        <v>50.9638</v>
+        <v>51.7791</v>
       </c>
     </row>
     <row r="133">
@@ -7700,19 +7700,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>14.4878</v>
+        <v>14.4175</v>
       </c>
       <c r="C133" t="n">
-        <v>50.3414</v>
+        <v>16.4525</v>
       </c>
       <c r="D133" t="n">
-        <v>61.0457</v>
+        <v>62.2603</v>
       </c>
       <c r="E133" t="n">
-        <v>14.8503</v>
+        <v>14.2275</v>
       </c>
       <c r="F133" t="n">
-        <v>50.5783</v>
+        <v>51.477</v>
       </c>
     </row>
     <row r="134">
@@ -7720,19 +7720,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.1809</v>
+        <v>14.0931</v>
       </c>
       <c r="C134" t="n">
-        <v>50.8325</v>
+        <v>16.3538</v>
       </c>
       <c r="D134" t="n">
-        <v>61.0184</v>
+        <v>62.1562</v>
       </c>
       <c r="E134" t="n">
-        <v>14.6145</v>
+        <v>13.9936</v>
       </c>
       <c r="F134" t="n">
-        <v>50.2721</v>
+        <v>51.2101</v>
       </c>
     </row>
     <row r="135">
@@ -7740,19 +7740,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>13.8249</v>
+        <v>13.8134</v>
       </c>
       <c r="C135" t="n">
-        <v>50.3694</v>
+        <v>16.2788</v>
       </c>
       <c r="D135" t="n">
-        <v>62.1759</v>
+        <v>63.1723</v>
       </c>
       <c r="E135" t="n">
-        <v>14.3637</v>
+        <v>13.745</v>
       </c>
       <c r="F135" t="n">
-        <v>49.9839</v>
+        <v>51.0083</v>
       </c>
     </row>
     <row r="136">
@@ -7760,19 +7760,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>13.4528</v>
+        <v>13.3799</v>
       </c>
       <c r="C136" t="n">
-        <v>48.9126</v>
+        <v>17.8384</v>
       </c>
       <c r="D136" t="n">
-        <v>61.8993</v>
+        <v>62.9595</v>
       </c>
       <c r="E136" t="n">
-        <v>14.0786</v>
+        <v>13.4658</v>
       </c>
       <c r="F136" t="n">
-        <v>49.7126</v>
+        <v>50.6911</v>
       </c>
     </row>
     <row r="137">
@@ -7780,19 +7780,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>13.0547</v>
+        <v>12.9304</v>
       </c>
       <c r="C137" t="n">
-        <v>48.2405</v>
+        <v>17.6507</v>
       </c>
       <c r="D137" t="n">
-        <v>61.8808</v>
+        <v>62.9536</v>
       </c>
       <c r="E137" t="n">
-        <v>17.6693</v>
+        <v>17.1041</v>
       </c>
       <c r="F137" t="n">
-        <v>53.3847</v>
+        <v>54.1795</v>
       </c>
     </row>
     <row r="138">
@@ -7800,19 +7800,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>17.673</v>
+        <v>17.4911</v>
       </c>
       <c r="C138" t="n">
-        <v>53.6674</v>
+        <v>17.4689</v>
       </c>
       <c r="D138" t="n">
-        <v>61.8082</v>
+        <v>62.9386</v>
       </c>
       <c r="E138" t="n">
-        <v>17.3153</v>
+        <v>16.5583</v>
       </c>
       <c r="F138" t="n">
-        <v>53.1049</v>
+        <v>53.6919</v>
       </c>
     </row>
     <row r="139">
@@ -7820,19 +7820,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>17.3376</v>
+        <v>17.2225</v>
       </c>
       <c r="C139" t="n">
-        <v>53.3948</v>
+        <v>17.3094</v>
       </c>
       <c r="D139" t="n">
-        <v>61.71</v>
+        <v>62.7111</v>
       </c>
       <c r="E139" t="n">
-        <v>17.0313</v>
+        <v>16.1803</v>
       </c>
       <c r="F139" t="n">
-        <v>52.6124</v>
+        <v>53.2956</v>
       </c>
     </row>
     <row r="140">
@@ -7840,19 +7840,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>16.9993</v>
+        <v>16.8607</v>
       </c>
       <c r="C140" t="n">
-        <v>52.6822</v>
+        <v>17.1718</v>
       </c>
       <c r="D140" t="n">
-        <v>61.6286</v>
+        <v>62.8017</v>
       </c>
       <c r="E140" t="n">
-        <v>16.7804</v>
+        <v>15.9832</v>
       </c>
       <c r="F140" t="n">
-        <v>52.4659</v>
+        <v>53.3794</v>
       </c>
     </row>
     <row r="141">
@@ -7860,19 +7860,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>16.606</v>
+        <v>16.5414</v>
       </c>
       <c r="C141" t="n">
-        <v>52.3879</v>
+        <v>17.0543</v>
       </c>
       <c r="D141" t="n">
-        <v>61.6394</v>
+        <v>62.6456</v>
       </c>
       <c r="E141" t="n">
-        <v>16.4219</v>
+        <v>15.7262</v>
       </c>
       <c r="F141" t="n">
-        <v>52.1092</v>
+        <v>52.7874</v>
       </c>
     </row>
     <row r="142">
@@ -7880,19 +7880,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>16.2652</v>
+        <v>16.1676</v>
       </c>
       <c r="C142" t="n">
-        <v>53.9819</v>
+        <v>16.9246</v>
       </c>
       <c r="D142" t="n">
-        <v>61.4977</v>
+        <v>62.71</v>
       </c>
       <c r="E142" t="n">
-        <v>16.1537</v>
+        <v>15.4621</v>
       </c>
       <c r="F142" t="n">
-        <v>51.9906</v>
+        <v>52.6411</v>
       </c>
     </row>
     <row r="143">
@@ -7900,19 +7900,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>15.8887</v>
+        <v>15.8053</v>
       </c>
       <c r="C143" t="n">
-        <v>51.8311</v>
+        <v>16.8218</v>
       </c>
       <c r="D143" t="n">
-        <v>61.5626</v>
+        <v>62.6706</v>
       </c>
       <c r="E143" t="n">
-        <v>15.8448</v>
+        <v>15.2731</v>
       </c>
       <c r="F143" t="n">
-        <v>51.6209</v>
+        <v>52.453</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Running erasure.xlsx
+++ b/vs-x64/Running erasure.xlsx
@@ -5080,19 +5080,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>14.6148</v>
+        <v>14.4861</v>
       </c>
       <c r="C2" t="n">
-        <v>15.0214</v>
+        <v>15.0881</v>
       </c>
       <c r="D2" t="n">
-        <v>41.8061</v>
+        <v>41.8336</v>
       </c>
       <c r="E2" t="n">
-        <v>13.8465</v>
+        <v>13.8705</v>
       </c>
       <c r="F2" t="n">
-        <v>34.4289</v>
+        <v>34.4017</v>
       </c>
     </row>
     <row r="3">
@@ -5100,19 +5100,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>14.1305</v>
+        <v>14.1949</v>
       </c>
       <c r="C3" t="n">
-        <v>15.0549</v>
+        <v>15.1025</v>
       </c>
       <c r="D3" t="n">
-        <v>41.631</v>
+        <v>41.7753</v>
       </c>
       <c r="E3" t="n">
-        <v>13.7399</v>
+        <v>13.7173</v>
       </c>
       <c r="F3" t="n">
-        <v>34.2051</v>
+        <v>34.1476</v>
       </c>
     </row>
     <row r="4">
@@ -5120,19 +5120,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>13.9851</v>
+        <v>13.859</v>
       </c>
       <c r="C4" t="n">
-        <v>15.256</v>
+        <v>15.2515</v>
       </c>
       <c r="D4" t="n">
-        <v>41.7351</v>
+        <v>41.7832</v>
       </c>
       <c r="E4" t="n">
-        <v>13.5547</v>
+        <v>13.547</v>
       </c>
       <c r="F4" t="n">
-        <v>33.8891</v>
+        <v>33.9759</v>
       </c>
     </row>
     <row r="5">
@@ -5140,19 +5140,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>13.7384</v>
+        <v>13.6457</v>
       </c>
       <c r="C5" t="n">
-        <v>15.149</v>
+        <v>15.1531</v>
       </c>
       <c r="D5" t="n">
-        <v>41.6287</v>
+        <v>41.6575</v>
       </c>
       <c r="E5" t="n">
-        <v>13.4196</v>
+        <v>13.3623</v>
       </c>
       <c r="F5" t="n">
-        <v>33.9165</v>
+        <v>33.9678</v>
       </c>
     </row>
     <row r="6">
@@ -5160,19 +5160,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>13.2938</v>
+        <v>13.4184</v>
       </c>
       <c r="C6" t="n">
-        <v>15.2262</v>
+        <v>15.2329</v>
       </c>
       <c r="D6" t="n">
-        <v>41.6455</v>
+        <v>41.6228</v>
       </c>
       <c r="E6" t="n">
-        <v>13.2169</v>
+        <v>13.2121</v>
       </c>
       <c r="F6" t="n">
-        <v>33.7243</v>
+        <v>33.7975</v>
       </c>
     </row>
     <row r="7">
@@ -5180,19 +5180,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>13.2283</v>
+        <v>13.091</v>
       </c>
       <c r="C7" t="n">
-        <v>15.2346</v>
+        <v>15.2798</v>
       </c>
       <c r="D7" t="n">
-        <v>42.611</v>
+        <v>42.4563</v>
       </c>
       <c r="E7" t="n">
-        <v>12.8809</v>
+        <v>19.4783</v>
       </c>
       <c r="F7" t="n">
-        <v>34.3162</v>
+        <v>37.2133</v>
       </c>
     </row>
     <row r="8">
@@ -5200,19 +5200,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>12.8691</v>
+        <v>12.843</v>
       </c>
       <c r="C8" t="n">
-        <v>17.0785</v>
+        <v>17.0006</v>
       </c>
       <c r="D8" t="n">
-        <v>42.5108</v>
+        <v>42.3909</v>
       </c>
       <c r="E8" t="n">
-        <v>12.5701</v>
+        <v>16.0037</v>
       </c>
       <c r="F8" t="n">
-        <v>33.2685</v>
+        <v>36.6404</v>
       </c>
     </row>
     <row r="9">
@@ -5220,19 +5220,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>12.4556</v>
+        <v>12.4562</v>
       </c>
       <c r="C9" t="n">
-        <v>17.0012</v>
+        <v>17.0216</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3706</v>
+        <v>42.4486</v>
       </c>
       <c r="E9" t="n">
-        <v>15.8488</v>
+        <v>15.8326</v>
       </c>
       <c r="F9" t="n">
-        <v>36.3092</v>
+        <v>36.5016</v>
       </c>
     </row>
     <row r="10">
@@ -5240,19 +5240,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>17.1625</v>
+        <v>17.1834</v>
       </c>
       <c r="C10" t="n">
-        <v>16.8382</v>
+        <v>16.8489</v>
       </c>
       <c r="D10" t="n">
-        <v>42.3858</v>
+        <v>42.4474</v>
       </c>
       <c r="E10" t="n">
-        <v>15.6543</v>
+        <v>15.6363</v>
       </c>
       <c r="F10" t="n">
-        <v>36.2135</v>
+        <v>36.5393</v>
       </c>
     </row>
     <row r="11">
@@ -5260,19 +5260,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>16.9418</v>
+        <v>16.9869</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8053</v>
+        <v>16.7915</v>
       </c>
       <c r="D11" t="n">
-        <v>42.4906</v>
+        <v>42.4308</v>
       </c>
       <c r="E11" t="n">
-        <v>15.3933</v>
+        <v>15.3581</v>
       </c>
       <c r="F11" t="n">
-        <v>36.0738</v>
+        <v>36.047</v>
       </c>
     </row>
     <row r="12">
@@ -5280,19 +5280,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>16.6284</v>
+        <v>16.5399</v>
       </c>
       <c r="C12" t="n">
-        <v>16.6857</v>
+        <v>16.693</v>
       </c>
       <c r="D12" t="n">
-        <v>42.5032</v>
+        <v>42.356</v>
       </c>
       <c r="E12" t="n">
-        <v>15.5169</v>
+        <v>15.4131</v>
       </c>
       <c r="F12" t="n">
-        <v>35.7817</v>
+        <v>35.8618</v>
       </c>
     </row>
     <row r="13">
@@ -5300,19 +5300,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>16.2777</v>
+        <v>16.161</v>
       </c>
       <c r="C13" t="n">
-        <v>16.6384</v>
+        <v>16.5862</v>
       </c>
       <c r="D13" t="n">
-        <v>42.5853</v>
+        <v>42.4332</v>
       </c>
       <c r="E13" t="n">
-        <v>15.1149</v>
+        <v>15.3263</v>
       </c>
       <c r="F13" t="n">
-        <v>35.5301</v>
+        <v>35.6842</v>
       </c>
     </row>
     <row r="14">
@@ -5320,19 +5320,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>16.0122</v>
+        <v>15.9167</v>
       </c>
       <c r="C14" t="n">
-        <v>16.5735</v>
+        <v>16.5866</v>
       </c>
       <c r="D14" t="n">
-        <v>42.4705</v>
+        <v>42.3759</v>
       </c>
       <c r="E14" t="n">
-        <v>14.9732</v>
+        <v>14.9429</v>
       </c>
       <c r="F14" t="n">
-        <v>35.4452</v>
+        <v>35.3853</v>
       </c>
     </row>
     <row r="15">
@@ -5340,19 +5340,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>15.5355</v>
+        <v>15.6213</v>
       </c>
       <c r="C15" t="n">
-        <v>16.4718</v>
+        <v>16.4954</v>
       </c>
       <c r="D15" t="n">
-        <v>42.7301</v>
+        <v>42.3579</v>
       </c>
       <c r="E15" t="n">
-        <v>14.715</v>
+        <v>14.7731</v>
       </c>
       <c r="F15" t="n">
-        <v>35.5296</v>
+        <v>35.5608</v>
       </c>
     </row>
     <row r="16">
@@ -5360,19 +5360,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>15.2589</v>
+        <v>15.1367</v>
       </c>
       <c r="C16" t="n">
-        <v>16.3777</v>
+        <v>16.3827</v>
       </c>
       <c r="D16" t="n">
-        <v>42.3742</v>
+        <v>42.425</v>
       </c>
       <c r="E16" t="n">
-        <v>14.6412</v>
+        <v>14.6992</v>
       </c>
       <c r="F16" t="n">
-        <v>35.1094</v>
+        <v>35.0544</v>
       </c>
     </row>
     <row r="17">
@@ -5380,19 +5380,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>14.9094</v>
+        <v>14.9229</v>
       </c>
       <c r="C17" t="n">
-        <v>16.2903</v>
+        <v>16.2669</v>
       </c>
       <c r="D17" t="n">
-        <v>42.4445</v>
+        <v>42.3659</v>
       </c>
       <c r="E17" t="n">
-        <v>14.343</v>
+        <v>14.4069</v>
       </c>
       <c r="F17" t="n">
-        <v>34.9663</v>
+        <v>34.7301</v>
       </c>
     </row>
     <row r="18">
@@ -5400,19 +5400,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>14.6827</v>
+        <v>14.7236</v>
       </c>
       <c r="C18" t="n">
-        <v>16.1697</v>
+        <v>16.1724</v>
       </c>
       <c r="D18" t="n">
-        <v>42.4232</v>
+        <v>42.4465</v>
       </c>
       <c r="E18" t="n">
-        <v>14.2628</v>
+        <v>15.2932</v>
       </c>
       <c r="F18" t="n">
-        <v>34.5505</v>
+        <v>34.6693</v>
       </c>
     </row>
     <row r="19">
@@ -5420,19 +5420,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>14.3806</v>
+        <v>14.3129</v>
       </c>
       <c r="C19" t="n">
-        <v>16.1159</v>
+        <v>16.106</v>
       </c>
       <c r="D19" t="n">
-        <v>42.3455</v>
+        <v>42.2643</v>
       </c>
       <c r="E19" t="n">
-        <v>13.9368</v>
+        <v>14.0131</v>
       </c>
       <c r="F19" t="n">
-        <v>34.4132</v>
+        <v>34.3857</v>
       </c>
     </row>
     <row r="20">
@@ -5440,19 +5440,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>13.9748</v>
+        <v>14.0834</v>
       </c>
       <c r="C20" t="n">
-        <v>16.0987</v>
+        <v>16.1608</v>
       </c>
       <c r="D20" t="n">
-        <v>42.3968</v>
+        <v>42.3159</v>
       </c>
       <c r="E20" t="n">
-        <v>13.7019</v>
+        <v>13.8314</v>
       </c>
       <c r="F20" t="n">
-        <v>34.113</v>
+        <v>34.1888</v>
       </c>
     </row>
     <row r="21">
@@ -5460,19 +5460,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>13.6677</v>
+        <v>13.7126</v>
       </c>
       <c r="C21" t="n">
-        <v>16.0553</v>
+        <v>16.0855</v>
       </c>
       <c r="D21" t="n">
-        <v>43.1986</v>
+        <v>43.0995</v>
       </c>
       <c r="E21" t="n">
-        <v>13.4544</v>
+        <v>16.6954</v>
       </c>
       <c r="F21" t="n">
-        <v>33.9261</v>
+        <v>37.5555</v>
       </c>
     </row>
     <row r="22">
@@ -5480,19 +5480,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>13.3881</v>
+        <v>13.2816</v>
       </c>
       <c r="C22" t="n">
-        <v>17.6718</v>
+        <v>17.6634</v>
       </c>
       <c r="D22" t="n">
-        <v>43.1635</v>
+        <v>43.1178</v>
       </c>
       <c r="E22" t="n">
-        <v>13.2087</v>
+        <v>16.4406</v>
       </c>
       <c r="F22" t="n">
-        <v>33.7387</v>
+        <v>37.3234</v>
       </c>
     </row>
     <row r="23">
@@ -5500,19 +5500,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.8006</v>
+        <v>12.901</v>
       </c>
       <c r="C23" t="n">
-        <v>17.5651</v>
+        <v>17.5424</v>
       </c>
       <c r="D23" t="n">
-        <v>43.1189</v>
+        <v>43.0892</v>
       </c>
       <c r="E23" t="n">
-        <v>16.1204</v>
+        <v>16.1585</v>
       </c>
       <c r="F23" t="n">
-        <v>36.9034</v>
+        <v>36.9747</v>
       </c>
     </row>
     <row r="24">
@@ -5520,19 +5520,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>17.4542</v>
+        <v>17.4736</v>
       </c>
       <c r="C24" t="n">
-        <v>17.3647</v>
+        <v>17.4106</v>
       </c>
       <c r="D24" t="n">
-        <v>43.0551</v>
+        <v>43.0277</v>
       </c>
       <c r="E24" t="n">
-        <v>15.8924</v>
+        <v>15.9947</v>
       </c>
       <c r="F24" t="n">
-        <v>36.8044</v>
+        <v>36.845</v>
       </c>
     </row>
     <row r="25">
@@ -5540,19 +5540,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>17.1748</v>
+        <v>17.191</v>
       </c>
       <c r="C25" t="n">
-        <v>17.2495</v>
+        <v>17.2732</v>
       </c>
       <c r="D25" t="n">
-        <v>43.0346</v>
+        <v>43.0856</v>
       </c>
       <c r="E25" t="n">
-        <v>15.8005</v>
+        <v>15.7947</v>
       </c>
       <c r="F25" t="n">
-        <v>36.4518</v>
+        <v>36.5202</v>
       </c>
     </row>
     <row r="26">
@@ -5560,19 +5560,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>16.8841</v>
+        <v>16.8874</v>
       </c>
       <c r="C26" t="n">
-        <v>17.0971</v>
+        <v>17.1195</v>
       </c>
       <c r="D26" t="n">
-        <v>43.1039</v>
+        <v>42.8998</v>
       </c>
       <c r="E26" t="n">
-        <v>15.5119</v>
+        <v>15.5014</v>
       </c>
       <c r="F26" t="n">
-        <v>36.3222</v>
+        <v>36.0768</v>
       </c>
     </row>
     <row r="27">
@@ -5580,19 +5580,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>16.5335</v>
+        <v>16.5459</v>
       </c>
       <c r="C27" t="n">
-        <v>16.9973</v>
+        <v>16.9736</v>
       </c>
       <c r="D27" t="n">
-        <v>42.9368</v>
+        <v>42.8705</v>
       </c>
       <c r="E27" t="n">
-        <v>15.363</v>
+        <v>15.3413</v>
       </c>
       <c r="F27" t="n">
-        <v>36.1463</v>
+        <v>36.0152</v>
       </c>
     </row>
     <row r="28">
@@ -5600,19 +5600,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>16.2036</v>
+        <v>16.2084</v>
       </c>
       <c r="C28" t="n">
-        <v>16.8954</v>
+        <v>16.8955</v>
       </c>
       <c r="D28" t="n">
-        <v>42.9757</v>
+        <v>42.9113</v>
       </c>
       <c r="E28" t="n">
-        <v>15.1748</v>
+        <v>15.0828</v>
       </c>
       <c r="F28" t="n">
-        <v>35.8828</v>
+        <v>35.7248</v>
       </c>
     </row>
     <row r="29">
@@ -5620,19 +5620,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>15.8711</v>
+        <v>15.8685</v>
       </c>
       <c r="C29" t="n">
-        <v>16.78</v>
+        <v>16.7879</v>
       </c>
       <c r="D29" t="n">
-        <v>43.045</v>
+        <v>42.8371</v>
       </c>
       <c r="E29" t="n">
-        <v>14.9686</v>
+        <v>14.9981</v>
       </c>
       <c r="F29" t="n">
-        <v>35.6187</v>
+        <v>35.663</v>
       </c>
     </row>
     <row r="30">
@@ -5640,19 +5640,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>15.5589</v>
+        <v>15.5497</v>
       </c>
       <c r="C30" t="n">
-        <v>16.7155</v>
+        <v>16.6964</v>
       </c>
       <c r="D30" t="n">
-        <v>42.9152</v>
+        <v>42.9277</v>
       </c>
       <c r="E30" t="n">
-        <v>14.7527</v>
+        <v>14.7474</v>
       </c>
       <c r="F30" t="n">
-        <v>35.4076</v>
+        <v>35.3048</v>
       </c>
     </row>
     <row r="31">
@@ -5660,19 +5660,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>15.2395</v>
+        <v>15.2126</v>
       </c>
       <c r="C31" t="n">
-        <v>16.5879</v>
+        <v>16.5827</v>
       </c>
       <c r="D31" t="n">
-        <v>42.9377</v>
+        <v>42.8816</v>
       </c>
       <c r="E31" t="n">
-        <v>14.5338</v>
+        <v>14.6118</v>
       </c>
       <c r="F31" t="n">
-        <v>35.0425</v>
+        <v>35.142</v>
       </c>
     </row>
     <row r="32">
@@ -5680,19 +5680,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>14.9203</v>
+        <v>14.8997</v>
       </c>
       <c r="C32" t="n">
-        <v>16.5521</v>
+        <v>16.5783</v>
       </c>
       <c r="D32" t="n">
-        <v>42.8191</v>
+        <v>42.7683</v>
       </c>
       <c r="E32" t="n">
-        <v>14.4195</v>
+        <v>14.4324</v>
       </c>
       <c r="F32" t="n">
-        <v>34.8775</v>
+        <v>34.8684</v>
       </c>
     </row>
     <row r="33">
@@ -5700,19 +5700,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>14.6297</v>
+        <v>14.616</v>
       </c>
       <c r="C33" t="n">
-        <v>16.4655</v>
+        <v>16.4986</v>
       </c>
       <c r="D33" t="n">
-        <v>42.7471</v>
+        <v>42.805</v>
       </c>
       <c r="E33" t="n">
-        <v>14.2501</v>
+        <v>14.2306</v>
       </c>
       <c r="F33" t="n">
-        <v>34.7348</v>
+        <v>34.7497</v>
       </c>
     </row>
     <row r="34">
@@ -5720,19 +5720,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>14.3293</v>
+        <v>14.3284</v>
       </c>
       <c r="C34" t="n">
-        <v>16.3927</v>
+        <v>16.4048</v>
       </c>
       <c r="D34" t="n">
-        <v>42.8549</v>
+        <v>42.7229</v>
       </c>
       <c r="E34" t="n">
-        <v>13.9607</v>
+        <v>13.9707</v>
       </c>
       <c r="F34" t="n">
-        <v>34.5125</v>
+        <v>34.3271</v>
       </c>
     </row>
     <row r="35">
@@ -5740,19 +5740,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>14.0202</v>
+        <v>13.9833</v>
       </c>
       <c r="C35" t="n">
-        <v>16.3029</v>
+        <v>16.3458</v>
       </c>
       <c r="D35" t="n">
-        <v>43.6491</v>
+        <v>43.5866</v>
       </c>
       <c r="E35" t="n">
-        <v>13.7126</v>
+        <v>17.1941</v>
       </c>
       <c r="F35" t="n">
-        <v>34.2075</v>
+        <v>37.8955</v>
       </c>
     </row>
     <row r="36">
@@ -5760,19 +5760,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>13.7082</v>
+        <v>13.6695</v>
       </c>
       <c r="C36" t="n">
-        <v>16.2675</v>
+        <v>16.2972</v>
       </c>
       <c r="D36" t="n">
-        <v>43.7195</v>
+        <v>43.6028</v>
       </c>
       <c r="E36" t="n">
-        <v>13.5071</v>
+        <v>16.8713</v>
       </c>
       <c r="F36" t="n">
-        <v>34.2652</v>
+        <v>37.7109</v>
       </c>
     </row>
     <row r="37">
@@ -5780,19 +5780,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.2594</v>
+        <v>13.2175</v>
       </c>
       <c r="C37" t="n">
-        <v>17.7735</v>
+        <v>17.7674</v>
       </c>
       <c r="D37" t="n">
-        <v>43.6412</v>
+        <v>43.4554</v>
       </c>
       <c r="E37" t="n">
-        <v>16.5005</v>
+        <v>16.5357</v>
       </c>
       <c r="F37" t="n">
-        <v>37.2732</v>
+        <v>37.4502</v>
       </c>
     </row>
     <row r="38">
@@ -5800,19 +5800,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>17.6067</v>
+        <v>17.6268</v>
       </c>
       <c r="C38" t="n">
-        <v>17.5942</v>
+        <v>17.6349</v>
       </c>
       <c r="D38" t="n">
-        <v>43.5902</v>
+        <v>43.4316</v>
       </c>
       <c r="E38" t="n">
-        <v>16.2063</v>
+        <v>16.2506</v>
       </c>
       <c r="F38" t="n">
-        <v>37.0873</v>
+        <v>37.1745</v>
       </c>
     </row>
     <row r="39">
@@ -5820,19 +5820,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>17.3501</v>
+        <v>17.3289</v>
       </c>
       <c r="C39" t="n">
-        <v>17.4676</v>
+        <v>17.4935</v>
       </c>
       <c r="D39" t="n">
-        <v>43.4203</v>
+        <v>43.461</v>
       </c>
       <c r="E39" t="n">
-        <v>15.9994</v>
+        <v>15.974</v>
       </c>
       <c r="F39" t="n">
-        <v>36.8424</v>
+        <v>37.2046</v>
       </c>
     </row>
     <row r="40">
@@ -5840,19 +5840,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>17.06</v>
+        <v>17.0585</v>
       </c>
       <c r="C40" t="n">
-        <v>17.419</v>
+        <v>17.387</v>
       </c>
       <c r="D40" t="n">
-        <v>43.3178</v>
+        <v>43.2847</v>
       </c>
       <c r="E40" t="n">
-        <v>15.7972</v>
+        <v>15.8024</v>
       </c>
       <c r="F40" t="n">
-        <v>36.6256</v>
+        <v>36.6126</v>
       </c>
     </row>
     <row r="41">
@@ -5860,19 +5860,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>16.7201</v>
+        <v>16.7332</v>
       </c>
       <c r="C41" t="n">
-        <v>17.2299</v>
+        <v>17.2324</v>
       </c>
       <c r="D41" t="n">
-        <v>43.3527</v>
+        <v>43.3999</v>
       </c>
       <c r="E41" t="n">
-        <v>15.5946</v>
+        <v>15.5888</v>
       </c>
       <c r="F41" t="n">
-        <v>36.6422</v>
+        <v>36.4758</v>
       </c>
     </row>
     <row r="42">
@@ -5880,19 +5880,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>16.3959</v>
+        <v>16.3829</v>
       </c>
       <c r="C42" t="n">
-        <v>17.0789</v>
+        <v>17.0997</v>
       </c>
       <c r="D42" t="n">
-        <v>43.3744</v>
+        <v>43.2567</v>
       </c>
       <c r="E42" t="n">
-        <v>15.3874</v>
+        <v>15.4119</v>
       </c>
       <c r="F42" t="n">
-        <v>36.4124</v>
+        <v>36.1415</v>
       </c>
     </row>
     <row r="43">
@@ -5900,19 +5900,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>16.0463</v>
+        <v>16.0351</v>
       </c>
       <c r="C43" t="n">
-        <v>16.952</v>
+        <v>16.9836</v>
       </c>
       <c r="D43" t="n">
-        <v>43.2904</v>
+        <v>43.1861</v>
       </c>
       <c r="E43" t="n">
-        <v>15.196</v>
+        <v>15.2331</v>
       </c>
       <c r="F43" t="n">
-        <v>35.902</v>
+        <v>35.9231</v>
       </c>
     </row>
     <row r="44">
@@ -5920,19 +5920,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>15.6795</v>
+        <v>15.6653</v>
       </c>
       <c r="C44" t="n">
-        <v>16.8242</v>
+        <v>16.8736</v>
       </c>
       <c r="D44" t="n">
-        <v>43.2148</v>
+        <v>43.3365</v>
       </c>
       <c r="E44" t="n">
-        <v>15.0167</v>
+        <v>15.0643</v>
       </c>
       <c r="F44" t="n">
-        <v>35.7515</v>
+        <v>35.6559</v>
       </c>
     </row>
     <row r="45">
@@ -5940,19 +5940,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>15.3383</v>
+        <v>15.3271</v>
       </c>
       <c r="C45" t="n">
-        <v>16.7496</v>
+        <v>16.767</v>
       </c>
       <c r="D45" t="n">
-        <v>43.1825</v>
+        <v>43.0495</v>
       </c>
       <c r="E45" t="n">
-        <v>14.8646</v>
+        <v>14.8622</v>
       </c>
       <c r="F45" t="n">
-        <v>35.4412</v>
+        <v>35.4157</v>
       </c>
     </row>
     <row r="46">
@@ -5960,19 +5960,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>15.0264</v>
+        <v>15.0206</v>
       </c>
       <c r="C46" t="n">
-        <v>16.678</v>
+        <v>16.6854</v>
       </c>
       <c r="D46" t="n">
-        <v>43.1218</v>
+        <v>43.1703</v>
       </c>
       <c r="E46" t="n">
-        <v>14.6861</v>
+        <v>14.7107</v>
       </c>
       <c r="F46" t="n">
-        <v>35.2956</v>
+        <v>35.3224</v>
       </c>
     </row>
     <row r="47">
@@ -5980,19 +5980,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>14.7231</v>
+        <v>14.7245</v>
       </c>
       <c r="C47" t="n">
-        <v>16.6002</v>
+        <v>16.6032</v>
       </c>
       <c r="D47" t="n">
-        <v>43.2366</v>
+        <v>43.0237</v>
       </c>
       <c r="E47" t="n">
-        <v>14.5144</v>
+        <v>14.4866</v>
       </c>
       <c r="F47" t="n">
-        <v>35.0761</v>
+        <v>35.0226</v>
       </c>
     </row>
     <row r="48">
@@ -6000,19 +6000,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>14.44</v>
+        <v>14.434</v>
       </c>
       <c r="C48" t="n">
-        <v>16.5341</v>
+        <v>16.5323</v>
       </c>
       <c r="D48" t="n">
-        <v>43.1198</v>
+        <v>43.0398</v>
       </c>
       <c r="E48" t="n">
-        <v>14.2179</v>
+        <v>14.2315</v>
       </c>
       <c r="F48" t="n">
-        <v>34.7812</v>
+        <v>34.7915</v>
       </c>
     </row>
     <row r="49">
@@ -6020,19 +6020,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>14.125</v>
+        <v>14.1041</v>
       </c>
       <c r="C49" t="n">
-        <v>16.4584</v>
+        <v>16.4575</v>
       </c>
       <c r="D49" t="n">
-        <v>42.9103</v>
+        <v>43.057</v>
       </c>
       <c r="E49" t="n">
-        <v>14.0596</v>
+        <v>14.0447</v>
       </c>
       <c r="F49" t="n">
-        <v>34.5047</v>
+        <v>34.5829</v>
       </c>
     </row>
     <row r="50">
@@ -6040,19 +6040,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>13.7766</v>
+        <v>13.7562</v>
       </c>
       <c r="C50" t="n">
-        <v>16.4069</v>
+        <v>16.3904</v>
       </c>
       <c r="D50" t="n">
-        <v>44.0628</v>
+        <v>44.0519</v>
       </c>
       <c r="E50" t="n">
-        <v>13.7996</v>
+        <v>17.0777</v>
       </c>
       <c r="F50" t="n">
-        <v>34.3735</v>
+        <v>38.1673</v>
       </c>
     </row>
     <row r="51">
@@ -6060,19 +6060,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>13.336</v>
+        <v>13.3194</v>
       </c>
       <c r="C51" t="n">
-        <v>17.8528</v>
+        <v>17.8831</v>
       </c>
       <c r="D51" t="n">
-        <v>44.0548</v>
+        <v>43.9133</v>
       </c>
       <c r="E51" t="n">
-        <v>16.7527</v>
+        <v>16.797</v>
       </c>
       <c r="F51" t="n">
-        <v>37.7991</v>
+        <v>37.9241</v>
       </c>
     </row>
     <row r="52">
@@ -6080,19 +6080,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>12.8173</v>
+        <v>12.7738</v>
       </c>
       <c r="C52" t="n">
-        <v>17.6765</v>
+        <v>17.7159</v>
       </c>
       <c r="D52" t="n">
-        <v>43.9911</v>
+        <v>43.9453</v>
       </c>
       <c r="E52" t="n">
-        <v>16.4614</v>
+        <v>16.4794</v>
       </c>
       <c r="F52" t="n">
-        <v>37.8376</v>
+        <v>37.8518</v>
       </c>
     </row>
     <row r="53">
@@ -6100,19 +6100,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>17.4046</v>
+        <v>17.4063</v>
       </c>
       <c r="C53" t="n">
-        <v>17.5141</v>
+        <v>17.5478</v>
       </c>
       <c r="D53" t="n">
-        <v>43.7967</v>
+        <v>43.8425</v>
       </c>
       <c r="E53" t="n">
-        <v>16.2149</v>
+        <v>16.2305</v>
       </c>
       <c r="F53" t="n">
-        <v>37.3531</v>
+        <v>37.235</v>
       </c>
     </row>
     <row r="54">
@@ -6120,19 +6120,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>17.1145</v>
+        <v>17.1219</v>
       </c>
       <c r="C54" t="n">
-        <v>17.3926</v>
+        <v>17.4457</v>
       </c>
       <c r="D54" t="n">
-        <v>43.8502</v>
+        <v>43.8851</v>
       </c>
       <c r="E54" t="n">
-        <v>15.9803</v>
+        <v>16.025</v>
       </c>
       <c r="F54" t="n">
-        <v>37.1255</v>
+        <v>37.4324</v>
       </c>
     </row>
     <row r="55">
@@ -6140,19 +6140,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>16.8076</v>
+        <v>16.8077</v>
       </c>
       <c r="C55" t="n">
-        <v>17.2738</v>
+        <v>17.3353</v>
       </c>
       <c r="D55" t="n">
-        <v>43.7471</v>
+        <v>43.6094</v>
       </c>
       <c r="E55" t="n">
-        <v>15.7701</v>
+        <v>15.7533</v>
       </c>
       <c r="F55" t="n">
-        <v>37.1173</v>
+        <v>37.331</v>
       </c>
     </row>
     <row r="56">
@@ -6160,19 +6160,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>16.468</v>
+        <v>16.4829</v>
       </c>
       <c r="C56" t="n">
-        <v>17.1118</v>
+        <v>17.1478</v>
       </c>
       <c r="D56" t="n">
-        <v>43.7049</v>
+        <v>43.593</v>
       </c>
       <c r="E56" t="n">
-        <v>15.5663</v>
+        <v>15.5864</v>
       </c>
       <c r="F56" t="n">
-        <v>37.4745</v>
+        <v>36.8629</v>
       </c>
     </row>
     <row r="57">
@@ -6180,19 +6180,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>16.1337</v>
+        <v>16.1106</v>
       </c>
       <c r="C57" t="n">
-        <v>17.0324</v>
+        <v>17.0633</v>
       </c>
       <c r="D57" t="n">
-        <v>43.7702</v>
+        <v>43.762</v>
       </c>
       <c r="E57" t="n">
-        <v>15.367</v>
+        <v>15.348</v>
       </c>
       <c r="F57" t="n">
-        <v>37.3604</v>
+        <v>37.3266</v>
       </c>
     </row>
     <row r="58">
@@ -6200,19 +6200,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>15.7708</v>
+        <v>15.784</v>
       </c>
       <c r="C58" t="n">
-        <v>16.9005</v>
+        <v>16.9243</v>
       </c>
       <c r="D58" t="n">
-        <v>43.7769</v>
+        <v>43.8341</v>
       </c>
       <c r="E58" t="n">
-        <v>15.1676</v>
+        <v>15.1708</v>
       </c>
       <c r="F58" t="n">
-        <v>36.2344</v>
+        <v>37.0067</v>
       </c>
     </row>
     <row r="59">
@@ -6220,19 +6220,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>15.4369</v>
+        <v>15.4378</v>
       </c>
       <c r="C59" t="n">
-        <v>16.8057</v>
+        <v>16.8162</v>
       </c>
       <c r="D59" t="n">
-        <v>44.3974</v>
+        <v>44.0272</v>
       </c>
       <c r="E59" t="n">
-        <v>14.9989</v>
+        <v>15.0061</v>
       </c>
       <c r="F59" t="n">
-        <v>37.0297</v>
+        <v>37.0654</v>
       </c>
     </row>
     <row r="60">
@@ -6240,19 +6240,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>15.1097</v>
+        <v>15.1183</v>
       </c>
       <c r="C60" t="n">
-        <v>16.7359</v>
+        <v>16.7526</v>
       </c>
       <c r="D60" t="n">
-        <v>44.2108</v>
+        <v>44.1538</v>
       </c>
       <c r="E60" t="n">
-        <v>14.8119</v>
+        <v>14.7978</v>
       </c>
       <c r="F60" t="n">
-        <v>36.9738</v>
+        <v>36.5044</v>
       </c>
     </row>
     <row r="61">
@@ -6260,19 +6260,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>14.8228</v>
+        <v>14.8147</v>
       </c>
       <c r="C61" t="n">
-        <v>16.6481</v>
+        <v>16.6473</v>
       </c>
       <c r="D61" t="n">
-        <v>44.6895</v>
+        <v>44.1103</v>
       </c>
       <c r="E61" t="n">
-        <v>14.5947</v>
+        <v>14.5774</v>
       </c>
       <c r="F61" t="n">
-        <v>36.3733</v>
+        <v>36.4676</v>
       </c>
     </row>
     <row r="62">
@@ -6280,19 +6280,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>14.5019</v>
+        <v>14.5128</v>
       </c>
       <c r="C62" t="n">
-        <v>16.5858</v>
+        <v>16.6019</v>
       </c>
       <c r="D62" t="n">
-        <v>45.2524</v>
+        <v>44.3155</v>
       </c>
       <c r="E62" t="n">
-        <v>14.3683</v>
+        <v>14.3704</v>
       </c>
       <c r="F62" t="n">
-        <v>37.3017</v>
+        <v>37.383</v>
       </c>
     </row>
     <row r="63">
@@ -6300,19 +6300,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>14.209</v>
+        <v>14.2205</v>
       </c>
       <c r="C63" t="n">
-        <v>16.5182</v>
+        <v>16.5262</v>
       </c>
       <c r="D63" t="n">
-        <v>44.6599</v>
+        <v>45.2649</v>
       </c>
       <c r="E63" t="n">
-        <v>14.1309</v>
+        <v>14.1281</v>
       </c>
       <c r="F63" t="n">
-        <v>37.9561</v>
+        <v>37.8634</v>
       </c>
     </row>
     <row r="64">
@@ -6320,19 +6320,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>13.9013</v>
+        <v>13.894</v>
       </c>
       <c r="C64" t="n">
-        <v>16.4306</v>
+        <v>16.4541</v>
       </c>
       <c r="D64" t="n">
-        <v>50.4226</v>
+        <v>50.4235</v>
       </c>
       <c r="E64" t="n">
-        <v>13.9085</v>
+        <v>17.292</v>
       </c>
       <c r="F64" t="n">
-        <v>37.7973</v>
+        <v>45.4701</v>
       </c>
     </row>
     <row r="65">
@@ -6340,19 +6340,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>13.4763</v>
+        <v>13.5085</v>
       </c>
       <c r="C65" t="n">
-        <v>17.8974</v>
+        <v>17.9191</v>
       </c>
       <c r="D65" t="n">
-        <v>50.6978</v>
+        <v>51.2498</v>
       </c>
       <c r="E65" t="n">
-        <v>13.7037</v>
+        <v>16.9373</v>
       </c>
       <c r="F65" t="n">
-        <v>38.3413</v>
+        <v>46.2965</v>
       </c>
     </row>
     <row r="66">
@@ -6360,19 +6360,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>12.99</v>
+        <v>13.02</v>
       </c>
       <c r="C66" t="n">
-        <v>17.7295</v>
+        <v>17.7244</v>
       </c>
       <c r="D66" t="n">
-        <v>51.3551</v>
+        <v>51.7401</v>
       </c>
       <c r="E66" t="n">
-        <v>16.6634</v>
+        <v>16.6755</v>
       </c>
       <c r="F66" t="n">
-        <v>46.5127</v>
+        <v>46.7127</v>
       </c>
     </row>
     <row r="67">
@@ -6380,19 +6380,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>17.5683</v>
+        <v>17.533</v>
       </c>
       <c r="C67" t="n">
-        <v>17.5799</v>
+        <v>17.5831</v>
       </c>
       <c r="D67" t="n">
-        <v>51.6528</v>
+        <v>51.9848</v>
       </c>
       <c r="E67" t="n">
-        <v>16.3482</v>
+        <v>16.3789</v>
       </c>
       <c r="F67" t="n">
-        <v>47.3351</v>
+        <v>46.999</v>
       </c>
     </row>
     <row r="68">
@@ -6400,19 +6400,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>17.2413</v>
+        <v>17.2528</v>
       </c>
       <c r="C68" t="n">
-        <v>17.4329</v>
+        <v>17.4587</v>
       </c>
       <c r="D68" t="n">
-        <v>51.9931</v>
+        <v>52.3024</v>
       </c>
       <c r="E68" t="n">
-        <v>16.1653</v>
+        <v>16.1711</v>
       </c>
       <c r="F68" t="n">
-        <v>47.0045</v>
+        <v>47.2337</v>
       </c>
     </row>
     <row r="69">
@@ -6420,19 +6420,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>16.9047</v>
+        <v>16.9256</v>
       </c>
       <c r="C69" t="n">
-        <v>17.3162</v>
+        <v>17.3211</v>
       </c>
       <c r="D69" t="n">
-        <v>52.3133</v>
+        <v>52.7539</v>
       </c>
       <c r="E69" t="n">
-        <v>15.9015</v>
+        <v>15.9495</v>
       </c>
       <c r="F69" t="n">
-        <v>47.1243</v>
+        <v>47.3002</v>
       </c>
     </row>
     <row r="70">
@@ -6440,19 +6440,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>16.5732</v>
+        <v>16.5861</v>
       </c>
       <c r="C70" t="n">
-        <v>17.1613</v>
+        <v>17.2002</v>
       </c>
       <c r="D70" t="n">
-        <v>52.6366</v>
+        <v>52.9351</v>
       </c>
       <c r="E70" t="n">
-        <v>15.6949</v>
+        <v>15.741</v>
       </c>
       <c r="F70" t="n">
-        <v>46.9883</v>
+        <v>47.2087</v>
       </c>
     </row>
     <row r="71">
@@ -6460,19 +6460,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>16.2125</v>
+        <v>16.2183</v>
       </c>
       <c r="C71" t="n">
-        <v>17.0554</v>
+        <v>17.0686</v>
       </c>
       <c r="D71" t="n">
-        <v>53.205</v>
+        <v>53.1753</v>
       </c>
       <c r="E71" t="n">
-        <v>15.4986</v>
+        <v>15.4998</v>
       </c>
       <c r="F71" t="n">
-        <v>47.0609</v>
+        <v>47.0978</v>
       </c>
     </row>
     <row r="72">
@@ -6480,19 +6480,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>15.8559</v>
+        <v>15.8556</v>
       </c>
       <c r="C72" t="n">
-        <v>16.9568</v>
+        <v>16.9681</v>
       </c>
       <c r="D72" t="n">
-        <v>53.3623</v>
+        <v>53.5728</v>
       </c>
       <c r="E72" t="n">
-        <v>15.2901</v>
+        <v>15.3088</v>
       </c>
       <c r="F72" t="n">
-        <v>47.3447</v>
+        <v>46.9706</v>
       </c>
     </row>
     <row r="73">
@@ -6500,19 +6500,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>15.517</v>
+        <v>15.5126</v>
       </c>
       <c r="C73" t="n">
-        <v>16.8617</v>
+        <v>16.8616</v>
       </c>
       <c r="D73" t="n">
-        <v>53.6569</v>
+        <v>53.7703</v>
       </c>
       <c r="E73" t="n">
-        <v>15.0915</v>
+        <v>15.1188</v>
       </c>
       <c r="F73" t="n">
-        <v>46.879</v>
+        <v>46.844</v>
       </c>
     </row>
     <row r="74">
@@ -6520,19 +6520,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>15.1974</v>
+        <v>15.1841</v>
       </c>
       <c r="C74" t="n">
-        <v>16.7901</v>
+        <v>16.7775</v>
       </c>
       <c r="D74" t="n">
-        <v>53.7256</v>
+        <v>54.0403</v>
       </c>
       <c r="E74" t="n">
-        <v>14.8911</v>
+        <v>14.9022</v>
       </c>
       <c r="F74" t="n">
-        <v>46.486</v>
+        <v>46.6913</v>
       </c>
     </row>
     <row r="75">
@@ -6540,19 +6540,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>14.8731</v>
+        <v>14.8812</v>
       </c>
       <c r="C75" t="n">
-        <v>16.6819</v>
+        <v>16.7215</v>
       </c>
       <c r="D75" t="n">
-        <v>54.0637</v>
+        <v>53.9825</v>
       </c>
       <c r="E75" t="n">
-        <v>14.669</v>
+        <v>14.6818</v>
       </c>
       <c r="F75" t="n">
-        <v>46.5175</v>
+        <v>46.4872</v>
       </c>
     </row>
     <row r="76">
@@ -6560,19 +6560,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>14.5887</v>
+        <v>14.6001</v>
       </c>
       <c r="C76" t="n">
-        <v>16.6167</v>
+        <v>16.6442</v>
       </c>
       <c r="D76" t="n">
-        <v>54.1568</v>
+        <v>54.3153</v>
       </c>
       <c r="E76" t="n">
-        <v>14.4561</v>
+        <v>14.4974</v>
       </c>
       <c r="F76" t="n">
-        <v>46.4127</v>
+        <v>46.2902</v>
       </c>
     </row>
     <row r="77">
@@ -6580,19 +6580,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>14.2719</v>
+        <v>14.3032</v>
       </c>
       <c r="C77" t="n">
-        <v>16.5427</v>
+        <v>16.5762</v>
       </c>
       <c r="D77" t="n">
-        <v>54.3344</v>
+        <v>54.3196</v>
       </c>
       <c r="E77" t="n">
-        <v>14.2267</v>
+        <v>14.2547</v>
       </c>
       <c r="F77" t="n">
-        <v>45.9944</v>
+        <v>46.1768</v>
       </c>
     </row>
     <row r="78">
@@ -6600,19 +6600,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>13.968</v>
+        <v>13.9555</v>
       </c>
       <c r="C78" t="n">
-        <v>16.4775</v>
+        <v>16.4933</v>
       </c>
       <c r="D78" t="n">
-        <v>57.0418</v>
+        <v>57.2658</v>
       </c>
       <c r="E78" t="n">
-        <v>13.9847</v>
+        <v>17.4025</v>
       </c>
       <c r="F78" t="n">
-        <v>45.8026</v>
+        <v>49.9538</v>
       </c>
     </row>
     <row r="79">
@@ -6620,19 +6620,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>13.5733</v>
+        <v>13.5949</v>
       </c>
       <c r="C79" t="n">
-        <v>17.9722</v>
+        <v>18.0293</v>
       </c>
       <c r="D79" t="n">
-        <v>57.1364</v>
+        <v>57.3404</v>
       </c>
       <c r="E79" t="n">
-        <v>13.7487</v>
+        <v>17.0956</v>
       </c>
       <c r="F79" t="n">
-        <v>45.6468</v>
+        <v>49.488</v>
       </c>
     </row>
     <row r="80">
@@ -6640,19 +6640,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>13.1385</v>
+        <v>13.1287</v>
       </c>
       <c r="C80" t="n">
-        <v>17.7953</v>
+        <v>17.8802</v>
       </c>
       <c r="D80" t="n">
-        <v>57.0864</v>
+        <v>57.2368</v>
       </c>
       <c r="E80" t="n">
-        <v>16.7068</v>
+        <v>16.8068</v>
       </c>
       <c r="F80" t="n">
-        <v>49.1466</v>
+        <v>49.2354</v>
       </c>
     </row>
     <row r="81">
@@ -6660,19 +6660,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>17.6455</v>
+        <v>17.6689</v>
       </c>
       <c r="C81" t="n">
-        <v>17.6435</v>
+        <v>17.7041</v>
       </c>
       <c r="D81" t="n">
-        <v>57.1846</v>
+        <v>57.3238</v>
       </c>
       <c r="E81" t="n">
-        <v>16.4309</v>
+        <v>16.5172</v>
       </c>
       <c r="F81" t="n">
-        <v>48.7369</v>
+        <v>48.9638</v>
       </c>
     </row>
     <row r="82">
@@ -6680,19 +6680,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>17.3602</v>
+        <v>17.3638</v>
       </c>
       <c r="C82" t="n">
-        <v>17.479</v>
+        <v>17.5286</v>
       </c>
       <c r="D82" t="n">
-        <v>56.9086</v>
+        <v>57.2734</v>
       </c>
       <c r="E82" t="n">
-        <v>16.2183</v>
+        <v>16.2929</v>
       </c>
       <c r="F82" t="n">
-        <v>48.6363</v>
+        <v>48.7378</v>
       </c>
     </row>
     <row r="83">
@@ -6700,19 +6700,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>17.021</v>
+        <v>17.0696</v>
       </c>
       <c r="C83" t="n">
-        <v>17.3498</v>
+        <v>17.3945</v>
       </c>
       <c r="D83" t="n">
-        <v>57.198</v>
+        <v>57.2633</v>
       </c>
       <c r="E83" t="n">
-        <v>15.9712</v>
+        <v>16.0268</v>
       </c>
       <c r="F83" t="n">
-        <v>48.5207</v>
+        <v>48.3224</v>
       </c>
     </row>
     <row r="84">
@@ -6720,19 +6720,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>16.6611</v>
+        <v>16.6933</v>
       </c>
       <c r="C84" t="n">
-        <v>17.2363</v>
+        <v>17.2759</v>
       </c>
       <c r="D84" t="n">
-        <v>60.4917</v>
+        <v>60.6881</v>
       </c>
       <c r="E84" t="n">
-        <v>15.7744</v>
+        <v>15.8233</v>
       </c>
       <c r="F84" t="n">
-        <v>53.3064</v>
+        <v>53.2343</v>
       </c>
     </row>
     <row r="85">
@@ -6740,19 +6740,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>16.3111</v>
+        <v>16.336</v>
       </c>
       <c r="C85" t="n">
-        <v>17.0898</v>
+        <v>17.1484</v>
       </c>
       <c r="D85" t="n">
-        <v>60.3137</v>
+        <v>60.7922</v>
       </c>
       <c r="E85" t="n">
-        <v>15.5596</v>
+        <v>15.6142</v>
       </c>
       <c r="F85" t="n">
-        <v>53.0068</v>
+        <v>53.0808</v>
       </c>
     </row>
     <row r="86">
@@ -6760,19 +6760,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>15.9448</v>
+        <v>15.9765</v>
       </c>
       <c r="C86" t="n">
-        <v>16.9832</v>
+        <v>17.0695</v>
       </c>
       <c r="D86" t="n">
-        <v>60.53</v>
+        <v>60.695</v>
       </c>
       <c r="E86" t="n">
-        <v>15.3677</v>
+        <v>15.4107</v>
       </c>
       <c r="F86" t="n">
-        <v>52.6984</v>
+        <v>52.8031</v>
       </c>
     </row>
     <row r="87">
@@ -6780,19 +6780,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>15.6064</v>
+        <v>15.6253</v>
       </c>
       <c r="C87" t="n">
-        <v>16.8927</v>
+        <v>16.9352</v>
       </c>
       <c r="D87" t="n">
-        <v>60.5216</v>
+        <v>60.6372</v>
       </c>
       <c r="E87" t="n">
-        <v>15.1722</v>
+        <v>15.2202</v>
       </c>
       <c r="F87" t="n">
-        <v>52.4518</v>
+        <v>52.5035</v>
       </c>
     </row>
     <row r="88">
@@ -6800,19 +6800,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>15.2857</v>
+        <v>15.291</v>
       </c>
       <c r="C88" t="n">
-        <v>16.8164</v>
+        <v>16.8355</v>
       </c>
       <c r="D88" t="n">
-        <v>60.3618</v>
+        <v>60.5746</v>
       </c>
       <c r="E88" t="n">
-        <v>14.9693</v>
+        <v>15.0097</v>
       </c>
       <c r="F88" t="n">
-        <v>52.1935</v>
+        <v>52.206</v>
       </c>
     </row>
     <row r="89">
@@ -6820,19 +6820,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>14.9555</v>
+        <v>14.9643</v>
       </c>
       <c r="C89" t="n">
-        <v>16.6974</v>
+        <v>16.7571</v>
       </c>
       <c r="D89" t="n">
-        <v>60.3325</v>
+        <v>60.522</v>
       </c>
       <c r="E89" t="n">
-        <v>14.7401</v>
+        <v>14.791</v>
       </c>
       <c r="F89" t="n">
-        <v>51.9495</v>
+        <v>52.0193</v>
       </c>
     </row>
     <row r="90">
@@ -6840,19 +6840,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>14.6507</v>
+        <v>14.6692</v>
       </c>
       <c r="C90" t="n">
-        <v>16.6411</v>
+        <v>16.6757</v>
       </c>
       <c r="D90" t="n">
-        <v>60.4014</v>
+        <v>60.5529</v>
       </c>
       <c r="E90" t="n">
-        <v>14.526</v>
+        <v>14.5591</v>
       </c>
       <c r="F90" t="n">
-        <v>51.7845</v>
+        <v>51.6981</v>
       </c>
     </row>
     <row r="91">
@@ -6860,19 +6860,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>14.3513</v>
+        <v>14.3623</v>
       </c>
       <c r="C91" t="n">
-        <v>16.5528</v>
+        <v>16.5897</v>
       </c>
       <c r="D91" t="n">
-        <v>60.3693</v>
+        <v>60.4016</v>
       </c>
       <c r="E91" t="n">
-        <v>14.3027</v>
+        <v>14.3216</v>
       </c>
       <c r="F91" t="n">
-        <v>51.3058</v>
+        <v>51.5118</v>
       </c>
     </row>
     <row r="92">
@@ -6880,19 +6880,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>14.02</v>
+        <v>14.0276</v>
       </c>
       <c r="C92" t="n">
-        <v>16.4685</v>
+        <v>16.5324</v>
       </c>
       <c r="D92" t="n">
-        <v>60.461</v>
+        <v>60.6677</v>
       </c>
       <c r="E92" t="n">
-        <v>14.0429</v>
+        <v>17.5571</v>
       </c>
       <c r="F92" t="n">
-        <v>51.2933</v>
+        <v>55.1172</v>
       </c>
     </row>
     <row r="93">
@@ -6900,19 +6900,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>13.6723</v>
+        <v>13.6903</v>
       </c>
       <c r="C93" t="n">
-        <v>16.4112</v>
+        <v>16.4729</v>
       </c>
       <c r="D93" t="n">
-        <v>60.4534</v>
+        <v>60.5182</v>
       </c>
       <c r="E93" t="n">
-        <v>13.7938</v>
+        <v>17.2109</v>
       </c>
       <c r="F93" t="n">
-        <v>51.0179</v>
+        <v>54.7306</v>
       </c>
     </row>
     <row r="94">
@@ -6920,19 +6920,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>13.2356</v>
+        <v>13.2033</v>
       </c>
       <c r="C94" t="n">
-        <v>17.8296</v>
+        <v>17.8774</v>
       </c>
       <c r="D94" t="n">
-        <v>60.3649</v>
+        <v>60.6239</v>
       </c>
       <c r="E94" t="n">
-        <v>16.8442</v>
+        <v>16.8391</v>
       </c>
       <c r="F94" t="n">
-        <v>54.6661</v>
+        <v>54.3977</v>
       </c>
     </row>
     <row r="95">
@@ -6940,19 +6940,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>17.7076</v>
+        <v>17.709</v>
       </c>
       <c r="C95" t="n">
-        <v>17.6646</v>
+        <v>17.7082</v>
       </c>
       <c r="D95" t="n">
-        <v>60.4023</v>
+        <v>60.3804</v>
       </c>
       <c r="E95" t="n">
-        <v>16.563</v>
+        <v>16.5756</v>
       </c>
       <c r="F95" t="n">
-        <v>54.2104</v>
+        <v>54.0604</v>
       </c>
     </row>
     <row r="96">
@@ -6960,19 +6960,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>17.419</v>
+        <v>17.4365</v>
       </c>
       <c r="C96" t="n">
-        <v>17.5009</v>
+        <v>17.5313</v>
       </c>
       <c r="D96" t="n">
-        <v>60.4124</v>
+        <v>60.2907</v>
       </c>
       <c r="E96" t="n">
-        <v>16.3243</v>
+        <v>16.3654</v>
       </c>
       <c r="F96" t="n">
-        <v>53.8107</v>
+        <v>53.9564</v>
       </c>
     </row>
     <row r="97">
@@ -6980,19 +6980,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>17.1187</v>
+        <v>17.0982</v>
       </c>
       <c r="C97" t="n">
-        <v>17.3856</v>
+        <v>17.3929</v>
       </c>
       <c r="D97" t="n">
-        <v>60.0798</v>
+        <v>60.4183</v>
       </c>
       <c r="E97" t="n">
-        <v>16.0888</v>
+        <v>16.1265</v>
       </c>
       <c r="F97" t="n">
-        <v>53.6334</v>
+        <v>53.7208</v>
       </c>
     </row>
     <row r="98">
@@ -7000,19 +7000,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>16.7508</v>
+        <v>16.7749</v>
       </c>
       <c r="C98" t="n">
-        <v>17.2426</v>
+        <v>17.2987</v>
       </c>
       <c r="D98" t="n">
-        <v>60.1861</v>
+        <v>60.2378</v>
       </c>
       <c r="E98" t="n">
-        <v>15.8516</v>
+        <v>15.9101</v>
       </c>
       <c r="F98" t="n">
-        <v>53.1855</v>
+        <v>53.2541</v>
       </c>
     </row>
     <row r="99">
@@ -7020,19 +7020,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>16.4005</v>
+        <v>16.3919</v>
       </c>
       <c r="C99" t="n">
-        <v>17.1274</v>
+        <v>17.1213</v>
       </c>
       <c r="D99" t="n">
-        <v>60.1532</v>
+        <v>60.2363</v>
       </c>
       <c r="E99" t="n">
-        <v>15.6142</v>
+        <v>15.6653</v>
       </c>
       <c r="F99" t="n">
-        <v>52.879</v>
+        <v>52.9286</v>
       </c>
     </row>
     <row r="100">
@@ -7040,19 +7040,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>16.0171</v>
+        <v>16.0269</v>
       </c>
       <c r="C100" t="n">
-        <v>17.0194</v>
+        <v>17.0425</v>
       </c>
       <c r="D100" t="n">
-        <v>60.1917</v>
+        <v>60.172</v>
       </c>
       <c r="E100" t="n">
-        <v>15.4055</v>
+        <v>15.4163</v>
       </c>
       <c r="F100" t="n">
-        <v>52.6054</v>
+        <v>52.719</v>
       </c>
     </row>
     <row r="101">
@@ -7060,19 +7060,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>15.6545</v>
+        <v>15.6675</v>
       </c>
       <c r="C101" t="n">
-        <v>16.8816</v>
+        <v>16.9468</v>
       </c>
       <c r="D101" t="n">
-        <v>60.1221</v>
+        <v>60.0489</v>
       </c>
       <c r="E101" t="n">
-        <v>15.223</v>
+        <v>15.2416</v>
       </c>
       <c r="F101" t="n">
-        <v>52.3431</v>
+        <v>52.4166</v>
       </c>
     </row>
     <row r="102">
@@ -7080,19 +7080,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>15.3301</v>
+        <v>15.3354</v>
       </c>
       <c r="C102" t="n">
-        <v>16.814</v>
+        <v>16.8308</v>
       </c>
       <c r="D102" t="n">
-        <v>60.0248</v>
+        <v>60.0764</v>
       </c>
       <c r="E102" t="n">
-        <v>15.0063</v>
+        <v>15.0485</v>
       </c>
       <c r="F102" t="n">
-        <v>52.0458</v>
+        <v>52.2174</v>
       </c>
     </row>
     <row r="103">
@@ -7100,19 +7100,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>15.0013</v>
+        <v>15.0298</v>
       </c>
       <c r="C103" t="n">
-        <v>16.7281</v>
+        <v>16.7719</v>
       </c>
       <c r="D103" t="n">
-        <v>59.9151</v>
+        <v>59.994</v>
       </c>
       <c r="E103" t="n">
-        <v>14.7909</v>
+        <v>14.815</v>
       </c>
       <c r="F103" t="n">
-        <v>51.797</v>
+        <v>52.0383</v>
       </c>
     </row>
     <row r="104">
@@ -7120,19 +7120,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>14.6869</v>
+        <v>14.7165</v>
       </c>
       <c r="C104" t="n">
-        <v>16.6283</v>
+        <v>16.6479</v>
       </c>
       <c r="D104" t="n">
-        <v>59.9769</v>
+        <v>60.0493</v>
       </c>
       <c r="E104" t="n">
-        <v>14.5693</v>
+        <v>14.5768</v>
       </c>
       <c r="F104" t="n">
-        <v>51.5404</v>
+        <v>51.6913</v>
       </c>
     </row>
     <row r="105">
@@ -7140,19 +7140,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>14.3984</v>
+        <v>14.4051</v>
       </c>
       <c r="C105" t="n">
-        <v>16.5554</v>
+        <v>16.6014</v>
       </c>
       <c r="D105" t="n">
-        <v>59.9699</v>
+        <v>59.9397</v>
       </c>
       <c r="E105" t="n">
-        <v>14.3376</v>
+        <v>14.3464</v>
       </c>
       <c r="F105" t="n">
-        <v>51.4792</v>
+        <v>51.5064</v>
       </c>
     </row>
     <row r="106">
@@ -7160,19 +7160,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>14.0783</v>
+        <v>14.0816</v>
       </c>
       <c r="C106" t="n">
-        <v>16.4804</v>
+        <v>16.5086</v>
       </c>
       <c r="D106" t="n">
-        <v>59.8579</v>
+        <v>59.8951</v>
       </c>
       <c r="E106" t="n">
-        <v>14.0975</v>
+        <v>14.1174</v>
       </c>
       <c r="F106" t="n">
-        <v>51.1333</v>
+        <v>51.6185</v>
       </c>
     </row>
     <row r="107">
@@ -7180,19 +7180,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>13.7227</v>
+        <v>13.7206</v>
       </c>
       <c r="C107" t="n">
-        <v>16.4139</v>
+        <v>16.4299</v>
       </c>
       <c r="D107" t="n">
-        <v>58.7641</v>
+        <v>58.8902</v>
       </c>
       <c r="E107" t="n">
-        <v>13.8463</v>
+        <v>17.326</v>
       </c>
       <c r="F107" t="n">
-        <v>51.034</v>
+        <v>54.6492</v>
       </c>
     </row>
     <row r="108">
@@ -7200,19 +7200,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>13.2881</v>
+        <v>13.2996</v>
       </c>
       <c r="C108" t="n">
-        <v>17.8386</v>
+        <v>17.8942</v>
       </c>
       <c r="D108" t="n">
-        <v>58.7267</v>
+        <v>58.8298</v>
       </c>
       <c r="E108" t="n">
-        <v>16.9736</v>
+        <v>17.0317</v>
       </c>
       <c r="F108" t="n">
-        <v>54.3815</v>
+        <v>54.5466</v>
       </c>
     </row>
     <row r="109">
@@ -7220,19 +7220,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>12.7778</v>
+        <v>12.7805</v>
       </c>
       <c r="C109" t="n">
-        <v>17.6681</v>
+        <v>17.6848</v>
       </c>
       <c r="D109" t="n">
-        <v>58.8485</v>
+        <v>58.7849</v>
       </c>
       <c r="E109" t="n">
-        <v>16.6251</v>
+        <v>16.6569</v>
       </c>
       <c r="F109" t="n">
-        <v>54.0617</v>
+        <v>54.3876</v>
       </c>
     </row>
     <row r="110">
@@ -7240,19 +7240,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>17.4744</v>
+        <v>17.4672</v>
       </c>
       <c r="C110" t="n">
-        <v>17.5413</v>
+        <v>17.5418</v>
       </c>
       <c r="D110" t="n">
-        <v>58.8735</v>
+        <v>58.7634</v>
       </c>
       <c r="E110" t="n">
-        <v>16.375</v>
+        <v>16.38</v>
       </c>
       <c r="F110" t="n">
-        <v>53.7597</v>
+        <v>53.9714</v>
       </c>
     </row>
     <row r="111">
@@ -7260,19 +7260,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>17.1467</v>
+        <v>17.1571</v>
       </c>
       <c r="C111" t="n">
-        <v>17.3867</v>
+        <v>17.4011</v>
       </c>
       <c r="D111" t="n">
-        <v>58.9617</v>
+        <v>58.9046</v>
       </c>
       <c r="E111" t="n">
-        <v>16.097</v>
+        <v>16.1306</v>
       </c>
       <c r="F111" t="n">
-        <v>53.5014</v>
+        <v>53.6502</v>
       </c>
     </row>
     <row r="112">
@@ -7280,19 +7280,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>16.8063</v>
+        <v>16.8154</v>
       </c>
       <c r="C112" t="n">
-        <v>17.2487</v>
+        <v>17.2533</v>
       </c>
       <c r="D112" t="n">
-        <v>58.9763</v>
+        <v>58.9082</v>
       </c>
       <c r="E112" t="n">
-        <v>15.8728</v>
+        <v>15.9164</v>
       </c>
       <c r="F112" t="n">
-        <v>53.2255</v>
+        <v>53.1648</v>
       </c>
     </row>
     <row r="113">
@@ -7300,19 +7300,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>16.4568</v>
+        <v>16.4529</v>
       </c>
       <c r="C113" t="n">
-        <v>17.1224</v>
+        <v>17.1299</v>
       </c>
       <c r="D113" t="n">
-        <v>58.9715</v>
+        <v>59.0335</v>
       </c>
       <c r="E113" t="n">
-        <v>15.6835</v>
+        <v>15.6901</v>
       </c>
       <c r="F113" t="n">
-        <v>53.0887</v>
+        <v>53.2503</v>
       </c>
     </row>
     <row r="114">
@@ -7320,19 +7320,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>16.089</v>
+        <v>16.0839</v>
       </c>
       <c r="C114" t="n">
-        <v>17.0188</v>
+        <v>17.0227</v>
       </c>
       <c r="D114" t="n">
-        <v>58.9974</v>
+        <v>58.9628</v>
       </c>
       <c r="E114" t="n">
-        <v>15.4515</v>
+        <v>15.4909</v>
       </c>
       <c r="F114" t="n">
-        <v>52.7066</v>
+        <v>52.7109</v>
       </c>
     </row>
     <row r="115">
@@ -7340,19 +7340,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>15.7365</v>
+        <v>15.7258</v>
       </c>
       <c r="C115" t="n">
-        <v>16.9093</v>
+        <v>16.9114</v>
       </c>
       <c r="D115" t="n">
-        <v>59.0868</v>
+        <v>58.9818</v>
       </c>
       <c r="E115" t="n">
-        <v>15.2449</v>
+        <v>15.2752</v>
       </c>
       <c r="F115" t="n">
-        <v>52.3885</v>
+        <v>52.4936</v>
       </c>
     </row>
     <row r="116">
@@ -7360,19 +7360,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>15.4039</v>
+        <v>15.3859</v>
       </c>
       <c r="C116" t="n">
-        <v>16.824</v>
+        <v>16.8158</v>
       </c>
       <c r="D116" t="n">
-        <v>59.1379</v>
+        <v>59.0686</v>
       </c>
       <c r="E116" t="n">
-        <v>15.0338</v>
+        <v>15.0609</v>
       </c>
       <c r="F116" t="n">
-        <v>52.0727</v>
+        <v>52.3517</v>
       </c>
     </row>
     <row r="117">
@@ -7380,19 +7380,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>15.0806</v>
+        <v>15.068</v>
       </c>
       <c r="C117" t="n">
-        <v>16.7123</v>
+        <v>16.7169</v>
       </c>
       <c r="D117" t="n">
-        <v>59.1909</v>
+        <v>59.0899</v>
       </c>
       <c r="E117" t="n">
-        <v>14.8163</v>
+        <v>14.8464</v>
       </c>
       <c r="F117" t="n">
-        <v>51.8216</v>
+        <v>51.9934</v>
       </c>
     </row>
     <row r="118">
@@ -7400,19 +7400,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>14.7665</v>
+        <v>14.7514</v>
       </c>
       <c r="C118" t="n">
-        <v>16.6352</v>
+        <v>16.6349</v>
       </c>
       <c r="D118" t="n">
-        <v>59.0066</v>
+        <v>59.0846</v>
       </c>
       <c r="E118" t="n">
-        <v>14.6008</v>
+        <v>14.6096</v>
       </c>
       <c r="F118" t="n">
-        <v>51.6123</v>
+        <v>51.7515</v>
       </c>
     </row>
     <row r="119">
@@ -7420,19 +7420,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>14.4696</v>
+        <v>14.4554</v>
       </c>
       <c r="C119" t="n">
-        <v>16.5722</v>
+        <v>16.56</v>
       </c>
       <c r="D119" t="n">
-        <v>59.2414</v>
+        <v>59.1434</v>
       </c>
       <c r="E119" t="n">
-        <v>14.4173</v>
+        <v>14.3746</v>
       </c>
       <c r="F119" t="n">
-        <v>51.3572</v>
+        <v>51.3945</v>
       </c>
     </row>
     <row r="120">
@@ -7440,19 +7440,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>14.1573</v>
+        <v>14.1277</v>
       </c>
       <c r="C120" t="n">
-        <v>16.4801</v>
+        <v>16.4901</v>
       </c>
       <c r="D120" t="n">
-        <v>59.2243</v>
+        <v>59.1092</v>
       </c>
       <c r="E120" t="n">
-        <v>14.1348</v>
+        <v>14.1463</v>
       </c>
       <c r="F120" t="n">
-        <v>51.1481</v>
+        <v>51.1067</v>
       </c>
     </row>
     <row r="121">
@@ -7460,19 +7460,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>13.7792</v>
+        <v>13.7976</v>
       </c>
       <c r="C121" t="n">
-        <v>16.4281</v>
+        <v>16.4306</v>
       </c>
       <c r="D121" t="n">
-        <v>61.1603</v>
+        <v>61.0705</v>
       </c>
       <c r="E121" t="n">
-        <v>13.8924</v>
+        <v>17.73</v>
       </c>
       <c r="F121" t="n">
-        <v>50.8761</v>
+        <v>54.8456</v>
       </c>
     </row>
     <row r="122">
@@ -7480,19 +7480,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>13.4155</v>
+        <v>13.4015</v>
       </c>
       <c r="C122" t="n">
-        <v>17.8875</v>
+        <v>17.9034</v>
       </c>
       <c r="D122" t="n">
-        <v>61.1134</v>
+        <v>61.073</v>
       </c>
       <c r="E122" t="n">
-        <v>13.6189</v>
+        <v>17.2674</v>
       </c>
       <c r="F122" t="n">
-        <v>50.5861</v>
+        <v>54.4839</v>
       </c>
     </row>
     <row r="123">
@@ -7500,19 +7500,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>12.8824</v>
+        <v>12.8742</v>
       </c>
       <c r="C123" t="n">
-        <v>17.723</v>
+        <v>17.7325</v>
       </c>
       <c r="D123" t="n">
-        <v>60.9458</v>
+        <v>61.0849</v>
       </c>
       <c r="E123" t="n">
-        <v>16.7322</v>
+        <v>16.8382</v>
       </c>
       <c r="F123" t="n">
-        <v>54.0145</v>
+        <v>54.1529</v>
       </c>
     </row>
     <row r="124">
@@ -7520,19 +7520,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>17.5366</v>
+        <v>17.5156</v>
       </c>
       <c r="C124" t="n">
-        <v>17.5817</v>
+        <v>17.5534</v>
       </c>
       <c r="D124" t="n">
-        <v>60.9288</v>
+        <v>60.9006</v>
       </c>
       <c r="E124" t="n">
-        <v>16.5998</v>
+        <v>16.5325</v>
       </c>
       <c r="F124" t="n">
-        <v>53.7234</v>
+        <v>53.8759</v>
       </c>
     </row>
     <row r="125">
@@ -7540,19 +7540,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>17.2159</v>
+        <v>17.2146</v>
       </c>
       <c r="C125" t="n">
-        <v>17.4067</v>
+        <v>17.4045</v>
       </c>
       <c r="D125" t="n">
-        <v>60.7408</v>
+        <v>60.7963</v>
       </c>
       <c r="E125" t="n">
-        <v>16.3203</v>
+        <v>16.4156</v>
       </c>
       <c r="F125" t="n">
-        <v>53.3317</v>
+        <v>53.478</v>
       </c>
     </row>
     <row r="126">
@@ -7560,19 +7560,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>16.8888</v>
+        <v>16.8781</v>
       </c>
       <c r="C126" t="n">
-        <v>17.2645</v>
+        <v>17.2698</v>
       </c>
       <c r="D126" t="n">
-        <v>60.7</v>
+        <v>60.6777</v>
       </c>
       <c r="E126" t="n">
-        <v>15.9479</v>
+        <v>16.0255</v>
       </c>
       <c r="F126" t="n">
-        <v>53.1524</v>
+        <v>53.1636</v>
       </c>
     </row>
     <row r="127">
@@ -7580,19 +7580,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>16.5268</v>
+        <v>16.521</v>
       </c>
       <c r="C127" t="n">
-        <v>17.1425</v>
+        <v>17.1574</v>
       </c>
       <c r="D127" t="n">
-        <v>60.6492</v>
+        <v>60.729</v>
       </c>
       <c r="E127" t="n">
-        <v>15.7638</v>
+        <v>15.7602</v>
       </c>
       <c r="F127" t="n">
-        <v>53.0106</v>
+        <v>52.8127</v>
       </c>
     </row>
     <row r="128">
@@ -7600,19 +7600,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>16.159</v>
+        <v>16.1528</v>
       </c>
       <c r="C128" t="n">
-        <v>17.0218</v>
+        <v>17.0409</v>
       </c>
       <c r="D128" t="n">
-        <v>60.6004</v>
+        <v>60.5739</v>
       </c>
       <c r="E128" t="n">
-        <v>15.5024</v>
+        <v>15.4982</v>
       </c>
       <c r="F128" t="n">
-        <v>52.6021</v>
+        <v>52.5835</v>
       </c>
     </row>
     <row r="129">
@@ -7620,19 +7620,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>15.8081</v>
+        <v>15.7958</v>
       </c>
       <c r="C129" t="n">
-        <v>16.9323</v>
+        <v>16.9305</v>
       </c>
       <c r="D129" t="n">
-        <v>60.5193</v>
+        <v>60.5251</v>
       </c>
       <c r="E129" t="n">
-        <v>15.2982</v>
+        <v>15.3247</v>
       </c>
       <c r="F129" t="n">
-        <v>52.4123</v>
+        <v>52.4086</v>
       </c>
     </row>
     <row r="130">
@@ -7640,19 +7640,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>15.4797</v>
+        <v>15.4456</v>
       </c>
       <c r="C130" t="n">
-        <v>16.8314</v>
+        <v>16.8334</v>
       </c>
       <c r="D130" t="n">
-        <v>60.5394</v>
+        <v>60.5013</v>
       </c>
       <c r="E130" t="n">
-        <v>15.0981</v>
+        <v>15.1167</v>
       </c>
       <c r="F130" t="n">
-        <v>52.1918</v>
+        <v>52.0004</v>
       </c>
     </row>
     <row r="131">
@@ -7660,19 +7660,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>15.1342</v>
+        <v>15.1372</v>
       </c>
       <c r="C131" t="n">
-        <v>16.7238</v>
+        <v>16.7417</v>
       </c>
       <c r="D131" t="n">
-        <v>60.5453</v>
+        <v>60.4086</v>
       </c>
       <c r="E131" t="n">
-        <v>14.863</v>
+        <v>14.8894</v>
       </c>
       <c r="F131" t="n">
-        <v>51.8762</v>
+        <v>51.7815</v>
       </c>
     </row>
     <row r="132">
@@ -7680,19 +7680,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>14.8111</v>
+        <v>14.8192</v>
       </c>
       <c r="C132" t="n">
-        <v>16.658</v>
+        <v>16.6557</v>
       </c>
       <c r="D132" t="n">
-        <v>60.4153</v>
+        <v>60.4056</v>
       </c>
       <c r="E132" t="n">
-        <v>14.6626</v>
+        <v>14.6748</v>
       </c>
       <c r="F132" t="n">
-        <v>51.671</v>
+        <v>51.535</v>
       </c>
     </row>
     <row r="133">
@@ -7700,19 +7700,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>14.5073</v>
+        <v>14.5004</v>
       </c>
       <c r="C133" t="n">
-        <v>16.5776</v>
+        <v>16.5836</v>
       </c>
       <c r="D133" t="n">
-        <v>60.3736</v>
+        <v>60.3289</v>
       </c>
       <c r="E133" t="n">
-        <v>14.4402</v>
+        <v>14.4377</v>
       </c>
       <c r="F133" t="n">
-        <v>51.327</v>
+        <v>51.2253</v>
       </c>
     </row>
     <row r="134">
@@ -7720,19 +7720,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.1809</v>
+        <v>14.2149</v>
       </c>
       <c r="C134" t="n">
-        <v>16.4989</v>
+        <v>16.5038</v>
       </c>
       <c r="D134" t="n">
-        <v>60.3043</v>
+        <v>60.2294</v>
       </c>
       <c r="E134" t="n">
-        <v>14.1846</v>
+        <v>14.197</v>
       </c>
       <c r="F134" t="n">
-        <v>51.0919</v>
+        <v>51.0156</v>
       </c>
     </row>
     <row r="135">
@@ -7740,19 +7740,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>13.874</v>
+        <v>13.9076</v>
       </c>
       <c r="C135" t="n">
-        <v>16.4276</v>
+        <v>16.4509</v>
       </c>
       <c r="D135" t="n">
-        <v>61.7077</v>
+        <v>61.587</v>
       </c>
       <c r="E135" t="n">
-        <v>13.9295</v>
+        <v>18.2309</v>
       </c>
       <c r="F135" t="n">
-        <v>50.9035</v>
+        <v>54.8146</v>
       </c>
     </row>
     <row r="136">
@@ -7760,19 +7760,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>13.4675</v>
+        <v>13.4498</v>
       </c>
       <c r="C136" t="n">
-        <v>17.9585</v>
+        <v>17.9145</v>
       </c>
       <c r="D136" t="n">
-        <v>61.6293</v>
+        <v>61.3857</v>
       </c>
       <c r="E136" t="n">
-        <v>13.6761</v>
+        <v>17.7098</v>
       </c>
       <c r="F136" t="n">
-        <v>50.6111</v>
+        <v>54.3705</v>
       </c>
     </row>
     <row r="137">
@@ -7780,19 +7780,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>12.9954</v>
+        <v>13.0428</v>
       </c>
       <c r="C137" t="n">
-        <v>17.7619</v>
+        <v>17.7392</v>
       </c>
       <c r="D137" t="n">
-        <v>61.2953</v>
+        <v>61.3845</v>
       </c>
       <c r="E137" t="n">
-        <v>17.19</v>
+        <v>16.9312</v>
       </c>
       <c r="F137" t="n">
-        <v>53.9417</v>
+        <v>53.926</v>
       </c>
     </row>
     <row r="138">
@@ -7800,19 +7800,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>17.5801</v>
+        <v>17.5812</v>
       </c>
       <c r="C138" t="n">
-        <v>17.5911</v>
+        <v>17.5769</v>
       </c>
       <c r="D138" t="n">
-        <v>61.2641</v>
+        <v>61.3086</v>
       </c>
       <c r="E138" t="n">
-        <v>16.6817</v>
+        <v>16.707</v>
       </c>
       <c r="F138" t="n">
-        <v>53.6646</v>
+        <v>53.7485</v>
       </c>
     </row>
     <row r="139">
@@ -7820,19 +7820,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>17.2826</v>
+        <v>17.2953</v>
       </c>
       <c r="C139" t="n">
-        <v>17.406</v>
+        <v>17.4152</v>
       </c>
       <c r="D139" t="n">
-        <v>61.1327</v>
+        <v>61.2108</v>
       </c>
       <c r="E139" t="n">
-        <v>16.3162</v>
+        <v>16.4445</v>
       </c>
       <c r="F139" t="n">
-        <v>53.3926</v>
+        <v>53.3285</v>
       </c>
     </row>
     <row r="140">
@@ -7840,19 +7840,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>16.9667</v>
+        <v>16.9662</v>
       </c>
       <c r="C140" t="n">
-        <v>17.291</v>
+        <v>17.2963</v>
       </c>
       <c r="D140" t="n">
-        <v>61.0033</v>
+        <v>61.0768</v>
       </c>
       <c r="E140" t="n">
-        <v>16.0635</v>
+        <v>16.1437</v>
       </c>
       <c r="F140" t="n">
-        <v>53.0997</v>
+        <v>53.0693</v>
       </c>
     </row>
     <row r="141">
@@ -7860,19 +7860,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>16.612</v>
+        <v>16.6281</v>
       </c>
       <c r="C141" t="n">
-        <v>17.1613</v>
+        <v>17.1793</v>
       </c>
       <c r="D141" t="n">
-        <v>60.9215</v>
+        <v>61.0089</v>
       </c>
       <c r="E141" t="n">
-        <v>15.7948</v>
+        <v>15.8902</v>
       </c>
       <c r="F141" t="n">
-        <v>52.7148</v>
+        <v>52.7291</v>
       </c>
     </row>
     <row r="142">
@@ -7880,19 +7880,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>16.2576</v>
+        <v>16.2441</v>
       </c>
       <c r="C142" t="n">
-        <v>17.0363</v>
+        <v>17.0717</v>
       </c>
       <c r="D142" t="n">
-        <v>60.9419</v>
+        <v>60.9074</v>
       </c>
       <c r="E142" t="n">
-        <v>15.5839</v>
+        <v>15.6527</v>
       </c>
       <c r="F142" t="n">
-        <v>52.5057</v>
+        <v>52.4791</v>
       </c>
     </row>
     <row r="143">
@@ -7900,19 +7900,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>15.8936</v>
+        <v>15.8825</v>
       </c>
       <c r="C143" t="n">
-        <v>16.9391</v>
+        <v>16.9305</v>
       </c>
       <c r="D143" t="n">
-        <v>60.8628</v>
+        <v>60.7621</v>
       </c>
       <c r="E143" t="n">
-        <v>15.3884</v>
+        <v>15.3486</v>
       </c>
       <c r="F143" t="n">
-        <v>52.3157</v>
+        <v>52.525</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Running erasure.xlsx
+++ b/vs-x64/Running erasure.xlsx
@@ -5080,19 +5080,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>14.4861</v>
+        <v>14.4077</v>
       </c>
       <c r="C2" t="n">
-        <v>15.0881</v>
+        <v>15.1588</v>
       </c>
       <c r="D2" t="n">
-        <v>41.8336</v>
+        <v>41.8122</v>
       </c>
       <c r="E2" t="n">
-        <v>13.8705</v>
+        <v>13.7256</v>
       </c>
       <c r="F2" t="n">
-        <v>34.4017</v>
+        <v>34.4435</v>
       </c>
     </row>
     <row r="3">
@@ -5100,19 +5100,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>14.1949</v>
+        <v>14.0008</v>
       </c>
       <c r="C3" t="n">
-        <v>15.1025</v>
+        <v>15.0944</v>
       </c>
       <c r="D3" t="n">
-        <v>41.7753</v>
+        <v>41.655</v>
       </c>
       <c r="E3" t="n">
-        <v>13.7173</v>
+        <v>13.5258</v>
       </c>
       <c r="F3" t="n">
-        <v>34.1476</v>
+        <v>34.1771</v>
       </c>
     </row>
     <row r="4">
@@ -5120,19 +5120,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>13.859</v>
+        <v>13.8495</v>
       </c>
       <c r="C4" t="n">
-        <v>15.2515</v>
+        <v>15.2364</v>
       </c>
       <c r="D4" t="n">
-        <v>41.7832</v>
+        <v>41.7107</v>
       </c>
       <c r="E4" t="n">
-        <v>13.547</v>
+        <v>13.4295</v>
       </c>
       <c r="F4" t="n">
-        <v>33.9759</v>
+        <v>33.8041</v>
       </c>
     </row>
     <row r="5">
@@ -5140,19 +5140,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>13.6457</v>
+        <v>13.7098</v>
       </c>
       <c r="C5" t="n">
-        <v>15.1531</v>
+        <v>15.1511</v>
       </c>
       <c r="D5" t="n">
-        <v>41.6575</v>
+        <v>41.7897</v>
       </c>
       <c r="E5" t="n">
-        <v>13.3623</v>
+        <v>13.2726</v>
       </c>
       <c r="F5" t="n">
-        <v>33.9678</v>
+        <v>33.8107</v>
       </c>
     </row>
     <row r="6">
@@ -5160,19 +5160,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>13.4184</v>
+        <v>13.3778</v>
       </c>
       <c r="C6" t="n">
-        <v>15.2329</v>
+        <v>15.254</v>
       </c>
       <c r="D6" t="n">
-        <v>41.6228</v>
+        <v>41.8271</v>
       </c>
       <c r="E6" t="n">
-        <v>13.2121</v>
+        <v>13.1263</v>
       </c>
       <c r="F6" t="n">
-        <v>33.7975</v>
+        <v>33.6436</v>
       </c>
     </row>
     <row r="7">
@@ -5180,19 +5180,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>13.091</v>
+        <v>13.1968</v>
       </c>
       <c r="C7" t="n">
-        <v>15.2798</v>
+        <v>15.2052</v>
       </c>
       <c r="D7" t="n">
-        <v>42.4563</v>
+        <v>42.5045</v>
       </c>
       <c r="E7" t="n">
-        <v>19.4783</v>
+        <v>16.3545</v>
       </c>
       <c r="F7" t="n">
-        <v>37.2133</v>
+        <v>37.7743</v>
       </c>
     </row>
     <row r="8">
@@ -5200,19 +5200,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>12.843</v>
+        <v>12.839</v>
       </c>
       <c r="C8" t="n">
-        <v>17.0006</v>
+        <v>17.0636</v>
       </c>
       <c r="D8" t="n">
-        <v>42.3909</v>
+        <v>42.3827</v>
       </c>
       <c r="E8" t="n">
-        <v>16.0037</v>
+        <v>15.8702</v>
       </c>
       <c r="F8" t="n">
-        <v>36.6404</v>
+        <v>37.574</v>
       </c>
     </row>
     <row r="9">
@@ -5220,19 +5220,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>12.4562</v>
+        <v>12.4908</v>
       </c>
       <c r="C9" t="n">
-        <v>17.0216</v>
+        <v>17.0549</v>
       </c>
       <c r="D9" t="n">
-        <v>42.4486</v>
+        <v>42.736</v>
       </c>
       <c r="E9" t="n">
-        <v>15.8326</v>
+        <v>15.8397</v>
       </c>
       <c r="F9" t="n">
-        <v>36.5016</v>
+        <v>37.227</v>
       </c>
     </row>
     <row r="10">
@@ -5240,19 +5240,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>17.1834</v>
+        <v>16.8029</v>
       </c>
       <c r="C10" t="n">
-        <v>16.8489</v>
+        <v>16.8912</v>
       </c>
       <c r="D10" t="n">
-        <v>42.4474</v>
+        <v>42.5454</v>
       </c>
       <c r="E10" t="n">
-        <v>15.6363</v>
+        <v>15.4161</v>
       </c>
       <c r="F10" t="n">
-        <v>36.5393</v>
+        <v>36.8183</v>
       </c>
     </row>
     <row r="11">
@@ -5260,19 +5260,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>16.9869</v>
+        <v>16.5689</v>
       </c>
       <c r="C11" t="n">
-        <v>16.7915</v>
+        <v>16.8095</v>
       </c>
       <c r="D11" t="n">
-        <v>42.4308</v>
+        <v>42.6874</v>
       </c>
       <c r="E11" t="n">
-        <v>15.3581</v>
+        <v>15.2566</v>
       </c>
       <c r="F11" t="n">
-        <v>36.047</v>
+        <v>36.5718</v>
       </c>
     </row>
     <row r="12">
@@ -5280,19 +5280,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>16.5399</v>
+        <v>16.1966</v>
       </c>
       <c r="C12" t="n">
-        <v>16.693</v>
+        <v>16.7496</v>
       </c>
       <c r="D12" t="n">
-        <v>42.356</v>
+        <v>42.455</v>
       </c>
       <c r="E12" t="n">
-        <v>15.4131</v>
+        <v>15.0905</v>
       </c>
       <c r="F12" t="n">
-        <v>35.8618</v>
+        <v>36.2667</v>
       </c>
     </row>
     <row r="13">
@@ -5300,19 +5300,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>16.161</v>
+        <v>15.9146</v>
       </c>
       <c r="C13" t="n">
-        <v>16.5862</v>
+        <v>16.6586</v>
       </c>
       <c r="D13" t="n">
-        <v>42.4332</v>
+        <v>42.5807</v>
       </c>
       <c r="E13" t="n">
-        <v>15.3263</v>
+        <v>14.9165</v>
       </c>
       <c r="F13" t="n">
-        <v>35.6842</v>
+        <v>36.0257</v>
       </c>
     </row>
     <row r="14">
@@ -5320,19 +5320,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>15.9167</v>
+        <v>15.7422</v>
       </c>
       <c r="C14" t="n">
-        <v>16.5866</v>
+        <v>16.587</v>
       </c>
       <c r="D14" t="n">
-        <v>42.3759</v>
+        <v>42.5672</v>
       </c>
       <c r="E14" t="n">
-        <v>14.9429</v>
+        <v>14.8024</v>
       </c>
       <c r="F14" t="n">
-        <v>35.3853</v>
+        <v>35.8297</v>
       </c>
     </row>
     <row r="15">
@@ -5340,19 +5340,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>15.6213</v>
+        <v>15.3749</v>
       </c>
       <c r="C15" t="n">
-        <v>16.4954</v>
+        <v>16.4644</v>
       </c>
       <c r="D15" t="n">
-        <v>42.3579</v>
+        <v>42.4464</v>
       </c>
       <c r="E15" t="n">
-        <v>14.7731</v>
+        <v>14.5581</v>
       </c>
       <c r="F15" t="n">
-        <v>35.5608</v>
+        <v>35.4231</v>
       </c>
     </row>
     <row r="16">
@@ -5360,19 +5360,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>15.1367</v>
+        <v>15.1374</v>
       </c>
       <c r="C16" t="n">
-        <v>16.3827</v>
+        <v>16.4806</v>
       </c>
       <c r="D16" t="n">
-        <v>42.425</v>
+        <v>42.3729</v>
       </c>
       <c r="E16" t="n">
-        <v>14.6992</v>
+        <v>14.5811</v>
       </c>
       <c r="F16" t="n">
-        <v>35.0544</v>
+        <v>35.3301</v>
       </c>
     </row>
     <row r="17">
@@ -5380,19 +5380,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>14.9229</v>
+        <v>14.7986</v>
       </c>
       <c r="C17" t="n">
-        <v>16.2669</v>
+        <v>16.208</v>
       </c>
       <c r="D17" t="n">
-        <v>42.3659</v>
+        <v>42.4978</v>
       </c>
       <c r="E17" t="n">
-        <v>14.4069</v>
+        <v>14.1219</v>
       </c>
       <c r="F17" t="n">
-        <v>34.7301</v>
+        <v>34.8116</v>
       </c>
     </row>
     <row r="18">
@@ -5400,19 +5400,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>14.7236</v>
+        <v>14.5657</v>
       </c>
       <c r="C18" t="n">
-        <v>16.1724</v>
+        <v>16.1618</v>
       </c>
       <c r="D18" t="n">
-        <v>42.4465</v>
+        <v>42.3958</v>
       </c>
       <c r="E18" t="n">
-        <v>15.2932</v>
+        <v>13.9614</v>
       </c>
       <c r="F18" t="n">
-        <v>34.6693</v>
+        <v>34.6265</v>
       </c>
     </row>
     <row r="19">
@@ -5420,19 +5420,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>14.3129</v>
+        <v>14.2163</v>
       </c>
       <c r="C19" t="n">
-        <v>16.106</v>
+        <v>16.1469</v>
       </c>
       <c r="D19" t="n">
-        <v>42.2643</v>
+        <v>42.5147</v>
       </c>
       <c r="E19" t="n">
-        <v>14.0131</v>
+        <v>13.743</v>
       </c>
       <c r="F19" t="n">
-        <v>34.3857</v>
+        <v>34.3048</v>
       </c>
     </row>
     <row r="20">
@@ -5440,19 +5440,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>14.0834</v>
+        <v>14.0318</v>
       </c>
       <c r="C20" t="n">
-        <v>16.1608</v>
+        <v>16.1215</v>
       </c>
       <c r="D20" t="n">
-        <v>42.3159</v>
+        <v>42.3806</v>
       </c>
       <c r="E20" t="n">
-        <v>13.8314</v>
+        <v>13.4798</v>
       </c>
       <c r="F20" t="n">
-        <v>34.1888</v>
+        <v>34.0324</v>
       </c>
     </row>
     <row r="21">
@@ -5460,19 +5460,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>13.7126</v>
+        <v>13.7695</v>
       </c>
       <c r="C21" t="n">
-        <v>16.0855</v>
+        <v>15.9329</v>
       </c>
       <c r="D21" t="n">
-        <v>43.0995</v>
+        <v>43.1143</v>
       </c>
       <c r="E21" t="n">
-        <v>16.6954</v>
+        <v>16.4636</v>
       </c>
       <c r="F21" t="n">
-        <v>37.5555</v>
+        <v>38.3907</v>
       </c>
     </row>
     <row r="22">
@@ -5480,19 +5480,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>13.2816</v>
+        <v>13.3818</v>
       </c>
       <c r="C22" t="n">
-        <v>17.6634</v>
+        <v>17.714</v>
       </c>
       <c r="D22" t="n">
-        <v>43.1178</v>
+        <v>43.2665</v>
       </c>
       <c r="E22" t="n">
-        <v>16.4406</v>
+        <v>16.2691</v>
       </c>
       <c r="F22" t="n">
-        <v>37.3234</v>
+        <v>38.0477</v>
       </c>
     </row>
     <row r="23">
@@ -5500,19 +5500,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.901</v>
+        <v>12.8895</v>
       </c>
       <c r="C23" t="n">
-        <v>17.5424</v>
+        <v>17.5599</v>
       </c>
       <c r="D23" t="n">
-        <v>43.0892</v>
+        <v>43.1163</v>
       </c>
       <c r="E23" t="n">
-        <v>16.1585</v>
+        <v>16.0098</v>
       </c>
       <c r="F23" t="n">
-        <v>36.9747</v>
+        <v>37.7315</v>
       </c>
     </row>
     <row r="24">
@@ -5520,19 +5520,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>17.4736</v>
+        <v>17.4845</v>
       </c>
       <c r="C24" t="n">
-        <v>17.4106</v>
+        <v>17.3934</v>
       </c>
       <c r="D24" t="n">
-        <v>43.0277</v>
+        <v>42.9584</v>
       </c>
       <c r="E24" t="n">
-        <v>15.9947</v>
+        <v>15.8425</v>
       </c>
       <c r="F24" t="n">
-        <v>36.845</v>
+        <v>37.3696</v>
       </c>
     </row>
     <row r="25">
@@ -5540,19 +5540,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>17.191</v>
+        <v>17.1896</v>
       </c>
       <c r="C25" t="n">
-        <v>17.2732</v>
+        <v>17.2632</v>
       </c>
       <c r="D25" t="n">
-        <v>43.0856</v>
+        <v>43.1464</v>
       </c>
       <c r="E25" t="n">
-        <v>15.7947</v>
+        <v>15.541</v>
       </c>
       <c r="F25" t="n">
-        <v>36.5202</v>
+        <v>36.9321</v>
       </c>
     </row>
     <row r="26">
@@ -5560,19 +5560,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>16.8874</v>
+        <v>16.8758</v>
       </c>
       <c r="C26" t="n">
-        <v>17.1195</v>
+        <v>17.1284</v>
       </c>
       <c r="D26" t="n">
-        <v>42.8998</v>
+        <v>43.0528</v>
       </c>
       <c r="E26" t="n">
-        <v>15.5014</v>
+        <v>15.2879</v>
       </c>
       <c r="F26" t="n">
-        <v>36.0768</v>
+        <v>36.6877</v>
       </c>
     </row>
     <row r="27">
@@ -5580,19 +5580,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>16.5459</v>
+        <v>16.5071</v>
       </c>
       <c r="C27" t="n">
-        <v>16.9736</v>
+        <v>17.024</v>
       </c>
       <c r="D27" t="n">
-        <v>42.8705</v>
+        <v>43.0579</v>
       </c>
       <c r="E27" t="n">
-        <v>15.3413</v>
+        <v>15.1021</v>
       </c>
       <c r="F27" t="n">
-        <v>36.0152</v>
+        <v>36.5396</v>
       </c>
     </row>
     <row r="28">
@@ -5600,19 +5600,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>16.2084</v>
+        <v>16.1795</v>
       </c>
       <c r="C28" t="n">
-        <v>16.8955</v>
+        <v>16.8874</v>
       </c>
       <c r="D28" t="n">
-        <v>42.9113</v>
+        <v>43.0637</v>
       </c>
       <c r="E28" t="n">
-        <v>15.0828</v>
+        <v>15.0132</v>
       </c>
       <c r="F28" t="n">
-        <v>35.7248</v>
+        <v>36.0818</v>
       </c>
     </row>
     <row r="29">
@@ -5620,19 +5620,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>15.8685</v>
+        <v>15.8488</v>
       </c>
       <c r="C29" t="n">
-        <v>16.7879</v>
+        <v>16.7823</v>
       </c>
       <c r="D29" t="n">
-        <v>42.8371</v>
+        <v>42.7993</v>
       </c>
       <c r="E29" t="n">
-        <v>14.9981</v>
+        <v>14.7746</v>
       </c>
       <c r="F29" t="n">
-        <v>35.663</v>
+        <v>36.1556</v>
       </c>
     </row>
     <row r="30">
@@ -5640,19 +5640,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>15.5497</v>
+        <v>15.5309</v>
       </c>
       <c r="C30" t="n">
-        <v>16.6964</v>
+        <v>16.7082</v>
       </c>
       <c r="D30" t="n">
-        <v>42.9277</v>
+        <v>42.8542</v>
       </c>
       <c r="E30" t="n">
-        <v>14.7474</v>
+        <v>14.6262</v>
       </c>
       <c r="F30" t="n">
-        <v>35.3048</v>
+        <v>35.4217</v>
       </c>
     </row>
     <row r="31">
@@ -5660,19 +5660,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>15.2126</v>
+        <v>15.1811</v>
       </c>
       <c r="C31" t="n">
-        <v>16.5827</v>
+        <v>16.5988</v>
       </c>
       <c r="D31" t="n">
-        <v>42.8816</v>
+        <v>42.8309</v>
       </c>
       <c r="E31" t="n">
-        <v>14.6118</v>
+        <v>14.3803</v>
       </c>
       <c r="F31" t="n">
-        <v>35.142</v>
+        <v>35.3901</v>
       </c>
     </row>
     <row r="32">
@@ -5680,19 +5680,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>14.8997</v>
+        <v>14.8842</v>
       </c>
       <c r="C32" t="n">
-        <v>16.5783</v>
+        <v>16.5716</v>
       </c>
       <c r="D32" t="n">
-        <v>42.7683</v>
+        <v>42.7709</v>
       </c>
       <c r="E32" t="n">
-        <v>14.4324</v>
+        <v>14.2416</v>
       </c>
       <c r="F32" t="n">
-        <v>34.8684</v>
+        <v>34.9163</v>
       </c>
     </row>
     <row r="33">
@@ -5700,19 +5700,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>14.616</v>
+        <v>14.598</v>
       </c>
       <c r="C33" t="n">
-        <v>16.4986</v>
+        <v>16.4464</v>
       </c>
       <c r="D33" t="n">
-        <v>42.805</v>
+        <v>42.9323</v>
       </c>
       <c r="E33" t="n">
-        <v>14.2306</v>
+        <v>13.9811</v>
       </c>
       <c r="F33" t="n">
-        <v>34.7497</v>
+        <v>34.6467</v>
       </c>
     </row>
     <row r="34">
@@ -5720,19 +5720,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>14.3284</v>
+        <v>14.3454</v>
       </c>
       <c r="C34" t="n">
-        <v>16.4048</v>
+        <v>16.407</v>
       </c>
       <c r="D34" t="n">
-        <v>42.7229</v>
+        <v>42.8316</v>
       </c>
       <c r="E34" t="n">
-        <v>13.9707</v>
+        <v>13.8483</v>
       </c>
       <c r="F34" t="n">
-        <v>34.3271</v>
+        <v>34.3383</v>
       </c>
     </row>
     <row r="35">
@@ -5740,19 +5740,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>13.9833</v>
+        <v>14.0492</v>
       </c>
       <c r="C35" t="n">
-        <v>16.3458</v>
+        <v>16.361</v>
       </c>
       <c r="D35" t="n">
-        <v>43.5866</v>
+        <v>43.7264</v>
       </c>
       <c r="E35" t="n">
-        <v>17.1941</v>
+        <v>17.1197</v>
       </c>
       <c r="F35" t="n">
-        <v>37.8955</v>
+        <v>38.8718</v>
       </c>
     </row>
     <row r="36">
@@ -5760,19 +5760,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>13.6695</v>
+        <v>13.7396</v>
       </c>
       <c r="C36" t="n">
-        <v>16.2972</v>
+        <v>16.2658</v>
       </c>
       <c r="D36" t="n">
-        <v>43.6028</v>
+        <v>43.7372</v>
       </c>
       <c r="E36" t="n">
-        <v>16.8713</v>
+        <v>16.6319</v>
       </c>
       <c r="F36" t="n">
-        <v>37.7109</v>
+        <v>38.602</v>
       </c>
     </row>
     <row r="37">
@@ -5780,19 +5780,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.2175</v>
+        <v>13.3043</v>
       </c>
       <c r="C37" t="n">
-        <v>17.7674</v>
+        <v>17.8204</v>
       </c>
       <c r="D37" t="n">
-        <v>43.4554</v>
+        <v>43.6699</v>
       </c>
       <c r="E37" t="n">
-        <v>16.5357</v>
+        <v>16.4044</v>
       </c>
       <c r="F37" t="n">
-        <v>37.4502</v>
+        <v>38.1983</v>
       </c>
     </row>
     <row r="38">
@@ -5800,19 +5800,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>17.6268</v>
+        <v>17.6252</v>
       </c>
       <c r="C38" t="n">
-        <v>17.6349</v>
+        <v>17.6602</v>
       </c>
       <c r="D38" t="n">
-        <v>43.4316</v>
+        <v>43.5556</v>
       </c>
       <c r="E38" t="n">
-        <v>16.2506</v>
+        <v>16.1136</v>
       </c>
       <c r="F38" t="n">
-        <v>37.1745</v>
+        <v>37.8046</v>
       </c>
     </row>
     <row r="39">
@@ -5820,19 +5820,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>17.3289</v>
+        <v>17.3627</v>
       </c>
       <c r="C39" t="n">
-        <v>17.4935</v>
+        <v>17.5151</v>
       </c>
       <c r="D39" t="n">
-        <v>43.461</v>
+        <v>43.3796</v>
       </c>
       <c r="E39" t="n">
-        <v>15.974</v>
+        <v>15.9937</v>
       </c>
       <c r="F39" t="n">
-        <v>37.2046</v>
+        <v>37.3234</v>
       </c>
     </row>
     <row r="40">
@@ -5840,19 +5840,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>17.0585</v>
+        <v>17.0846</v>
       </c>
       <c r="C40" t="n">
-        <v>17.387</v>
+        <v>17.3801</v>
       </c>
       <c r="D40" t="n">
-        <v>43.2847</v>
+        <v>43.4514</v>
       </c>
       <c r="E40" t="n">
-        <v>15.8024</v>
+        <v>15.6829</v>
       </c>
       <c r="F40" t="n">
-        <v>36.6126</v>
+        <v>37.1005</v>
       </c>
     </row>
     <row r="41">
@@ -5860,19 +5860,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>16.7332</v>
+        <v>16.7542</v>
       </c>
       <c r="C41" t="n">
-        <v>17.2324</v>
+        <v>17.2271</v>
       </c>
       <c r="D41" t="n">
-        <v>43.3999</v>
+        <v>43.3256</v>
       </c>
       <c r="E41" t="n">
-        <v>15.5888</v>
+        <v>15.437</v>
       </c>
       <c r="F41" t="n">
-        <v>36.4758</v>
+        <v>36.8519</v>
       </c>
     </row>
     <row r="42">
@@ -5880,19 +5880,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>16.3829</v>
+        <v>16.4015</v>
       </c>
       <c r="C42" t="n">
-        <v>17.0997</v>
+        <v>17.095</v>
       </c>
       <c r="D42" t="n">
-        <v>43.2567</v>
+        <v>43.5516</v>
       </c>
       <c r="E42" t="n">
-        <v>15.4119</v>
+        <v>15.2639</v>
       </c>
       <c r="F42" t="n">
-        <v>36.1415</v>
+        <v>36.6072</v>
       </c>
     </row>
     <row r="43">
@@ -5900,19 +5900,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>16.0351</v>
+        <v>16.0418</v>
       </c>
       <c r="C43" t="n">
-        <v>16.9836</v>
+        <v>16.9909</v>
       </c>
       <c r="D43" t="n">
-        <v>43.1861</v>
+        <v>43.2817</v>
       </c>
       <c r="E43" t="n">
-        <v>15.2331</v>
+        <v>15.0841</v>
       </c>
       <c r="F43" t="n">
-        <v>35.9231</v>
+        <v>36.1497</v>
       </c>
     </row>
     <row r="44">
@@ -5920,19 +5920,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>15.6653</v>
+        <v>15.6803</v>
       </c>
       <c r="C44" t="n">
-        <v>16.8736</v>
+        <v>16.8749</v>
       </c>
       <c r="D44" t="n">
-        <v>43.3365</v>
+        <v>43.2653</v>
       </c>
       <c r="E44" t="n">
-        <v>15.0643</v>
+        <v>14.8974</v>
       </c>
       <c r="F44" t="n">
-        <v>35.6559</v>
+        <v>35.7875</v>
       </c>
     </row>
     <row r="45">
@@ -5940,19 +5940,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>15.3271</v>
+        <v>15.3604</v>
       </c>
       <c r="C45" t="n">
-        <v>16.767</v>
+        <v>16.7743</v>
       </c>
       <c r="D45" t="n">
-        <v>43.0495</v>
+        <v>43.3447</v>
       </c>
       <c r="E45" t="n">
-        <v>14.8622</v>
+        <v>14.7401</v>
       </c>
       <c r="F45" t="n">
-        <v>35.4157</v>
+        <v>35.5255</v>
       </c>
     </row>
     <row r="46">
@@ -5960,19 +5960,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>15.0206</v>
+        <v>15.0302</v>
       </c>
       <c r="C46" t="n">
-        <v>16.6854</v>
+        <v>16.671</v>
       </c>
       <c r="D46" t="n">
-        <v>43.1703</v>
+        <v>43.2183</v>
       </c>
       <c r="E46" t="n">
-        <v>14.7107</v>
+        <v>14.5759</v>
       </c>
       <c r="F46" t="n">
-        <v>35.3224</v>
+        <v>35.2299</v>
       </c>
     </row>
     <row r="47">
@@ -5980,19 +5980,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>14.7245</v>
+        <v>14.7389</v>
       </c>
       <c r="C47" t="n">
-        <v>16.6032</v>
+        <v>16.5767</v>
       </c>
       <c r="D47" t="n">
-        <v>43.0237</v>
+        <v>43.0062</v>
       </c>
       <c r="E47" t="n">
-        <v>14.4866</v>
+        <v>14.3499</v>
       </c>
       <c r="F47" t="n">
-        <v>35.0226</v>
+        <v>34.8657</v>
       </c>
     </row>
     <row r="48">
@@ -6000,19 +6000,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>14.434</v>
+        <v>14.449</v>
       </c>
       <c r="C48" t="n">
-        <v>16.5323</v>
+        <v>16.5079</v>
       </c>
       <c r="D48" t="n">
-        <v>43.0398</v>
+        <v>43.237</v>
       </c>
       <c r="E48" t="n">
-        <v>14.2315</v>
+        <v>14.1117</v>
       </c>
       <c r="F48" t="n">
-        <v>34.7915</v>
+        <v>34.6978</v>
       </c>
     </row>
     <row r="49">
@@ -6020,19 +6020,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>14.1041</v>
+        <v>14.1284</v>
       </c>
       <c r="C49" t="n">
-        <v>16.4575</v>
+        <v>16.4458</v>
       </c>
       <c r="D49" t="n">
-        <v>43.057</v>
+        <v>43.1221</v>
       </c>
       <c r="E49" t="n">
-        <v>14.0447</v>
+        <v>13.9128</v>
       </c>
       <c r="F49" t="n">
-        <v>34.5829</v>
+        <v>34.3038</v>
       </c>
     </row>
     <row r="50">
@@ -6040,19 +6040,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>13.7562</v>
+        <v>13.8223</v>
       </c>
       <c r="C50" t="n">
-        <v>16.3904</v>
+        <v>16.3869</v>
       </c>
       <c r="D50" t="n">
-        <v>44.0519</v>
+        <v>44.2248</v>
       </c>
       <c r="E50" t="n">
-        <v>17.0777</v>
+        <v>16.9454</v>
       </c>
       <c r="F50" t="n">
-        <v>38.1673</v>
+        <v>38.7662</v>
       </c>
     </row>
     <row r="51">
@@ -6060,19 +6060,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>13.3194</v>
+        <v>13.3768</v>
       </c>
       <c r="C51" t="n">
-        <v>17.8831</v>
+        <v>17.915</v>
       </c>
       <c r="D51" t="n">
-        <v>43.9133</v>
+        <v>44.0016</v>
       </c>
       <c r="E51" t="n">
-        <v>16.797</v>
+        <v>16.6836</v>
       </c>
       <c r="F51" t="n">
-        <v>37.9241</v>
+        <v>38.4427</v>
       </c>
     </row>
     <row r="52">
@@ -6080,19 +6080,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>12.7738</v>
+        <v>12.8239</v>
       </c>
       <c r="C52" t="n">
-        <v>17.7159</v>
+        <v>17.7227</v>
       </c>
       <c r="D52" t="n">
-        <v>43.9453</v>
+        <v>43.9093</v>
       </c>
       <c r="E52" t="n">
-        <v>16.4794</v>
+        <v>16.3376</v>
       </c>
       <c r="F52" t="n">
-        <v>37.8518</v>
+        <v>38.2584</v>
       </c>
     </row>
     <row r="53">
@@ -6100,19 +6100,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>17.4063</v>
+        <v>17.3977</v>
       </c>
       <c r="C53" t="n">
-        <v>17.5478</v>
+        <v>17.5394</v>
       </c>
       <c r="D53" t="n">
-        <v>43.8425</v>
+        <v>43.9825</v>
       </c>
       <c r="E53" t="n">
-        <v>16.2305</v>
+        <v>16.0678</v>
       </c>
       <c r="F53" t="n">
-        <v>37.235</v>
+        <v>37.7475</v>
       </c>
     </row>
     <row r="54">
@@ -6120,19 +6120,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>17.1219</v>
+        <v>17.1175</v>
       </c>
       <c r="C54" t="n">
-        <v>17.4457</v>
+        <v>17.4331</v>
       </c>
       <c r="D54" t="n">
-        <v>43.8851</v>
+        <v>43.8133</v>
       </c>
       <c r="E54" t="n">
-        <v>16.025</v>
+        <v>15.8463</v>
       </c>
       <c r="F54" t="n">
-        <v>37.4324</v>
+        <v>37.5814</v>
       </c>
     </row>
     <row r="55">
@@ -6140,19 +6140,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>16.8077</v>
+        <v>16.8045</v>
       </c>
       <c r="C55" t="n">
-        <v>17.3353</v>
+        <v>17.3045</v>
       </c>
       <c r="D55" t="n">
-        <v>43.6094</v>
+        <v>43.7347</v>
       </c>
       <c r="E55" t="n">
-        <v>15.7533</v>
+        <v>15.6676</v>
       </c>
       <c r="F55" t="n">
-        <v>37.331</v>
+        <v>37.3556</v>
       </c>
     </row>
     <row r="56">
@@ -6160,19 +6160,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>16.4829</v>
+        <v>16.4549</v>
       </c>
       <c r="C56" t="n">
-        <v>17.1478</v>
+        <v>17.1601</v>
       </c>
       <c r="D56" t="n">
-        <v>43.593</v>
+        <v>43.5401</v>
       </c>
       <c r="E56" t="n">
-        <v>15.5864</v>
+        <v>15.4828</v>
       </c>
       <c r="F56" t="n">
-        <v>36.8629</v>
+        <v>36.7376</v>
       </c>
     </row>
     <row r="57">
@@ -6180,19 +6180,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>16.1106</v>
+        <v>16.0996</v>
       </c>
       <c r="C57" t="n">
-        <v>17.0633</v>
+        <v>17.0627</v>
       </c>
       <c r="D57" t="n">
-        <v>43.762</v>
+        <v>43.8824</v>
       </c>
       <c r="E57" t="n">
-        <v>15.348</v>
+        <v>15.2621</v>
       </c>
       <c r="F57" t="n">
-        <v>37.3266</v>
+        <v>37.3623</v>
       </c>
     </row>
     <row r="58">
@@ -6200,19 +6200,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>15.784</v>
+        <v>15.7565</v>
       </c>
       <c r="C58" t="n">
-        <v>16.9243</v>
+        <v>16.9239</v>
       </c>
       <c r="D58" t="n">
-        <v>43.8341</v>
+        <v>43.8617</v>
       </c>
       <c r="E58" t="n">
-        <v>15.1708</v>
+        <v>15.0421</v>
       </c>
       <c r="F58" t="n">
-        <v>37.0067</v>
+        <v>36.605</v>
       </c>
     </row>
     <row r="59">
@@ -6220,19 +6220,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>15.4378</v>
+        <v>15.4162</v>
       </c>
       <c r="C59" t="n">
-        <v>16.8162</v>
+        <v>16.8204</v>
       </c>
       <c r="D59" t="n">
-        <v>44.0272</v>
+        <v>43.9189</v>
       </c>
       <c r="E59" t="n">
-        <v>15.0061</v>
+        <v>14.8228</v>
       </c>
       <c r="F59" t="n">
-        <v>37.0654</v>
+        <v>36.2131</v>
       </c>
     </row>
     <row r="60">
@@ -6240,19 +6240,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>15.1183</v>
+        <v>15.1035</v>
       </c>
       <c r="C60" t="n">
-        <v>16.7526</v>
+        <v>16.7364</v>
       </c>
       <c r="D60" t="n">
-        <v>44.1538</v>
+        <v>43.8397</v>
       </c>
       <c r="E60" t="n">
-        <v>14.7978</v>
+        <v>14.6748</v>
       </c>
       <c r="F60" t="n">
-        <v>36.5044</v>
+        <v>36.4803</v>
       </c>
     </row>
     <row r="61">
@@ -6260,19 +6260,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>14.8147</v>
+        <v>14.8047</v>
       </c>
       <c r="C61" t="n">
-        <v>16.6473</v>
+        <v>16.6601</v>
       </c>
       <c r="D61" t="n">
-        <v>44.1103</v>
+        <v>44.0566</v>
       </c>
       <c r="E61" t="n">
-        <v>14.5774</v>
+        <v>14.4369</v>
       </c>
       <c r="F61" t="n">
-        <v>36.4676</v>
+        <v>36.2604</v>
       </c>
     </row>
     <row r="62">
@@ -6280,19 +6280,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>14.5128</v>
+        <v>14.494</v>
       </c>
       <c r="C62" t="n">
-        <v>16.6019</v>
+        <v>16.5703</v>
       </c>
       <c r="D62" t="n">
-        <v>44.3155</v>
+        <v>44.7219</v>
       </c>
       <c r="E62" t="n">
-        <v>14.3704</v>
+        <v>14.2062</v>
       </c>
       <c r="F62" t="n">
-        <v>37.383</v>
+        <v>36.9487</v>
       </c>
     </row>
     <row r="63">
@@ -6300,19 +6300,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>14.2205</v>
+        <v>14.2177</v>
       </c>
       <c r="C63" t="n">
-        <v>16.5262</v>
+        <v>16.5019</v>
       </c>
       <c r="D63" t="n">
-        <v>45.2649</v>
+        <v>45.2448</v>
       </c>
       <c r="E63" t="n">
-        <v>14.1281</v>
+        <v>13.9482</v>
       </c>
       <c r="F63" t="n">
-        <v>37.8634</v>
+        <v>36.6109</v>
       </c>
     </row>
     <row r="64">
@@ -6320,19 +6320,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>13.894</v>
+        <v>13.9098</v>
       </c>
       <c r="C64" t="n">
-        <v>16.4541</v>
+        <v>16.4164</v>
       </c>
       <c r="D64" t="n">
-        <v>50.4235</v>
+        <v>50.3766</v>
       </c>
       <c r="E64" t="n">
-        <v>17.292</v>
+        <v>17.1647</v>
       </c>
       <c r="F64" t="n">
-        <v>45.4701</v>
+        <v>46.3951</v>
       </c>
     </row>
     <row r="65">
@@ -6340,19 +6340,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>13.5085</v>
+        <v>13.5386</v>
       </c>
       <c r="C65" t="n">
-        <v>17.9191</v>
+        <v>17.9836</v>
       </c>
       <c r="D65" t="n">
-        <v>51.2498</v>
+        <v>50.9963</v>
       </c>
       <c r="E65" t="n">
-        <v>16.9373</v>
+        <v>16.9032</v>
       </c>
       <c r="F65" t="n">
-        <v>46.2965</v>
+        <v>45.8201</v>
       </c>
     </row>
     <row r="66">
@@ -6360,19 +6360,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>13.02</v>
+        <v>13.0505</v>
       </c>
       <c r="C66" t="n">
-        <v>17.7244</v>
+        <v>17.7699</v>
       </c>
       <c r="D66" t="n">
-        <v>51.7401</v>
+        <v>51.4493</v>
       </c>
       <c r="E66" t="n">
-        <v>16.6755</v>
+        <v>16.5747</v>
       </c>
       <c r="F66" t="n">
-        <v>46.7127</v>
+        <v>46.5718</v>
       </c>
     </row>
     <row r="67">
@@ -6380,19 +6380,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>17.533</v>
+        <v>17.5375</v>
       </c>
       <c r="C67" t="n">
-        <v>17.5831</v>
+        <v>17.6179</v>
       </c>
       <c r="D67" t="n">
-        <v>51.9848</v>
+        <v>51.7959</v>
       </c>
       <c r="E67" t="n">
-        <v>16.3789</v>
+        <v>16.2999</v>
       </c>
       <c r="F67" t="n">
-        <v>46.999</v>
+        <v>47.1093</v>
       </c>
     </row>
     <row r="68">
@@ -6400,19 +6400,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>17.2528</v>
+        <v>17.2228</v>
       </c>
       <c r="C68" t="n">
-        <v>17.4587</v>
+        <v>17.4562</v>
       </c>
       <c r="D68" t="n">
-        <v>52.3024</v>
+        <v>52.2086</v>
       </c>
       <c r="E68" t="n">
-        <v>16.1711</v>
+        <v>16.0366</v>
       </c>
       <c r="F68" t="n">
-        <v>47.2337</v>
+        <v>47.5544</v>
       </c>
     </row>
     <row r="69">
@@ -6420,19 +6420,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>16.9256</v>
+        <v>16.8839</v>
       </c>
       <c r="C69" t="n">
-        <v>17.3211</v>
+        <v>17.3194</v>
       </c>
       <c r="D69" t="n">
-        <v>52.7539</v>
+        <v>52.5477</v>
       </c>
       <c r="E69" t="n">
-        <v>15.9495</v>
+        <v>15.8227</v>
       </c>
       <c r="F69" t="n">
-        <v>47.3002</v>
+        <v>47.4576</v>
       </c>
     </row>
     <row r="70">
@@ -6440,19 +6440,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>16.5861</v>
+        <v>16.542</v>
       </c>
       <c r="C70" t="n">
-        <v>17.2002</v>
+        <v>17.1906</v>
       </c>
       <c r="D70" t="n">
-        <v>52.9351</v>
+        <v>52.8818</v>
       </c>
       <c r="E70" t="n">
-        <v>15.741</v>
+        <v>15.6015</v>
       </c>
       <c r="F70" t="n">
-        <v>47.2087</v>
+        <v>47.3862</v>
       </c>
     </row>
     <row r="71">
@@ -6460,19 +6460,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>16.2183</v>
+        <v>16.19</v>
       </c>
       <c r="C71" t="n">
-        <v>17.0686</v>
+        <v>17.0529</v>
       </c>
       <c r="D71" t="n">
-        <v>53.1753</v>
+        <v>53.4714</v>
       </c>
       <c r="E71" t="n">
-        <v>15.4998</v>
+        <v>15.381</v>
       </c>
       <c r="F71" t="n">
-        <v>47.0978</v>
+        <v>46.9787</v>
       </c>
     </row>
     <row r="72">
@@ -6480,19 +6480,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>15.8556</v>
+        <v>15.8368</v>
       </c>
       <c r="C72" t="n">
-        <v>16.9681</v>
+        <v>16.9666</v>
       </c>
       <c r="D72" t="n">
-        <v>53.5728</v>
+        <v>53.2733</v>
       </c>
       <c r="E72" t="n">
-        <v>15.3088</v>
+        <v>15.1835</v>
       </c>
       <c r="F72" t="n">
-        <v>46.9706</v>
+        <v>47.1274</v>
       </c>
     </row>
     <row r="73">
@@ -6500,19 +6500,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>15.5126</v>
+        <v>15.4896</v>
       </c>
       <c r="C73" t="n">
-        <v>16.8616</v>
+        <v>16.871</v>
       </c>
       <c r="D73" t="n">
-        <v>53.7703</v>
+        <v>53.5379</v>
       </c>
       <c r="E73" t="n">
-        <v>15.1188</v>
+        <v>14.9807</v>
       </c>
       <c r="F73" t="n">
-        <v>46.844</v>
+        <v>46.8411</v>
       </c>
     </row>
     <row r="74">
@@ -6520,19 +6520,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>15.1841</v>
+        <v>15.1752</v>
       </c>
       <c r="C74" t="n">
-        <v>16.7775</v>
+        <v>16.7734</v>
       </c>
       <c r="D74" t="n">
-        <v>54.0403</v>
+        <v>53.8675</v>
       </c>
       <c r="E74" t="n">
-        <v>14.9022</v>
+        <v>14.79</v>
       </c>
       <c r="F74" t="n">
-        <v>46.6913</v>
+        <v>46.6682</v>
       </c>
     </row>
     <row r="75">
@@ -6540,19 +6540,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>14.8812</v>
+        <v>14.8737</v>
       </c>
       <c r="C75" t="n">
-        <v>16.7215</v>
+        <v>16.6814</v>
       </c>
       <c r="D75" t="n">
-        <v>53.9825</v>
+        <v>54.1479</v>
       </c>
       <c r="E75" t="n">
-        <v>14.6818</v>
+        <v>14.5462</v>
       </c>
       <c r="F75" t="n">
-        <v>46.4872</v>
+        <v>46.3856</v>
       </c>
     </row>
     <row r="76">
@@ -6560,19 +6560,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>14.6001</v>
+        <v>14.5862</v>
       </c>
       <c r="C76" t="n">
-        <v>16.6442</v>
+        <v>16.6135</v>
       </c>
       <c r="D76" t="n">
-        <v>54.3153</v>
+        <v>54.1687</v>
       </c>
       <c r="E76" t="n">
-        <v>14.4974</v>
+        <v>14.314</v>
       </c>
       <c r="F76" t="n">
-        <v>46.2902</v>
+        <v>46.139</v>
       </c>
     </row>
     <row r="77">
@@ -6583,16 +6583,16 @@
         <v>14.3032</v>
       </c>
       <c r="C77" t="n">
-        <v>16.5762</v>
+        <v>16.5487</v>
       </c>
       <c r="D77" t="n">
-        <v>54.3196</v>
+        <v>54.085</v>
       </c>
       <c r="E77" t="n">
-        <v>14.2547</v>
+        <v>14.0999</v>
       </c>
       <c r="F77" t="n">
-        <v>46.1768</v>
+        <v>45.7169</v>
       </c>
     </row>
     <row r="78">
@@ -6600,19 +6600,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>13.9555</v>
+        <v>14.0034</v>
       </c>
       <c r="C78" t="n">
-        <v>16.4933</v>
+        <v>16.4482</v>
       </c>
       <c r="D78" t="n">
-        <v>57.2658</v>
+        <v>57.2072</v>
       </c>
       <c r="E78" t="n">
-        <v>17.4025</v>
+        <v>17.5696</v>
       </c>
       <c r="F78" t="n">
-        <v>49.9538</v>
+        <v>50.455</v>
       </c>
     </row>
     <row r="79">
@@ -6620,19 +6620,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>13.5949</v>
+        <v>13.5821</v>
       </c>
       <c r="C79" t="n">
-        <v>18.0293</v>
+        <v>18.0301</v>
       </c>
       <c r="D79" t="n">
-        <v>57.3404</v>
+        <v>57.1822</v>
       </c>
       <c r="E79" t="n">
-        <v>17.0956</v>
+        <v>17.0461</v>
       </c>
       <c r="F79" t="n">
-        <v>49.488</v>
+        <v>50.0907</v>
       </c>
     </row>
     <row r="80">
@@ -6640,19 +6640,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>13.1287</v>
+        <v>13.1055</v>
       </c>
       <c r="C80" t="n">
-        <v>17.8802</v>
+        <v>17.8592</v>
       </c>
       <c r="D80" t="n">
-        <v>57.2368</v>
+        <v>57.0833</v>
       </c>
       <c r="E80" t="n">
-        <v>16.8068</v>
+        <v>16.6519</v>
       </c>
       <c r="F80" t="n">
-        <v>49.2354</v>
+        <v>49.8319</v>
       </c>
     </row>
     <row r="81">
@@ -6660,19 +6660,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>17.6689</v>
+        <v>17.6363</v>
       </c>
       <c r="C81" t="n">
-        <v>17.7041</v>
+        <v>17.6783</v>
       </c>
       <c r="D81" t="n">
-        <v>57.3238</v>
+        <v>57.1265</v>
       </c>
       <c r="E81" t="n">
-        <v>16.5172</v>
+        <v>16.3725</v>
       </c>
       <c r="F81" t="n">
-        <v>48.9638</v>
+        <v>49.3311</v>
       </c>
     </row>
     <row r="82">
@@ -6680,19 +6680,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>17.3638</v>
+        <v>17.3376</v>
       </c>
       <c r="C82" t="n">
-        <v>17.5286</v>
+        <v>17.5236</v>
       </c>
       <c r="D82" t="n">
-        <v>57.2734</v>
+        <v>56.9856</v>
       </c>
       <c r="E82" t="n">
-        <v>16.2929</v>
+        <v>16.1626</v>
       </c>
       <c r="F82" t="n">
-        <v>48.7378</v>
+        <v>48.9606</v>
       </c>
     </row>
     <row r="83">
@@ -6700,19 +6700,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>17.0696</v>
+        <v>17.0151</v>
       </c>
       <c r="C83" t="n">
-        <v>17.3945</v>
+        <v>17.373</v>
       </c>
       <c r="D83" t="n">
-        <v>57.2633</v>
+        <v>57.072</v>
       </c>
       <c r="E83" t="n">
-        <v>16.0268</v>
+        <v>15.9007</v>
       </c>
       <c r="F83" t="n">
-        <v>48.3224</v>
+        <v>48.6393</v>
       </c>
     </row>
     <row r="84">
@@ -6720,19 +6720,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>16.6933</v>
+        <v>16.6636</v>
       </c>
       <c r="C84" t="n">
-        <v>17.2759</v>
+        <v>17.2504</v>
       </c>
       <c r="D84" t="n">
-        <v>60.6881</v>
+        <v>60.3887</v>
       </c>
       <c r="E84" t="n">
-        <v>15.8233</v>
+        <v>15.6921</v>
       </c>
       <c r="F84" t="n">
-        <v>53.2343</v>
+        <v>52.9923</v>
       </c>
     </row>
     <row r="85">
@@ -6740,19 +6740,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>16.336</v>
+        <v>16.2957</v>
       </c>
       <c r="C85" t="n">
-        <v>17.1484</v>
+        <v>17.1092</v>
       </c>
       <c r="D85" t="n">
-        <v>60.7922</v>
+        <v>60.4072</v>
       </c>
       <c r="E85" t="n">
-        <v>15.6142</v>
+        <v>15.4516</v>
       </c>
       <c r="F85" t="n">
-        <v>53.0808</v>
+        <v>52.9625</v>
       </c>
     </row>
     <row r="86">
@@ -6760,19 +6760,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>15.9765</v>
+        <v>15.9365</v>
       </c>
       <c r="C86" t="n">
-        <v>17.0695</v>
+        <v>17.0079</v>
       </c>
       <c r="D86" t="n">
-        <v>60.695</v>
+        <v>60.5701</v>
       </c>
       <c r="E86" t="n">
-        <v>15.4107</v>
+        <v>15.2359</v>
       </c>
       <c r="F86" t="n">
-        <v>52.8031</v>
+        <v>52.4847</v>
       </c>
     </row>
     <row r="87">
@@ -6780,19 +6780,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>15.6253</v>
+        <v>15.5953</v>
       </c>
       <c r="C87" t="n">
-        <v>16.9352</v>
+        <v>16.89</v>
       </c>
       <c r="D87" t="n">
-        <v>60.6372</v>
+        <v>60.547</v>
       </c>
       <c r="E87" t="n">
-        <v>15.2202</v>
+        <v>15.0439</v>
       </c>
       <c r="F87" t="n">
-        <v>52.5035</v>
+        <v>52.2012</v>
       </c>
     </row>
     <row r="88">
@@ -6800,19 +6800,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>15.291</v>
+        <v>15.2556</v>
       </c>
       <c r="C88" t="n">
-        <v>16.8355</v>
+        <v>16.7903</v>
       </c>
       <c r="D88" t="n">
-        <v>60.5746</v>
+        <v>60.5034</v>
       </c>
       <c r="E88" t="n">
-        <v>15.0097</v>
+        <v>14.8547</v>
       </c>
       <c r="F88" t="n">
-        <v>52.206</v>
+        <v>52.0451</v>
       </c>
     </row>
     <row r="89">
@@ -6820,19 +6820,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>14.9643</v>
+        <v>14.9392</v>
       </c>
       <c r="C89" t="n">
-        <v>16.7571</v>
+        <v>16.6889</v>
       </c>
       <c r="D89" t="n">
-        <v>60.522</v>
+        <v>60.4519</v>
       </c>
       <c r="E89" t="n">
-        <v>14.791</v>
+        <v>14.6242</v>
       </c>
       <c r="F89" t="n">
-        <v>52.0193</v>
+        <v>51.7012</v>
       </c>
     </row>
     <row r="90">
@@ -6840,19 +6840,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>14.6692</v>
+        <v>14.639</v>
       </c>
       <c r="C90" t="n">
-        <v>16.6757</v>
+        <v>16.617</v>
       </c>
       <c r="D90" t="n">
-        <v>60.5529</v>
+        <v>60.4102</v>
       </c>
       <c r="E90" t="n">
-        <v>14.5591</v>
+        <v>14.3688</v>
       </c>
       <c r="F90" t="n">
-        <v>51.6981</v>
+        <v>51.3764</v>
       </c>
     </row>
     <row r="91">
@@ -6860,19 +6860,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>14.3623</v>
+        <v>14.3618</v>
       </c>
       <c r="C91" t="n">
-        <v>16.5897</v>
+        <v>16.5281</v>
       </c>
       <c r="D91" t="n">
-        <v>60.4016</v>
+        <v>60.4371</v>
       </c>
       <c r="E91" t="n">
-        <v>14.3216</v>
+        <v>14.1507</v>
       </c>
       <c r="F91" t="n">
-        <v>51.5118</v>
+        <v>51.0134</v>
       </c>
     </row>
     <row r="92">
@@ -6880,19 +6880,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>14.0276</v>
+        <v>14.0599</v>
       </c>
       <c r="C92" t="n">
-        <v>16.5324</v>
+        <v>16.4568</v>
       </c>
       <c r="D92" t="n">
-        <v>60.6677</v>
+        <v>60.5445</v>
       </c>
       <c r="E92" t="n">
-        <v>17.5571</v>
+        <v>17.9074</v>
       </c>
       <c r="F92" t="n">
-        <v>55.1172</v>
+        <v>55.2104</v>
       </c>
     </row>
     <row r="93">
@@ -6900,19 +6900,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>13.6903</v>
+        <v>13.7069</v>
       </c>
       <c r="C93" t="n">
-        <v>16.4729</v>
+        <v>16.3893</v>
       </c>
       <c r="D93" t="n">
-        <v>60.5182</v>
+        <v>60.4672</v>
       </c>
       <c r="E93" t="n">
-        <v>17.2109</v>
+        <v>17.1396</v>
       </c>
       <c r="F93" t="n">
-        <v>54.7306</v>
+        <v>54.8085</v>
       </c>
     </row>
     <row r="94">
@@ -6920,19 +6920,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>13.2033</v>
+        <v>13.2531</v>
       </c>
       <c r="C94" t="n">
-        <v>17.8774</v>
+        <v>17.8975</v>
       </c>
       <c r="D94" t="n">
-        <v>60.6239</v>
+        <v>60.3645</v>
       </c>
       <c r="E94" t="n">
-        <v>16.8391</v>
+        <v>16.9497</v>
       </c>
       <c r="F94" t="n">
-        <v>54.3977</v>
+        <v>54.4775</v>
       </c>
     </row>
     <row r="95">
@@ -6940,19 +6940,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>17.709</v>
+        <v>17.6938</v>
       </c>
       <c r="C95" t="n">
-        <v>17.7082</v>
+        <v>17.7229</v>
       </c>
       <c r="D95" t="n">
-        <v>60.3804</v>
+        <v>60.365</v>
       </c>
       <c r="E95" t="n">
-        <v>16.5756</v>
+        <v>16.4574</v>
       </c>
       <c r="F95" t="n">
-        <v>54.0604</v>
+        <v>54.0405</v>
       </c>
     </row>
     <row r="96">
@@ -6960,19 +6960,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>17.4365</v>
+        <v>17.3836</v>
       </c>
       <c r="C96" t="n">
-        <v>17.5313</v>
+        <v>17.5244</v>
       </c>
       <c r="D96" t="n">
-        <v>60.2907</v>
+        <v>60.3348</v>
       </c>
       <c r="E96" t="n">
-        <v>16.3654</v>
+        <v>16.2229</v>
       </c>
       <c r="F96" t="n">
-        <v>53.9564</v>
+        <v>53.7823</v>
       </c>
     </row>
     <row r="97">
@@ -6980,19 +6980,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>17.0982</v>
+        <v>17.0689</v>
       </c>
       <c r="C97" t="n">
-        <v>17.3929</v>
+        <v>17.3923</v>
       </c>
       <c r="D97" t="n">
-        <v>60.4183</v>
+        <v>60.2558</v>
       </c>
       <c r="E97" t="n">
-        <v>16.1265</v>
+        <v>15.9553</v>
       </c>
       <c r="F97" t="n">
-        <v>53.7208</v>
+        <v>53.3501</v>
       </c>
     </row>
     <row r="98">
@@ -7000,19 +7000,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>16.7749</v>
+        <v>16.7338</v>
       </c>
       <c r="C98" t="n">
-        <v>17.2987</v>
+        <v>17.2544</v>
       </c>
       <c r="D98" t="n">
-        <v>60.2378</v>
+        <v>60.2331</v>
       </c>
       <c r="E98" t="n">
-        <v>15.9101</v>
+        <v>15.7378</v>
       </c>
       <c r="F98" t="n">
-        <v>53.2541</v>
+        <v>52.9664</v>
       </c>
     </row>
     <row r="99">
@@ -7020,19 +7020,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>16.3919</v>
+        <v>16.3869</v>
       </c>
       <c r="C99" t="n">
-        <v>17.1213</v>
+        <v>17.1106</v>
       </c>
       <c r="D99" t="n">
-        <v>60.2363</v>
+        <v>60.1681</v>
       </c>
       <c r="E99" t="n">
-        <v>15.6653</v>
+        <v>15.5012</v>
       </c>
       <c r="F99" t="n">
-        <v>52.9286</v>
+        <v>52.7365</v>
       </c>
     </row>
     <row r="100">
@@ -7040,19 +7040,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>16.0269</v>
+        <v>16.014</v>
       </c>
       <c r="C100" t="n">
-        <v>17.0425</v>
+        <v>17.0002</v>
       </c>
       <c r="D100" t="n">
-        <v>60.172</v>
+        <v>60.1985</v>
       </c>
       <c r="E100" t="n">
-        <v>15.4163</v>
+        <v>15.3099</v>
       </c>
       <c r="F100" t="n">
-        <v>52.719</v>
+        <v>52.6001</v>
       </c>
     </row>
     <row r="101">
@@ -7060,19 +7060,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>15.6675</v>
+        <v>15.652</v>
       </c>
       <c r="C101" t="n">
-        <v>16.9468</v>
+        <v>16.8826</v>
       </c>
       <c r="D101" t="n">
-        <v>60.0489</v>
+        <v>60.1658</v>
       </c>
       <c r="E101" t="n">
-        <v>15.2416</v>
+        <v>15.0933</v>
       </c>
       <c r="F101" t="n">
-        <v>52.4166</v>
+        <v>52.1408</v>
       </c>
     </row>
     <row r="102">
@@ -7080,19 +7080,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>15.3354</v>
+        <v>15.3187</v>
       </c>
       <c r="C102" t="n">
-        <v>16.8308</v>
+        <v>16.7999</v>
       </c>
       <c r="D102" t="n">
-        <v>60.0764</v>
+        <v>60.1588</v>
       </c>
       <c r="E102" t="n">
-        <v>15.0485</v>
+        <v>14.8995</v>
       </c>
       <c r="F102" t="n">
-        <v>52.2174</v>
+        <v>52.0085</v>
       </c>
     </row>
     <row r="103">
@@ -7100,19 +7100,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>15.0298</v>
+        <v>14.997</v>
       </c>
       <c r="C103" t="n">
-        <v>16.7719</v>
+        <v>16.7061</v>
       </c>
       <c r="D103" t="n">
-        <v>59.994</v>
+        <v>60.0551</v>
       </c>
       <c r="E103" t="n">
-        <v>14.815</v>
+        <v>14.6516</v>
       </c>
       <c r="F103" t="n">
-        <v>52.0383</v>
+        <v>51.6414</v>
       </c>
     </row>
     <row r="104">
@@ -7120,19 +7120,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>14.7165</v>
+        <v>14.6939</v>
       </c>
       <c r="C104" t="n">
-        <v>16.6479</v>
+        <v>16.6256</v>
       </c>
       <c r="D104" t="n">
-        <v>60.0493</v>
+        <v>60.0678</v>
       </c>
       <c r="E104" t="n">
-        <v>14.5768</v>
+        <v>14.4275</v>
       </c>
       <c r="F104" t="n">
-        <v>51.6913</v>
+        <v>51.3718</v>
       </c>
     </row>
     <row r="105">
@@ -7140,19 +7140,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>14.4051</v>
+        <v>14.4171</v>
       </c>
       <c r="C105" t="n">
-        <v>16.6014</v>
+        <v>16.5418</v>
       </c>
       <c r="D105" t="n">
-        <v>59.9397</v>
+        <v>60.0773</v>
       </c>
       <c r="E105" t="n">
-        <v>14.3464</v>
+        <v>14.1926</v>
       </c>
       <c r="F105" t="n">
-        <v>51.5064</v>
+        <v>51.0597</v>
       </c>
     </row>
     <row r="106">
@@ -7160,19 +7160,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>14.0816</v>
+        <v>14.1087</v>
       </c>
       <c r="C106" t="n">
-        <v>16.5086</v>
+        <v>16.4853</v>
       </c>
       <c r="D106" t="n">
-        <v>59.8951</v>
+        <v>60.0729</v>
       </c>
       <c r="E106" t="n">
-        <v>14.1174</v>
+        <v>13.9541</v>
       </c>
       <c r="F106" t="n">
-        <v>51.6185</v>
+        <v>50.8791</v>
       </c>
     </row>
     <row r="107">
@@ -7180,19 +7180,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>13.7206</v>
+        <v>13.7649</v>
       </c>
       <c r="C107" t="n">
-        <v>16.4299</v>
+        <v>16.4001</v>
       </c>
       <c r="D107" t="n">
-        <v>58.8902</v>
+        <v>58.7758</v>
       </c>
       <c r="E107" t="n">
-        <v>17.326</v>
+        <v>17.5013</v>
       </c>
       <c r="F107" t="n">
-        <v>54.6492</v>
+        <v>55.0659</v>
       </c>
     </row>
     <row r="108">
@@ -7200,19 +7200,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>13.2996</v>
+        <v>13.3467</v>
       </c>
       <c r="C108" t="n">
-        <v>17.8942</v>
+        <v>17.8972</v>
       </c>
       <c r="D108" t="n">
-        <v>58.8298</v>
+        <v>58.7737</v>
       </c>
       <c r="E108" t="n">
-        <v>17.0317</v>
+        <v>17.1873</v>
       </c>
       <c r="F108" t="n">
-        <v>54.5466</v>
+        <v>54.6004</v>
       </c>
     </row>
     <row r="109">
@@ -7220,19 +7220,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>12.7805</v>
+        <v>12.8403</v>
       </c>
       <c r="C109" t="n">
-        <v>17.6848</v>
+        <v>17.7147</v>
       </c>
       <c r="D109" t="n">
-        <v>58.7849</v>
+        <v>58.9277</v>
       </c>
       <c r="E109" t="n">
-        <v>16.6569</v>
+        <v>16.9929</v>
       </c>
       <c r="F109" t="n">
-        <v>54.3876</v>
+        <v>54.1962</v>
       </c>
     </row>
     <row r="110">
@@ -7240,19 +7240,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>17.4672</v>
+        <v>17.437</v>
       </c>
       <c r="C110" t="n">
-        <v>17.5418</v>
+        <v>17.5474</v>
       </c>
       <c r="D110" t="n">
-        <v>58.7634</v>
+        <v>58.9469</v>
       </c>
       <c r="E110" t="n">
-        <v>16.38</v>
+        <v>16.3848</v>
       </c>
       <c r="F110" t="n">
-        <v>53.9714</v>
+        <v>53.7838</v>
       </c>
     </row>
     <row r="111">
@@ -7260,19 +7260,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>17.1571</v>
+        <v>17.1726</v>
       </c>
       <c r="C111" t="n">
-        <v>17.4011</v>
+        <v>17.4135</v>
       </c>
       <c r="D111" t="n">
-        <v>58.9046</v>
+        <v>59.0227</v>
       </c>
       <c r="E111" t="n">
-        <v>16.1306</v>
+        <v>16.1817</v>
       </c>
       <c r="F111" t="n">
-        <v>53.6502</v>
+        <v>53.4102</v>
       </c>
     </row>
     <row r="112">
@@ -7280,19 +7280,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>16.8154</v>
+        <v>16.7944</v>
       </c>
       <c r="C112" t="n">
-        <v>17.2533</v>
+        <v>17.2709</v>
       </c>
       <c r="D112" t="n">
-        <v>58.9082</v>
+        <v>59.1088</v>
       </c>
       <c r="E112" t="n">
-        <v>15.9164</v>
+        <v>15.8733</v>
       </c>
       <c r="F112" t="n">
-        <v>53.1648</v>
+        <v>53.235</v>
       </c>
     </row>
     <row r="113">
@@ -7300,19 +7300,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>16.4529</v>
+        <v>16.4292</v>
       </c>
       <c r="C113" t="n">
-        <v>17.1299</v>
+        <v>17.1209</v>
       </c>
       <c r="D113" t="n">
-        <v>59.0335</v>
+        <v>59.0817</v>
       </c>
       <c r="E113" t="n">
-        <v>15.6901</v>
+        <v>15.5855</v>
       </c>
       <c r="F113" t="n">
-        <v>53.2503</v>
+        <v>52.9271</v>
       </c>
     </row>
     <row r="114">
@@ -7320,19 +7320,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>16.0839</v>
+        <v>16.0688</v>
       </c>
       <c r="C114" t="n">
-        <v>17.0227</v>
+        <v>17.0205</v>
       </c>
       <c r="D114" t="n">
-        <v>58.9628</v>
+        <v>59.2254</v>
       </c>
       <c r="E114" t="n">
-        <v>15.4909</v>
+        <v>15.3909</v>
       </c>
       <c r="F114" t="n">
-        <v>52.7109</v>
+        <v>52.5556</v>
       </c>
     </row>
     <row r="115">
@@ -7340,19 +7340,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>15.7258</v>
+        <v>15.7201</v>
       </c>
       <c r="C115" t="n">
-        <v>16.9114</v>
+        <v>16.9088</v>
       </c>
       <c r="D115" t="n">
-        <v>58.9818</v>
+        <v>59.2864</v>
       </c>
       <c r="E115" t="n">
-        <v>15.2752</v>
+        <v>15.1744</v>
       </c>
       <c r="F115" t="n">
-        <v>52.4936</v>
+        <v>52.3891</v>
       </c>
     </row>
     <row r="116">
@@ -7360,19 +7360,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>15.3859</v>
+        <v>15.376</v>
       </c>
       <c r="C116" t="n">
-        <v>16.8158</v>
+        <v>16.7983</v>
       </c>
       <c r="D116" t="n">
-        <v>59.0686</v>
+        <v>59.2742</v>
       </c>
       <c r="E116" t="n">
-        <v>15.0609</v>
+        <v>14.9608</v>
       </c>
       <c r="F116" t="n">
-        <v>52.3517</v>
+        <v>51.8705</v>
       </c>
     </row>
     <row r="117">
@@ -7380,19 +7380,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>15.068</v>
+        <v>15.0572</v>
       </c>
       <c r="C117" t="n">
-        <v>16.7169</v>
+        <v>16.7123</v>
       </c>
       <c r="D117" t="n">
-        <v>59.0899</v>
+        <v>59.3129</v>
       </c>
       <c r="E117" t="n">
-        <v>14.8464</v>
+        <v>14.7218</v>
       </c>
       <c r="F117" t="n">
-        <v>51.9934</v>
+        <v>51.4402</v>
       </c>
     </row>
     <row r="118">
@@ -7400,19 +7400,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>14.7514</v>
+        <v>14.7446</v>
       </c>
       <c r="C118" t="n">
-        <v>16.6349</v>
+        <v>16.6394</v>
       </c>
       <c r="D118" t="n">
-        <v>59.0846</v>
+        <v>59.3716</v>
       </c>
       <c r="E118" t="n">
-        <v>14.6096</v>
+        <v>14.4859</v>
       </c>
       <c r="F118" t="n">
-        <v>51.7515</v>
+        <v>51.3676</v>
       </c>
     </row>
     <row r="119">
@@ -7420,19 +7420,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>14.4554</v>
+        <v>14.4694</v>
       </c>
       <c r="C119" t="n">
-        <v>16.56</v>
+        <v>16.553</v>
       </c>
       <c r="D119" t="n">
-        <v>59.1434</v>
+        <v>59.3338</v>
       </c>
       <c r="E119" t="n">
-        <v>14.3746</v>
+        <v>14.2597</v>
       </c>
       <c r="F119" t="n">
-        <v>51.3945</v>
+        <v>51.3604</v>
       </c>
     </row>
     <row r="120">
@@ -7440,19 +7440,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>14.1277</v>
+        <v>14.169</v>
       </c>
       <c r="C120" t="n">
-        <v>16.4901</v>
+        <v>16.4882</v>
       </c>
       <c r="D120" t="n">
-        <v>59.1092</v>
+        <v>59.3157</v>
       </c>
       <c r="E120" t="n">
-        <v>14.1463</v>
+        <v>13.9883</v>
       </c>
       <c r="F120" t="n">
-        <v>51.1067</v>
+        <v>50.6178</v>
       </c>
     </row>
     <row r="121">
@@ -7460,19 +7460,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>13.7976</v>
+        <v>13.8493</v>
       </c>
       <c r="C121" t="n">
-        <v>16.4306</v>
+        <v>16.4033</v>
       </c>
       <c r="D121" t="n">
-        <v>61.0705</v>
+        <v>61.1998</v>
       </c>
       <c r="E121" t="n">
-        <v>17.73</v>
+        <v>17.9374</v>
       </c>
       <c r="F121" t="n">
-        <v>54.8456</v>
+        <v>54.893</v>
       </c>
     </row>
     <row r="122">
@@ -7480,19 +7480,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>13.4015</v>
+        <v>13.4505</v>
       </c>
       <c r="C122" t="n">
-        <v>17.9034</v>
+        <v>17.9437</v>
       </c>
       <c r="D122" t="n">
-        <v>61.073</v>
+        <v>61.0933</v>
       </c>
       <c r="E122" t="n">
-        <v>17.2674</v>
+        <v>17.1086</v>
       </c>
       <c r="F122" t="n">
-        <v>54.4839</v>
+        <v>54.4761</v>
       </c>
     </row>
     <row r="123">
@@ -7500,19 +7500,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>12.8742</v>
+        <v>12.9439</v>
       </c>
       <c r="C123" t="n">
-        <v>17.7325</v>
+        <v>17.7608</v>
       </c>
       <c r="D123" t="n">
-        <v>61.0849</v>
+        <v>60.9468</v>
       </c>
       <c r="E123" t="n">
-        <v>16.8382</v>
+        <v>16.9265</v>
       </c>
       <c r="F123" t="n">
-        <v>54.1529</v>
+        <v>54.1299</v>
       </c>
     </row>
     <row r="124">
@@ -7520,19 +7520,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>17.5156</v>
+        <v>17.4967</v>
       </c>
       <c r="C124" t="n">
-        <v>17.5534</v>
+        <v>17.5844</v>
       </c>
       <c r="D124" t="n">
-        <v>60.9006</v>
+        <v>60.9985</v>
       </c>
       <c r="E124" t="n">
-        <v>16.5325</v>
+        <v>16.4535</v>
       </c>
       <c r="F124" t="n">
-        <v>53.8759</v>
+        <v>53.7921</v>
       </c>
     </row>
     <row r="125">
@@ -7540,19 +7540,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>17.2146</v>
+        <v>17.2127</v>
       </c>
       <c r="C125" t="n">
-        <v>17.4045</v>
+        <v>17.4348</v>
       </c>
       <c r="D125" t="n">
-        <v>60.7963</v>
+        <v>60.8885</v>
       </c>
       <c r="E125" t="n">
-        <v>16.4156</v>
+        <v>16.2449</v>
       </c>
       <c r="F125" t="n">
-        <v>53.478</v>
+        <v>53.5884</v>
       </c>
     </row>
     <row r="126">
@@ -7560,19 +7560,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>16.8781</v>
+        <v>16.881</v>
       </c>
       <c r="C126" t="n">
-        <v>17.2698</v>
+        <v>17.2994</v>
       </c>
       <c r="D126" t="n">
-        <v>60.6777</v>
+        <v>60.7538</v>
       </c>
       <c r="E126" t="n">
-        <v>16.0255</v>
+        <v>16.005</v>
       </c>
       <c r="F126" t="n">
-        <v>53.1636</v>
+        <v>53.1812</v>
       </c>
     </row>
     <row r="127">
@@ -7580,19 +7580,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>16.521</v>
+        <v>16.5289</v>
       </c>
       <c r="C127" t="n">
-        <v>17.1574</v>
+        <v>17.1585</v>
       </c>
       <c r="D127" t="n">
-        <v>60.729</v>
+        <v>60.7281</v>
       </c>
       <c r="E127" t="n">
-        <v>15.7602</v>
+        <v>15.6707</v>
       </c>
       <c r="F127" t="n">
-        <v>52.8127</v>
+        <v>52.8255</v>
       </c>
     </row>
     <row r="128">
@@ -7600,19 +7600,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>16.1528</v>
+        <v>16.1455</v>
       </c>
       <c r="C128" t="n">
-        <v>17.0409</v>
+        <v>17.0391</v>
       </c>
       <c r="D128" t="n">
-        <v>60.5739</v>
+        <v>60.6957</v>
       </c>
       <c r="E128" t="n">
-        <v>15.4982</v>
+        <v>15.435</v>
       </c>
       <c r="F128" t="n">
-        <v>52.5835</v>
+        <v>52.527</v>
       </c>
     </row>
     <row r="129">
@@ -7620,19 +7620,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>15.7958</v>
+        <v>15.788</v>
       </c>
       <c r="C129" t="n">
-        <v>16.9305</v>
+        <v>16.9436</v>
       </c>
       <c r="D129" t="n">
-        <v>60.5251</v>
+        <v>60.6325</v>
       </c>
       <c r="E129" t="n">
-        <v>15.3247</v>
+        <v>15.2458</v>
       </c>
       <c r="F129" t="n">
-        <v>52.4086</v>
+        <v>52.3082</v>
       </c>
     </row>
     <row r="130">
@@ -7640,19 +7640,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>15.4456</v>
+        <v>15.4431</v>
       </c>
       <c r="C130" t="n">
-        <v>16.8334</v>
+        <v>16.8094</v>
       </c>
       <c r="D130" t="n">
-        <v>60.5013</v>
+        <v>60.5167</v>
       </c>
       <c r="E130" t="n">
-        <v>15.1167</v>
+        <v>14.9853</v>
       </c>
       <c r="F130" t="n">
-        <v>52.0004</v>
+        <v>52.1672</v>
       </c>
     </row>
     <row r="131">
@@ -7660,19 +7660,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>15.1372</v>
+        <v>15.1215</v>
       </c>
       <c r="C131" t="n">
-        <v>16.7417</v>
+        <v>16.7189</v>
       </c>
       <c r="D131" t="n">
-        <v>60.4086</v>
+        <v>60.5947</v>
       </c>
       <c r="E131" t="n">
-        <v>14.8894</v>
+        <v>14.7923</v>
       </c>
       <c r="F131" t="n">
-        <v>51.7815</v>
+        <v>51.5889</v>
       </c>
     </row>
     <row r="132">
@@ -7680,19 +7680,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>14.8192</v>
+        <v>14.8008</v>
       </c>
       <c r="C132" t="n">
-        <v>16.6557</v>
+        <v>16.6356</v>
       </c>
       <c r="D132" t="n">
-        <v>60.4056</v>
+        <v>60.5329</v>
       </c>
       <c r="E132" t="n">
-        <v>14.6748</v>
+        <v>14.53</v>
       </c>
       <c r="F132" t="n">
-        <v>51.535</v>
+        <v>51.3674</v>
       </c>
     </row>
     <row r="133">
@@ -7700,19 +7700,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>14.5004</v>
+        <v>14.506</v>
       </c>
       <c r="C133" t="n">
-        <v>16.5836</v>
+        <v>16.5528</v>
       </c>
       <c r="D133" t="n">
-        <v>60.3289</v>
+        <v>60.4002</v>
       </c>
       <c r="E133" t="n">
-        <v>14.4377</v>
+        <v>14.2836</v>
       </c>
       <c r="F133" t="n">
-        <v>51.2253</v>
+        <v>51.1215</v>
       </c>
     </row>
     <row r="134">
@@ -7720,19 +7720,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.2149</v>
+        <v>14.2254</v>
       </c>
       <c r="C134" t="n">
-        <v>16.5038</v>
+        <v>16.4773</v>
       </c>
       <c r="D134" t="n">
-        <v>60.2294</v>
+        <v>60.4117</v>
       </c>
       <c r="E134" t="n">
-        <v>14.197</v>
+        <v>14.0432</v>
       </c>
       <c r="F134" t="n">
-        <v>51.0156</v>
+        <v>50.7876</v>
       </c>
     </row>
     <row r="135">
@@ -7740,19 +7740,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>13.9076</v>
+        <v>13.9111</v>
       </c>
       <c r="C135" t="n">
-        <v>16.4509</v>
+        <v>16.4129</v>
       </c>
       <c r="D135" t="n">
-        <v>61.587</v>
+        <v>61.8142</v>
       </c>
       <c r="E135" t="n">
-        <v>18.2309</v>
+        <v>18.1122</v>
       </c>
       <c r="F135" t="n">
-        <v>54.8146</v>
+        <v>54.9827</v>
       </c>
     </row>
     <row r="136">
@@ -7760,19 +7760,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>13.4498</v>
+        <v>13.5433</v>
       </c>
       <c r="C136" t="n">
-        <v>17.9145</v>
+        <v>17.972</v>
       </c>
       <c r="D136" t="n">
-        <v>61.3857</v>
+        <v>61.5245</v>
       </c>
       <c r="E136" t="n">
-        <v>17.7098</v>
+        <v>17.6917</v>
       </c>
       <c r="F136" t="n">
-        <v>54.3705</v>
+        <v>54.5476</v>
       </c>
     </row>
     <row r="137">
@@ -7780,19 +7780,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>13.0428</v>
+        <v>13.07</v>
       </c>
       <c r="C137" t="n">
-        <v>17.7392</v>
+        <v>17.799</v>
       </c>
       <c r="D137" t="n">
-        <v>61.3845</v>
+        <v>61.4455</v>
       </c>
       <c r="E137" t="n">
-        <v>16.9312</v>
+        <v>17.0416</v>
       </c>
       <c r="F137" t="n">
-        <v>53.926</v>
+        <v>54.2224</v>
       </c>
     </row>
     <row r="138">
@@ -7800,19 +7800,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>17.5812</v>
+        <v>17.611</v>
       </c>
       <c r="C138" t="n">
-        <v>17.5769</v>
+        <v>17.6395</v>
       </c>
       <c r="D138" t="n">
-        <v>61.3086</v>
+        <v>61.3415</v>
       </c>
       <c r="E138" t="n">
-        <v>16.707</v>
+        <v>16.7115</v>
       </c>
       <c r="F138" t="n">
-        <v>53.7485</v>
+        <v>53.7257</v>
       </c>
     </row>
     <row r="139">
@@ -7820,19 +7820,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>17.2953</v>
+        <v>17.3098</v>
       </c>
       <c r="C139" t="n">
-        <v>17.4152</v>
+        <v>17.4749</v>
       </c>
       <c r="D139" t="n">
-        <v>61.2108</v>
+        <v>61.1975</v>
       </c>
       <c r="E139" t="n">
-        <v>16.4445</v>
+        <v>16.2402</v>
       </c>
       <c r="F139" t="n">
-        <v>53.3285</v>
+        <v>53.5169</v>
       </c>
     </row>
     <row r="140">
@@ -7840,19 +7840,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>16.9662</v>
+        <v>16.9743</v>
       </c>
       <c r="C140" t="n">
-        <v>17.2963</v>
+        <v>17.3245</v>
       </c>
       <c r="D140" t="n">
-        <v>61.0768</v>
+        <v>61.1148</v>
       </c>
       <c r="E140" t="n">
-        <v>16.1437</v>
+        <v>16.0057</v>
       </c>
       <c r="F140" t="n">
-        <v>53.0693</v>
+        <v>53.1637</v>
       </c>
     </row>
     <row r="141">
@@ -7860,19 +7860,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>16.6281</v>
+        <v>16.6274</v>
       </c>
       <c r="C141" t="n">
-        <v>17.1793</v>
+        <v>17.1797</v>
       </c>
       <c r="D141" t="n">
-        <v>61.0089</v>
+        <v>61.0771</v>
       </c>
       <c r="E141" t="n">
-        <v>15.8902</v>
+        <v>15.7711</v>
       </c>
       <c r="F141" t="n">
-        <v>52.7291</v>
+        <v>52.8556</v>
       </c>
     </row>
     <row r="142">
@@ -7880,19 +7880,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>16.2441</v>
+        <v>16.2443</v>
       </c>
       <c r="C142" t="n">
-        <v>17.0717</v>
+        <v>17.0733</v>
       </c>
       <c r="D142" t="n">
-        <v>60.9074</v>
+        <v>61.065</v>
       </c>
       <c r="E142" t="n">
-        <v>15.6527</v>
+        <v>15.6084</v>
       </c>
       <c r="F142" t="n">
-        <v>52.4791</v>
+        <v>52.4079</v>
       </c>
     </row>
     <row r="143">
@@ -7900,19 +7900,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>15.8825</v>
+        <v>15.8747</v>
       </c>
       <c r="C143" t="n">
-        <v>16.9305</v>
+        <v>16.9426</v>
       </c>
       <c r="D143" t="n">
-        <v>60.7621</v>
+        <v>60.9662</v>
       </c>
       <c r="E143" t="n">
-        <v>15.3486</v>
+        <v>15.2802</v>
       </c>
       <c r="F143" t="n">
-        <v>52.525</v>
+        <v>52.2603</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Running erasure.xlsx
+++ b/vs-x64/Running erasure.xlsx
@@ -5080,19 +5080,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>14.4077</v>
+        <v>14.4771</v>
       </c>
       <c r="C2" t="n">
-        <v>15.1588</v>
+        <v>15.0101</v>
       </c>
       <c r="D2" t="n">
-        <v>41.8122</v>
+        <v>41.9478</v>
       </c>
       <c r="E2" t="n">
-        <v>13.7256</v>
+        <v>14.1638</v>
       </c>
       <c r="F2" t="n">
-        <v>34.4435</v>
+        <v>35.5457</v>
       </c>
     </row>
     <row r="3">
@@ -5100,19 +5100,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>14.0008</v>
+        <v>14.303</v>
       </c>
       <c r="C3" t="n">
-        <v>15.0944</v>
+        <v>15.0783</v>
       </c>
       <c r="D3" t="n">
-        <v>41.655</v>
+        <v>41.9602</v>
       </c>
       <c r="E3" t="n">
-        <v>13.5258</v>
+        <v>14.1283</v>
       </c>
       <c r="F3" t="n">
-        <v>34.1771</v>
+        <v>35.1585</v>
       </c>
     </row>
     <row r="4">
@@ -5120,19 +5120,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>13.8495</v>
+        <v>13.9407</v>
       </c>
       <c r="C4" t="n">
-        <v>15.2364</v>
+        <v>15.1551</v>
       </c>
       <c r="D4" t="n">
-        <v>41.7107</v>
+        <v>42.0028</v>
       </c>
       <c r="E4" t="n">
-        <v>13.4295</v>
+        <v>13.904</v>
       </c>
       <c r="F4" t="n">
-        <v>33.8041</v>
+        <v>34.7342</v>
       </c>
     </row>
     <row r="5">
@@ -5140,19 +5140,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>13.7098</v>
+        <v>13.8434</v>
       </c>
       <c r="C5" t="n">
-        <v>15.1511</v>
+        <v>15.1379</v>
       </c>
       <c r="D5" t="n">
-        <v>41.7897</v>
+        <v>41.9078</v>
       </c>
       <c r="E5" t="n">
-        <v>13.2726</v>
+        <v>13.709</v>
       </c>
       <c r="F5" t="n">
-        <v>33.8107</v>
+        <v>34.983</v>
       </c>
     </row>
     <row r="6">
@@ -5160,19 +5160,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>13.3778</v>
+        <v>13.3885</v>
       </c>
       <c r="C6" t="n">
-        <v>15.254</v>
+        <v>15.2178</v>
       </c>
       <c r="D6" t="n">
-        <v>41.8271</v>
+        <v>41.9319</v>
       </c>
       <c r="E6" t="n">
-        <v>13.1263</v>
+        <v>13.5016</v>
       </c>
       <c r="F6" t="n">
-        <v>33.6436</v>
+        <v>34.4106</v>
       </c>
     </row>
     <row r="7">
@@ -5180,19 +5180,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>13.1968</v>
+        <v>13.3542</v>
       </c>
       <c r="C7" t="n">
-        <v>15.2052</v>
+        <v>15.1591</v>
       </c>
       <c r="D7" t="n">
-        <v>42.5045</v>
+        <v>42.8145</v>
       </c>
       <c r="E7" t="n">
-        <v>16.3545</v>
+        <v>16.8397</v>
       </c>
       <c r="F7" t="n">
-        <v>37.7743</v>
+        <v>38.5922</v>
       </c>
     </row>
     <row r="8">
@@ -5200,19 +5200,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>12.839</v>
+        <v>12.8376</v>
       </c>
       <c r="C8" t="n">
-        <v>17.0636</v>
+        <v>17.0336</v>
       </c>
       <c r="D8" t="n">
-        <v>42.3827</v>
+        <v>42.8841</v>
       </c>
       <c r="E8" t="n">
-        <v>15.8702</v>
+        <v>16.8034</v>
       </c>
       <c r="F8" t="n">
-        <v>37.574</v>
+        <v>38.0734</v>
       </c>
     </row>
     <row r="9">
@@ -5220,19 +5220,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>12.4908</v>
+        <v>12.5856</v>
       </c>
       <c r="C9" t="n">
-        <v>17.0549</v>
+        <v>16.9933</v>
       </c>
       <c r="D9" t="n">
-        <v>42.736</v>
+        <v>43.0152</v>
       </c>
       <c r="E9" t="n">
-        <v>15.8397</v>
+        <v>19.2084</v>
       </c>
       <c r="F9" t="n">
-        <v>37.227</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="10">
@@ -5240,19 +5240,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>16.8029</v>
+        <v>17.1465</v>
       </c>
       <c r="C10" t="n">
-        <v>16.8912</v>
+        <v>16.755</v>
       </c>
       <c r="D10" t="n">
-        <v>42.5454</v>
+        <v>42.745</v>
       </c>
       <c r="E10" t="n">
-        <v>15.4161</v>
+        <v>16.2452</v>
       </c>
       <c r="F10" t="n">
-        <v>36.8183</v>
+        <v>38.0029</v>
       </c>
     </row>
     <row r="11">
@@ -5260,19 +5260,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>16.5689</v>
+        <v>16.996</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8095</v>
+        <v>16.7674</v>
       </c>
       <c r="D11" t="n">
-        <v>42.6874</v>
+        <v>42.7421</v>
       </c>
       <c r="E11" t="n">
-        <v>15.2566</v>
+        <v>15.9127</v>
       </c>
       <c r="F11" t="n">
-        <v>36.5718</v>
+        <v>37.5266</v>
       </c>
     </row>
     <row r="12">
@@ -5280,19 +5280,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>16.1966</v>
+        <v>16.6576</v>
       </c>
       <c r="C12" t="n">
-        <v>16.7496</v>
+        <v>16.6644</v>
       </c>
       <c r="D12" t="n">
-        <v>42.455</v>
+        <v>42.616</v>
       </c>
       <c r="E12" t="n">
-        <v>15.0905</v>
+        <v>15.7157</v>
       </c>
       <c r="F12" t="n">
-        <v>36.2667</v>
+        <v>37.4137</v>
       </c>
     </row>
     <row r="13">
@@ -5300,19 +5300,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>15.9146</v>
+        <v>16.3804</v>
       </c>
       <c r="C13" t="n">
-        <v>16.6586</v>
+        <v>16.6069</v>
       </c>
       <c r="D13" t="n">
-        <v>42.5807</v>
+        <v>42.5957</v>
       </c>
       <c r="E13" t="n">
-        <v>14.9165</v>
+        <v>15.4696</v>
       </c>
       <c r="F13" t="n">
-        <v>36.0257</v>
+        <v>36.8478</v>
       </c>
     </row>
     <row r="14">
@@ -5320,19 +5320,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>15.7422</v>
+        <v>16.0408</v>
       </c>
       <c r="C14" t="n">
-        <v>16.587</v>
+        <v>16.585</v>
       </c>
       <c r="D14" t="n">
-        <v>42.5672</v>
+        <v>42.8402</v>
       </c>
       <c r="E14" t="n">
-        <v>14.8024</v>
+        <v>15.9269</v>
       </c>
       <c r="F14" t="n">
-        <v>35.8297</v>
+        <v>36.6931</v>
       </c>
     </row>
     <row r="15">
@@ -5340,19 +5340,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>15.3749</v>
+        <v>15.5427</v>
       </c>
       <c r="C15" t="n">
-        <v>16.4644</v>
+        <v>16.4637</v>
       </c>
       <c r="D15" t="n">
-        <v>42.4464</v>
+        <v>42.648</v>
       </c>
       <c r="E15" t="n">
-        <v>14.5581</v>
+        <v>15.059</v>
       </c>
       <c r="F15" t="n">
-        <v>35.4231</v>
+        <v>36.3073</v>
       </c>
     </row>
     <row r="16">
@@ -5360,19 +5360,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>15.1374</v>
+        <v>15.3015</v>
       </c>
       <c r="C16" t="n">
-        <v>16.4806</v>
+        <v>16.4091</v>
       </c>
       <c r="D16" t="n">
-        <v>42.3729</v>
+        <v>42.6058</v>
       </c>
       <c r="E16" t="n">
-        <v>14.5811</v>
+        <v>14.8901</v>
       </c>
       <c r="F16" t="n">
-        <v>35.3301</v>
+        <v>36.2297</v>
       </c>
     </row>
     <row r="17">
@@ -5380,19 +5380,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>14.7986</v>
+        <v>14.9978</v>
       </c>
       <c r="C17" t="n">
-        <v>16.208</v>
+        <v>16.1689</v>
       </c>
       <c r="D17" t="n">
-        <v>42.4978</v>
+        <v>42.7485</v>
       </c>
       <c r="E17" t="n">
-        <v>14.1219</v>
+        <v>14.7025</v>
       </c>
       <c r="F17" t="n">
-        <v>34.8116</v>
+        <v>35.9601</v>
       </c>
     </row>
     <row r="18">
@@ -5400,19 +5400,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>14.5657</v>
+        <v>14.6447</v>
       </c>
       <c r="C18" t="n">
-        <v>16.1618</v>
+        <v>16.0964</v>
       </c>
       <c r="D18" t="n">
-        <v>42.3958</v>
+        <v>42.7463</v>
       </c>
       <c r="E18" t="n">
-        <v>13.9614</v>
+        <v>14.5501</v>
       </c>
       <c r="F18" t="n">
-        <v>34.6265</v>
+        <v>35.5897</v>
       </c>
     </row>
     <row r="19">
@@ -5420,19 +5420,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>14.2163</v>
+        <v>14.4052</v>
       </c>
       <c r="C19" t="n">
-        <v>16.1469</v>
+        <v>16.1193</v>
       </c>
       <c r="D19" t="n">
-        <v>42.5147</v>
+        <v>42.6503</v>
       </c>
       <c r="E19" t="n">
-        <v>13.743</v>
+        <v>14.2845</v>
       </c>
       <c r="F19" t="n">
-        <v>34.3048</v>
+        <v>35.2914</v>
       </c>
     </row>
     <row r="20">
@@ -5440,19 +5440,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>14.0318</v>
+        <v>13.9877</v>
       </c>
       <c r="C20" t="n">
-        <v>16.1215</v>
+        <v>16.1329</v>
       </c>
       <c r="D20" t="n">
-        <v>42.3806</v>
+        <v>42.5903</v>
       </c>
       <c r="E20" t="n">
-        <v>13.4798</v>
+        <v>14.4876</v>
       </c>
       <c r="F20" t="n">
-        <v>34.0324</v>
+        <v>34.6861</v>
       </c>
     </row>
     <row r="21">
@@ -5460,19 +5460,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>13.7695</v>
+        <v>13.6905</v>
       </c>
       <c r="C21" t="n">
-        <v>15.9329</v>
+        <v>15.9322</v>
       </c>
       <c r="D21" t="n">
-        <v>43.1143</v>
+        <v>43.4984</v>
       </c>
       <c r="E21" t="n">
-        <v>16.4636</v>
+        <v>17.1486</v>
       </c>
       <c r="F21" t="n">
-        <v>38.3907</v>
+        <v>38.8665</v>
       </c>
     </row>
     <row r="22">
@@ -5480,19 +5480,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>13.3818</v>
+        <v>13.4471</v>
       </c>
       <c r="C22" t="n">
-        <v>17.714</v>
+        <v>17.6428</v>
       </c>
       <c r="D22" t="n">
-        <v>43.2665</v>
+        <v>43.2578</v>
       </c>
       <c r="E22" t="n">
-        <v>16.2691</v>
+        <v>16.8985</v>
       </c>
       <c r="F22" t="n">
-        <v>38.0477</v>
+        <v>38.791</v>
       </c>
     </row>
     <row r="23">
@@ -5500,19 +5500,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.8895</v>
+        <v>12.8719</v>
       </c>
       <c r="C23" t="n">
-        <v>17.5599</v>
+        <v>17.4831</v>
       </c>
       <c r="D23" t="n">
-        <v>43.1163</v>
+        <v>43.3573</v>
       </c>
       <c r="E23" t="n">
-        <v>16.0098</v>
+        <v>16.6403</v>
       </c>
       <c r="F23" t="n">
-        <v>37.7315</v>
+        <v>38.3203</v>
       </c>
     </row>
     <row r="24">
@@ -5520,19 +5520,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>17.4845</v>
+        <v>17.4727</v>
       </c>
       <c r="C24" t="n">
-        <v>17.3934</v>
+        <v>17.3625</v>
       </c>
       <c r="D24" t="n">
-        <v>42.9584</v>
+        <v>43.4547</v>
       </c>
       <c r="E24" t="n">
-        <v>15.8425</v>
+        <v>16.4042</v>
       </c>
       <c r="F24" t="n">
-        <v>37.3696</v>
+        <v>38.128</v>
       </c>
     </row>
     <row r="25">
@@ -5540,19 +5540,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>17.1896</v>
+        <v>17.1744</v>
       </c>
       <c r="C25" t="n">
-        <v>17.2632</v>
+        <v>17.1992</v>
       </c>
       <c r="D25" t="n">
-        <v>43.1464</v>
+        <v>43.3385</v>
       </c>
       <c r="E25" t="n">
-        <v>15.541</v>
+        <v>16.1407</v>
       </c>
       <c r="F25" t="n">
-        <v>36.9321</v>
+        <v>37.7389</v>
       </c>
     </row>
     <row r="26">
@@ -5560,19 +5560,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>16.8758</v>
+        <v>16.8496</v>
       </c>
       <c r="C26" t="n">
-        <v>17.1284</v>
+        <v>17.0889</v>
       </c>
       <c r="D26" t="n">
-        <v>43.0528</v>
+        <v>43.4638</v>
       </c>
       <c r="E26" t="n">
-        <v>15.2879</v>
+        <v>15.9412</v>
       </c>
       <c r="F26" t="n">
-        <v>36.6877</v>
+        <v>37.2949</v>
       </c>
     </row>
     <row r="27">
@@ -5580,19 +5580,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>16.5071</v>
+        <v>16.4907</v>
       </c>
       <c r="C27" t="n">
-        <v>17.024</v>
+        <v>16.9794</v>
       </c>
       <c r="D27" t="n">
-        <v>43.0579</v>
+        <v>43.1702</v>
       </c>
       <c r="E27" t="n">
-        <v>15.1021</v>
+        <v>15.7573</v>
       </c>
       <c r="F27" t="n">
-        <v>36.5396</v>
+        <v>36.8207</v>
       </c>
     </row>
     <row r="28">
@@ -5600,19 +5600,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>16.1795</v>
+        <v>16.1358</v>
       </c>
       <c r="C28" t="n">
-        <v>16.8874</v>
+        <v>16.8608</v>
       </c>
       <c r="D28" t="n">
-        <v>43.0637</v>
+        <v>43.1626</v>
       </c>
       <c r="E28" t="n">
-        <v>15.0132</v>
+        <v>15.5612</v>
       </c>
       <c r="F28" t="n">
-        <v>36.0818</v>
+        <v>36.6381</v>
       </c>
     </row>
     <row r="29">
@@ -5620,19 +5620,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>15.8488</v>
+        <v>15.7688</v>
       </c>
       <c r="C29" t="n">
-        <v>16.7823</v>
+        <v>16.6855</v>
       </c>
       <c r="D29" t="n">
-        <v>42.7993</v>
+        <v>43.0502</v>
       </c>
       <c r="E29" t="n">
-        <v>14.7746</v>
+        <v>15.3968</v>
       </c>
       <c r="F29" t="n">
-        <v>36.1556</v>
+        <v>36.4643</v>
       </c>
     </row>
     <row r="30">
@@ -5640,19 +5640,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>15.5309</v>
+        <v>15.4737</v>
       </c>
       <c r="C30" t="n">
-        <v>16.7082</v>
+        <v>16.669</v>
       </c>
       <c r="D30" t="n">
-        <v>42.8542</v>
+        <v>43.1299</v>
       </c>
       <c r="E30" t="n">
-        <v>14.6262</v>
+        <v>15.1796</v>
       </c>
       <c r="F30" t="n">
-        <v>35.4217</v>
+        <v>36.4819</v>
       </c>
     </row>
     <row r="31">
@@ -5660,19 +5660,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>15.1811</v>
+        <v>15.1256</v>
       </c>
       <c r="C31" t="n">
-        <v>16.5988</v>
+        <v>16.5788</v>
       </c>
       <c r="D31" t="n">
-        <v>42.8309</v>
+        <v>43.162</v>
       </c>
       <c r="E31" t="n">
-        <v>14.3803</v>
+        <v>14.9952</v>
       </c>
       <c r="F31" t="n">
-        <v>35.3901</v>
+        <v>36.1055</v>
       </c>
     </row>
     <row r="32">
@@ -5680,19 +5680,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>14.8842</v>
+        <v>14.809</v>
       </c>
       <c r="C32" t="n">
-        <v>16.5716</v>
+        <v>16.568</v>
       </c>
       <c r="D32" t="n">
-        <v>42.7709</v>
+        <v>43.1112</v>
       </c>
       <c r="E32" t="n">
-        <v>14.2416</v>
+        <v>14.7605</v>
       </c>
       <c r="F32" t="n">
-        <v>34.9163</v>
+        <v>35.8199</v>
       </c>
     </row>
     <row r="33">
@@ -5700,19 +5700,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>14.598</v>
+        <v>14.5321</v>
       </c>
       <c r="C33" t="n">
-        <v>16.4464</v>
+        <v>16.4135</v>
       </c>
       <c r="D33" t="n">
-        <v>42.9323</v>
+        <v>42.9075</v>
       </c>
       <c r="E33" t="n">
-        <v>13.9811</v>
+        <v>14.498</v>
       </c>
       <c r="F33" t="n">
-        <v>34.6467</v>
+        <v>35.6114</v>
       </c>
     </row>
     <row r="34">
@@ -5720,19 +5720,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>14.3454</v>
+        <v>14.2482</v>
       </c>
       <c r="C34" t="n">
-        <v>16.407</v>
+        <v>16.3793</v>
       </c>
       <c r="D34" t="n">
-        <v>42.8316</v>
+        <v>42.8476</v>
       </c>
       <c r="E34" t="n">
-        <v>13.8483</v>
+        <v>14.3492</v>
       </c>
       <c r="F34" t="n">
-        <v>34.3383</v>
+        <v>35.3455</v>
       </c>
     </row>
     <row r="35">
@@ -5740,19 +5740,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>14.0492</v>
+        <v>13.9828</v>
       </c>
       <c r="C35" t="n">
-        <v>16.361</v>
+        <v>16.3027</v>
       </c>
       <c r="D35" t="n">
-        <v>43.7264</v>
+        <v>43.9724</v>
       </c>
       <c r="E35" t="n">
-        <v>17.1197</v>
+        <v>17.7887</v>
       </c>
       <c r="F35" t="n">
-        <v>38.8718</v>
+        <v>39.7551</v>
       </c>
     </row>
     <row r="36">
@@ -5760,19 +5760,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>13.7396</v>
+        <v>13.6143</v>
       </c>
       <c r="C36" t="n">
-        <v>16.2658</v>
+        <v>16.1962</v>
       </c>
       <c r="D36" t="n">
-        <v>43.7372</v>
+        <v>43.8626</v>
       </c>
       <c r="E36" t="n">
-        <v>16.6319</v>
+        <v>17.4408</v>
       </c>
       <c r="F36" t="n">
-        <v>38.602</v>
+        <v>39.2294</v>
       </c>
     </row>
     <row r="37">
@@ -5780,19 +5780,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.3043</v>
+        <v>13.2276</v>
       </c>
       <c r="C37" t="n">
-        <v>17.8204</v>
+        <v>17.7774</v>
       </c>
       <c r="D37" t="n">
-        <v>43.6699</v>
+        <v>43.7448</v>
       </c>
       <c r="E37" t="n">
-        <v>16.4044</v>
+        <v>17.0146</v>
       </c>
       <c r="F37" t="n">
-        <v>38.1983</v>
+        <v>38.7005</v>
       </c>
     </row>
     <row r="38">
@@ -5800,19 +5800,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>17.6252</v>
+        <v>17.6151</v>
       </c>
       <c r="C38" t="n">
-        <v>17.6602</v>
+        <v>17.5971</v>
       </c>
       <c r="D38" t="n">
-        <v>43.5556</v>
+        <v>43.7494</v>
       </c>
       <c r="E38" t="n">
-        <v>16.1136</v>
+        <v>16.7459</v>
       </c>
       <c r="F38" t="n">
-        <v>37.8046</v>
+        <v>38.7607</v>
       </c>
     </row>
     <row r="39">
@@ -5820,19 +5820,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>17.3627</v>
+        <v>17.3268</v>
       </c>
       <c r="C39" t="n">
-        <v>17.5151</v>
+        <v>17.4914</v>
       </c>
       <c r="D39" t="n">
-        <v>43.3796</v>
+        <v>43.6033</v>
       </c>
       <c r="E39" t="n">
-        <v>15.9937</v>
+        <v>16.4775</v>
       </c>
       <c r="F39" t="n">
-        <v>37.3234</v>
+        <v>38.274</v>
       </c>
     </row>
     <row r="40">
@@ -5840,19 +5840,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>17.0846</v>
+        <v>17.0236</v>
       </c>
       <c r="C40" t="n">
-        <v>17.3801</v>
+        <v>17.3721</v>
       </c>
       <c r="D40" t="n">
-        <v>43.4514</v>
+        <v>43.6336</v>
       </c>
       <c r="E40" t="n">
-        <v>15.6829</v>
+        <v>16.2827</v>
       </c>
       <c r="F40" t="n">
-        <v>37.1005</v>
+        <v>37.892</v>
       </c>
     </row>
     <row r="41">
@@ -5860,19 +5860,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>16.7542</v>
+        <v>16.6865</v>
       </c>
       <c r="C41" t="n">
-        <v>17.2271</v>
+        <v>17.1661</v>
       </c>
       <c r="D41" t="n">
-        <v>43.3256</v>
+        <v>43.6163</v>
       </c>
       <c r="E41" t="n">
-        <v>15.437</v>
+        <v>16.0294</v>
       </c>
       <c r="F41" t="n">
-        <v>36.8519</v>
+        <v>37.5523</v>
       </c>
     </row>
     <row r="42">
@@ -5880,19 +5880,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>16.4015</v>
+        <v>16.3263</v>
       </c>
       <c r="C42" t="n">
-        <v>17.095</v>
+        <v>17.0317</v>
       </c>
       <c r="D42" t="n">
-        <v>43.5516</v>
+        <v>43.6468</v>
       </c>
       <c r="E42" t="n">
-        <v>15.2639</v>
+        <v>15.7985</v>
       </c>
       <c r="F42" t="n">
-        <v>36.6072</v>
+        <v>37.0579</v>
       </c>
     </row>
     <row r="43">
@@ -5900,19 +5900,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>16.0418</v>
+        <v>15.9804</v>
       </c>
       <c r="C43" t="n">
-        <v>16.9909</v>
+        <v>16.9174</v>
       </c>
       <c r="D43" t="n">
-        <v>43.2817</v>
+        <v>43.4849</v>
       </c>
       <c r="E43" t="n">
-        <v>15.0841</v>
+        <v>15.6149</v>
       </c>
       <c r="F43" t="n">
-        <v>36.1497</v>
+        <v>36.8014</v>
       </c>
     </row>
     <row r="44">
@@ -5920,19 +5920,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>15.6803</v>
+        <v>15.6049</v>
       </c>
       <c r="C44" t="n">
-        <v>16.8749</v>
+        <v>16.8275</v>
       </c>
       <c r="D44" t="n">
-        <v>43.2653</v>
+        <v>43.4154</v>
       </c>
       <c r="E44" t="n">
-        <v>14.8974</v>
+        <v>15.4274</v>
       </c>
       <c r="F44" t="n">
-        <v>35.7875</v>
+        <v>37.2356</v>
       </c>
     </row>
     <row r="45">
@@ -5940,19 +5940,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>15.3604</v>
+        <v>15.2808</v>
       </c>
       <c r="C45" t="n">
-        <v>16.7743</v>
+        <v>16.736</v>
       </c>
       <c r="D45" t="n">
-        <v>43.3447</v>
+        <v>43.3618</v>
       </c>
       <c r="E45" t="n">
-        <v>14.7401</v>
+        <v>15.1893</v>
       </c>
       <c r="F45" t="n">
-        <v>35.5255</v>
+        <v>36.5487</v>
       </c>
     </row>
     <row r="46">
@@ -5960,19 +5960,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>15.0302</v>
+        <v>14.9485</v>
       </c>
       <c r="C46" t="n">
-        <v>16.671</v>
+        <v>16.6178</v>
       </c>
       <c r="D46" t="n">
-        <v>43.2183</v>
+        <v>43.3166</v>
       </c>
       <c r="E46" t="n">
-        <v>14.5759</v>
+        <v>15.0427</v>
       </c>
       <c r="F46" t="n">
-        <v>35.2299</v>
+        <v>36.05</v>
       </c>
     </row>
     <row r="47">
@@ -5980,19 +5980,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>14.7389</v>
+        <v>14.6528</v>
       </c>
       <c r="C47" t="n">
-        <v>16.5767</v>
+        <v>16.5489</v>
       </c>
       <c r="D47" t="n">
-        <v>43.0062</v>
+        <v>43.3931</v>
       </c>
       <c r="E47" t="n">
-        <v>14.3499</v>
+        <v>14.8634</v>
       </c>
       <c r="F47" t="n">
-        <v>34.8657</v>
+        <v>36.1987</v>
       </c>
     </row>
     <row r="48">
@@ -6000,19 +6000,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>14.449</v>
+        <v>14.3969</v>
       </c>
       <c r="C48" t="n">
-        <v>16.5079</v>
+        <v>16.483</v>
       </c>
       <c r="D48" t="n">
-        <v>43.237</v>
+        <v>43.1756</v>
       </c>
       <c r="E48" t="n">
-        <v>14.1117</v>
+        <v>14.5538</v>
       </c>
       <c r="F48" t="n">
-        <v>34.6978</v>
+        <v>35.5837</v>
       </c>
     </row>
     <row r="49">
@@ -6020,19 +6020,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>14.1284</v>
+        <v>14.0483</v>
       </c>
       <c r="C49" t="n">
-        <v>16.4458</v>
+        <v>16.3983</v>
       </c>
       <c r="D49" t="n">
-        <v>43.1221</v>
+        <v>43.268</v>
       </c>
       <c r="E49" t="n">
-        <v>13.9128</v>
+        <v>14.4521</v>
       </c>
       <c r="F49" t="n">
-        <v>34.3038</v>
+        <v>35.3322</v>
       </c>
     </row>
     <row r="50">
@@ -6040,19 +6040,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>13.8223</v>
+        <v>13.7783</v>
       </c>
       <c r="C50" t="n">
-        <v>16.3869</v>
+        <v>16.3293</v>
       </c>
       <c r="D50" t="n">
-        <v>44.2248</v>
+        <v>44.2127</v>
       </c>
       <c r="E50" t="n">
-        <v>16.9454</v>
+        <v>17.6486</v>
       </c>
       <c r="F50" t="n">
-        <v>38.7662</v>
+        <v>39.4126</v>
       </c>
     </row>
     <row r="51">
@@ -6060,19 +6060,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>13.3768</v>
+        <v>13.3336</v>
       </c>
       <c r="C51" t="n">
-        <v>17.915</v>
+        <v>17.9001</v>
       </c>
       <c r="D51" t="n">
-        <v>44.0016</v>
+        <v>44.1745</v>
       </c>
       <c r="E51" t="n">
-        <v>16.6836</v>
+        <v>17.2883</v>
       </c>
       <c r="F51" t="n">
-        <v>38.4427</v>
+        <v>39.0728</v>
       </c>
     </row>
     <row r="52">
@@ -6080,19 +6080,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>12.8239</v>
+        <v>12.7899</v>
       </c>
       <c r="C52" t="n">
-        <v>17.7227</v>
+        <v>17.6954</v>
       </c>
       <c r="D52" t="n">
-        <v>43.9093</v>
+        <v>44.076</v>
       </c>
       <c r="E52" t="n">
-        <v>16.3376</v>
+        <v>19.3947</v>
       </c>
       <c r="F52" t="n">
-        <v>38.2584</v>
+        <v>38.7721</v>
       </c>
     </row>
     <row r="53">
@@ -6100,19 +6100,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>17.3977</v>
+        <v>17.4002</v>
       </c>
       <c r="C53" t="n">
-        <v>17.5394</v>
+        <v>17.5233</v>
       </c>
       <c r="D53" t="n">
-        <v>43.9825</v>
+        <v>44.0528</v>
       </c>
       <c r="E53" t="n">
-        <v>16.0678</v>
+        <v>16.7922</v>
       </c>
       <c r="F53" t="n">
-        <v>37.7475</v>
+        <v>38.347</v>
       </c>
     </row>
     <row r="54">
@@ -6120,19 +6120,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>17.1175</v>
+        <v>17.1066</v>
       </c>
       <c r="C54" t="n">
-        <v>17.4331</v>
+        <v>17.4138</v>
       </c>
       <c r="D54" t="n">
-        <v>43.8133</v>
+        <v>43.9194</v>
       </c>
       <c r="E54" t="n">
-        <v>15.8463</v>
+        <v>16.4896</v>
       </c>
       <c r="F54" t="n">
-        <v>37.5814</v>
+        <v>39.0983</v>
       </c>
     </row>
     <row r="55">
@@ -6140,19 +6140,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>16.8045</v>
+        <v>16.7827</v>
       </c>
       <c r="C55" t="n">
-        <v>17.3045</v>
+        <v>17.269</v>
       </c>
       <c r="D55" t="n">
-        <v>43.7347</v>
+        <v>43.8756</v>
       </c>
       <c r="E55" t="n">
-        <v>15.6676</v>
+        <v>16.2759</v>
       </c>
       <c r="F55" t="n">
-        <v>37.3556</v>
+        <v>38.222</v>
       </c>
     </row>
     <row r="56">
@@ -6160,19 +6160,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>16.4549</v>
+        <v>16.425</v>
       </c>
       <c r="C56" t="n">
-        <v>17.1601</v>
+        <v>17.1213</v>
       </c>
       <c r="D56" t="n">
-        <v>43.5401</v>
+        <v>43.9462</v>
       </c>
       <c r="E56" t="n">
-        <v>15.4828</v>
+        <v>16.0327</v>
       </c>
       <c r="F56" t="n">
-        <v>36.7376</v>
+        <v>37.487</v>
       </c>
     </row>
     <row r="57">
@@ -6180,19 +6180,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>16.0996</v>
+        <v>16.0581</v>
       </c>
       <c r="C57" t="n">
-        <v>17.0627</v>
+        <v>17.044</v>
       </c>
       <c r="D57" t="n">
-        <v>43.8824</v>
+        <v>43.8966</v>
       </c>
       <c r="E57" t="n">
-        <v>15.2621</v>
+        <v>15.7915</v>
       </c>
       <c r="F57" t="n">
-        <v>37.3623</v>
+        <v>37.7896</v>
       </c>
     </row>
     <row r="58">
@@ -6200,19 +6200,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>15.7565</v>
+        <v>15.6973</v>
       </c>
       <c r="C58" t="n">
-        <v>16.9239</v>
+        <v>16.8805</v>
       </c>
       <c r="D58" t="n">
-        <v>43.8617</v>
+        <v>43.8998</v>
       </c>
       <c r="E58" t="n">
-        <v>15.0421</v>
+        <v>15.568</v>
       </c>
       <c r="F58" t="n">
-        <v>36.605</v>
+        <v>37.5109</v>
       </c>
     </row>
     <row r="59">
@@ -6220,19 +6220,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>15.4162</v>
+        <v>15.3652</v>
       </c>
       <c r="C59" t="n">
-        <v>16.8204</v>
+        <v>16.8152</v>
       </c>
       <c r="D59" t="n">
-        <v>43.9189</v>
+        <v>43.8229</v>
       </c>
       <c r="E59" t="n">
-        <v>14.8228</v>
+        <v>15.352</v>
       </c>
       <c r="F59" t="n">
-        <v>36.2131</v>
+        <v>37.8878</v>
       </c>
     </row>
     <row r="60">
@@ -6240,19 +6240,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>15.1035</v>
+        <v>15.0178</v>
       </c>
       <c r="C60" t="n">
-        <v>16.7364</v>
+        <v>16.705</v>
       </c>
       <c r="D60" t="n">
-        <v>43.8397</v>
+        <v>44.1861</v>
       </c>
       <c r="E60" t="n">
-        <v>14.6748</v>
+        <v>15.1814</v>
       </c>
       <c r="F60" t="n">
-        <v>36.4803</v>
+        <v>37.7618</v>
       </c>
     </row>
     <row r="61">
@@ -6260,19 +6260,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>14.8047</v>
+        <v>14.7274</v>
       </c>
       <c r="C61" t="n">
-        <v>16.6601</v>
+        <v>16.6317</v>
       </c>
       <c r="D61" t="n">
-        <v>44.0566</v>
+        <v>44.4159</v>
       </c>
       <c r="E61" t="n">
-        <v>14.4369</v>
+        <v>14.9551</v>
       </c>
       <c r="F61" t="n">
-        <v>36.2604</v>
+        <v>37.1096</v>
       </c>
     </row>
     <row r="62">
@@ -6280,19 +6280,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>14.494</v>
+        <v>14.4247</v>
       </c>
       <c r="C62" t="n">
-        <v>16.5703</v>
+        <v>16.5472</v>
       </c>
       <c r="D62" t="n">
-        <v>44.7219</v>
+        <v>44.6321</v>
       </c>
       <c r="E62" t="n">
-        <v>14.2062</v>
+        <v>14.7483</v>
       </c>
       <c r="F62" t="n">
-        <v>36.9487</v>
+        <v>37.4156</v>
       </c>
     </row>
     <row r="63">
@@ -6300,19 +6300,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>14.2177</v>
+        <v>14.1292</v>
       </c>
       <c r="C63" t="n">
-        <v>16.5019</v>
+        <v>16.499</v>
       </c>
       <c r="D63" t="n">
-        <v>45.2448</v>
+        <v>45.6565</v>
       </c>
       <c r="E63" t="n">
-        <v>13.9482</v>
+        <v>14.4956</v>
       </c>
       <c r="F63" t="n">
-        <v>36.6109</v>
+        <v>38.1304</v>
       </c>
     </row>
     <row r="64">
@@ -6320,19 +6320,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>13.9098</v>
+        <v>13.8101</v>
       </c>
       <c r="C64" t="n">
-        <v>16.4164</v>
+        <v>16.4145</v>
       </c>
       <c r="D64" t="n">
-        <v>50.3766</v>
+        <v>50.8731</v>
       </c>
       <c r="E64" t="n">
-        <v>17.1647</v>
+        <v>17.9365</v>
       </c>
       <c r="F64" t="n">
-        <v>46.3951</v>
+        <v>47.3965</v>
       </c>
     </row>
     <row r="65">
@@ -6340,19 +6340,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>13.5386</v>
+        <v>13.4617</v>
       </c>
       <c r="C65" t="n">
-        <v>17.9836</v>
+        <v>17.9077</v>
       </c>
       <c r="D65" t="n">
-        <v>50.9963</v>
+        <v>51.1356</v>
       </c>
       <c r="E65" t="n">
-        <v>16.9032</v>
+        <v>17.5678</v>
       </c>
       <c r="F65" t="n">
-        <v>45.8201</v>
+        <v>47.0408</v>
       </c>
     </row>
     <row r="66">
@@ -6360,19 +6360,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>13.0505</v>
+        <v>12.9578</v>
       </c>
       <c r="C66" t="n">
-        <v>17.7699</v>
+        <v>17.7247</v>
       </c>
       <c r="D66" t="n">
-        <v>51.4493</v>
+        <v>51.5389</v>
       </c>
       <c r="E66" t="n">
-        <v>16.5747</v>
+        <v>17.2079</v>
       </c>
       <c r="F66" t="n">
-        <v>46.5718</v>
+        <v>47.7176</v>
       </c>
     </row>
     <row r="67">
@@ -6380,19 +6380,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>17.5375</v>
+        <v>17.5367</v>
       </c>
       <c r="C67" t="n">
-        <v>17.6179</v>
+        <v>17.5975</v>
       </c>
       <c r="D67" t="n">
-        <v>51.7959</v>
+        <v>52.0926</v>
       </c>
       <c r="E67" t="n">
-        <v>16.2999</v>
+        <v>16.9554</v>
       </c>
       <c r="F67" t="n">
-        <v>47.1093</v>
+        <v>48.2119</v>
       </c>
     </row>
     <row r="68">
@@ -6400,19 +6400,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>17.2228</v>
+        <v>17.2113</v>
       </c>
       <c r="C68" t="n">
-        <v>17.4562</v>
+        <v>17.4129</v>
       </c>
       <c r="D68" t="n">
-        <v>52.2086</v>
+        <v>52.6832</v>
       </c>
       <c r="E68" t="n">
-        <v>16.0366</v>
+        <v>16.6521</v>
       </c>
       <c r="F68" t="n">
-        <v>47.5544</v>
+        <v>48.5233</v>
       </c>
     </row>
     <row r="69">
@@ -6420,19 +6420,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>16.8839</v>
+        <v>16.8757</v>
       </c>
       <c r="C69" t="n">
-        <v>17.3194</v>
+        <v>17.3035</v>
       </c>
       <c r="D69" t="n">
-        <v>52.5477</v>
+        <v>52.8396</v>
       </c>
       <c r="E69" t="n">
-        <v>15.8227</v>
+        <v>16.4589</v>
       </c>
       <c r="F69" t="n">
-        <v>47.4576</v>
+        <v>48.2059</v>
       </c>
     </row>
     <row r="70">
@@ -6440,19 +6440,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>16.542</v>
+        <v>16.5272</v>
       </c>
       <c r="C70" t="n">
-        <v>17.1906</v>
+        <v>17.1499</v>
       </c>
       <c r="D70" t="n">
-        <v>52.8818</v>
+        <v>53.2744</v>
       </c>
       <c r="E70" t="n">
-        <v>15.6015</v>
+        <v>16.1883</v>
       </c>
       <c r="F70" t="n">
-        <v>47.3862</v>
+        <v>48.387</v>
       </c>
     </row>
     <row r="71">
@@ -6460,19 +6460,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>16.19</v>
+        <v>16.1447</v>
       </c>
       <c r="C71" t="n">
-        <v>17.0529</v>
+        <v>17.048</v>
       </c>
       <c r="D71" t="n">
-        <v>53.4714</v>
+        <v>53.5225</v>
       </c>
       <c r="E71" t="n">
-        <v>15.381</v>
+        <v>15.9616</v>
       </c>
       <c r="F71" t="n">
-        <v>46.9787</v>
+        <v>47.9976</v>
       </c>
     </row>
     <row r="72">
@@ -6480,19 +6480,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>15.8368</v>
+        <v>15.7864</v>
       </c>
       <c r="C72" t="n">
-        <v>16.9666</v>
+        <v>16.9379</v>
       </c>
       <c r="D72" t="n">
-        <v>53.2733</v>
+        <v>53.6078</v>
       </c>
       <c r="E72" t="n">
-        <v>15.1835</v>
+        <v>15.7492</v>
       </c>
       <c r="F72" t="n">
-        <v>47.1274</v>
+        <v>47.9299</v>
       </c>
     </row>
     <row r="73">
@@ -6500,19 +6500,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>15.4896</v>
+        <v>15.4346</v>
       </c>
       <c r="C73" t="n">
-        <v>16.871</v>
+        <v>16.8475</v>
       </c>
       <c r="D73" t="n">
-        <v>53.5379</v>
+        <v>54.0419</v>
       </c>
       <c r="E73" t="n">
-        <v>14.9807</v>
+        <v>15.5023</v>
       </c>
       <c r="F73" t="n">
-        <v>46.8411</v>
+        <v>47.8037</v>
       </c>
     </row>
     <row r="74">
@@ -6520,19 +6520,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>15.1752</v>
+        <v>15.1003</v>
       </c>
       <c r="C74" t="n">
-        <v>16.7734</v>
+        <v>16.7569</v>
       </c>
       <c r="D74" t="n">
-        <v>53.8675</v>
+        <v>54.0726</v>
       </c>
       <c r="E74" t="n">
-        <v>14.79</v>
+        <v>15.2807</v>
       </c>
       <c r="F74" t="n">
-        <v>46.6682</v>
+        <v>47.4745</v>
       </c>
     </row>
     <row r="75">
@@ -6540,19 +6540,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>14.8737</v>
+        <v>14.7868</v>
       </c>
       <c r="C75" t="n">
-        <v>16.6814</v>
+        <v>16.6488</v>
       </c>
       <c r="D75" t="n">
-        <v>54.1479</v>
+        <v>54.3155</v>
       </c>
       <c r="E75" t="n">
-        <v>14.5462</v>
+        <v>15.0479</v>
       </c>
       <c r="F75" t="n">
-        <v>46.3856</v>
+        <v>47.2612</v>
       </c>
     </row>
     <row r="76">
@@ -6560,19 +6560,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>14.5862</v>
+        <v>14.4854</v>
       </c>
       <c r="C76" t="n">
-        <v>16.6135</v>
+        <v>16.5788</v>
       </c>
       <c r="D76" t="n">
-        <v>54.1687</v>
+        <v>54.3463</v>
       </c>
       <c r="E76" t="n">
-        <v>14.314</v>
+        <v>14.8196</v>
       </c>
       <c r="F76" t="n">
-        <v>46.139</v>
+        <v>46.9232</v>
       </c>
     </row>
     <row r="77">
@@ -6580,19 +6580,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>14.3032</v>
+        <v>14.1958</v>
       </c>
       <c r="C77" t="n">
-        <v>16.5487</v>
+        <v>16.5219</v>
       </c>
       <c r="D77" t="n">
-        <v>54.085</v>
+        <v>54.5084</v>
       </c>
       <c r="E77" t="n">
-        <v>14.0999</v>
+        <v>14.5895</v>
       </c>
       <c r="F77" t="n">
-        <v>45.7169</v>
+        <v>46.8867</v>
       </c>
     </row>
     <row r="78">
@@ -6600,19 +6600,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>14.0034</v>
+        <v>13.8668</v>
       </c>
       <c r="C78" t="n">
-        <v>16.4482</v>
+        <v>16.4198</v>
       </c>
       <c r="D78" t="n">
-        <v>57.2072</v>
+        <v>57.4385</v>
       </c>
       <c r="E78" t="n">
-        <v>17.5696</v>
+        <v>17.9703</v>
       </c>
       <c r="F78" t="n">
-        <v>50.455</v>
+        <v>51.2617</v>
       </c>
     </row>
     <row r="79">
@@ -6620,19 +6620,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>13.5821</v>
+        <v>13.5131</v>
       </c>
       <c r="C79" t="n">
-        <v>18.0301</v>
+        <v>17.9745</v>
       </c>
       <c r="D79" t="n">
-        <v>57.1822</v>
+        <v>57.3228</v>
       </c>
       <c r="E79" t="n">
-        <v>17.0461</v>
+        <v>18.5671</v>
       </c>
       <c r="F79" t="n">
-        <v>50.0907</v>
+        <v>50.8954</v>
       </c>
     </row>
     <row r="80">
@@ -6640,19 +6640,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>13.1055</v>
+        <v>13.0941</v>
       </c>
       <c r="C80" t="n">
-        <v>17.8592</v>
+        <v>17.7936</v>
       </c>
       <c r="D80" t="n">
-        <v>57.0833</v>
+        <v>57.292</v>
       </c>
       <c r="E80" t="n">
-        <v>16.6519</v>
+        <v>18.1467</v>
       </c>
       <c r="F80" t="n">
-        <v>49.8319</v>
+        <v>50.3245</v>
       </c>
     </row>
     <row r="81">
@@ -6660,19 +6660,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>17.6363</v>
+        <v>17.646</v>
       </c>
       <c r="C81" t="n">
-        <v>17.6783</v>
+        <v>17.637</v>
       </c>
       <c r="D81" t="n">
-        <v>57.1265</v>
+        <v>57.2891</v>
       </c>
       <c r="E81" t="n">
-        <v>16.3725</v>
+        <v>17.0073</v>
       </c>
       <c r="F81" t="n">
-        <v>49.3311</v>
+        <v>50.3669</v>
       </c>
     </row>
     <row r="82">
@@ -6680,19 +6680,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>17.3376</v>
+        <v>17.3418</v>
       </c>
       <c r="C82" t="n">
-        <v>17.5236</v>
+        <v>17.481</v>
       </c>
       <c r="D82" t="n">
-        <v>56.9856</v>
+        <v>57.1848</v>
       </c>
       <c r="E82" t="n">
-        <v>16.1626</v>
+        <v>16.7768</v>
       </c>
       <c r="F82" t="n">
-        <v>48.9606</v>
+        <v>49.7689</v>
       </c>
     </row>
     <row r="83">
@@ -6700,19 +6700,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>17.0151</v>
+        <v>16.9886</v>
       </c>
       <c r="C83" t="n">
-        <v>17.373</v>
+        <v>17.3341</v>
       </c>
       <c r="D83" t="n">
-        <v>57.072</v>
+        <v>57.2093</v>
       </c>
       <c r="E83" t="n">
-        <v>15.9007</v>
+        <v>16.5045</v>
       </c>
       <c r="F83" t="n">
-        <v>48.6393</v>
+        <v>49.3646</v>
       </c>
     </row>
     <row r="84">
@@ -6720,19 +6720,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>16.6636</v>
+        <v>16.6304</v>
       </c>
       <c r="C84" t="n">
-        <v>17.2504</v>
+        <v>17.2174</v>
       </c>
       <c r="D84" t="n">
-        <v>60.3887</v>
+        <v>60.912</v>
       </c>
       <c r="E84" t="n">
-        <v>15.6921</v>
+        <v>16.2607</v>
       </c>
       <c r="F84" t="n">
-        <v>52.9923</v>
+        <v>54.0435</v>
       </c>
     </row>
     <row r="85">
@@ -6740,19 +6740,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>16.2957</v>
+        <v>16.2563</v>
       </c>
       <c r="C85" t="n">
-        <v>17.1092</v>
+        <v>17.0819</v>
       </c>
       <c r="D85" t="n">
-        <v>60.4072</v>
+        <v>60.8434</v>
       </c>
       <c r="E85" t="n">
-        <v>15.4516</v>
+        <v>16.0596</v>
       </c>
       <c r="F85" t="n">
-        <v>52.9625</v>
+        <v>53.7713</v>
       </c>
     </row>
     <row r="86">
@@ -6760,19 +6760,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>15.9365</v>
+        <v>15.8888</v>
       </c>
       <c r="C86" t="n">
-        <v>17.0079</v>
+        <v>16.9855</v>
       </c>
       <c r="D86" t="n">
-        <v>60.5701</v>
+        <v>60.8232</v>
       </c>
       <c r="E86" t="n">
-        <v>15.2359</v>
+        <v>15.804</v>
       </c>
       <c r="F86" t="n">
-        <v>52.4847</v>
+        <v>53.4631</v>
       </c>
     </row>
     <row r="87">
@@ -6780,19 +6780,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>15.5953</v>
+        <v>15.5263</v>
       </c>
       <c r="C87" t="n">
-        <v>16.89</v>
+        <v>16.8781</v>
       </c>
       <c r="D87" t="n">
-        <v>60.547</v>
+        <v>60.8886</v>
       </c>
       <c r="E87" t="n">
-        <v>15.0439</v>
+        <v>15.5606</v>
       </c>
       <c r="F87" t="n">
-        <v>52.2012</v>
+        <v>52.9809</v>
       </c>
     </row>
     <row r="88">
@@ -6800,19 +6800,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>15.2556</v>
+        <v>15.1768</v>
       </c>
       <c r="C88" t="n">
-        <v>16.7903</v>
+        <v>16.7773</v>
       </c>
       <c r="D88" t="n">
-        <v>60.5034</v>
+        <v>60.7027</v>
       </c>
       <c r="E88" t="n">
-        <v>14.8547</v>
+        <v>15.3475</v>
       </c>
       <c r="F88" t="n">
-        <v>52.0451</v>
+        <v>53.0896</v>
       </c>
     </row>
     <row r="89">
@@ -6820,19 +6820,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>14.9392</v>
+        <v>14.8631</v>
       </c>
       <c r="C89" t="n">
-        <v>16.6889</v>
+        <v>16.6816</v>
       </c>
       <c r="D89" t="n">
-        <v>60.4519</v>
+        <v>60.6635</v>
       </c>
       <c r="E89" t="n">
-        <v>14.6242</v>
+        <v>15.1315</v>
       </c>
       <c r="F89" t="n">
-        <v>51.7012</v>
+        <v>52.5767</v>
       </c>
     </row>
     <row r="90">
@@ -6840,19 +6840,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>14.639</v>
+        <v>14.5646</v>
       </c>
       <c r="C90" t="n">
-        <v>16.617</v>
+        <v>16.6089</v>
       </c>
       <c r="D90" t="n">
-        <v>60.4102</v>
+        <v>60.7105</v>
       </c>
       <c r="E90" t="n">
-        <v>14.3688</v>
+        <v>14.8971</v>
       </c>
       <c r="F90" t="n">
-        <v>51.3764</v>
+        <v>52.2714</v>
       </c>
     </row>
     <row r="91">
@@ -6860,19 +6860,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>14.3618</v>
+        <v>14.2647</v>
       </c>
       <c r="C91" t="n">
-        <v>16.5281</v>
+        <v>16.5081</v>
       </c>
       <c r="D91" t="n">
-        <v>60.4371</v>
+        <v>60.7585</v>
       </c>
       <c r="E91" t="n">
-        <v>14.1507</v>
+        <v>14.6394</v>
       </c>
       <c r="F91" t="n">
-        <v>51.0134</v>
+        <v>51.9015</v>
       </c>
     </row>
     <row r="92">
@@ -6880,19 +6880,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>14.0599</v>
+        <v>13.921</v>
       </c>
       <c r="C92" t="n">
-        <v>16.4568</v>
+        <v>16.4438</v>
       </c>
       <c r="D92" t="n">
-        <v>60.5445</v>
+        <v>60.9405</v>
       </c>
       <c r="E92" t="n">
-        <v>17.9074</v>
+        <v>18.8865</v>
       </c>
       <c r="F92" t="n">
-        <v>55.2104</v>
+        <v>56.3488</v>
       </c>
     </row>
     <row r="93">
@@ -6900,19 +6900,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>13.7069</v>
+        <v>13.5611</v>
       </c>
       <c r="C93" t="n">
-        <v>16.3893</v>
+        <v>16.3817</v>
       </c>
       <c r="D93" t="n">
-        <v>60.4672</v>
+        <v>61.0358</v>
       </c>
       <c r="E93" t="n">
-        <v>17.1396</v>
+        <v>17.8882</v>
       </c>
       <c r="F93" t="n">
-        <v>54.8085</v>
+        <v>55.9305</v>
       </c>
     </row>
     <row r="94">
@@ -6920,19 +6920,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>13.2531</v>
+        <v>13.1463</v>
       </c>
       <c r="C94" t="n">
-        <v>17.8975</v>
+        <v>17.8413</v>
       </c>
       <c r="D94" t="n">
-        <v>60.3645</v>
+        <v>61.0053</v>
       </c>
       <c r="E94" t="n">
-        <v>16.9497</v>
+        <v>17.7045</v>
       </c>
       <c r="F94" t="n">
-        <v>54.4775</v>
+        <v>55.4928</v>
       </c>
     </row>
     <row r="95">
@@ -6940,19 +6940,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>17.6938</v>
+        <v>17.7124</v>
       </c>
       <c r="C95" t="n">
-        <v>17.7229</v>
+        <v>17.6786</v>
       </c>
       <c r="D95" t="n">
-        <v>60.365</v>
+        <v>60.7719</v>
       </c>
       <c r="E95" t="n">
-        <v>16.4574</v>
+        <v>17.2172</v>
       </c>
       <c r="F95" t="n">
-        <v>54.0405</v>
+        <v>55.1616</v>
       </c>
     </row>
     <row r="96">
@@ -6960,19 +6960,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>17.3836</v>
+        <v>17.3992</v>
       </c>
       <c r="C96" t="n">
-        <v>17.5244</v>
+        <v>17.502</v>
       </c>
       <c r="D96" t="n">
-        <v>60.3348</v>
+        <v>60.8074</v>
       </c>
       <c r="E96" t="n">
-        <v>16.2229</v>
+        <v>19.3865</v>
       </c>
       <c r="F96" t="n">
-        <v>53.7823</v>
+        <v>54.6856</v>
       </c>
     </row>
     <row r="97">
@@ -6980,19 +6980,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>17.0689</v>
+        <v>17.0583</v>
       </c>
       <c r="C97" t="n">
-        <v>17.3923</v>
+        <v>17.3721</v>
       </c>
       <c r="D97" t="n">
-        <v>60.2558</v>
+        <v>60.6663</v>
       </c>
       <c r="E97" t="n">
-        <v>15.9553</v>
+        <v>16.5588</v>
       </c>
       <c r="F97" t="n">
-        <v>53.3501</v>
+        <v>54.4263</v>
       </c>
     </row>
     <row r="98">
@@ -7000,19 +7000,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>16.7338</v>
+        <v>16.7099</v>
       </c>
       <c r="C98" t="n">
-        <v>17.2544</v>
+        <v>17.2292</v>
       </c>
       <c r="D98" t="n">
-        <v>60.2331</v>
+        <v>60.6804</v>
       </c>
       <c r="E98" t="n">
-        <v>15.7378</v>
+        <v>17.0877</v>
       </c>
       <c r="F98" t="n">
-        <v>52.9664</v>
+        <v>53.9264</v>
       </c>
     </row>
     <row r="99">
@@ -7020,19 +7020,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>16.3869</v>
+        <v>16.3319</v>
       </c>
       <c r="C99" t="n">
-        <v>17.1106</v>
+        <v>17.1159</v>
       </c>
       <c r="D99" t="n">
-        <v>60.1681</v>
+        <v>60.6279</v>
       </c>
       <c r="E99" t="n">
-        <v>15.5012</v>
+        <v>16.0569</v>
       </c>
       <c r="F99" t="n">
-        <v>52.7365</v>
+        <v>53.832</v>
       </c>
     </row>
     <row r="100">
@@ -7040,19 +7040,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>16.014</v>
+        <v>15.9612</v>
       </c>
       <c r="C100" t="n">
-        <v>17.0002</v>
+        <v>16.9885</v>
       </c>
       <c r="D100" t="n">
-        <v>60.1985</v>
+        <v>60.5678</v>
       </c>
       <c r="E100" t="n">
-        <v>15.3099</v>
+        <v>16.0423</v>
       </c>
       <c r="F100" t="n">
-        <v>52.6001</v>
+        <v>53.4601</v>
       </c>
     </row>
     <row r="101">
@@ -7060,19 +7060,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>15.652</v>
+        <v>15.5896</v>
       </c>
       <c r="C101" t="n">
-        <v>16.8826</v>
+        <v>16.8725</v>
       </c>
       <c r="D101" t="n">
-        <v>60.1658</v>
+        <v>60.5221</v>
       </c>
       <c r="E101" t="n">
-        <v>15.0933</v>
+        <v>15.6078</v>
       </c>
       <c r="F101" t="n">
-        <v>52.1408</v>
+        <v>53.0953</v>
       </c>
     </row>
     <row r="102">
@@ -7080,19 +7080,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>15.3187</v>
+        <v>15.2489</v>
       </c>
       <c r="C102" t="n">
-        <v>16.7999</v>
+        <v>16.7896</v>
       </c>
       <c r="D102" t="n">
-        <v>60.1588</v>
+        <v>60.5884</v>
       </c>
       <c r="E102" t="n">
-        <v>14.8995</v>
+        <v>15.4032</v>
       </c>
       <c r="F102" t="n">
-        <v>52.0085</v>
+        <v>52.6994</v>
       </c>
     </row>
     <row r="103">
@@ -7100,19 +7100,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>14.997</v>
+        <v>14.9264</v>
       </c>
       <c r="C103" t="n">
-        <v>16.7061</v>
+        <v>16.7177</v>
       </c>
       <c r="D103" t="n">
-        <v>60.0551</v>
+        <v>60.42</v>
       </c>
       <c r="E103" t="n">
-        <v>14.6516</v>
+        <v>15.164</v>
       </c>
       <c r="F103" t="n">
-        <v>51.6414</v>
+        <v>52.7127</v>
       </c>
     </row>
     <row r="104">
@@ -7120,19 +7120,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>14.6939</v>
+        <v>14.6142</v>
       </c>
       <c r="C104" t="n">
-        <v>16.6256</v>
+        <v>16.6069</v>
       </c>
       <c r="D104" t="n">
-        <v>60.0678</v>
+        <v>60.4867</v>
       </c>
       <c r="E104" t="n">
-        <v>14.4275</v>
+        <v>14.9194</v>
       </c>
       <c r="F104" t="n">
-        <v>51.3718</v>
+        <v>52.5186</v>
       </c>
     </row>
     <row r="105">
@@ -7140,19 +7140,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>14.4171</v>
+        <v>14.3054</v>
       </c>
       <c r="C105" t="n">
-        <v>16.5418</v>
+        <v>16.5297</v>
       </c>
       <c r="D105" t="n">
-        <v>60.0773</v>
+        <v>60.4459</v>
       </c>
       <c r="E105" t="n">
-        <v>14.1926</v>
+        <v>14.6895</v>
       </c>
       <c r="F105" t="n">
-        <v>51.0597</v>
+        <v>52.0275</v>
       </c>
     </row>
     <row r="106">
@@ -7160,19 +7160,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>14.1087</v>
+        <v>13.9931</v>
       </c>
       <c r="C106" t="n">
-        <v>16.4853</v>
+        <v>16.4617</v>
       </c>
       <c r="D106" t="n">
-        <v>60.0729</v>
+        <v>60.2739</v>
       </c>
       <c r="E106" t="n">
-        <v>13.9541</v>
+        <v>14.448</v>
       </c>
       <c r="F106" t="n">
-        <v>50.8791</v>
+        <v>51.6896</v>
       </c>
     </row>
     <row r="107">
@@ -7180,19 +7180,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>13.7649</v>
+        <v>13.7042</v>
       </c>
       <c r="C107" t="n">
-        <v>16.4001</v>
+        <v>16.4128</v>
       </c>
       <c r="D107" t="n">
-        <v>58.7758</v>
+        <v>59.279</v>
       </c>
       <c r="E107" t="n">
-        <v>17.5013</v>
+        <v>19.9887</v>
       </c>
       <c r="F107" t="n">
-        <v>55.0659</v>
+        <v>55.6845</v>
       </c>
     </row>
     <row r="108">
@@ -7200,19 +7200,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>13.3467</v>
+        <v>13.243</v>
       </c>
       <c r="C108" t="n">
-        <v>17.8972</v>
+        <v>17.8635</v>
       </c>
       <c r="D108" t="n">
-        <v>58.7737</v>
+        <v>59.1902</v>
       </c>
       <c r="E108" t="n">
-        <v>17.1873</v>
+        <v>19.2513</v>
       </c>
       <c r="F108" t="n">
-        <v>54.6004</v>
+        <v>55.517</v>
       </c>
     </row>
     <row r="109">
@@ -7220,19 +7220,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>12.8403</v>
+        <v>12.6981</v>
       </c>
       <c r="C109" t="n">
-        <v>17.7147</v>
+        <v>17.6922</v>
       </c>
       <c r="D109" t="n">
-        <v>58.9277</v>
+        <v>59.3018</v>
       </c>
       <c r="E109" t="n">
-        <v>16.9929</v>
+        <v>18.439</v>
       </c>
       <c r="F109" t="n">
-        <v>54.1962</v>
+        <v>55.1568</v>
       </c>
     </row>
     <row r="110">
@@ -7240,19 +7240,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>17.437</v>
+        <v>17.4697</v>
       </c>
       <c r="C110" t="n">
-        <v>17.5474</v>
+        <v>17.5189</v>
       </c>
       <c r="D110" t="n">
-        <v>58.9469</v>
+        <v>59.2769</v>
       </c>
       <c r="E110" t="n">
-        <v>16.3848</v>
+        <v>17.8896</v>
       </c>
       <c r="F110" t="n">
-        <v>53.7838</v>
+        <v>54.6871</v>
       </c>
     </row>
     <row r="111">
@@ -7260,19 +7260,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>17.1726</v>
+        <v>17.1389</v>
       </c>
       <c r="C111" t="n">
-        <v>17.4135</v>
+        <v>17.412</v>
       </c>
       <c r="D111" t="n">
-        <v>59.0227</v>
+        <v>59.3491</v>
       </c>
       <c r="E111" t="n">
-        <v>16.1817</v>
+        <v>17.3122</v>
       </c>
       <c r="F111" t="n">
-        <v>53.4102</v>
+        <v>54.5651</v>
       </c>
     </row>
     <row r="112">
@@ -7280,19 +7280,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>16.7944</v>
+        <v>16.7842</v>
       </c>
       <c r="C112" t="n">
-        <v>17.2709</v>
+        <v>17.2596</v>
       </c>
       <c r="D112" t="n">
-        <v>59.1088</v>
+        <v>59.4189</v>
       </c>
       <c r="E112" t="n">
-        <v>15.8733</v>
+        <v>18.3389</v>
       </c>
       <c r="F112" t="n">
-        <v>53.235</v>
+        <v>54.1146</v>
       </c>
     </row>
     <row r="113">
@@ -7300,19 +7300,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>16.4292</v>
+        <v>16.4196</v>
       </c>
       <c r="C113" t="n">
-        <v>17.1209</v>
+        <v>17.1537</v>
       </c>
       <c r="D113" t="n">
-        <v>59.0817</v>
+        <v>59.4777</v>
       </c>
       <c r="E113" t="n">
-        <v>15.5855</v>
+        <v>16.2313</v>
       </c>
       <c r="F113" t="n">
-        <v>52.9271</v>
+        <v>53.7283</v>
       </c>
     </row>
     <row r="114">
@@ -7320,19 +7320,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>16.0688</v>
+        <v>16.0453</v>
       </c>
       <c r="C114" t="n">
-        <v>17.0205</v>
+        <v>17.0174</v>
       </c>
       <c r="D114" t="n">
-        <v>59.2254</v>
+        <v>59.5869</v>
       </c>
       <c r="E114" t="n">
-        <v>15.3909</v>
+        <v>15.9273</v>
       </c>
       <c r="F114" t="n">
-        <v>52.5556</v>
+        <v>53.4588</v>
       </c>
     </row>
     <row r="115">
@@ -7340,19 +7340,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>15.7201</v>
+        <v>15.678</v>
       </c>
       <c r="C115" t="n">
-        <v>16.9088</v>
+        <v>16.8977</v>
       </c>
       <c r="D115" t="n">
-        <v>59.2864</v>
+        <v>59.5844</v>
       </c>
       <c r="E115" t="n">
-        <v>15.1744</v>
+        <v>15.6923</v>
       </c>
       <c r="F115" t="n">
-        <v>52.3891</v>
+        <v>53.2742</v>
       </c>
     </row>
     <row r="116">
@@ -7360,19 +7360,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>15.376</v>
+        <v>15.3228</v>
       </c>
       <c r="C116" t="n">
-        <v>16.7983</v>
+        <v>16.8237</v>
       </c>
       <c r="D116" t="n">
-        <v>59.2742</v>
+        <v>59.592</v>
       </c>
       <c r="E116" t="n">
-        <v>14.9608</v>
+        <v>15.46</v>
       </c>
       <c r="F116" t="n">
-        <v>51.8705</v>
+        <v>52.8734</v>
       </c>
     </row>
     <row r="117">
@@ -7380,19 +7380,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>15.0572</v>
+        <v>15.0017</v>
       </c>
       <c r="C117" t="n">
-        <v>16.7123</v>
+        <v>16.7132</v>
       </c>
       <c r="D117" t="n">
-        <v>59.3129</v>
+        <v>59.6108</v>
       </c>
       <c r="E117" t="n">
-        <v>14.7218</v>
+        <v>15.2136</v>
       </c>
       <c r="F117" t="n">
-        <v>51.4402</v>
+        <v>52.5489</v>
       </c>
     </row>
     <row r="118">
@@ -7400,19 +7400,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>14.7446</v>
+        <v>14.678</v>
       </c>
       <c r="C118" t="n">
-        <v>16.6394</v>
+        <v>16.6073</v>
       </c>
       <c r="D118" t="n">
-        <v>59.3716</v>
+        <v>59.6318</v>
       </c>
       <c r="E118" t="n">
-        <v>14.4859</v>
+        <v>14.9537</v>
       </c>
       <c r="F118" t="n">
-        <v>51.3676</v>
+        <v>52.2471</v>
       </c>
     </row>
     <row r="119">
@@ -7420,19 +7420,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>14.4694</v>
+        <v>14.3614</v>
       </c>
       <c r="C119" t="n">
-        <v>16.553</v>
+        <v>16.5357</v>
       </c>
       <c r="D119" t="n">
-        <v>59.3338</v>
+        <v>59.6077</v>
       </c>
       <c r="E119" t="n">
-        <v>14.2597</v>
+        <v>14.7461</v>
       </c>
       <c r="F119" t="n">
-        <v>51.3604</v>
+        <v>51.8759</v>
       </c>
     </row>
     <row r="120">
@@ -7440,19 +7440,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>14.169</v>
+        <v>14.068</v>
       </c>
       <c r="C120" t="n">
-        <v>16.4882</v>
+        <v>16.4525</v>
       </c>
       <c r="D120" t="n">
-        <v>59.3157</v>
+        <v>59.5326</v>
       </c>
       <c r="E120" t="n">
-        <v>13.9883</v>
+        <v>14.5024</v>
       </c>
       <c r="F120" t="n">
-        <v>50.6178</v>
+        <v>51.9329</v>
       </c>
     </row>
     <row r="121">
@@ -7460,19 +7460,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>13.8493</v>
+        <v>13.7191</v>
       </c>
       <c r="C121" t="n">
-        <v>16.4033</v>
+        <v>16.4037</v>
       </c>
       <c r="D121" t="n">
-        <v>61.1998</v>
+        <v>61.6092</v>
       </c>
       <c r="E121" t="n">
-        <v>17.9374</v>
+        <v>19.8894</v>
       </c>
       <c r="F121" t="n">
-        <v>54.893</v>
+        <v>55.7508</v>
       </c>
     </row>
     <row r="122">
@@ -7480,19 +7480,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>13.4505</v>
+        <v>13.3319</v>
       </c>
       <c r="C122" t="n">
-        <v>17.9437</v>
+        <v>17.8832</v>
       </c>
       <c r="D122" t="n">
-        <v>61.0933</v>
+        <v>61.5314</v>
       </c>
       <c r="E122" t="n">
-        <v>17.1086</v>
+        <v>19.2858</v>
       </c>
       <c r="F122" t="n">
-        <v>54.4761</v>
+        <v>55.382</v>
       </c>
     </row>
     <row r="123">
@@ -7500,19 +7500,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>12.9439</v>
+        <v>12.8083</v>
       </c>
       <c r="C123" t="n">
-        <v>17.7608</v>
+        <v>17.7221</v>
       </c>
       <c r="D123" t="n">
-        <v>60.9468</v>
+        <v>61.3932</v>
       </c>
       <c r="E123" t="n">
-        <v>16.9265</v>
+        <v>18.3326</v>
       </c>
       <c r="F123" t="n">
-        <v>54.1299</v>
+        <v>55.0947</v>
       </c>
     </row>
     <row r="124">
@@ -7520,19 +7520,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>17.4967</v>
+        <v>17.5328</v>
       </c>
       <c r="C124" t="n">
-        <v>17.5844</v>
+        <v>17.5723</v>
       </c>
       <c r="D124" t="n">
-        <v>60.9985</v>
+        <v>61.2959</v>
       </c>
       <c r="E124" t="n">
-        <v>16.4535</v>
+        <v>19.5608</v>
       </c>
       <c r="F124" t="n">
-        <v>53.7921</v>
+        <v>54.7226</v>
       </c>
     </row>
     <row r="125">
@@ -7540,19 +7540,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>17.2127</v>
+        <v>17.1978</v>
       </c>
       <c r="C125" t="n">
-        <v>17.4348</v>
+        <v>17.376</v>
       </c>
       <c r="D125" t="n">
-        <v>60.8885</v>
+        <v>61.2624</v>
       </c>
       <c r="E125" t="n">
-        <v>16.2449</v>
+        <v>18.3935</v>
       </c>
       <c r="F125" t="n">
-        <v>53.5884</v>
+        <v>54.3155</v>
       </c>
     </row>
     <row r="126">
@@ -7560,19 +7560,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>16.881</v>
+        <v>16.8639</v>
       </c>
       <c r="C126" t="n">
-        <v>17.2994</v>
+        <v>17.2542</v>
       </c>
       <c r="D126" t="n">
-        <v>60.7538</v>
+        <v>61.1253</v>
       </c>
       <c r="E126" t="n">
-        <v>16.005</v>
+        <v>17.003</v>
       </c>
       <c r="F126" t="n">
-        <v>53.1812</v>
+        <v>54.0283</v>
       </c>
     </row>
     <row r="127">
@@ -7580,19 +7580,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>16.5289</v>
+        <v>16.4785</v>
       </c>
       <c r="C127" t="n">
-        <v>17.1585</v>
+        <v>17.1255</v>
       </c>
       <c r="D127" t="n">
-        <v>60.7281</v>
+        <v>61.0607</v>
       </c>
       <c r="E127" t="n">
-        <v>15.6707</v>
+        <v>16.6689</v>
       </c>
       <c r="F127" t="n">
-        <v>52.8255</v>
+        <v>53.7918</v>
       </c>
     </row>
     <row r="128">
@@ -7600,19 +7600,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>16.1455</v>
+        <v>16.1034</v>
       </c>
       <c r="C128" t="n">
-        <v>17.0391</v>
+        <v>17.0219</v>
       </c>
       <c r="D128" t="n">
-        <v>60.6957</v>
+        <v>61.1297</v>
       </c>
       <c r="E128" t="n">
-        <v>15.435</v>
+        <v>16.5089</v>
       </c>
       <c r="F128" t="n">
-        <v>52.527</v>
+        <v>53.5088</v>
       </c>
     </row>
     <row r="129">
@@ -7620,19 +7620,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>15.788</v>
+        <v>15.7417</v>
       </c>
       <c r="C129" t="n">
-        <v>16.9436</v>
+        <v>16.9089</v>
       </c>
       <c r="D129" t="n">
-        <v>60.6325</v>
+        <v>60.9436</v>
       </c>
       <c r="E129" t="n">
-        <v>15.2458</v>
+        <v>15.8168</v>
       </c>
       <c r="F129" t="n">
-        <v>52.3082</v>
+        <v>53.1618</v>
       </c>
     </row>
     <row r="130">
@@ -7640,19 +7640,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>15.4431</v>
+        <v>15.3865</v>
       </c>
       <c r="C130" t="n">
-        <v>16.8094</v>
+        <v>16.8259</v>
       </c>
       <c r="D130" t="n">
-        <v>60.5167</v>
+        <v>60.9515</v>
       </c>
       <c r="E130" t="n">
-        <v>14.9853</v>
+        <v>15.5496</v>
       </c>
       <c r="F130" t="n">
-        <v>52.1672</v>
+        <v>52.7565</v>
       </c>
     </row>
     <row r="131">
@@ -7660,19 +7660,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>15.1215</v>
+        <v>15.0604</v>
       </c>
       <c r="C131" t="n">
-        <v>16.7189</v>
+        <v>16.7069</v>
       </c>
       <c r="D131" t="n">
-        <v>60.5947</v>
+        <v>61.1319</v>
       </c>
       <c r="E131" t="n">
-        <v>14.7923</v>
+        <v>15.3077</v>
       </c>
       <c r="F131" t="n">
-        <v>51.5889</v>
+        <v>52.7733</v>
       </c>
     </row>
     <row r="132">
@@ -7680,19 +7680,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>14.8008</v>
+        <v>14.8237</v>
       </c>
       <c r="C132" t="n">
-        <v>16.6356</v>
+        <v>16.7312</v>
       </c>
       <c r="D132" t="n">
-        <v>60.5329</v>
+        <v>61.0313</v>
       </c>
       <c r="E132" t="n">
-        <v>14.53</v>
+        <v>15.0144</v>
       </c>
       <c r="F132" t="n">
-        <v>51.3674</v>
+        <v>52.2446</v>
       </c>
     </row>
     <row r="133">
@@ -7700,19 +7700,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>14.506</v>
+        <v>14.4311</v>
       </c>
       <c r="C133" t="n">
-        <v>16.5528</v>
+        <v>16.5681</v>
       </c>
       <c r="D133" t="n">
-        <v>60.4002</v>
+        <v>60.7391</v>
       </c>
       <c r="E133" t="n">
-        <v>14.2836</v>
+        <v>14.7896</v>
       </c>
       <c r="F133" t="n">
-        <v>51.1215</v>
+        <v>51.698</v>
       </c>
     </row>
     <row r="134">
@@ -7720,19 +7720,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.2254</v>
+        <v>14.1134</v>
       </c>
       <c r="C134" t="n">
-        <v>16.4773</v>
+        <v>16.4698</v>
       </c>
       <c r="D134" t="n">
-        <v>60.4117</v>
+        <v>60.6666</v>
       </c>
       <c r="E134" t="n">
-        <v>14.0432</v>
+        <v>14.5344</v>
       </c>
       <c r="F134" t="n">
-        <v>50.7876</v>
+        <v>51.5156</v>
       </c>
     </row>
     <row r="135">
@@ -7740,19 +7740,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>13.9111</v>
+        <v>13.7839</v>
       </c>
       <c r="C135" t="n">
-        <v>16.4129</v>
+        <v>16.4014</v>
       </c>
       <c r="D135" t="n">
-        <v>61.8142</v>
+        <v>62.1833</v>
       </c>
       <c r="E135" t="n">
-        <v>18.1122</v>
+        <v>20.7501</v>
       </c>
       <c r="F135" t="n">
-        <v>54.9827</v>
+        <v>55.543</v>
       </c>
     </row>
     <row r="136">
@@ -7760,19 +7760,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>13.5433</v>
+        <v>13.409</v>
       </c>
       <c r="C136" t="n">
-        <v>17.972</v>
+        <v>17.9085</v>
       </c>
       <c r="D136" t="n">
-        <v>61.5245</v>
+        <v>61.9955</v>
       </c>
       <c r="E136" t="n">
-        <v>17.6917</v>
+        <v>19.5655</v>
       </c>
       <c r="F136" t="n">
-        <v>54.5476</v>
+        <v>55.1847</v>
       </c>
     </row>
     <row r="137">
@@ -7780,19 +7780,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>13.07</v>
+        <v>12.9521</v>
       </c>
       <c r="C137" t="n">
-        <v>17.799</v>
+        <v>17.7532</v>
       </c>
       <c r="D137" t="n">
-        <v>61.4455</v>
+        <v>61.7764</v>
       </c>
       <c r="E137" t="n">
-        <v>17.0416</v>
+        <v>18.6134</v>
       </c>
       <c r="F137" t="n">
-        <v>54.2224</v>
+        <v>54.7313</v>
       </c>
     </row>
     <row r="138">
@@ -7800,19 +7800,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>17.611</v>
+        <v>17.6015</v>
       </c>
       <c r="C138" t="n">
-        <v>17.6395</v>
+        <v>17.5682</v>
       </c>
       <c r="D138" t="n">
-        <v>61.3415</v>
+        <v>61.7821</v>
       </c>
       <c r="E138" t="n">
-        <v>16.7115</v>
+        <v>18.2308</v>
       </c>
       <c r="F138" t="n">
-        <v>53.7257</v>
+        <v>54.4708</v>
       </c>
     </row>
     <row r="139">
@@ -7820,19 +7820,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>17.3098</v>
+        <v>17.274</v>
       </c>
       <c r="C139" t="n">
-        <v>17.4749</v>
+        <v>17.3978</v>
       </c>
       <c r="D139" t="n">
-        <v>61.1975</v>
+        <v>61.4905</v>
       </c>
       <c r="E139" t="n">
-        <v>16.2402</v>
+        <v>17.7418</v>
       </c>
       <c r="F139" t="n">
-        <v>53.5169</v>
+        <v>54.0349</v>
       </c>
     </row>
     <row r="140">
@@ -7840,19 +7840,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>16.9743</v>
+        <v>16.9335</v>
       </c>
       <c r="C140" t="n">
-        <v>17.3245</v>
+        <v>17.2714</v>
       </c>
       <c r="D140" t="n">
-        <v>61.1148</v>
+        <v>61.5684</v>
       </c>
       <c r="E140" t="n">
-        <v>16.0057</v>
+        <v>18.2855</v>
       </c>
       <c r="F140" t="n">
-        <v>53.1637</v>
+        <v>53.843</v>
       </c>
     </row>
     <row r="141">
@@ -7860,19 +7860,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>16.6274</v>
+        <v>16.5678</v>
       </c>
       <c r="C141" t="n">
-        <v>17.1797</v>
+        <v>17.1551</v>
       </c>
       <c r="D141" t="n">
-        <v>61.0771</v>
+        <v>61.4408</v>
       </c>
       <c r="E141" t="n">
-        <v>15.7711</v>
+        <v>16.2968</v>
       </c>
       <c r="F141" t="n">
-        <v>52.8556</v>
+        <v>53.5811</v>
       </c>
     </row>
     <row r="142">
@@ -7880,19 +7880,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>16.2443</v>
+        <v>16.1878</v>
       </c>
       <c r="C142" t="n">
-        <v>17.0733</v>
+        <v>17.0378</v>
       </c>
       <c r="D142" t="n">
-        <v>61.065</v>
+        <v>61.3926</v>
       </c>
       <c r="E142" t="n">
-        <v>15.6084</v>
+        <v>16.1327</v>
       </c>
       <c r="F142" t="n">
-        <v>52.4079</v>
+        <v>53.1545</v>
       </c>
     </row>
     <row r="143">
@@ -7900,19 +7900,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>15.8747</v>
+        <v>15.8387</v>
       </c>
       <c r="C143" t="n">
-        <v>16.9426</v>
+        <v>16.9241</v>
       </c>
       <c r="D143" t="n">
-        <v>60.9662</v>
+        <v>61.3106</v>
       </c>
       <c r="E143" t="n">
-        <v>15.2802</v>
+        <v>16.4086</v>
       </c>
       <c r="F143" t="n">
-        <v>52.2603</v>
+        <v>52.9201</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Running erasure.xlsx
+++ b/vs-x64/Running erasure.xlsx
@@ -5080,19 +5080,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>14.4771</v>
+        <v>14.4743</v>
       </c>
       <c r="C2" t="n">
-        <v>15.0101</v>
+        <v>14.9591</v>
       </c>
       <c r="D2" t="n">
-        <v>41.9478</v>
+        <v>41.9952</v>
       </c>
       <c r="E2" t="n">
-        <v>14.1638</v>
+        <v>14.2945</v>
       </c>
       <c r="F2" t="n">
-        <v>35.5457</v>
+        <v>35.5566</v>
       </c>
     </row>
     <row r="3">
@@ -5100,19 +5100,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>14.303</v>
+        <v>14.1469</v>
       </c>
       <c r="C3" t="n">
-        <v>15.0783</v>
+        <v>15.0749</v>
       </c>
       <c r="D3" t="n">
-        <v>41.9602</v>
+        <v>41.9813</v>
       </c>
       <c r="E3" t="n">
-        <v>14.1283</v>
+        <v>14.0936</v>
       </c>
       <c r="F3" t="n">
-        <v>35.1585</v>
+        <v>35.1442</v>
       </c>
     </row>
     <row r="4">
@@ -5120,19 +5120,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>13.9407</v>
+        <v>13.8607</v>
       </c>
       <c r="C4" t="n">
-        <v>15.1551</v>
+        <v>15.1479</v>
       </c>
       <c r="D4" t="n">
-        <v>42.0028</v>
+        <v>42.03</v>
       </c>
       <c r="E4" t="n">
-        <v>13.904</v>
+        <v>13.8859</v>
       </c>
       <c r="F4" t="n">
-        <v>34.7342</v>
+        <v>34.8041</v>
       </c>
     </row>
     <row r="5">
@@ -5140,19 +5140,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>13.8434</v>
+        <v>13.7655</v>
       </c>
       <c r="C5" t="n">
-        <v>15.1379</v>
+        <v>15.0779</v>
       </c>
       <c r="D5" t="n">
-        <v>41.9078</v>
+        <v>42.0191</v>
       </c>
       <c r="E5" t="n">
-        <v>13.709</v>
+        <v>13.6789</v>
       </c>
       <c r="F5" t="n">
-        <v>34.983</v>
+        <v>34.7845</v>
       </c>
     </row>
     <row r="6">
@@ -5160,19 +5160,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>13.3885</v>
+        <v>13.4484</v>
       </c>
       <c r="C6" t="n">
-        <v>15.2178</v>
+        <v>15.1581</v>
       </c>
       <c r="D6" t="n">
-        <v>41.9319</v>
+        <v>42.095</v>
       </c>
       <c r="E6" t="n">
-        <v>13.5016</v>
+        <v>13.533</v>
       </c>
       <c r="F6" t="n">
-        <v>34.4106</v>
+        <v>34.6114</v>
       </c>
     </row>
     <row r="7">
@@ -5180,19 +5180,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>13.3542</v>
+        <v>13.0809</v>
       </c>
       <c r="C7" t="n">
-        <v>15.1591</v>
+        <v>15.1537</v>
       </c>
       <c r="D7" t="n">
-        <v>42.8145</v>
+        <v>42.9579</v>
       </c>
       <c r="E7" t="n">
-        <v>16.8397</v>
+        <v>16.8592</v>
       </c>
       <c r="F7" t="n">
-        <v>38.5922</v>
+        <v>38.3505</v>
       </c>
     </row>
     <row r="8">
@@ -5200,19 +5200,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>12.8376</v>
+        <v>12.9748</v>
       </c>
       <c r="C8" t="n">
-        <v>17.0336</v>
+        <v>16.9426</v>
       </c>
       <c r="D8" t="n">
-        <v>42.8841</v>
+        <v>42.7967</v>
       </c>
       <c r="E8" t="n">
-        <v>16.8034</v>
+        <v>16.4342</v>
       </c>
       <c r="F8" t="n">
-        <v>38.0734</v>
+        <v>38.1904</v>
       </c>
     </row>
     <row r="9">
@@ -5220,19 +5220,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>12.5856</v>
+        <v>12.5144</v>
       </c>
       <c r="C9" t="n">
-        <v>16.9933</v>
+        <v>16.9123</v>
       </c>
       <c r="D9" t="n">
-        <v>43.0152</v>
+        <v>42.7242</v>
       </c>
       <c r="E9" t="n">
-        <v>19.2084</v>
+        <v>17.1198</v>
       </c>
       <c r="F9" t="n">
-        <v>37.84</v>
+        <v>38.027</v>
       </c>
     </row>
     <row r="10">
@@ -5240,19 +5240,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>17.1465</v>
+        <v>17.2287</v>
       </c>
       <c r="C10" t="n">
-        <v>16.755</v>
+        <v>16.7457</v>
       </c>
       <c r="D10" t="n">
-        <v>42.745</v>
+        <v>42.8152</v>
       </c>
       <c r="E10" t="n">
-        <v>16.2452</v>
+        <v>16.1661</v>
       </c>
       <c r="F10" t="n">
-        <v>38.0029</v>
+        <v>37.5716</v>
       </c>
     </row>
     <row r="11">
@@ -5260,19 +5260,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>16.996</v>
+        <v>17.0031</v>
       </c>
       <c r="C11" t="n">
-        <v>16.7674</v>
+        <v>16.7278</v>
       </c>
       <c r="D11" t="n">
-        <v>42.7421</v>
+        <v>42.6606</v>
       </c>
       <c r="E11" t="n">
-        <v>15.9127</v>
+        <v>15.9231</v>
       </c>
       <c r="F11" t="n">
-        <v>37.5266</v>
+        <v>37.4649</v>
       </c>
     </row>
     <row r="12">
@@ -5280,19 +5280,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>16.6576</v>
+        <v>16.701</v>
       </c>
       <c r="C12" t="n">
-        <v>16.6644</v>
+        <v>16.6668</v>
       </c>
       <c r="D12" t="n">
-        <v>42.616</v>
+        <v>42.624</v>
       </c>
       <c r="E12" t="n">
-        <v>15.7157</v>
+        <v>15.673</v>
       </c>
       <c r="F12" t="n">
-        <v>37.4137</v>
+        <v>37.0096</v>
       </c>
     </row>
     <row r="13">
@@ -5300,19 +5300,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>16.3804</v>
+        <v>16.2763</v>
       </c>
       <c r="C13" t="n">
-        <v>16.6069</v>
+        <v>16.6465</v>
       </c>
       <c r="D13" t="n">
-        <v>42.5957</v>
+        <v>42.5846</v>
       </c>
       <c r="E13" t="n">
-        <v>15.4696</v>
+        <v>15.5154</v>
       </c>
       <c r="F13" t="n">
-        <v>36.8478</v>
+        <v>36.8683</v>
       </c>
     </row>
     <row r="14">
@@ -5320,19 +5320,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>16.0408</v>
+        <v>15.8804</v>
       </c>
       <c r="C14" t="n">
-        <v>16.585</v>
+        <v>16.5506</v>
       </c>
       <c r="D14" t="n">
-        <v>42.8402</v>
+        <v>42.67</v>
       </c>
       <c r="E14" t="n">
-        <v>15.9269</v>
+        <v>15.3618</v>
       </c>
       <c r="F14" t="n">
-        <v>36.6931</v>
+        <v>36.5169</v>
       </c>
     </row>
     <row r="15">
@@ -5340,19 +5340,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>15.5427</v>
+        <v>15.5404</v>
       </c>
       <c r="C15" t="n">
-        <v>16.4637</v>
+        <v>16.4349</v>
       </c>
       <c r="D15" t="n">
-        <v>42.648</v>
+        <v>42.6899</v>
       </c>
       <c r="E15" t="n">
-        <v>15.059</v>
+        <v>15.1157</v>
       </c>
       <c r="F15" t="n">
-        <v>36.3073</v>
+        <v>36.5963</v>
       </c>
     </row>
     <row r="16">
@@ -5360,19 +5360,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>15.3015</v>
+        <v>15.2434</v>
       </c>
       <c r="C16" t="n">
-        <v>16.4091</v>
+        <v>16.3586</v>
       </c>
       <c r="D16" t="n">
-        <v>42.6058</v>
+        <v>42.4281</v>
       </c>
       <c r="E16" t="n">
-        <v>14.8901</v>
+        <v>14.946</v>
       </c>
       <c r="F16" t="n">
-        <v>36.2297</v>
+        <v>36.0191</v>
       </c>
     </row>
     <row r="17">
@@ -5380,19 +5380,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>14.9978</v>
+        <v>15.0366</v>
       </c>
       <c r="C17" t="n">
-        <v>16.1689</v>
+        <v>16.2141</v>
       </c>
       <c r="D17" t="n">
-        <v>42.7485</v>
+        <v>42.5884</v>
       </c>
       <c r="E17" t="n">
-        <v>14.7025</v>
+        <v>14.7163</v>
       </c>
       <c r="F17" t="n">
-        <v>35.9601</v>
+        <v>35.6102</v>
       </c>
     </row>
     <row r="18">
@@ -5400,19 +5400,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>14.6447</v>
+        <v>14.701</v>
       </c>
       <c r="C18" t="n">
-        <v>16.0964</v>
+        <v>16.1357</v>
       </c>
       <c r="D18" t="n">
-        <v>42.7463</v>
+        <v>42.5309</v>
       </c>
       <c r="E18" t="n">
-        <v>14.5501</v>
+        <v>14.558</v>
       </c>
       <c r="F18" t="n">
-        <v>35.5897</v>
+        <v>35.577</v>
       </c>
     </row>
     <row r="19">
@@ -5420,19 +5420,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>14.4052</v>
+        <v>14.235</v>
       </c>
       <c r="C19" t="n">
-        <v>16.1193</v>
+        <v>16.1152</v>
       </c>
       <c r="D19" t="n">
-        <v>42.6503</v>
+        <v>42.6102</v>
       </c>
       <c r="E19" t="n">
-        <v>14.2845</v>
+        <v>14.26</v>
       </c>
       <c r="F19" t="n">
-        <v>35.2914</v>
+        <v>35.1099</v>
       </c>
     </row>
     <row r="20">
@@ -5440,19 +5440,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>13.9877</v>
+        <v>14.1313</v>
       </c>
       <c r="C20" t="n">
-        <v>16.1329</v>
+        <v>16.1069</v>
       </c>
       <c r="D20" t="n">
-        <v>42.5903</v>
+        <v>42.6214</v>
       </c>
       <c r="E20" t="n">
-        <v>14.4876</v>
+        <v>14.0572</v>
       </c>
       <c r="F20" t="n">
-        <v>34.6861</v>
+        <v>34.7328</v>
       </c>
     </row>
     <row r="21">
@@ -5460,19 +5460,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>13.6905</v>
+        <v>13.7497</v>
       </c>
       <c r="C21" t="n">
-        <v>15.9322</v>
+        <v>15.94</v>
       </c>
       <c r="D21" t="n">
-        <v>43.4984</v>
+        <v>43.4832</v>
       </c>
       <c r="E21" t="n">
-        <v>17.1486</v>
+        <v>17.179</v>
       </c>
       <c r="F21" t="n">
-        <v>38.8665</v>
+        <v>38.7759</v>
       </c>
     </row>
     <row r="22">
@@ -5480,19 +5480,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>13.4471</v>
+        <v>13.3123</v>
       </c>
       <c r="C22" t="n">
-        <v>17.6428</v>
+        <v>17.6372</v>
       </c>
       <c r="D22" t="n">
-        <v>43.2578</v>
+        <v>43.3513</v>
       </c>
       <c r="E22" t="n">
-        <v>16.8985</v>
+        <v>16.9936</v>
       </c>
       <c r="F22" t="n">
-        <v>38.791</v>
+        <v>38.6501</v>
       </c>
     </row>
     <row r="23">
@@ -5500,19 +5500,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.8719</v>
+        <v>12.8417</v>
       </c>
       <c r="C23" t="n">
-        <v>17.4831</v>
+        <v>17.5312</v>
       </c>
       <c r="D23" t="n">
-        <v>43.3573</v>
+        <v>43.3578</v>
       </c>
       <c r="E23" t="n">
-        <v>16.6403</v>
+        <v>16.7031</v>
       </c>
       <c r="F23" t="n">
-        <v>38.3203</v>
+        <v>38.368</v>
       </c>
     </row>
     <row r="24">
@@ -5520,19 +5520,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>17.4727</v>
+        <v>17.4793</v>
       </c>
       <c r="C24" t="n">
-        <v>17.3625</v>
+        <v>17.337</v>
       </c>
       <c r="D24" t="n">
-        <v>43.4547</v>
+        <v>43.2257</v>
       </c>
       <c r="E24" t="n">
-        <v>16.4042</v>
+        <v>16.3788</v>
       </c>
       <c r="F24" t="n">
-        <v>38.128</v>
+        <v>38.0533</v>
       </c>
     </row>
     <row r="25">
@@ -5540,19 +5540,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>17.1744</v>
+        <v>17.1854</v>
       </c>
       <c r="C25" t="n">
-        <v>17.1992</v>
+        <v>17.2339</v>
       </c>
       <c r="D25" t="n">
-        <v>43.3385</v>
+        <v>43.3091</v>
       </c>
       <c r="E25" t="n">
-        <v>16.1407</v>
+        <v>16.1899</v>
       </c>
       <c r="F25" t="n">
-        <v>37.7389</v>
+        <v>37.7216</v>
       </c>
     </row>
     <row r="26">
@@ -5560,19 +5560,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>16.8496</v>
+        <v>16.8594</v>
       </c>
       <c r="C26" t="n">
-        <v>17.0889</v>
+        <v>17.0766</v>
       </c>
       <c r="D26" t="n">
-        <v>43.4638</v>
+        <v>43.2536</v>
       </c>
       <c r="E26" t="n">
-        <v>15.9412</v>
+        <v>15.9659</v>
       </c>
       <c r="F26" t="n">
-        <v>37.2949</v>
+        <v>37.3004</v>
       </c>
     </row>
     <row r="27">
@@ -5580,19 +5580,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>16.4907</v>
+        <v>16.4863</v>
       </c>
       <c r="C27" t="n">
-        <v>16.9794</v>
+        <v>16.9531</v>
       </c>
       <c r="D27" t="n">
-        <v>43.1702</v>
+        <v>43.3924</v>
       </c>
       <c r="E27" t="n">
-        <v>15.7573</v>
+        <v>15.7534</v>
       </c>
       <c r="F27" t="n">
-        <v>36.8207</v>
+        <v>37.2695</v>
       </c>
     </row>
     <row r="28">
@@ -5600,19 +5600,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>16.1358</v>
+        <v>16.1319</v>
       </c>
       <c r="C28" t="n">
-        <v>16.8608</v>
+        <v>16.881</v>
       </c>
       <c r="D28" t="n">
-        <v>43.1626</v>
+        <v>43.0472</v>
       </c>
       <c r="E28" t="n">
-        <v>15.5612</v>
+        <v>15.5468</v>
       </c>
       <c r="F28" t="n">
-        <v>36.6381</v>
+        <v>36.8865</v>
       </c>
     </row>
     <row r="29">
@@ -5620,19 +5620,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>15.7688</v>
+        <v>15.783</v>
       </c>
       <c r="C29" t="n">
-        <v>16.6855</v>
+        <v>16.7115</v>
       </c>
       <c r="D29" t="n">
-        <v>43.0502</v>
+        <v>43.1328</v>
       </c>
       <c r="E29" t="n">
-        <v>15.3968</v>
+        <v>15.4351</v>
       </c>
       <c r="F29" t="n">
-        <v>36.4643</v>
+        <v>36.5712</v>
       </c>
     </row>
     <row r="30">
@@ -5640,19 +5640,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>15.4737</v>
+        <v>15.4579</v>
       </c>
       <c r="C30" t="n">
-        <v>16.669</v>
+        <v>16.7012</v>
       </c>
       <c r="D30" t="n">
-        <v>43.1299</v>
+        <v>43.2208</v>
       </c>
       <c r="E30" t="n">
-        <v>15.1796</v>
+        <v>15.1829</v>
       </c>
       <c r="F30" t="n">
-        <v>36.4819</v>
+        <v>36.5229</v>
       </c>
     </row>
     <row r="31">
@@ -5660,19 +5660,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>15.1256</v>
+        <v>15.1479</v>
       </c>
       <c r="C31" t="n">
-        <v>16.5788</v>
+        <v>16.5737</v>
       </c>
       <c r="D31" t="n">
-        <v>43.162</v>
+        <v>43.0827</v>
       </c>
       <c r="E31" t="n">
-        <v>14.9952</v>
+        <v>14.9827</v>
       </c>
       <c r="F31" t="n">
-        <v>36.1055</v>
+        <v>36.1181</v>
       </c>
     </row>
     <row r="32">
@@ -5680,19 +5680,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>14.809</v>
+        <v>14.8431</v>
       </c>
       <c r="C32" t="n">
-        <v>16.568</v>
+        <v>16.5564</v>
       </c>
       <c r="D32" t="n">
-        <v>43.1112</v>
+        <v>42.8806</v>
       </c>
       <c r="E32" t="n">
-        <v>14.7605</v>
+        <v>14.8203</v>
       </c>
       <c r="F32" t="n">
-        <v>35.8199</v>
+        <v>35.7488</v>
       </c>
     </row>
     <row r="33">
@@ -5700,19 +5700,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>14.5321</v>
+        <v>14.5281</v>
       </c>
       <c r="C33" t="n">
-        <v>16.4135</v>
+        <v>16.4297</v>
       </c>
       <c r="D33" t="n">
-        <v>42.9075</v>
+        <v>43.0057</v>
       </c>
       <c r="E33" t="n">
-        <v>14.498</v>
+        <v>14.5498</v>
       </c>
       <c r="F33" t="n">
-        <v>35.6114</v>
+        <v>35.5303</v>
       </c>
     </row>
     <row r="34">
@@ -5720,19 +5720,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>14.2482</v>
+        <v>14.2621</v>
       </c>
       <c r="C34" t="n">
-        <v>16.3793</v>
+        <v>16.3561</v>
       </c>
       <c r="D34" t="n">
-        <v>42.8476</v>
+        <v>42.8813</v>
       </c>
       <c r="E34" t="n">
-        <v>14.3492</v>
+        <v>14.3636</v>
       </c>
       <c r="F34" t="n">
-        <v>35.3455</v>
+        <v>35.2562</v>
       </c>
     </row>
     <row r="35">
@@ -5740,19 +5740,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>13.9828</v>
+        <v>13.9127</v>
       </c>
       <c r="C35" t="n">
-        <v>16.3027</v>
+        <v>16.3241</v>
       </c>
       <c r="D35" t="n">
-        <v>43.9724</v>
+        <v>43.9536</v>
       </c>
       <c r="E35" t="n">
-        <v>17.7887</v>
+        <v>17.7782</v>
       </c>
       <c r="F35" t="n">
-        <v>39.7551</v>
+        <v>39.6254</v>
       </c>
     </row>
     <row r="36">
@@ -5760,19 +5760,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>13.6143</v>
+        <v>13.6378</v>
       </c>
       <c r="C36" t="n">
-        <v>16.1962</v>
+        <v>16.225</v>
       </c>
       <c r="D36" t="n">
-        <v>43.8626</v>
+        <v>43.973</v>
       </c>
       <c r="E36" t="n">
-        <v>17.4408</v>
+        <v>17.3839</v>
       </c>
       <c r="F36" t="n">
-        <v>39.2294</v>
+        <v>39.1793</v>
       </c>
     </row>
     <row r="37">
@@ -5780,19 +5780,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.2276</v>
+        <v>13.2016</v>
       </c>
       <c r="C37" t="n">
-        <v>17.7774</v>
+        <v>17.7753</v>
       </c>
       <c r="D37" t="n">
-        <v>43.7448</v>
+        <v>43.6442</v>
       </c>
       <c r="E37" t="n">
-        <v>17.0146</v>
+        <v>17.1115</v>
       </c>
       <c r="F37" t="n">
-        <v>38.7005</v>
+        <v>38.991</v>
       </c>
     </row>
     <row r="38">
@@ -5800,19 +5800,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>17.6151</v>
+        <v>17.607</v>
       </c>
       <c r="C38" t="n">
-        <v>17.5971</v>
+        <v>17.6091</v>
       </c>
       <c r="D38" t="n">
-        <v>43.7494</v>
+        <v>43.6141</v>
       </c>
       <c r="E38" t="n">
-        <v>16.7459</v>
+        <v>16.835</v>
       </c>
       <c r="F38" t="n">
-        <v>38.7607</v>
+        <v>38.3153</v>
       </c>
     </row>
     <row r="39">
@@ -5820,19 +5820,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>17.3268</v>
+        <v>17.3354</v>
       </c>
       <c r="C39" t="n">
-        <v>17.4914</v>
+        <v>17.4867</v>
       </c>
       <c r="D39" t="n">
-        <v>43.6033</v>
+        <v>43.5026</v>
       </c>
       <c r="E39" t="n">
-        <v>16.4775</v>
+        <v>16.4817</v>
       </c>
       <c r="F39" t="n">
-        <v>38.274</v>
+        <v>38.1856</v>
       </c>
     </row>
     <row r="40">
@@ -5840,19 +5840,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>17.0236</v>
+        <v>17.0208</v>
       </c>
       <c r="C40" t="n">
-        <v>17.3721</v>
+        <v>17.3742</v>
       </c>
       <c r="D40" t="n">
-        <v>43.6336</v>
+        <v>43.4575</v>
       </c>
       <c r="E40" t="n">
-        <v>16.2827</v>
+        <v>16.2922</v>
       </c>
       <c r="F40" t="n">
-        <v>37.892</v>
+        <v>37.73</v>
       </c>
     </row>
     <row r="41">
@@ -5860,19 +5860,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>16.6865</v>
+        <v>16.6867</v>
       </c>
       <c r="C41" t="n">
-        <v>17.1661</v>
+        <v>17.1848</v>
       </c>
       <c r="D41" t="n">
-        <v>43.6163</v>
+        <v>43.4961</v>
       </c>
       <c r="E41" t="n">
-        <v>16.0294</v>
+        <v>16.0409</v>
       </c>
       <c r="F41" t="n">
-        <v>37.5523</v>
+        <v>37.4491</v>
       </c>
     </row>
     <row r="42">
@@ -5880,19 +5880,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>16.3263</v>
+        <v>16.3438</v>
       </c>
       <c r="C42" t="n">
-        <v>17.0317</v>
+        <v>17.0355</v>
       </c>
       <c r="D42" t="n">
-        <v>43.6468</v>
+        <v>43.5659</v>
       </c>
       <c r="E42" t="n">
-        <v>15.7985</v>
+        <v>15.8576</v>
       </c>
       <c r="F42" t="n">
-        <v>37.0579</v>
+        <v>37.0615</v>
       </c>
     </row>
     <row r="43">
@@ -5900,19 +5900,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>15.9804</v>
+        <v>15.9778</v>
       </c>
       <c r="C43" t="n">
-        <v>16.9174</v>
+        <v>16.915</v>
       </c>
       <c r="D43" t="n">
-        <v>43.4849</v>
+        <v>43.4339</v>
       </c>
       <c r="E43" t="n">
-        <v>15.6149</v>
+        <v>15.6397</v>
       </c>
       <c r="F43" t="n">
-        <v>36.8014</v>
+        <v>36.8957</v>
       </c>
     </row>
     <row r="44">
@@ -5920,19 +5920,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>15.6049</v>
+        <v>15.616</v>
       </c>
       <c r="C44" t="n">
-        <v>16.8275</v>
+        <v>16.8485</v>
       </c>
       <c r="D44" t="n">
-        <v>43.4154</v>
+        <v>43.3561</v>
       </c>
       <c r="E44" t="n">
-        <v>15.4274</v>
+        <v>15.4546</v>
       </c>
       <c r="F44" t="n">
-        <v>37.2356</v>
+        <v>36.7044</v>
       </c>
     </row>
     <row r="45">
@@ -5940,19 +5940,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>15.2808</v>
+        <v>15.257</v>
       </c>
       <c r="C45" t="n">
-        <v>16.736</v>
+        <v>16.7391</v>
       </c>
       <c r="D45" t="n">
-        <v>43.3618</v>
+        <v>43.183</v>
       </c>
       <c r="E45" t="n">
-        <v>15.1893</v>
+        <v>15.2632</v>
       </c>
       <c r="F45" t="n">
-        <v>36.5487</v>
+        <v>36.3411</v>
       </c>
     </row>
     <row r="46">
@@ -5960,19 +5960,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>14.9485</v>
+        <v>14.9287</v>
       </c>
       <c r="C46" t="n">
-        <v>16.6178</v>
+        <v>16.6221</v>
       </c>
       <c r="D46" t="n">
-        <v>43.3166</v>
+        <v>43.2591</v>
       </c>
       <c r="E46" t="n">
-        <v>15.0427</v>
+        <v>15.0623</v>
       </c>
       <c r="F46" t="n">
-        <v>36.05</v>
+        <v>36.5729</v>
       </c>
     </row>
     <row r="47">
@@ -5980,19 +5980,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>14.6528</v>
+        <v>14.6404</v>
       </c>
       <c r="C47" t="n">
-        <v>16.5489</v>
+        <v>16.5381</v>
       </c>
       <c r="D47" t="n">
-        <v>43.3931</v>
+        <v>43.1326</v>
       </c>
       <c r="E47" t="n">
-        <v>14.8634</v>
+        <v>14.8641</v>
       </c>
       <c r="F47" t="n">
-        <v>36.1987</v>
+        <v>35.7457</v>
       </c>
     </row>
     <row r="48">
@@ -6000,19 +6000,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>14.3969</v>
+        <v>14.3538</v>
       </c>
       <c r="C48" t="n">
-        <v>16.483</v>
+        <v>16.4955</v>
       </c>
       <c r="D48" t="n">
-        <v>43.1756</v>
+        <v>43.1714</v>
       </c>
       <c r="E48" t="n">
-        <v>14.5538</v>
+        <v>14.6071</v>
       </c>
       <c r="F48" t="n">
-        <v>35.5837</v>
+        <v>35.497</v>
       </c>
     </row>
     <row r="49">
@@ -6020,19 +6020,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>14.0483</v>
+        <v>14.0416</v>
       </c>
       <c r="C49" t="n">
-        <v>16.3983</v>
+        <v>16.4144</v>
       </c>
       <c r="D49" t="n">
-        <v>43.268</v>
+        <v>43.1235</v>
       </c>
       <c r="E49" t="n">
-        <v>14.4521</v>
+        <v>14.3734</v>
       </c>
       <c r="F49" t="n">
-        <v>35.3322</v>
+        <v>35.1868</v>
       </c>
     </row>
     <row r="50">
@@ -6040,19 +6040,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>13.7783</v>
+        <v>13.7452</v>
       </c>
       <c r="C50" t="n">
-        <v>16.3293</v>
+        <v>16.3806</v>
       </c>
       <c r="D50" t="n">
-        <v>44.2127</v>
+        <v>44.2824</v>
       </c>
       <c r="E50" t="n">
-        <v>17.6486</v>
+        <v>17.7289</v>
       </c>
       <c r="F50" t="n">
-        <v>39.4126</v>
+        <v>39.6775</v>
       </c>
     </row>
     <row r="51">
@@ -6060,19 +6060,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>13.3336</v>
+        <v>13.3159</v>
       </c>
       <c r="C51" t="n">
-        <v>17.9001</v>
+        <v>17.8547</v>
       </c>
       <c r="D51" t="n">
-        <v>44.1745</v>
+        <v>44.0504</v>
       </c>
       <c r="E51" t="n">
-        <v>17.2883</v>
+        <v>17.291</v>
       </c>
       <c r="F51" t="n">
-        <v>39.0728</v>
+        <v>39.2658</v>
       </c>
     </row>
     <row r="52">
@@ -6080,19 +6080,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>12.7899</v>
+        <v>12.7333</v>
       </c>
       <c r="C52" t="n">
-        <v>17.6954</v>
+        <v>17.6922</v>
       </c>
       <c r="D52" t="n">
-        <v>44.076</v>
+        <v>44.0755</v>
       </c>
       <c r="E52" t="n">
-        <v>19.3947</v>
+        <v>16.9791</v>
       </c>
       <c r="F52" t="n">
-        <v>38.7721</v>
+        <v>38.9742</v>
       </c>
     </row>
     <row r="53">
@@ -6100,19 +6100,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>17.4002</v>
+        <v>17.4074</v>
       </c>
       <c r="C53" t="n">
-        <v>17.5233</v>
+        <v>17.4833</v>
       </c>
       <c r="D53" t="n">
-        <v>44.0528</v>
+        <v>44.0507</v>
       </c>
       <c r="E53" t="n">
-        <v>16.7922</v>
+        <v>16.7715</v>
       </c>
       <c r="F53" t="n">
-        <v>38.347</v>
+        <v>38.7097</v>
       </c>
     </row>
     <row r="54">
@@ -6120,19 +6120,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>17.1066</v>
+        <v>17.1125</v>
       </c>
       <c r="C54" t="n">
-        <v>17.4138</v>
+        <v>17.3858</v>
       </c>
       <c r="D54" t="n">
-        <v>43.9194</v>
+        <v>44.1081</v>
       </c>
       <c r="E54" t="n">
-        <v>16.4896</v>
+        <v>16.5198</v>
       </c>
       <c r="F54" t="n">
-        <v>39.0983</v>
+        <v>38.4058</v>
       </c>
     </row>
     <row r="55">
@@ -6140,19 +6140,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>16.7827</v>
+        <v>16.7818</v>
       </c>
       <c r="C55" t="n">
-        <v>17.269</v>
+        <v>17.2637</v>
       </c>
       <c r="D55" t="n">
-        <v>43.8756</v>
+        <v>43.9076</v>
       </c>
       <c r="E55" t="n">
-        <v>16.2759</v>
+        <v>16.218</v>
       </c>
       <c r="F55" t="n">
-        <v>38.222</v>
+        <v>38.2834</v>
       </c>
     </row>
     <row r="56">
@@ -6160,19 +6160,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>16.425</v>
+        <v>16.4197</v>
       </c>
       <c r="C56" t="n">
-        <v>17.1213</v>
+        <v>17.114</v>
       </c>
       <c r="D56" t="n">
-        <v>43.9462</v>
+        <v>44.1096</v>
       </c>
       <c r="E56" t="n">
-        <v>16.0327</v>
+        <v>15.9884</v>
       </c>
       <c r="F56" t="n">
-        <v>37.487</v>
+        <v>38.3626</v>
       </c>
     </row>
     <row r="57">
@@ -6180,19 +6180,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>16.0581</v>
+        <v>16.0543</v>
       </c>
       <c r="C57" t="n">
-        <v>17.044</v>
+        <v>17.0255</v>
       </c>
       <c r="D57" t="n">
-        <v>43.8966</v>
+        <v>44.0514</v>
       </c>
       <c r="E57" t="n">
-        <v>15.7915</v>
+        <v>15.7943</v>
       </c>
       <c r="F57" t="n">
-        <v>37.7896</v>
+        <v>37.7913</v>
       </c>
     </row>
     <row r="58">
@@ -6200,19 +6200,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>15.6973</v>
+        <v>15.7002</v>
       </c>
       <c r="C58" t="n">
-        <v>16.8805</v>
+        <v>16.88</v>
       </c>
       <c r="D58" t="n">
-        <v>43.8998</v>
+        <v>44.388</v>
       </c>
       <c r="E58" t="n">
-        <v>15.568</v>
+        <v>15.5801</v>
       </c>
       <c r="F58" t="n">
-        <v>37.5109</v>
+        <v>37.9832</v>
       </c>
     </row>
     <row r="59">
@@ -6220,19 +6220,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>15.3652</v>
+        <v>15.3456</v>
       </c>
       <c r="C59" t="n">
-        <v>16.8152</v>
+        <v>16.7834</v>
       </c>
       <c r="D59" t="n">
-        <v>43.8229</v>
+        <v>44.1498</v>
       </c>
       <c r="E59" t="n">
-        <v>15.352</v>
+        <v>15.3662</v>
       </c>
       <c r="F59" t="n">
-        <v>37.8878</v>
+        <v>37.9811</v>
       </c>
     </row>
     <row r="60">
@@ -6240,19 +6240,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>15.0178</v>
+        <v>15.0232</v>
       </c>
       <c r="C60" t="n">
-        <v>16.705</v>
+        <v>16.6944</v>
       </c>
       <c r="D60" t="n">
-        <v>44.1861</v>
+        <v>44.5405</v>
       </c>
       <c r="E60" t="n">
-        <v>15.1814</v>
+        <v>15.1576</v>
       </c>
       <c r="F60" t="n">
-        <v>37.7618</v>
+        <v>37.6057</v>
       </c>
     </row>
     <row r="61">
@@ -6260,19 +6260,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>14.7274</v>
+        <v>14.7195</v>
       </c>
       <c r="C61" t="n">
-        <v>16.6317</v>
+        <v>16.6239</v>
       </c>
       <c r="D61" t="n">
-        <v>44.4159</v>
+        <v>44.2402</v>
       </c>
       <c r="E61" t="n">
-        <v>14.9551</v>
+        <v>14.9446</v>
       </c>
       <c r="F61" t="n">
-        <v>37.1096</v>
+        <v>38.086</v>
       </c>
     </row>
     <row r="62">
@@ -6280,19 +6280,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>14.4247</v>
+        <v>14.4441</v>
       </c>
       <c r="C62" t="n">
-        <v>16.5472</v>
+        <v>16.5743</v>
       </c>
       <c r="D62" t="n">
-        <v>44.6321</v>
+        <v>45.15</v>
       </c>
       <c r="E62" t="n">
-        <v>14.7483</v>
+        <v>14.7035</v>
       </c>
       <c r="F62" t="n">
-        <v>37.4156</v>
+        <v>38.0478</v>
       </c>
     </row>
     <row r="63">
@@ -6300,19 +6300,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>14.1292</v>
+        <v>14.1547</v>
       </c>
       <c r="C63" t="n">
-        <v>16.499</v>
+        <v>16.5035</v>
       </c>
       <c r="D63" t="n">
-        <v>45.6565</v>
+        <v>45.1639</v>
       </c>
       <c r="E63" t="n">
-        <v>14.4956</v>
+        <v>14.5085</v>
       </c>
       <c r="F63" t="n">
-        <v>38.1304</v>
+        <v>38.8214</v>
       </c>
     </row>
     <row r="64">
@@ -6320,19 +6320,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>13.8101</v>
+        <v>13.8519</v>
       </c>
       <c r="C64" t="n">
-        <v>16.4145</v>
+        <v>16.4193</v>
       </c>
       <c r="D64" t="n">
-        <v>50.8731</v>
+        <v>51.0023</v>
       </c>
       <c r="E64" t="n">
-        <v>17.9365</v>
+        <v>19.7453</v>
       </c>
       <c r="F64" t="n">
-        <v>47.3965</v>
+        <v>47.1375</v>
       </c>
     </row>
     <row r="65">
@@ -6340,19 +6340,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>13.4617</v>
+        <v>13.4396</v>
       </c>
       <c r="C65" t="n">
-        <v>17.9077</v>
+        <v>17.9036</v>
       </c>
       <c r="D65" t="n">
-        <v>51.1356</v>
+        <v>51.3046</v>
       </c>
       <c r="E65" t="n">
-        <v>17.5678</v>
+        <v>17.5715</v>
       </c>
       <c r="F65" t="n">
-        <v>47.0408</v>
+        <v>47.3736</v>
       </c>
     </row>
     <row r="66">
@@ -6360,19 +6360,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>12.9578</v>
+        <v>12.987</v>
       </c>
       <c r="C66" t="n">
-        <v>17.7247</v>
+        <v>17.7341</v>
       </c>
       <c r="D66" t="n">
-        <v>51.5389</v>
+        <v>51.3703</v>
       </c>
       <c r="E66" t="n">
-        <v>17.2079</v>
+        <v>17.252</v>
       </c>
       <c r="F66" t="n">
-        <v>47.7176</v>
+        <v>47.6659</v>
       </c>
     </row>
     <row r="67">
@@ -6380,19 +6380,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>17.5367</v>
+        <v>17.5413</v>
       </c>
       <c r="C67" t="n">
-        <v>17.5975</v>
+        <v>17.5904</v>
       </c>
       <c r="D67" t="n">
-        <v>52.0926</v>
+        <v>52.0535</v>
       </c>
       <c r="E67" t="n">
-        <v>16.9554</v>
+        <v>16.9766</v>
       </c>
       <c r="F67" t="n">
-        <v>48.2119</v>
+        <v>47.9033</v>
       </c>
     </row>
     <row r="68">
@@ -6400,19 +6400,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>17.2113</v>
+        <v>17.2345</v>
       </c>
       <c r="C68" t="n">
-        <v>17.4129</v>
+        <v>17.4336</v>
       </c>
       <c r="D68" t="n">
-        <v>52.6832</v>
+        <v>52.4444</v>
       </c>
       <c r="E68" t="n">
-        <v>16.6521</v>
+        <v>16.6997</v>
       </c>
       <c r="F68" t="n">
-        <v>48.5233</v>
+        <v>48.3682</v>
       </c>
     </row>
     <row r="69">
@@ -6420,19 +6420,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>16.8757</v>
+        <v>16.8842</v>
       </c>
       <c r="C69" t="n">
-        <v>17.3035</v>
+        <v>17.295</v>
       </c>
       <c r="D69" t="n">
-        <v>52.8396</v>
+        <v>52.8792</v>
       </c>
       <c r="E69" t="n">
-        <v>16.4589</v>
+        <v>16.4326</v>
       </c>
       <c r="F69" t="n">
-        <v>48.2059</v>
+        <v>48.6989</v>
       </c>
     </row>
     <row r="70">
@@ -6440,19 +6440,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>16.5272</v>
+        <v>16.5452</v>
       </c>
       <c r="C70" t="n">
-        <v>17.1499</v>
+        <v>17.1708</v>
       </c>
       <c r="D70" t="n">
-        <v>53.2744</v>
+        <v>53.2234</v>
       </c>
       <c r="E70" t="n">
-        <v>16.1883</v>
+        <v>16.1828</v>
       </c>
       <c r="F70" t="n">
-        <v>48.387</v>
+        <v>48.4122</v>
       </c>
     </row>
     <row r="71">
@@ -6460,19 +6460,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>16.1447</v>
+        <v>16.1622</v>
       </c>
       <c r="C71" t="n">
-        <v>17.048</v>
+        <v>17.051</v>
       </c>
       <c r="D71" t="n">
-        <v>53.5225</v>
+        <v>53.3832</v>
       </c>
       <c r="E71" t="n">
-        <v>15.9616</v>
+        <v>15.9543</v>
       </c>
       <c r="F71" t="n">
-        <v>47.9976</v>
+        <v>48.2807</v>
       </c>
     </row>
     <row r="72">
@@ -6480,19 +6480,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>15.7864</v>
+        <v>15.8019</v>
       </c>
       <c r="C72" t="n">
-        <v>16.9379</v>
+        <v>16.9428</v>
       </c>
       <c r="D72" t="n">
-        <v>53.6078</v>
+        <v>53.7613</v>
       </c>
       <c r="E72" t="n">
-        <v>15.7492</v>
+        <v>15.7462</v>
       </c>
       <c r="F72" t="n">
-        <v>47.9299</v>
+        <v>48.0893</v>
       </c>
     </row>
     <row r="73">
@@ -6500,19 +6500,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>15.4346</v>
+        <v>15.4388</v>
       </c>
       <c r="C73" t="n">
-        <v>16.8475</v>
+        <v>16.8485</v>
       </c>
       <c r="D73" t="n">
-        <v>54.0419</v>
+        <v>53.9657</v>
       </c>
       <c r="E73" t="n">
-        <v>15.5023</v>
+        <v>15.5026</v>
       </c>
       <c r="F73" t="n">
-        <v>47.8037</v>
+        <v>47.7594</v>
       </c>
     </row>
     <row r="74">
@@ -6520,19 +6520,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>15.1003</v>
+        <v>15.0961</v>
       </c>
       <c r="C74" t="n">
-        <v>16.7569</v>
+        <v>16.7466</v>
       </c>
       <c r="D74" t="n">
-        <v>54.0726</v>
+        <v>54.1572</v>
       </c>
       <c r="E74" t="n">
-        <v>15.2807</v>
+        <v>15.3108</v>
       </c>
       <c r="F74" t="n">
-        <v>47.4745</v>
+        <v>47.6639</v>
       </c>
     </row>
     <row r="75">
@@ -6540,19 +6540,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>14.7868</v>
+        <v>14.7956</v>
       </c>
       <c r="C75" t="n">
-        <v>16.6488</v>
+        <v>16.6546</v>
       </c>
       <c r="D75" t="n">
-        <v>54.3155</v>
+        <v>54.3156</v>
       </c>
       <c r="E75" t="n">
-        <v>15.0479</v>
+        <v>15.0662</v>
       </c>
       <c r="F75" t="n">
-        <v>47.2612</v>
+        <v>47.2275</v>
       </c>
     </row>
     <row r="76">
@@ -6560,19 +6560,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>14.4854</v>
+        <v>14.491</v>
       </c>
       <c r="C76" t="n">
-        <v>16.5788</v>
+        <v>16.5819</v>
       </c>
       <c r="D76" t="n">
-        <v>54.3463</v>
+        <v>54.4768</v>
       </c>
       <c r="E76" t="n">
-        <v>14.8196</v>
+        <v>14.836</v>
       </c>
       <c r="F76" t="n">
-        <v>46.9232</v>
+        <v>47.0009</v>
       </c>
     </row>
     <row r="77">
@@ -6580,19 +6580,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>14.1958</v>
+        <v>14.1895</v>
       </c>
       <c r="C77" t="n">
-        <v>16.5219</v>
+        <v>16.5211</v>
       </c>
       <c r="D77" t="n">
-        <v>54.5084</v>
+        <v>54.4986</v>
       </c>
       <c r="E77" t="n">
-        <v>14.5895</v>
+        <v>14.5936</v>
       </c>
       <c r="F77" t="n">
-        <v>46.8867</v>
+        <v>46.8658</v>
       </c>
     </row>
     <row r="78">
@@ -6600,19 +6600,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>13.8668</v>
+        <v>13.9156</v>
       </c>
       <c r="C78" t="n">
-        <v>16.4198</v>
+        <v>16.431</v>
       </c>
       <c r="D78" t="n">
-        <v>57.4385</v>
+        <v>57.5132</v>
       </c>
       <c r="E78" t="n">
-        <v>17.9703</v>
+        <v>18.2879</v>
       </c>
       <c r="F78" t="n">
-        <v>51.2617</v>
+        <v>51.0628</v>
       </c>
     </row>
     <row r="79">
@@ -6620,19 +6620,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>13.5131</v>
+        <v>13.5609</v>
       </c>
       <c r="C79" t="n">
-        <v>17.9745</v>
+        <v>17.9811</v>
       </c>
       <c r="D79" t="n">
-        <v>57.3228</v>
+        <v>57.2526</v>
       </c>
       <c r="E79" t="n">
-        <v>18.5671</v>
+        <v>17.669</v>
       </c>
       <c r="F79" t="n">
-        <v>50.8954</v>
+        <v>50.7649</v>
       </c>
     </row>
     <row r="80">
@@ -6640,19 +6640,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>13.0941</v>
+        <v>13.0811</v>
       </c>
       <c r="C80" t="n">
-        <v>17.7936</v>
+        <v>17.8026</v>
       </c>
       <c r="D80" t="n">
-        <v>57.292</v>
+        <v>57.3181</v>
       </c>
       <c r="E80" t="n">
-        <v>18.1467</v>
+        <v>17.3426</v>
       </c>
       <c r="F80" t="n">
-        <v>50.3245</v>
+        <v>50.4211</v>
       </c>
     </row>
     <row r="81">
@@ -6660,19 +6660,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>17.646</v>
+        <v>17.6636</v>
       </c>
       <c r="C81" t="n">
-        <v>17.637</v>
+        <v>17.6582</v>
       </c>
       <c r="D81" t="n">
-        <v>57.2891</v>
+        <v>57.2157</v>
       </c>
       <c r="E81" t="n">
-        <v>17.0073</v>
+        <v>17.0784</v>
       </c>
       <c r="F81" t="n">
-        <v>50.3669</v>
+        <v>50.0431</v>
       </c>
     </row>
     <row r="82">
@@ -6680,19 +6680,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>17.3418</v>
+        <v>17.3468</v>
       </c>
       <c r="C82" t="n">
-        <v>17.481</v>
+        <v>17.4725</v>
       </c>
       <c r="D82" t="n">
-        <v>57.1848</v>
+        <v>57.2757</v>
       </c>
       <c r="E82" t="n">
-        <v>16.7768</v>
+        <v>16.8153</v>
       </c>
       <c r="F82" t="n">
-        <v>49.7689</v>
+        <v>49.8785</v>
       </c>
     </row>
     <row r="83">
@@ -6700,19 +6700,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>16.9886</v>
+        <v>17.0036</v>
       </c>
       <c r="C83" t="n">
-        <v>17.3341</v>
+        <v>17.343</v>
       </c>
       <c r="D83" t="n">
-        <v>57.2093</v>
+        <v>57.2038</v>
       </c>
       <c r="E83" t="n">
-        <v>16.5045</v>
+        <v>16.5157</v>
       </c>
       <c r="F83" t="n">
-        <v>49.3646</v>
+        <v>49.6261</v>
       </c>
     </row>
     <row r="84">
@@ -6720,19 +6720,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>16.6304</v>
+        <v>16.6251</v>
       </c>
       <c r="C84" t="n">
-        <v>17.2174</v>
+        <v>17.2252</v>
       </c>
       <c r="D84" t="n">
-        <v>60.912</v>
+        <v>60.9245</v>
       </c>
       <c r="E84" t="n">
-        <v>16.2607</v>
+        <v>16.2687</v>
       </c>
       <c r="F84" t="n">
-        <v>54.0435</v>
+        <v>54.1092</v>
       </c>
     </row>
     <row r="85">
@@ -6740,19 +6740,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>16.2563</v>
+        <v>16.2596</v>
       </c>
       <c r="C85" t="n">
-        <v>17.0819</v>
+        <v>17.0811</v>
       </c>
       <c r="D85" t="n">
-        <v>60.8434</v>
+        <v>60.7236</v>
       </c>
       <c r="E85" t="n">
-        <v>16.0596</v>
+        <v>16.0387</v>
       </c>
       <c r="F85" t="n">
-        <v>53.7713</v>
+        <v>53.5683</v>
       </c>
     </row>
     <row r="86">
@@ -6760,19 +6760,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>15.8888</v>
+        <v>15.883</v>
       </c>
       <c r="C86" t="n">
-        <v>16.9855</v>
+        <v>16.9606</v>
       </c>
       <c r="D86" t="n">
-        <v>60.8232</v>
+        <v>60.7585</v>
       </c>
       <c r="E86" t="n">
-        <v>15.804</v>
+        <v>15.7889</v>
       </c>
       <c r="F86" t="n">
-        <v>53.4631</v>
+        <v>53.2879</v>
       </c>
     </row>
     <row r="87">
@@ -6780,19 +6780,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>15.5263</v>
+        <v>15.5247</v>
       </c>
       <c r="C87" t="n">
-        <v>16.8781</v>
+        <v>16.8891</v>
       </c>
       <c r="D87" t="n">
-        <v>60.8886</v>
+        <v>60.8016</v>
       </c>
       <c r="E87" t="n">
-        <v>15.5606</v>
+        <v>15.595</v>
       </c>
       <c r="F87" t="n">
-        <v>52.9809</v>
+        <v>53.5695</v>
       </c>
     </row>
     <row r="88">
@@ -6800,19 +6800,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>15.1768</v>
+        <v>15.1789</v>
       </c>
       <c r="C88" t="n">
-        <v>16.7773</v>
+        <v>16.7783</v>
       </c>
       <c r="D88" t="n">
-        <v>60.7027</v>
+        <v>60.9001</v>
       </c>
       <c r="E88" t="n">
-        <v>15.3475</v>
+        <v>15.3536</v>
       </c>
       <c r="F88" t="n">
-        <v>53.0896</v>
+        <v>52.9726</v>
       </c>
     </row>
     <row r="89">
@@ -6820,19 +6820,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>14.8631</v>
+        <v>14.8697</v>
       </c>
       <c r="C89" t="n">
-        <v>16.6816</v>
+        <v>16.6833</v>
       </c>
       <c r="D89" t="n">
-        <v>60.6635</v>
+        <v>60.823</v>
       </c>
       <c r="E89" t="n">
-        <v>15.1315</v>
+        <v>15.1153</v>
       </c>
       <c r="F89" t="n">
-        <v>52.5767</v>
+        <v>52.6977</v>
       </c>
     </row>
     <row r="90">
@@ -6840,19 +6840,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>14.5646</v>
+        <v>14.5559</v>
       </c>
       <c r="C90" t="n">
-        <v>16.6089</v>
+        <v>16.6082</v>
       </c>
       <c r="D90" t="n">
-        <v>60.7105</v>
+        <v>60.7676</v>
       </c>
       <c r="E90" t="n">
-        <v>14.8971</v>
+        <v>14.9099</v>
       </c>
       <c r="F90" t="n">
-        <v>52.2714</v>
+        <v>52.2705</v>
       </c>
     </row>
     <row r="91">
@@ -6860,19 +6860,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>14.2647</v>
+        <v>14.2539</v>
       </c>
       <c r="C91" t="n">
-        <v>16.5081</v>
+        <v>16.5285</v>
       </c>
       <c r="D91" t="n">
-        <v>60.7585</v>
+        <v>60.6833</v>
       </c>
       <c r="E91" t="n">
-        <v>14.6394</v>
+        <v>14.6498</v>
       </c>
       <c r="F91" t="n">
-        <v>51.9015</v>
+        <v>51.9667</v>
       </c>
     </row>
     <row r="92">
@@ -6880,19 +6880,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>13.921</v>
+        <v>14.003</v>
       </c>
       <c r="C92" t="n">
-        <v>16.4438</v>
+        <v>16.442</v>
       </c>
       <c r="D92" t="n">
-        <v>60.9405</v>
+        <v>60.962</v>
       </c>
       <c r="E92" t="n">
-        <v>18.8865</v>
+        <v>20.2426</v>
       </c>
       <c r="F92" t="n">
-        <v>56.3488</v>
+        <v>55.9464</v>
       </c>
     </row>
     <row r="93">
@@ -6900,19 +6900,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>13.5611</v>
+        <v>13.6168</v>
       </c>
       <c r="C93" t="n">
-        <v>16.3817</v>
+        <v>16.3756</v>
       </c>
       <c r="D93" t="n">
-        <v>61.0358</v>
+        <v>61.2383</v>
       </c>
       <c r="E93" t="n">
-        <v>17.8882</v>
+        <v>20.6794</v>
       </c>
       <c r="F93" t="n">
-        <v>55.9305</v>
+        <v>55.7391</v>
       </c>
     </row>
     <row r="94">
@@ -6920,19 +6920,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>13.1463</v>
+        <v>13.197</v>
       </c>
       <c r="C94" t="n">
-        <v>17.8413</v>
+        <v>17.8457</v>
       </c>
       <c r="D94" t="n">
-        <v>61.0053</v>
+        <v>61.291</v>
       </c>
       <c r="E94" t="n">
-        <v>17.7045</v>
+        <v>18.3686</v>
       </c>
       <c r="F94" t="n">
-        <v>55.4928</v>
+        <v>55.5435</v>
       </c>
     </row>
     <row r="95">
@@ -6940,19 +6940,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>17.7124</v>
+        <v>17.6917</v>
       </c>
       <c r="C95" t="n">
-        <v>17.6786</v>
+        <v>17.6654</v>
       </c>
       <c r="D95" t="n">
-        <v>60.7719</v>
+        <v>60.8036</v>
       </c>
       <c r="E95" t="n">
-        <v>17.2172</v>
+        <v>17.4138</v>
       </c>
       <c r="F95" t="n">
-        <v>55.1616</v>
+        <v>55.2558</v>
       </c>
     </row>
     <row r="96">
@@ -6960,19 +6960,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>17.3992</v>
+        <v>17.3989</v>
       </c>
       <c r="C96" t="n">
-        <v>17.502</v>
+        <v>17.5065</v>
       </c>
       <c r="D96" t="n">
-        <v>60.8074</v>
+        <v>60.6928</v>
       </c>
       <c r="E96" t="n">
-        <v>19.3865</v>
+        <v>17.0513</v>
       </c>
       <c r="F96" t="n">
-        <v>54.6856</v>
+        <v>54.6701</v>
       </c>
     </row>
     <row r="97">
@@ -6980,19 +6980,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>17.0583</v>
+        <v>17.0665</v>
       </c>
       <c r="C97" t="n">
-        <v>17.3721</v>
+        <v>17.3625</v>
       </c>
       <c r="D97" t="n">
-        <v>60.6663</v>
+        <v>60.7511</v>
       </c>
       <c r="E97" t="n">
-        <v>16.5588</v>
+        <v>16.5652</v>
       </c>
       <c r="F97" t="n">
-        <v>54.4263</v>
+        <v>54.4805</v>
       </c>
     </row>
     <row r="98">
@@ -7000,19 +7000,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>16.7099</v>
+        <v>16.7011</v>
       </c>
       <c r="C98" t="n">
-        <v>17.2292</v>
+        <v>17.21</v>
       </c>
       <c r="D98" t="n">
-        <v>60.6804</v>
+        <v>60.8591</v>
       </c>
       <c r="E98" t="n">
-        <v>17.0877</v>
+        <v>16.4985</v>
       </c>
       <c r="F98" t="n">
-        <v>53.9264</v>
+        <v>54.2799</v>
       </c>
     </row>
     <row r="99">
@@ -7020,19 +7020,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>16.3319</v>
+        <v>16.3422</v>
       </c>
       <c r="C99" t="n">
-        <v>17.1159</v>
+        <v>17.1001</v>
       </c>
       <c r="D99" t="n">
-        <v>60.6279</v>
+        <v>60.9286</v>
       </c>
       <c r="E99" t="n">
-        <v>16.0569</v>
+        <v>16.1877</v>
       </c>
       <c r="F99" t="n">
-        <v>53.832</v>
+        <v>53.9087</v>
       </c>
     </row>
     <row r="100">
@@ -7040,19 +7040,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>15.9612</v>
+        <v>15.9665</v>
       </c>
       <c r="C100" t="n">
-        <v>16.9885</v>
+        <v>17.0085</v>
       </c>
       <c r="D100" t="n">
-        <v>60.5678</v>
+        <v>60.6865</v>
       </c>
       <c r="E100" t="n">
-        <v>16.0423</v>
+        <v>15.843</v>
       </c>
       <c r="F100" t="n">
-        <v>53.4601</v>
+        <v>53.3628</v>
       </c>
     </row>
     <row r="101">
@@ -7060,19 +7060,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>15.5896</v>
+        <v>15.6051</v>
       </c>
       <c r="C101" t="n">
-        <v>16.8725</v>
+        <v>16.8864</v>
       </c>
       <c r="D101" t="n">
-        <v>60.5221</v>
+        <v>60.5511</v>
       </c>
       <c r="E101" t="n">
-        <v>15.6078</v>
+        <v>15.6115</v>
       </c>
       <c r="F101" t="n">
-        <v>53.0953</v>
+        <v>53.2102</v>
       </c>
     </row>
     <row r="102">
@@ -7080,19 +7080,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>15.2489</v>
+        <v>15.2618</v>
       </c>
       <c r="C102" t="n">
-        <v>16.7896</v>
+        <v>16.7957</v>
       </c>
       <c r="D102" t="n">
-        <v>60.5884</v>
+        <v>60.6266</v>
       </c>
       <c r="E102" t="n">
-        <v>15.4032</v>
+        <v>15.4203</v>
       </c>
       <c r="F102" t="n">
-        <v>52.6994</v>
+        <v>52.9865</v>
       </c>
     </row>
     <row r="103">
@@ -7100,19 +7100,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>14.9264</v>
+        <v>14.9246</v>
       </c>
       <c r="C103" t="n">
-        <v>16.7177</v>
+        <v>16.7021</v>
       </c>
       <c r="D103" t="n">
-        <v>60.42</v>
+        <v>60.5957</v>
       </c>
       <c r="E103" t="n">
-        <v>15.164</v>
+        <v>15.1765</v>
       </c>
       <c r="F103" t="n">
-        <v>52.7127</v>
+        <v>52.6945</v>
       </c>
     </row>
     <row r="104">
@@ -7120,19 +7120,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>14.6142</v>
+        <v>14.6251</v>
       </c>
       <c r="C104" t="n">
-        <v>16.6069</v>
+        <v>16.6204</v>
       </c>
       <c r="D104" t="n">
-        <v>60.4867</v>
+        <v>60.5179</v>
       </c>
       <c r="E104" t="n">
-        <v>14.9194</v>
+        <v>14.9116</v>
       </c>
       <c r="F104" t="n">
-        <v>52.5186</v>
+        <v>52.4584</v>
       </c>
     </row>
     <row r="105">
@@ -7140,19 +7140,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>14.3054</v>
+        <v>14.3151</v>
       </c>
       <c r="C105" t="n">
-        <v>16.5297</v>
+        <v>16.5305</v>
       </c>
       <c r="D105" t="n">
-        <v>60.4459</v>
+        <v>60.357</v>
       </c>
       <c r="E105" t="n">
-        <v>14.6895</v>
+        <v>14.7009</v>
       </c>
       <c r="F105" t="n">
-        <v>52.0275</v>
+        <v>51.7684</v>
       </c>
     </row>
     <row r="106">
@@ -7160,19 +7160,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>13.9931</v>
+        <v>13.9969</v>
       </c>
       <c r="C106" t="n">
-        <v>16.4617</v>
+        <v>16.4574</v>
       </c>
       <c r="D106" t="n">
-        <v>60.2739</v>
+        <v>60.315</v>
       </c>
       <c r="E106" t="n">
-        <v>14.448</v>
+        <v>14.4381</v>
       </c>
       <c r="F106" t="n">
-        <v>51.6896</v>
+        <v>51.7776</v>
       </c>
     </row>
     <row r="107">
@@ -7180,19 +7180,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>13.7042</v>
+        <v>13.6527</v>
       </c>
       <c r="C107" t="n">
-        <v>16.4128</v>
+        <v>16.3725</v>
       </c>
       <c r="D107" t="n">
-        <v>59.279</v>
+        <v>59.3668</v>
       </c>
       <c r="E107" t="n">
-        <v>19.9887</v>
+        <v>19.6779</v>
       </c>
       <c r="F107" t="n">
-        <v>55.6845</v>
+        <v>55.7943</v>
       </c>
     </row>
     <row r="108">
@@ -7200,19 +7200,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>13.243</v>
+        <v>13.2427</v>
       </c>
       <c r="C108" t="n">
-        <v>17.8635</v>
+        <v>17.8695</v>
       </c>
       <c r="D108" t="n">
-        <v>59.1902</v>
+        <v>59.5172</v>
       </c>
       <c r="E108" t="n">
-        <v>19.2513</v>
+        <v>17.9274</v>
       </c>
       <c r="F108" t="n">
-        <v>55.517</v>
+        <v>55.5262</v>
       </c>
     </row>
     <row r="109">
@@ -7220,19 +7220,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>12.6981</v>
+        <v>12.7671</v>
       </c>
       <c r="C109" t="n">
-        <v>17.6922</v>
+        <v>17.6825</v>
       </c>
       <c r="D109" t="n">
-        <v>59.3018</v>
+        <v>59.4397</v>
       </c>
       <c r="E109" t="n">
-        <v>18.439</v>
+        <v>17.2041</v>
       </c>
       <c r="F109" t="n">
-        <v>55.1568</v>
+        <v>55.0523</v>
       </c>
     </row>
     <row r="110">
@@ -7240,19 +7240,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>17.4697</v>
+        <v>17.4678</v>
       </c>
       <c r="C110" t="n">
-        <v>17.5189</v>
+        <v>17.518</v>
       </c>
       <c r="D110" t="n">
-        <v>59.2769</v>
+        <v>59.3139</v>
       </c>
       <c r="E110" t="n">
-        <v>17.8896</v>
+        <v>18.3156</v>
       </c>
       <c r="F110" t="n">
-        <v>54.6871</v>
+        <v>54.9519</v>
       </c>
     </row>
     <row r="111">
@@ -7260,19 +7260,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>17.1389</v>
+        <v>17.1399</v>
       </c>
       <c r="C111" t="n">
-        <v>17.412</v>
+        <v>17.3706</v>
       </c>
       <c r="D111" t="n">
-        <v>59.3491</v>
+        <v>59.5312</v>
       </c>
       <c r="E111" t="n">
-        <v>17.3122</v>
+        <v>17.8331</v>
       </c>
       <c r="F111" t="n">
-        <v>54.5651</v>
+        <v>54.599</v>
       </c>
     </row>
     <row r="112">
@@ -7280,19 +7280,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>16.7842</v>
+        <v>16.7911</v>
       </c>
       <c r="C112" t="n">
-        <v>17.2596</v>
+        <v>17.251</v>
       </c>
       <c r="D112" t="n">
-        <v>59.4189</v>
+        <v>59.6644</v>
       </c>
       <c r="E112" t="n">
-        <v>18.3389</v>
+        <v>17.2713</v>
       </c>
       <c r="F112" t="n">
-        <v>54.1146</v>
+        <v>54.4319</v>
       </c>
     </row>
     <row r="113">
@@ -7300,19 +7300,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>16.4196</v>
+        <v>16.4215</v>
       </c>
       <c r="C113" t="n">
-        <v>17.1537</v>
+        <v>17.1274</v>
       </c>
       <c r="D113" t="n">
-        <v>59.4777</v>
+        <v>59.5957</v>
       </c>
       <c r="E113" t="n">
-        <v>16.2313</v>
+        <v>16.2084</v>
       </c>
       <c r="F113" t="n">
-        <v>53.7283</v>
+        <v>53.9128</v>
       </c>
     </row>
     <row r="114">
@@ -7320,19 +7320,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>16.0453</v>
+        <v>16.035</v>
       </c>
       <c r="C114" t="n">
-        <v>17.0174</v>
+        <v>16.9997</v>
       </c>
       <c r="D114" t="n">
-        <v>59.5869</v>
+        <v>59.5091</v>
       </c>
       <c r="E114" t="n">
-        <v>15.9273</v>
+        <v>16.0863</v>
       </c>
       <c r="F114" t="n">
-        <v>53.4588</v>
+        <v>53.5735</v>
       </c>
     </row>
     <row r="115">
@@ -7340,19 +7340,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>15.678</v>
+        <v>15.6696</v>
       </c>
       <c r="C115" t="n">
-        <v>16.8977</v>
+        <v>16.8919</v>
       </c>
       <c r="D115" t="n">
-        <v>59.5844</v>
+        <v>59.5729</v>
       </c>
       <c r="E115" t="n">
-        <v>15.6923</v>
+        <v>15.6828</v>
       </c>
       <c r="F115" t="n">
-        <v>53.2742</v>
+        <v>53.3453</v>
       </c>
     </row>
     <row r="116">
@@ -7360,19 +7360,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>15.3228</v>
+        <v>15.3106</v>
       </c>
       <c r="C116" t="n">
-        <v>16.8237</v>
+        <v>16.7799</v>
       </c>
       <c r="D116" t="n">
-        <v>59.592</v>
+        <v>59.5211</v>
       </c>
       <c r="E116" t="n">
-        <v>15.46</v>
+        <v>15.694</v>
       </c>
       <c r="F116" t="n">
-        <v>52.8734</v>
+        <v>53.1106</v>
       </c>
     </row>
     <row r="117">
@@ -7380,19 +7380,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>15.0017</v>
+        <v>15.0072</v>
       </c>
       <c r="C117" t="n">
-        <v>16.7132</v>
+        <v>16.6975</v>
       </c>
       <c r="D117" t="n">
-        <v>59.6108</v>
+        <v>59.5496</v>
       </c>
       <c r="E117" t="n">
-        <v>15.2136</v>
+        <v>15.2179</v>
       </c>
       <c r="F117" t="n">
-        <v>52.5489</v>
+        <v>52.5971</v>
       </c>
     </row>
     <row r="118">
@@ -7400,19 +7400,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>14.678</v>
+        <v>14.6763</v>
       </c>
       <c r="C118" t="n">
-        <v>16.6073</v>
+        <v>16.617</v>
       </c>
       <c r="D118" t="n">
-        <v>59.6318</v>
+        <v>59.6331</v>
       </c>
       <c r="E118" t="n">
-        <v>14.9537</v>
+        <v>14.9748</v>
       </c>
       <c r="F118" t="n">
-        <v>52.2471</v>
+        <v>52.2282</v>
       </c>
     </row>
     <row r="119">
@@ -7420,19 +7420,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>14.3614</v>
+        <v>14.3597</v>
       </c>
       <c r="C119" t="n">
-        <v>16.5357</v>
+        <v>16.536</v>
       </c>
       <c r="D119" t="n">
-        <v>59.6077</v>
+        <v>59.617</v>
       </c>
       <c r="E119" t="n">
-        <v>14.7461</v>
+        <v>14.7294</v>
       </c>
       <c r="F119" t="n">
-        <v>51.8759</v>
+        <v>52.0821</v>
       </c>
     </row>
     <row r="120">
@@ -7440,19 +7440,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>14.068</v>
+        <v>14.0732</v>
       </c>
       <c r="C120" t="n">
-        <v>16.4525</v>
+        <v>16.4645</v>
       </c>
       <c r="D120" t="n">
-        <v>59.5326</v>
+        <v>59.6687</v>
       </c>
       <c r="E120" t="n">
-        <v>14.5024</v>
+        <v>15.2133</v>
       </c>
       <c r="F120" t="n">
-        <v>51.9329</v>
+        <v>51.6319</v>
       </c>
     </row>
     <row r="121">
@@ -7460,19 +7460,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>13.7191</v>
+        <v>13.7339</v>
       </c>
       <c r="C121" t="n">
-        <v>16.4037</v>
+        <v>16.4204</v>
       </c>
       <c r="D121" t="n">
-        <v>61.6092</v>
+        <v>61.7389</v>
       </c>
       <c r="E121" t="n">
-        <v>19.8894</v>
+        <v>19.086</v>
       </c>
       <c r="F121" t="n">
-        <v>55.7508</v>
+        <v>55.5135</v>
       </c>
     </row>
     <row r="122">
@@ -7480,19 +7480,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>13.3319</v>
+        <v>13.3912</v>
       </c>
       <c r="C122" t="n">
-        <v>17.8832</v>
+        <v>17.8871</v>
       </c>
       <c r="D122" t="n">
-        <v>61.5314</v>
+        <v>61.4593</v>
       </c>
       <c r="E122" t="n">
-        <v>19.2858</v>
+        <v>18.2615</v>
       </c>
       <c r="F122" t="n">
-        <v>55.382</v>
+        <v>55.2433</v>
       </c>
     </row>
     <row r="123">
@@ -7500,19 +7500,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>12.8083</v>
+        <v>12.8714</v>
       </c>
       <c r="C123" t="n">
-        <v>17.7221</v>
+        <v>17.7145</v>
       </c>
       <c r="D123" t="n">
-        <v>61.3932</v>
+        <v>61.5998</v>
       </c>
       <c r="E123" t="n">
-        <v>18.3326</v>
+        <v>18.0481</v>
       </c>
       <c r="F123" t="n">
-        <v>55.0947</v>
+        <v>55.027</v>
       </c>
     </row>
     <row r="124">
@@ -7520,19 +7520,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>17.5328</v>
+        <v>17.538</v>
       </c>
       <c r="C124" t="n">
-        <v>17.5723</v>
+        <v>17.5365</v>
       </c>
       <c r="D124" t="n">
-        <v>61.2959</v>
+        <v>61.2665</v>
       </c>
       <c r="E124" t="n">
-        <v>19.5608</v>
+        <v>17.8825</v>
       </c>
       <c r="F124" t="n">
-        <v>54.7226</v>
+        <v>55.0842</v>
       </c>
     </row>
     <row r="125">
@@ -7540,19 +7540,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>17.1978</v>
+        <v>17.2062</v>
       </c>
       <c r="C125" t="n">
-        <v>17.376</v>
+        <v>17.3874</v>
       </c>
       <c r="D125" t="n">
-        <v>61.2624</v>
+        <v>61.4218</v>
       </c>
       <c r="E125" t="n">
-        <v>18.3935</v>
+        <v>17.7798</v>
       </c>
       <c r="F125" t="n">
-        <v>54.3155</v>
+        <v>54.387</v>
       </c>
     </row>
     <row r="126">
@@ -7560,19 +7560,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>16.8639</v>
+        <v>16.8742</v>
       </c>
       <c r="C126" t="n">
-        <v>17.2542</v>
+        <v>17.2591</v>
       </c>
       <c r="D126" t="n">
-        <v>61.1253</v>
+        <v>61.2411</v>
       </c>
       <c r="E126" t="n">
-        <v>17.003</v>
+        <v>17.1537</v>
       </c>
       <c r="F126" t="n">
-        <v>54.0283</v>
+        <v>53.9881</v>
       </c>
     </row>
     <row r="127">
@@ -7580,19 +7580,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>16.4785</v>
+        <v>16.4911</v>
       </c>
       <c r="C127" t="n">
-        <v>17.1255</v>
+        <v>17.1364</v>
       </c>
       <c r="D127" t="n">
-        <v>61.0607</v>
+        <v>61.1949</v>
       </c>
       <c r="E127" t="n">
-        <v>16.6689</v>
+        <v>16.9464</v>
       </c>
       <c r="F127" t="n">
-        <v>53.7918</v>
+        <v>53.7416</v>
       </c>
     </row>
     <row r="128">
@@ -7600,19 +7600,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>16.1034</v>
+        <v>16.1081</v>
       </c>
       <c r="C128" t="n">
-        <v>17.0219</v>
+        <v>17.0059</v>
       </c>
       <c r="D128" t="n">
-        <v>61.1297</v>
+        <v>61.1689</v>
       </c>
       <c r="E128" t="n">
-        <v>16.5089</v>
+        <v>16.1071</v>
       </c>
       <c r="F128" t="n">
-        <v>53.5088</v>
+        <v>53.5558</v>
       </c>
     </row>
     <row r="129">
@@ -7620,19 +7620,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>15.7417</v>
+        <v>15.7332</v>
       </c>
       <c r="C129" t="n">
-        <v>16.9089</v>
+        <v>16.9019</v>
       </c>
       <c r="D129" t="n">
-        <v>60.9436</v>
+        <v>61.0144</v>
       </c>
       <c r="E129" t="n">
-        <v>15.8168</v>
+        <v>16.6126</v>
       </c>
       <c r="F129" t="n">
-        <v>53.1618</v>
+        <v>53.1788</v>
       </c>
     </row>
     <row r="130">
@@ -7640,19 +7640,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>15.3865</v>
+        <v>15.3974</v>
       </c>
       <c r="C130" t="n">
-        <v>16.8259</v>
+        <v>16.8022</v>
       </c>
       <c r="D130" t="n">
-        <v>60.9515</v>
+        <v>60.9263</v>
       </c>
       <c r="E130" t="n">
-        <v>15.5496</v>
+        <v>15.5386</v>
       </c>
       <c r="F130" t="n">
-        <v>52.7565</v>
+        <v>52.7481</v>
       </c>
     </row>
     <row r="131">
@@ -7660,19 +7660,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>15.0604</v>
+        <v>15.063</v>
       </c>
       <c r="C131" t="n">
-        <v>16.7069</v>
+        <v>16.715</v>
       </c>
       <c r="D131" t="n">
-        <v>61.1319</v>
+        <v>60.7671</v>
       </c>
       <c r="E131" t="n">
-        <v>15.3077</v>
+        <v>15.2863</v>
       </c>
       <c r="F131" t="n">
-        <v>52.7733</v>
+        <v>52.4012</v>
       </c>
     </row>
     <row r="132">
@@ -7680,19 +7680,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>14.8237</v>
+        <v>14.7468</v>
       </c>
       <c r="C132" t="n">
-        <v>16.7312</v>
+        <v>16.6282</v>
       </c>
       <c r="D132" t="n">
-        <v>61.0313</v>
+        <v>60.7892</v>
       </c>
       <c r="E132" t="n">
-        <v>15.0144</v>
+        <v>15.0343</v>
       </c>
       <c r="F132" t="n">
-        <v>52.2446</v>
+        <v>52.1591</v>
       </c>
     </row>
     <row r="133">
@@ -7700,19 +7700,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>14.4311</v>
+        <v>14.4315</v>
       </c>
       <c r="C133" t="n">
-        <v>16.5681</v>
+        <v>16.5482</v>
       </c>
       <c r="D133" t="n">
-        <v>60.7391</v>
+        <v>60.718</v>
       </c>
       <c r="E133" t="n">
-        <v>14.7896</v>
+        <v>14.7941</v>
       </c>
       <c r="F133" t="n">
-        <v>51.698</v>
+        <v>51.8833</v>
       </c>
     </row>
     <row r="134">
@@ -7720,19 +7720,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.1134</v>
+        <v>14.138</v>
       </c>
       <c r="C134" t="n">
-        <v>16.4698</v>
+        <v>16.4826</v>
       </c>
       <c r="D134" t="n">
-        <v>60.6666</v>
+        <v>60.6902</v>
       </c>
       <c r="E134" t="n">
-        <v>14.5344</v>
+        <v>14.5679</v>
       </c>
       <c r="F134" t="n">
-        <v>51.5156</v>
+        <v>51.5035</v>
       </c>
     </row>
     <row r="135">
@@ -7740,19 +7740,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>13.7839</v>
+        <v>13.7738</v>
       </c>
       <c r="C135" t="n">
-        <v>16.4014</v>
+        <v>16.3994</v>
       </c>
       <c r="D135" t="n">
-        <v>62.1833</v>
+        <v>62.1486</v>
       </c>
       <c r="E135" t="n">
-        <v>20.7501</v>
+        <v>20.8787</v>
       </c>
       <c r="F135" t="n">
-        <v>55.543</v>
+        <v>55.5496</v>
       </c>
     </row>
     <row r="136">
@@ -7760,19 +7760,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>13.409</v>
+        <v>13.4721</v>
       </c>
       <c r="C136" t="n">
-        <v>17.9085</v>
+        <v>17.8992</v>
       </c>
       <c r="D136" t="n">
-        <v>61.9955</v>
+        <v>61.8856</v>
       </c>
       <c r="E136" t="n">
-        <v>19.5655</v>
+        <v>20.3903</v>
       </c>
       <c r="F136" t="n">
-        <v>55.1847</v>
+        <v>55.1765</v>
       </c>
     </row>
     <row r="137">
@@ -7780,19 +7780,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>12.9521</v>
+        <v>12.927</v>
       </c>
       <c r="C137" t="n">
-        <v>17.7532</v>
+        <v>17.712</v>
       </c>
       <c r="D137" t="n">
-        <v>61.7764</v>
+        <v>61.8337</v>
       </c>
       <c r="E137" t="n">
-        <v>18.6134</v>
+        <v>19.8377</v>
       </c>
       <c r="F137" t="n">
-        <v>54.7313</v>
+        <v>54.7085</v>
       </c>
     </row>
     <row r="138">
@@ -7800,19 +7800,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>17.6015</v>
+        <v>17.6137</v>
       </c>
       <c r="C138" t="n">
-        <v>17.5682</v>
+        <v>17.5755</v>
       </c>
       <c r="D138" t="n">
-        <v>61.7821</v>
+        <v>61.8146</v>
       </c>
       <c r="E138" t="n">
-        <v>18.2308</v>
+        <v>18.2999</v>
       </c>
       <c r="F138" t="n">
-        <v>54.4708</v>
+        <v>54.6818</v>
       </c>
     </row>
     <row r="139">
@@ -7820,19 +7820,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>17.274</v>
+        <v>17.2802</v>
       </c>
       <c r="C139" t="n">
-        <v>17.3978</v>
+        <v>17.4217</v>
       </c>
       <c r="D139" t="n">
-        <v>61.4905</v>
+        <v>61.6344</v>
       </c>
       <c r="E139" t="n">
-        <v>17.7418</v>
+        <v>18.8725</v>
       </c>
       <c r="F139" t="n">
-        <v>54.0349</v>
+        <v>54.1201</v>
       </c>
     </row>
     <row r="140">
@@ -7840,19 +7840,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>16.9335</v>
+        <v>16.94</v>
       </c>
       <c r="C140" t="n">
-        <v>17.2714</v>
+        <v>17.2618</v>
       </c>
       <c r="D140" t="n">
-        <v>61.5684</v>
+        <v>61.5797</v>
       </c>
       <c r="E140" t="n">
-        <v>18.2855</v>
+        <v>17.3583</v>
       </c>
       <c r="F140" t="n">
-        <v>53.843</v>
+        <v>54.0434</v>
       </c>
     </row>
     <row r="141">
@@ -7860,19 +7860,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>16.5678</v>
+        <v>16.572</v>
       </c>
       <c r="C141" t="n">
-        <v>17.1551</v>
+        <v>17.1352</v>
       </c>
       <c r="D141" t="n">
-        <v>61.4408</v>
+        <v>61.6253</v>
       </c>
       <c r="E141" t="n">
-        <v>16.2968</v>
+        <v>16.5137</v>
       </c>
       <c r="F141" t="n">
-        <v>53.5811</v>
+        <v>53.4831</v>
       </c>
     </row>
     <row r="142">
@@ -7880,19 +7880,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>16.1878</v>
+        <v>16.1982</v>
       </c>
       <c r="C142" t="n">
-        <v>17.0378</v>
+        <v>17.0361</v>
       </c>
       <c r="D142" t="n">
-        <v>61.3926</v>
+        <v>61.3581</v>
       </c>
       <c r="E142" t="n">
-        <v>16.1327</v>
+        <v>16.4881</v>
       </c>
       <c r="F142" t="n">
-        <v>53.1545</v>
+        <v>53.0532</v>
       </c>
     </row>
     <row r="143">
@@ -7900,19 +7900,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>15.8387</v>
+        <v>15.8515</v>
       </c>
       <c r="C143" t="n">
-        <v>16.9241</v>
+        <v>16.914</v>
       </c>
       <c r="D143" t="n">
-        <v>61.3106</v>
+        <v>61.2597</v>
       </c>
       <c r="E143" t="n">
-        <v>16.4086</v>
+        <v>16.721</v>
       </c>
       <c r="F143" t="n">
-        <v>52.9201</v>
+        <v>52.7332</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Running erasure.xlsx
+++ b/vs-x64/Running erasure.xlsx
@@ -5080,19 +5080,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>14.4743</v>
+        <v>14.4896</v>
       </c>
       <c r="C2" t="n">
-        <v>14.9591</v>
+        <v>14.9681</v>
       </c>
       <c r="D2" t="n">
-        <v>41.9952</v>
+        <v>41.7763</v>
       </c>
       <c r="E2" t="n">
-        <v>14.2945</v>
+        <v>14.2164</v>
       </c>
       <c r="F2" t="n">
-        <v>35.5566</v>
+        <v>35.4526</v>
       </c>
     </row>
     <row r="3">
@@ -5100,19 +5100,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>14.1469</v>
+        <v>14.2366</v>
       </c>
       <c r="C3" t="n">
-        <v>15.0749</v>
+        <v>15.0114</v>
       </c>
       <c r="D3" t="n">
-        <v>41.9813</v>
+        <v>41.8693</v>
       </c>
       <c r="E3" t="n">
-        <v>14.0936</v>
+        <v>14.1502</v>
       </c>
       <c r="F3" t="n">
-        <v>35.1442</v>
+        <v>35.0973</v>
       </c>
     </row>
     <row r="4">
@@ -5120,19 +5120,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>13.8607</v>
+        <v>13.9325</v>
       </c>
       <c r="C4" t="n">
-        <v>15.1479</v>
+        <v>15.2027</v>
       </c>
       <c r="D4" t="n">
-        <v>42.03</v>
+        <v>41.92</v>
       </c>
       <c r="E4" t="n">
-        <v>13.8859</v>
+        <v>13.8629</v>
       </c>
       <c r="F4" t="n">
-        <v>34.8041</v>
+        <v>34.5077</v>
       </c>
     </row>
     <row r="5">
@@ -5140,19 +5140,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>13.7655</v>
+        <v>13.8633</v>
       </c>
       <c r="C5" t="n">
-        <v>15.0779</v>
+        <v>15.1526</v>
       </c>
       <c r="D5" t="n">
-        <v>42.0191</v>
+        <v>41.7884</v>
       </c>
       <c r="E5" t="n">
-        <v>13.6789</v>
+        <v>13.6838</v>
       </c>
       <c r="F5" t="n">
-        <v>34.7845</v>
+        <v>34.6108</v>
       </c>
     </row>
     <row r="6">
@@ -5160,19 +5160,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>13.4484</v>
+        <v>13.4194</v>
       </c>
       <c r="C6" t="n">
-        <v>15.1581</v>
+        <v>15.1535</v>
       </c>
       <c r="D6" t="n">
-        <v>42.095</v>
+        <v>41.8788</v>
       </c>
       <c r="E6" t="n">
-        <v>13.533</v>
+        <v>13.5548</v>
       </c>
       <c r="F6" t="n">
-        <v>34.6114</v>
+        <v>34.5053</v>
       </c>
     </row>
     <row r="7">
@@ -5180,19 +5180,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>13.0809</v>
+        <v>13.1498</v>
       </c>
       <c r="C7" t="n">
-        <v>15.1537</v>
+        <v>15.1642</v>
       </c>
       <c r="D7" t="n">
-        <v>42.9579</v>
+        <v>42.575</v>
       </c>
       <c r="E7" t="n">
-        <v>16.8592</v>
+        <v>16.8169</v>
       </c>
       <c r="F7" t="n">
-        <v>38.3505</v>
+        <v>38.3208</v>
       </c>
     </row>
     <row r="8">
@@ -5200,19 +5200,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>12.9748</v>
+        <v>12.719</v>
       </c>
       <c r="C8" t="n">
-        <v>16.9426</v>
+        <v>16.9338</v>
       </c>
       <c r="D8" t="n">
-        <v>42.7967</v>
+        <v>42.6441</v>
       </c>
       <c r="E8" t="n">
-        <v>16.4342</v>
+        <v>16.5475</v>
       </c>
       <c r="F8" t="n">
-        <v>38.1904</v>
+        <v>38.115</v>
       </c>
     </row>
     <row r="9">
@@ -5220,19 +5220,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>12.5144</v>
+        <v>12.3714</v>
       </c>
       <c r="C9" t="n">
-        <v>16.9123</v>
+        <v>16.9496</v>
       </c>
       <c r="D9" t="n">
-        <v>42.7242</v>
+        <v>42.7578</v>
       </c>
       <c r="E9" t="n">
-        <v>17.1198</v>
+        <v>16.4188</v>
       </c>
       <c r="F9" t="n">
-        <v>38.027</v>
+        <v>37.8796</v>
       </c>
     </row>
     <row r="10">
@@ -5240,19 +5240,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>17.2287</v>
+        <v>17.2002</v>
       </c>
       <c r="C10" t="n">
-        <v>16.7457</v>
+        <v>16.7602</v>
       </c>
       <c r="D10" t="n">
-        <v>42.8152</v>
+        <v>42.6282</v>
       </c>
       <c r="E10" t="n">
-        <v>16.1661</v>
+        <v>16.2762</v>
       </c>
       <c r="F10" t="n">
-        <v>37.5716</v>
+        <v>37.8271</v>
       </c>
     </row>
     <row r="11">
@@ -5260,19 +5260,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>17.0031</v>
+        <v>16.8827</v>
       </c>
       <c r="C11" t="n">
-        <v>16.7278</v>
+        <v>16.6774</v>
       </c>
       <c r="D11" t="n">
-        <v>42.6606</v>
+        <v>42.6089</v>
       </c>
       <c r="E11" t="n">
-        <v>15.9231</v>
+        <v>15.9754</v>
       </c>
       <c r="F11" t="n">
-        <v>37.4649</v>
+        <v>37.2241</v>
       </c>
     </row>
     <row r="12">
@@ -5280,19 +5280,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>16.701</v>
+        <v>16.6076</v>
       </c>
       <c r="C12" t="n">
-        <v>16.6668</v>
+        <v>16.6572</v>
       </c>
       <c r="D12" t="n">
-        <v>42.624</v>
+        <v>42.6349</v>
       </c>
       <c r="E12" t="n">
-        <v>15.673</v>
+        <v>15.7261</v>
       </c>
       <c r="F12" t="n">
-        <v>37.0096</v>
+        <v>36.8937</v>
       </c>
     </row>
     <row r="13">
@@ -5300,19 +5300,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>16.2763</v>
+        <v>16.1755</v>
       </c>
       <c r="C13" t="n">
-        <v>16.6465</v>
+        <v>16.5521</v>
       </c>
       <c r="D13" t="n">
-        <v>42.5846</v>
+        <v>42.5207</v>
       </c>
       <c r="E13" t="n">
-        <v>15.5154</v>
+        <v>15.5257</v>
       </c>
       <c r="F13" t="n">
-        <v>36.8683</v>
+        <v>36.6262</v>
       </c>
     </row>
     <row r="14">
@@ -5320,19 +5320,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>15.8804</v>
+        <v>15.9356</v>
       </c>
       <c r="C14" t="n">
-        <v>16.5506</v>
+        <v>16.4492</v>
       </c>
       <c r="D14" t="n">
-        <v>42.67</v>
+        <v>42.5984</v>
       </c>
       <c r="E14" t="n">
-        <v>15.3618</v>
+        <v>15.3783</v>
       </c>
       <c r="F14" t="n">
-        <v>36.5169</v>
+        <v>36.3601</v>
       </c>
     </row>
     <row r="15">
@@ -5340,19 +5340,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>15.5404</v>
+        <v>15.5821</v>
       </c>
       <c r="C15" t="n">
-        <v>16.4349</v>
+        <v>16.3849</v>
       </c>
       <c r="D15" t="n">
-        <v>42.6899</v>
+        <v>42.5794</v>
       </c>
       <c r="E15" t="n">
-        <v>15.1157</v>
+        <v>15.1119</v>
       </c>
       <c r="F15" t="n">
-        <v>36.5963</v>
+        <v>36.1313</v>
       </c>
     </row>
     <row r="16">
@@ -5360,19 +5360,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>15.2434</v>
+        <v>15.2678</v>
       </c>
       <c r="C16" t="n">
-        <v>16.3586</v>
+        <v>16.3393</v>
       </c>
       <c r="D16" t="n">
-        <v>42.4281</v>
+        <v>42.4986</v>
       </c>
       <c r="E16" t="n">
-        <v>14.946</v>
+        <v>14.9258</v>
       </c>
       <c r="F16" t="n">
-        <v>36.0191</v>
+        <v>35.8597</v>
       </c>
     </row>
     <row r="17">
@@ -5380,19 +5380,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>15.0366</v>
+        <v>15.0279</v>
       </c>
       <c r="C17" t="n">
-        <v>16.2141</v>
+        <v>16.1511</v>
       </c>
       <c r="D17" t="n">
-        <v>42.5884</v>
+        <v>42.4607</v>
       </c>
       <c r="E17" t="n">
-        <v>14.7163</v>
+        <v>14.6949</v>
       </c>
       <c r="F17" t="n">
-        <v>35.6102</v>
+        <v>35.4375</v>
       </c>
     </row>
     <row r="18">
@@ -5400,19 +5400,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>14.701</v>
+        <v>14.78</v>
       </c>
       <c r="C18" t="n">
-        <v>16.1357</v>
+        <v>16.1339</v>
       </c>
       <c r="D18" t="n">
-        <v>42.5309</v>
+        <v>42.4371</v>
       </c>
       <c r="E18" t="n">
-        <v>14.558</v>
+        <v>14.5018</v>
       </c>
       <c r="F18" t="n">
-        <v>35.577</v>
+        <v>35.3494</v>
       </c>
     </row>
     <row r="19">
@@ -5420,19 +5420,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>14.235</v>
+        <v>14.3521</v>
       </c>
       <c r="C19" t="n">
-        <v>16.1152</v>
+        <v>16.0357</v>
       </c>
       <c r="D19" t="n">
-        <v>42.6102</v>
+        <v>42.4825</v>
       </c>
       <c r="E19" t="n">
-        <v>14.26</v>
+        <v>14.2851</v>
       </c>
       <c r="F19" t="n">
-        <v>35.1099</v>
+        <v>35.0447</v>
       </c>
     </row>
     <row r="20">
@@ -5440,19 +5440,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>14.1313</v>
+        <v>14.0101</v>
       </c>
       <c r="C20" t="n">
-        <v>16.1069</v>
+        <v>16.0773</v>
       </c>
       <c r="D20" t="n">
-        <v>42.6214</v>
+        <v>42.4342</v>
       </c>
       <c r="E20" t="n">
-        <v>14.0572</v>
+        <v>14.0674</v>
       </c>
       <c r="F20" t="n">
-        <v>34.7328</v>
+        <v>34.6252</v>
       </c>
     </row>
     <row r="21">
@@ -5460,19 +5460,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>13.7497</v>
+        <v>13.675</v>
       </c>
       <c r="C21" t="n">
-        <v>15.94</v>
+        <v>15.9096</v>
       </c>
       <c r="D21" t="n">
-        <v>43.4832</v>
+        <v>43.24</v>
       </c>
       <c r="E21" t="n">
-        <v>17.179</v>
+        <v>17.2037</v>
       </c>
       <c r="F21" t="n">
-        <v>38.7759</v>
+        <v>38.7654</v>
       </c>
     </row>
     <row r="22">
@@ -5480,19 +5480,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>13.3123</v>
+        <v>13.3467</v>
       </c>
       <c r="C22" t="n">
-        <v>17.6372</v>
+        <v>17.6317</v>
       </c>
       <c r="D22" t="n">
-        <v>43.3513</v>
+        <v>43.309</v>
       </c>
       <c r="E22" t="n">
-        <v>16.9936</v>
+        <v>16.97</v>
       </c>
       <c r="F22" t="n">
-        <v>38.6501</v>
+        <v>38.4794</v>
       </c>
     </row>
     <row r="23">
@@ -5500,19 +5500,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.8417</v>
+        <v>12.7668</v>
       </c>
       <c r="C23" t="n">
-        <v>17.5312</v>
+        <v>17.4922</v>
       </c>
       <c r="D23" t="n">
-        <v>43.3578</v>
+        <v>43.225</v>
       </c>
       <c r="E23" t="n">
-        <v>16.7031</v>
+        <v>16.5987</v>
       </c>
       <c r="F23" t="n">
-        <v>38.368</v>
+        <v>38.1943</v>
       </c>
     </row>
     <row r="24">
@@ -5520,19 +5520,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>17.4793</v>
+        <v>17.4641</v>
       </c>
       <c r="C24" t="n">
-        <v>17.337</v>
+        <v>17.324</v>
       </c>
       <c r="D24" t="n">
-        <v>43.2257</v>
+        <v>43.1791</v>
       </c>
       <c r="E24" t="n">
-        <v>16.3788</v>
+        <v>16.4032</v>
       </c>
       <c r="F24" t="n">
-        <v>38.0533</v>
+        <v>37.7571</v>
       </c>
     </row>
     <row r="25">
@@ -5540,19 +5540,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>17.1854</v>
+        <v>17.1834</v>
       </c>
       <c r="C25" t="n">
-        <v>17.2339</v>
+        <v>17.1831</v>
       </c>
       <c r="D25" t="n">
-        <v>43.3091</v>
+        <v>43.0896</v>
       </c>
       <c r="E25" t="n">
-        <v>16.1899</v>
+        <v>16.1911</v>
       </c>
       <c r="F25" t="n">
-        <v>37.7216</v>
+        <v>37.4512</v>
       </c>
     </row>
     <row r="26">
@@ -5560,19 +5560,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>16.8594</v>
+        <v>16.8399</v>
       </c>
       <c r="C26" t="n">
-        <v>17.0766</v>
+        <v>17.0996</v>
       </c>
       <c r="D26" t="n">
-        <v>43.2536</v>
+        <v>43.0842</v>
       </c>
       <c r="E26" t="n">
-        <v>15.9659</v>
+        <v>15.9662</v>
       </c>
       <c r="F26" t="n">
-        <v>37.3004</v>
+        <v>37.3886</v>
       </c>
     </row>
     <row r="27">
@@ -5580,19 +5580,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>16.4863</v>
+        <v>16.483</v>
       </c>
       <c r="C27" t="n">
-        <v>16.9531</v>
+        <v>16.9605</v>
       </c>
       <c r="D27" t="n">
-        <v>43.3924</v>
+        <v>43.1547</v>
       </c>
       <c r="E27" t="n">
-        <v>15.7534</v>
+        <v>15.659</v>
       </c>
       <c r="F27" t="n">
-        <v>37.2695</v>
+        <v>37.1146</v>
       </c>
     </row>
     <row r="28">
@@ -5600,19 +5600,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>16.1319</v>
+        <v>16.1276</v>
       </c>
       <c r="C28" t="n">
-        <v>16.881</v>
+        <v>16.8503</v>
       </c>
       <c r="D28" t="n">
-        <v>43.0472</v>
+        <v>43.0853</v>
       </c>
       <c r="E28" t="n">
-        <v>15.5468</v>
+        <v>15.556</v>
       </c>
       <c r="F28" t="n">
-        <v>36.8865</v>
+        <v>36.9174</v>
       </c>
     </row>
     <row r="29">
@@ -5620,19 +5620,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>15.783</v>
+        <v>15.7689</v>
       </c>
       <c r="C29" t="n">
-        <v>16.7115</v>
+        <v>16.7306</v>
       </c>
       <c r="D29" t="n">
-        <v>43.1328</v>
+        <v>43.1932</v>
       </c>
       <c r="E29" t="n">
-        <v>15.4351</v>
+        <v>15.3519</v>
       </c>
       <c r="F29" t="n">
-        <v>36.5712</v>
+        <v>36.6441</v>
       </c>
     </row>
     <row r="30">
@@ -5640,19 +5640,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>15.4579</v>
+        <v>15.4543</v>
       </c>
       <c r="C30" t="n">
-        <v>16.7012</v>
+        <v>16.6853</v>
       </c>
       <c r="D30" t="n">
-        <v>43.2208</v>
+        <v>43.1342</v>
       </c>
       <c r="E30" t="n">
-        <v>15.1829</v>
+        <v>15.1755</v>
       </c>
       <c r="F30" t="n">
-        <v>36.5229</v>
+        <v>36.34</v>
       </c>
     </row>
     <row r="31">
@@ -5660,19 +5660,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>15.1479</v>
+        <v>15.1241</v>
       </c>
       <c r="C31" t="n">
-        <v>16.5737</v>
+        <v>16.5645</v>
       </c>
       <c r="D31" t="n">
-        <v>43.0827</v>
+        <v>43.0055</v>
       </c>
       <c r="E31" t="n">
-        <v>14.9827</v>
+        <v>14.9525</v>
       </c>
       <c r="F31" t="n">
-        <v>36.1181</v>
+        <v>36.1923</v>
       </c>
     </row>
     <row r="32">
@@ -5680,19 +5680,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>14.8431</v>
+        <v>14.8378</v>
       </c>
       <c r="C32" t="n">
-        <v>16.5564</v>
+        <v>16.5382</v>
       </c>
       <c r="D32" t="n">
-        <v>42.8806</v>
+        <v>43.0229</v>
       </c>
       <c r="E32" t="n">
-        <v>14.8203</v>
+        <v>14.7963</v>
       </c>
       <c r="F32" t="n">
-        <v>35.7488</v>
+        <v>35.77</v>
       </c>
     </row>
     <row r="33">
@@ -5700,19 +5700,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>14.5281</v>
+        <v>14.5429</v>
       </c>
       <c r="C33" t="n">
-        <v>16.4297</v>
+        <v>16.4173</v>
       </c>
       <c r="D33" t="n">
-        <v>43.0057</v>
+        <v>42.9263</v>
       </c>
       <c r="E33" t="n">
-        <v>14.5498</v>
+        <v>14.5425</v>
       </c>
       <c r="F33" t="n">
-        <v>35.5303</v>
+        <v>35.4789</v>
       </c>
     </row>
     <row r="34">
@@ -5720,19 +5720,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>14.2621</v>
+        <v>14.2495</v>
       </c>
       <c r="C34" t="n">
-        <v>16.3561</v>
+        <v>16.3671</v>
       </c>
       <c r="D34" t="n">
-        <v>42.8813</v>
+        <v>42.8679</v>
       </c>
       <c r="E34" t="n">
-        <v>14.3636</v>
+        <v>14.3405</v>
       </c>
       <c r="F34" t="n">
-        <v>35.2562</v>
+        <v>35.3687</v>
       </c>
     </row>
     <row r="35">
@@ -5740,19 +5740,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>13.9127</v>
+        <v>13.9561</v>
       </c>
       <c r="C35" t="n">
-        <v>16.3241</v>
+        <v>16.3112</v>
       </c>
       <c r="D35" t="n">
-        <v>43.9536</v>
+        <v>43.8373</v>
       </c>
       <c r="E35" t="n">
-        <v>17.7782</v>
+        <v>17.754</v>
       </c>
       <c r="F35" t="n">
-        <v>39.6254</v>
+        <v>39.3138</v>
       </c>
     </row>
     <row r="36">
@@ -5760,19 +5760,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>13.6378</v>
+        <v>13.6548</v>
       </c>
       <c r="C36" t="n">
-        <v>16.225</v>
+        <v>16.203</v>
       </c>
       <c r="D36" t="n">
-        <v>43.973</v>
+        <v>43.8191</v>
       </c>
       <c r="E36" t="n">
-        <v>17.3839</v>
+        <v>17.4129</v>
       </c>
       <c r="F36" t="n">
-        <v>39.1793</v>
+        <v>38.9517</v>
       </c>
     </row>
     <row r="37">
@@ -5780,19 +5780,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.2016</v>
+        <v>13.1978</v>
       </c>
       <c r="C37" t="n">
-        <v>17.7753</v>
+        <v>17.7603</v>
       </c>
       <c r="D37" t="n">
-        <v>43.6442</v>
+        <v>43.8446</v>
       </c>
       <c r="E37" t="n">
-        <v>17.1115</v>
+        <v>17.0576</v>
       </c>
       <c r="F37" t="n">
-        <v>38.991</v>
+        <v>38.823</v>
       </c>
     </row>
     <row r="38">
@@ -5800,19 +5800,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>17.607</v>
+        <v>17.622</v>
       </c>
       <c r="C38" t="n">
-        <v>17.6091</v>
+        <v>17.606</v>
       </c>
       <c r="D38" t="n">
-        <v>43.6141</v>
+        <v>43.693</v>
       </c>
       <c r="E38" t="n">
-        <v>16.835</v>
+        <v>16.838</v>
       </c>
       <c r="F38" t="n">
-        <v>38.3153</v>
+        <v>38.4074</v>
       </c>
     </row>
     <row r="39">
@@ -5820,19 +5820,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>17.3354</v>
+        <v>17.3389</v>
       </c>
       <c r="C39" t="n">
-        <v>17.4867</v>
+        <v>17.5091</v>
       </c>
       <c r="D39" t="n">
-        <v>43.5026</v>
+        <v>43.6127</v>
       </c>
       <c r="E39" t="n">
-        <v>16.4817</v>
+        <v>16.4826</v>
       </c>
       <c r="F39" t="n">
-        <v>38.1856</v>
+        <v>37.9601</v>
       </c>
     </row>
     <row r="40">
@@ -5840,19 +5840,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>17.0208</v>
+        <v>17.0316</v>
       </c>
       <c r="C40" t="n">
-        <v>17.3742</v>
+        <v>17.3797</v>
       </c>
       <c r="D40" t="n">
-        <v>43.4575</v>
+        <v>43.5852</v>
       </c>
       <c r="E40" t="n">
-        <v>16.2922</v>
+        <v>16.2742</v>
       </c>
       <c r="F40" t="n">
-        <v>37.73</v>
+        <v>37.7392</v>
       </c>
     </row>
     <row r="41">
@@ -5860,19 +5860,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>16.6867</v>
+        <v>16.6804</v>
       </c>
       <c r="C41" t="n">
-        <v>17.1848</v>
+        <v>17.1981</v>
       </c>
       <c r="D41" t="n">
-        <v>43.4961</v>
+        <v>43.484</v>
       </c>
       <c r="E41" t="n">
-        <v>16.0409</v>
+        <v>15.9886</v>
       </c>
       <c r="F41" t="n">
-        <v>37.4491</v>
+        <v>37.4061</v>
       </c>
     </row>
     <row r="42">
@@ -5880,19 +5880,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>16.3438</v>
+        <v>16.3457</v>
       </c>
       <c r="C42" t="n">
-        <v>17.0355</v>
+        <v>17.0274</v>
       </c>
       <c r="D42" t="n">
-        <v>43.5659</v>
+        <v>43.5669</v>
       </c>
       <c r="E42" t="n">
-        <v>15.8576</v>
+        <v>15.77</v>
       </c>
       <c r="F42" t="n">
-        <v>37.0615</v>
+        <v>37.0107</v>
       </c>
     </row>
     <row r="43">
@@ -5900,19 +5900,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>15.9778</v>
+        <v>15.9749</v>
       </c>
       <c r="C43" t="n">
-        <v>16.915</v>
+        <v>16.9143</v>
       </c>
       <c r="D43" t="n">
-        <v>43.4339</v>
+        <v>43.291</v>
       </c>
       <c r="E43" t="n">
-        <v>15.6397</v>
+        <v>15.6249</v>
       </c>
       <c r="F43" t="n">
-        <v>36.8957</v>
+        <v>36.9579</v>
       </c>
     </row>
     <row r="44">
@@ -5920,19 +5920,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>15.616</v>
+        <v>15.5973</v>
       </c>
       <c r="C44" t="n">
-        <v>16.8485</v>
+        <v>16.8179</v>
       </c>
       <c r="D44" t="n">
-        <v>43.3561</v>
+        <v>43.398</v>
       </c>
       <c r="E44" t="n">
-        <v>15.4546</v>
+        <v>15.4075</v>
       </c>
       <c r="F44" t="n">
-        <v>36.7044</v>
+        <v>36.4585</v>
       </c>
     </row>
     <row r="45">
@@ -5940,19 +5940,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>15.257</v>
+        <v>15.2638</v>
       </c>
       <c r="C45" t="n">
-        <v>16.7391</v>
+        <v>16.7198</v>
       </c>
       <c r="D45" t="n">
-        <v>43.183</v>
+        <v>43.2733</v>
       </c>
       <c r="E45" t="n">
-        <v>15.2632</v>
+        <v>15.2613</v>
       </c>
       <c r="F45" t="n">
-        <v>36.3411</v>
+        <v>36.3256</v>
       </c>
     </row>
     <row r="46">
@@ -5960,19 +5960,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>14.9287</v>
+        <v>14.9412</v>
       </c>
       <c r="C46" t="n">
-        <v>16.6221</v>
+        <v>16.6284</v>
       </c>
       <c r="D46" t="n">
-        <v>43.2591</v>
+        <v>43.2341</v>
       </c>
       <c r="E46" t="n">
-        <v>15.0623</v>
+        <v>15.03</v>
       </c>
       <c r="F46" t="n">
-        <v>36.5729</v>
+        <v>35.946</v>
       </c>
     </row>
     <row r="47">
@@ -5980,19 +5980,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>14.6404</v>
+        <v>14.6332</v>
       </c>
       <c r="C47" t="n">
-        <v>16.5381</v>
+        <v>16.5462</v>
       </c>
       <c r="D47" t="n">
-        <v>43.1326</v>
+        <v>43.1067</v>
       </c>
       <c r="E47" t="n">
-        <v>14.8641</v>
+        <v>14.8403</v>
       </c>
       <c r="F47" t="n">
-        <v>35.7457</v>
+        <v>35.7547</v>
       </c>
     </row>
     <row r="48">
@@ -6000,19 +6000,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>14.3538</v>
+        <v>14.3541</v>
       </c>
       <c r="C48" t="n">
-        <v>16.4955</v>
+        <v>16.4802</v>
       </c>
       <c r="D48" t="n">
-        <v>43.1714</v>
+        <v>43.1438</v>
       </c>
       <c r="E48" t="n">
-        <v>14.6071</v>
+        <v>14.5868</v>
       </c>
       <c r="F48" t="n">
-        <v>35.497</v>
+        <v>35.6274</v>
       </c>
     </row>
     <row r="49">
@@ -6020,19 +6020,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>14.0416</v>
+        <v>14.0822</v>
       </c>
       <c r="C49" t="n">
-        <v>16.4144</v>
+        <v>16.4045</v>
       </c>
       <c r="D49" t="n">
-        <v>43.1235</v>
+        <v>43.2062</v>
       </c>
       <c r="E49" t="n">
-        <v>14.3734</v>
+        <v>14.366</v>
       </c>
       <c r="F49" t="n">
-        <v>35.1868</v>
+        <v>35.0424</v>
       </c>
     </row>
     <row r="50">
@@ -6040,19 +6040,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>13.7452</v>
+        <v>13.7137</v>
       </c>
       <c r="C50" t="n">
-        <v>16.3806</v>
+        <v>16.3315</v>
       </c>
       <c r="D50" t="n">
-        <v>44.2824</v>
+        <v>44.1207</v>
       </c>
       <c r="E50" t="n">
-        <v>17.7289</v>
+        <v>17.5694</v>
       </c>
       <c r="F50" t="n">
-        <v>39.6775</v>
+        <v>39.4401</v>
       </c>
     </row>
     <row r="51">
@@ -6060,19 +6060,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>13.3159</v>
+        <v>13.3498</v>
       </c>
       <c r="C51" t="n">
-        <v>17.8547</v>
+        <v>17.8656</v>
       </c>
       <c r="D51" t="n">
-        <v>44.0504</v>
+        <v>44.0869</v>
       </c>
       <c r="E51" t="n">
-        <v>17.291</v>
+        <v>17.2188</v>
       </c>
       <c r="F51" t="n">
-        <v>39.2658</v>
+        <v>39.1854</v>
       </c>
     </row>
     <row r="52">
@@ -6080,19 +6080,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>12.7333</v>
+        <v>12.8062</v>
       </c>
       <c r="C52" t="n">
-        <v>17.6922</v>
+        <v>17.6707</v>
       </c>
       <c r="D52" t="n">
-        <v>44.0755</v>
+        <v>44.0653</v>
       </c>
       <c r="E52" t="n">
-        <v>16.9791</v>
+        <v>16.9603</v>
       </c>
       <c r="F52" t="n">
-        <v>38.9742</v>
+        <v>38.7367</v>
       </c>
     </row>
     <row r="53">
@@ -6100,19 +6100,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>17.4074</v>
+        <v>17.4139</v>
       </c>
       <c r="C53" t="n">
-        <v>17.4833</v>
+        <v>17.4912</v>
       </c>
       <c r="D53" t="n">
-        <v>44.0507</v>
+        <v>43.9065</v>
       </c>
       <c r="E53" t="n">
-        <v>16.7715</v>
+        <v>16.7047</v>
       </c>
       <c r="F53" t="n">
-        <v>38.7097</v>
+        <v>38.3237</v>
       </c>
     </row>
     <row r="54">
@@ -6120,19 +6120,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>17.1125</v>
+        <v>17.1131</v>
       </c>
       <c r="C54" t="n">
-        <v>17.3858</v>
+        <v>17.3972</v>
       </c>
       <c r="D54" t="n">
-        <v>44.1081</v>
+        <v>43.8299</v>
       </c>
       <c r="E54" t="n">
-        <v>16.5198</v>
+        <v>16.46</v>
       </c>
       <c r="F54" t="n">
-        <v>38.4058</v>
+        <v>38.4367</v>
       </c>
     </row>
     <row r="55">
@@ -6140,19 +6140,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>16.7818</v>
+        <v>16.7893</v>
       </c>
       <c r="C55" t="n">
-        <v>17.2637</v>
+        <v>17.256</v>
       </c>
       <c r="D55" t="n">
-        <v>43.9076</v>
+        <v>43.8821</v>
       </c>
       <c r="E55" t="n">
-        <v>16.218</v>
+        <v>16.2371</v>
       </c>
       <c r="F55" t="n">
-        <v>38.2834</v>
+        <v>38.5304</v>
       </c>
     </row>
     <row r="56">
@@ -6160,19 +6160,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>16.4197</v>
+        <v>16.4193</v>
       </c>
       <c r="C56" t="n">
-        <v>17.114</v>
+        <v>17.125</v>
       </c>
       <c r="D56" t="n">
-        <v>44.1096</v>
+        <v>43.8387</v>
       </c>
       <c r="E56" t="n">
-        <v>15.9884</v>
+        <v>16.0062</v>
       </c>
       <c r="F56" t="n">
-        <v>38.3626</v>
+        <v>38.109</v>
       </c>
     </row>
     <row r="57">
@@ -6180,19 +6180,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>16.0543</v>
+        <v>16.045</v>
       </c>
       <c r="C57" t="n">
-        <v>17.0255</v>
+        <v>17.0385</v>
       </c>
       <c r="D57" t="n">
-        <v>44.0514</v>
+        <v>43.8481</v>
       </c>
       <c r="E57" t="n">
-        <v>15.7943</v>
+        <v>15.7788</v>
       </c>
       <c r="F57" t="n">
-        <v>37.7913</v>
+        <v>38.4622</v>
       </c>
     </row>
     <row r="58">
@@ -6200,19 +6200,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>15.7002</v>
+        <v>15.6931</v>
       </c>
       <c r="C58" t="n">
-        <v>16.88</v>
+        <v>16.8784</v>
       </c>
       <c r="D58" t="n">
-        <v>44.388</v>
+        <v>43.9193</v>
       </c>
       <c r="E58" t="n">
-        <v>15.5801</v>
+        <v>15.557</v>
       </c>
       <c r="F58" t="n">
-        <v>37.9832</v>
+        <v>37.8449</v>
       </c>
     </row>
     <row r="59">
@@ -6220,19 +6220,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>15.3456</v>
+        <v>15.3429</v>
       </c>
       <c r="C59" t="n">
-        <v>16.7834</v>
+        <v>16.783</v>
       </c>
       <c r="D59" t="n">
-        <v>44.1498</v>
+        <v>43.8117</v>
       </c>
       <c r="E59" t="n">
-        <v>15.3662</v>
+        <v>15.3318</v>
       </c>
       <c r="F59" t="n">
-        <v>37.9811</v>
+        <v>37.8862</v>
       </c>
     </row>
     <row r="60">
@@ -6240,19 +6240,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>15.0232</v>
+        <v>15.0142</v>
       </c>
       <c r="C60" t="n">
-        <v>16.6944</v>
+        <v>16.6983</v>
       </c>
       <c r="D60" t="n">
-        <v>44.5405</v>
+        <v>44.4636</v>
       </c>
       <c r="E60" t="n">
-        <v>15.1576</v>
+        <v>15.1691</v>
       </c>
       <c r="F60" t="n">
-        <v>37.6057</v>
+        <v>37.7404</v>
       </c>
     </row>
     <row r="61">
@@ -6260,19 +6260,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>14.7195</v>
+        <v>14.717</v>
       </c>
       <c r="C61" t="n">
-        <v>16.6239</v>
+        <v>16.6209</v>
       </c>
       <c r="D61" t="n">
-        <v>44.2402</v>
+        <v>44.474</v>
       </c>
       <c r="E61" t="n">
-        <v>14.9446</v>
+        <v>14.9502</v>
       </c>
       <c r="F61" t="n">
-        <v>38.086</v>
+        <v>37.4624</v>
       </c>
     </row>
     <row r="62">
@@ -6280,19 +6280,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>14.4441</v>
+        <v>14.4596</v>
       </c>
       <c r="C62" t="n">
-        <v>16.5743</v>
+        <v>16.57</v>
       </c>
       <c r="D62" t="n">
-        <v>45.15</v>
+        <v>44.7118</v>
       </c>
       <c r="E62" t="n">
-        <v>14.7035</v>
+        <v>14.7112</v>
       </c>
       <c r="F62" t="n">
-        <v>38.0478</v>
+        <v>38.3028</v>
       </c>
     </row>
     <row r="63">
@@ -6300,19 +6300,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>14.1547</v>
+        <v>14.137</v>
       </c>
       <c r="C63" t="n">
-        <v>16.5035</v>
+        <v>16.4927</v>
       </c>
       <c r="D63" t="n">
-        <v>45.1639</v>
+        <v>45.6514</v>
       </c>
       <c r="E63" t="n">
-        <v>14.5085</v>
+        <v>14.4811</v>
       </c>
       <c r="F63" t="n">
-        <v>38.8214</v>
+        <v>38.3544</v>
       </c>
     </row>
     <row r="64">
@@ -6320,19 +6320,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>13.8519</v>
+        <v>13.8308</v>
       </c>
       <c r="C64" t="n">
-        <v>16.4193</v>
+        <v>16.4211</v>
       </c>
       <c r="D64" t="n">
-        <v>51.0023</v>
+        <v>50.7006</v>
       </c>
       <c r="E64" t="n">
-        <v>19.7453</v>
+        <v>17.8589</v>
       </c>
       <c r="F64" t="n">
-        <v>47.1375</v>
+        <v>47.1284</v>
       </c>
     </row>
     <row r="65">
@@ -6340,19 +6340,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>13.4396</v>
+        <v>13.4365</v>
       </c>
       <c r="C65" t="n">
-        <v>17.9036</v>
+        <v>17.8899</v>
       </c>
       <c r="D65" t="n">
-        <v>51.3046</v>
+        <v>51.0246</v>
       </c>
       <c r="E65" t="n">
-        <v>17.5715</v>
+        <v>17.505</v>
       </c>
       <c r="F65" t="n">
-        <v>47.3736</v>
+        <v>47.3773</v>
       </c>
     </row>
     <row r="66">
@@ -6360,19 +6360,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>12.987</v>
+        <v>13.0074</v>
       </c>
       <c r="C66" t="n">
-        <v>17.7341</v>
+        <v>17.7162</v>
       </c>
       <c r="D66" t="n">
-        <v>51.3703</v>
+        <v>51.4464</v>
       </c>
       <c r="E66" t="n">
-        <v>17.252</v>
+        <v>17.1835</v>
       </c>
       <c r="F66" t="n">
-        <v>47.6659</v>
+        <v>47.7953</v>
       </c>
     </row>
     <row r="67">
@@ -6380,19 +6380,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>17.5413</v>
+        <v>17.5543</v>
       </c>
       <c r="C67" t="n">
-        <v>17.5904</v>
+        <v>17.569</v>
       </c>
       <c r="D67" t="n">
-        <v>52.0535</v>
+        <v>52.2852</v>
       </c>
       <c r="E67" t="n">
-        <v>16.9766</v>
+        <v>16.9225</v>
       </c>
       <c r="F67" t="n">
-        <v>47.9033</v>
+        <v>48.1404</v>
       </c>
     </row>
     <row r="68">
@@ -6400,19 +6400,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>17.2345</v>
+        <v>17.2465</v>
       </c>
       <c r="C68" t="n">
-        <v>17.4336</v>
+        <v>17.4093</v>
       </c>
       <c r="D68" t="n">
-        <v>52.4444</v>
+        <v>52.552</v>
       </c>
       <c r="E68" t="n">
-        <v>16.6997</v>
+        <v>16.7</v>
       </c>
       <c r="F68" t="n">
-        <v>48.3682</v>
+        <v>48.2877</v>
       </c>
     </row>
     <row r="69">
@@ -6420,19 +6420,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>16.8842</v>
+        <v>16.8887</v>
       </c>
       <c r="C69" t="n">
-        <v>17.295</v>
+        <v>17.3061</v>
       </c>
       <c r="D69" t="n">
-        <v>52.8792</v>
+        <v>52.9807</v>
       </c>
       <c r="E69" t="n">
-        <v>16.4326</v>
+        <v>16.4238</v>
       </c>
       <c r="F69" t="n">
-        <v>48.6989</v>
+        <v>48.2993</v>
       </c>
     </row>
     <row r="70">
@@ -6440,19 +6440,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>16.5452</v>
+        <v>16.5332</v>
       </c>
       <c r="C70" t="n">
-        <v>17.1708</v>
+        <v>17.1752</v>
       </c>
       <c r="D70" t="n">
-        <v>53.2234</v>
+        <v>53.1585</v>
       </c>
       <c r="E70" t="n">
-        <v>16.1828</v>
+        <v>16.1605</v>
       </c>
       <c r="F70" t="n">
-        <v>48.4122</v>
+        <v>48.1454</v>
       </c>
     </row>
     <row r="71">
@@ -6460,19 +6460,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>16.1622</v>
+        <v>16.1493</v>
       </c>
       <c r="C71" t="n">
-        <v>17.051</v>
+        <v>17.0377</v>
       </c>
       <c r="D71" t="n">
-        <v>53.3832</v>
+        <v>53.3423</v>
       </c>
       <c r="E71" t="n">
-        <v>15.9543</v>
+        <v>15.933</v>
       </c>
       <c r="F71" t="n">
-        <v>48.2807</v>
+        <v>47.9162</v>
       </c>
     </row>
     <row r="72">
@@ -6480,19 +6480,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>15.8019</v>
+        <v>15.7863</v>
       </c>
       <c r="C72" t="n">
-        <v>16.9428</v>
+        <v>16.9533</v>
       </c>
       <c r="D72" t="n">
-        <v>53.7613</v>
+        <v>53.6159</v>
       </c>
       <c r="E72" t="n">
-        <v>15.7462</v>
+        <v>15.7106</v>
       </c>
       <c r="F72" t="n">
-        <v>48.0893</v>
+        <v>47.7342</v>
       </c>
     </row>
     <row r="73">
@@ -6500,19 +6500,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>15.4388</v>
+        <v>15.4372</v>
       </c>
       <c r="C73" t="n">
-        <v>16.8485</v>
+        <v>16.8496</v>
       </c>
       <c r="D73" t="n">
-        <v>53.9657</v>
+        <v>53.8561</v>
       </c>
       <c r="E73" t="n">
-        <v>15.5026</v>
+        <v>15.5205</v>
       </c>
       <c r="F73" t="n">
-        <v>47.7594</v>
+        <v>47.7337</v>
       </c>
     </row>
     <row r="74">
@@ -6520,19 +6520,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>15.0961</v>
+        <v>15.1059</v>
       </c>
       <c r="C74" t="n">
-        <v>16.7466</v>
+        <v>16.747</v>
       </c>
       <c r="D74" t="n">
-        <v>54.1572</v>
+        <v>54.0378</v>
       </c>
       <c r="E74" t="n">
-        <v>15.3108</v>
+        <v>15.3058</v>
       </c>
       <c r="F74" t="n">
-        <v>47.6639</v>
+        <v>47.5312</v>
       </c>
     </row>
     <row r="75">
@@ -6540,19 +6540,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>14.7956</v>
+        <v>14.7993</v>
       </c>
       <c r="C75" t="n">
-        <v>16.6546</v>
+        <v>16.6778</v>
       </c>
       <c r="D75" t="n">
-        <v>54.3156</v>
+        <v>54.2983</v>
       </c>
       <c r="E75" t="n">
-        <v>15.0662</v>
+        <v>15.0578</v>
       </c>
       <c r="F75" t="n">
-        <v>47.2275</v>
+        <v>47.2881</v>
       </c>
     </row>
     <row r="76">
@@ -6560,19 +6560,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>14.491</v>
+        <v>14.4876</v>
       </c>
       <c r="C76" t="n">
-        <v>16.5819</v>
+        <v>16.5939</v>
       </c>
       <c r="D76" t="n">
-        <v>54.4768</v>
+        <v>54.5247</v>
       </c>
       <c r="E76" t="n">
-        <v>14.836</v>
+        <v>14.8412</v>
       </c>
       <c r="F76" t="n">
-        <v>47.0009</v>
+        <v>47.0291</v>
       </c>
     </row>
     <row r="77">
@@ -6580,19 +6580,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>14.1895</v>
+        <v>14.2275</v>
       </c>
       <c r="C77" t="n">
-        <v>16.5211</v>
+        <v>16.5166</v>
       </c>
       <c r="D77" t="n">
-        <v>54.4986</v>
+        <v>54.5211</v>
       </c>
       <c r="E77" t="n">
-        <v>14.5936</v>
+        <v>14.6117</v>
       </c>
       <c r="F77" t="n">
-        <v>46.8658</v>
+        <v>46.7806</v>
       </c>
     </row>
     <row r="78">
@@ -6600,19 +6600,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>13.9156</v>
+        <v>13.878</v>
       </c>
       <c r="C78" t="n">
-        <v>16.431</v>
+        <v>16.4326</v>
       </c>
       <c r="D78" t="n">
-        <v>57.5132</v>
+        <v>57.4647</v>
       </c>
       <c r="E78" t="n">
-        <v>18.2879</v>
+        <v>17.9401</v>
       </c>
       <c r="F78" t="n">
-        <v>51.0628</v>
+        <v>50.939</v>
       </c>
     </row>
     <row r="79">
@@ -6620,19 +6620,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>13.5609</v>
+        <v>13.5554</v>
       </c>
       <c r="C79" t="n">
-        <v>17.9811</v>
+        <v>17.9893</v>
       </c>
       <c r="D79" t="n">
-        <v>57.2526</v>
+        <v>57.4901</v>
       </c>
       <c r="E79" t="n">
-        <v>17.669</v>
+        <v>17.6669</v>
       </c>
       <c r="F79" t="n">
-        <v>50.7649</v>
+        <v>50.615</v>
       </c>
     </row>
     <row r="80">
@@ -6640,19 +6640,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>13.0811</v>
+        <v>13.1261</v>
       </c>
       <c r="C80" t="n">
-        <v>17.8026</v>
+        <v>17.7893</v>
       </c>
       <c r="D80" t="n">
-        <v>57.3181</v>
+        <v>57.2599</v>
       </c>
       <c r="E80" t="n">
-        <v>17.3426</v>
+        <v>17.282</v>
       </c>
       <c r="F80" t="n">
-        <v>50.4211</v>
+        <v>50.3227</v>
       </c>
     </row>
     <row r="81">
@@ -6663,16 +6663,16 @@
         <v>17.6636</v>
       </c>
       <c r="C81" t="n">
-        <v>17.6582</v>
+        <v>17.64</v>
       </c>
       <c r="D81" t="n">
-        <v>57.2157</v>
+        <v>57.3005</v>
       </c>
       <c r="E81" t="n">
-        <v>17.0784</v>
+        <v>16.9628</v>
       </c>
       <c r="F81" t="n">
-        <v>50.0431</v>
+        <v>50.036</v>
       </c>
     </row>
     <row r="82">
@@ -6680,19 +6680,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>17.3468</v>
+        <v>17.3545</v>
       </c>
       <c r="C82" t="n">
-        <v>17.4725</v>
+        <v>17.4935</v>
       </c>
       <c r="D82" t="n">
-        <v>57.2757</v>
+        <v>57.2923</v>
       </c>
       <c r="E82" t="n">
-        <v>16.8153</v>
+        <v>16.7844</v>
       </c>
       <c r="F82" t="n">
-        <v>49.8785</v>
+        <v>49.7747</v>
       </c>
     </row>
     <row r="83">
@@ -6700,19 +6700,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>17.0036</v>
+        <v>17.0076</v>
       </c>
       <c r="C83" t="n">
-        <v>17.343</v>
+        <v>17.3404</v>
       </c>
       <c r="D83" t="n">
-        <v>57.2038</v>
+        <v>57.4042</v>
       </c>
       <c r="E83" t="n">
-        <v>16.5157</v>
+        <v>16.5476</v>
       </c>
       <c r="F83" t="n">
-        <v>49.6261</v>
+        <v>49.3419</v>
       </c>
     </row>
     <row r="84">
@@ -6720,19 +6720,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>16.6251</v>
+        <v>16.6576</v>
       </c>
       <c r="C84" t="n">
-        <v>17.2252</v>
+        <v>17.2337</v>
       </c>
       <c r="D84" t="n">
-        <v>60.9245</v>
+        <v>60.8584</v>
       </c>
       <c r="E84" t="n">
-        <v>16.2687</v>
+        <v>16.2283</v>
       </c>
       <c r="F84" t="n">
-        <v>54.1092</v>
+        <v>53.8967</v>
       </c>
     </row>
     <row r="85">
@@ -6740,19 +6740,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>16.2596</v>
+        <v>16.2613</v>
       </c>
       <c r="C85" t="n">
-        <v>17.0811</v>
+        <v>17.102</v>
       </c>
       <c r="D85" t="n">
-        <v>60.7236</v>
+        <v>60.6628</v>
       </c>
       <c r="E85" t="n">
-        <v>16.0387</v>
+        <v>16.0368</v>
       </c>
       <c r="F85" t="n">
-        <v>53.5683</v>
+        <v>53.6046</v>
       </c>
     </row>
     <row r="86">
@@ -6760,19 +6760,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>15.883</v>
+        <v>15.8853</v>
       </c>
       <c r="C86" t="n">
-        <v>16.9606</v>
+        <v>16.9965</v>
       </c>
       <c r="D86" t="n">
-        <v>60.7585</v>
+        <v>60.8131</v>
       </c>
       <c r="E86" t="n">
-        <v>15.7889</v>
+        <v>15.7732</v>
       </c>
       <c r="F86" t="n">
-        <v>53.2879</v>
+        <v>53.5903</v>
       </c>
     </row>
     <row r="87">
@@ -6780,19 +6780,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>15.5247</v>
+        <v>15.5315</v>
       </c>
       <c r="C87" t="n">
-        <v>16.8891</v>
+        <v>16.8852</v>
       </c>
       <c r="D87" t="n">
-        <v>60.8016</v>
+        <v>60.8223</v>
       </c>
       <c r="E87" t="n">
-        <v>15.595</v>
+        <v>15.5638</v>
       </c>
       <c r="F87" t="n">
-        <v>53.5695</v>
+        <v>53.1424</v>
       </c>
     </row>
     <row r="88">
@@ -6800,19 +6800,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>15.1789</v>
+        <v>15.1965</v>
       </c>
       <c r="C88" t="n">
-        <v>16.7783</v>
+        <v>16.7958</v>
       </c>
       <c r="D88" t="n">
-        <v>60.9001</v>
+        <v>60.8997</v>
       </c>
       <c r="E88" t="n">
-        <v>15.3536</v>
+        <v>15.3478</v>
       </c>
       <c r="F88" t="n">
-        <v>52.9726</v>
+        <v>52.7695</v>
       </c>
     </row>
     <row r="89">
@@ -6820,19 +6820,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>14.8697</v>
+        <v>14.8742</v>
       </c>
       <c r="C89" t="n">
-        <v>16.6833</v>
+        <v>16.6917</v>
       </c>
       <c r="D89" t="n">
-        <v>60.823</v>
+        <v>60.7298</v>
       </c>
       <c r="E89" t="n">
-        <v>15.1153</v>
+        <v>15.1136</v>
       </c>
       <c r="F89" t="n">
-        <v>52.6977</v>
+        <v>52.4342</v>
       </c>
     </row>
     <row r="90">
@@ -6840,19 +6840,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>14.5559</v>
+        <v>14.5612</v>
       </c>
       <c r="C90" t="n">
-        <v>16.6082</v>
+        <v>16.6043</v>
       </c>
       <c r="D90" t="n">
-        <v>60.7676</v>
+        <v>60.7765</v>
       </c>
       <c r="E90" t="n">
-        <v>14.9099</v>
+        <v>14.8857</v>
       </c>
       <c r="F90" t="n">
-        <v>52.2705</v>
+        <v>52.1736</v>
       </c>
     </row>
     <row r="91">
@@ -6860,19 +6860,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>14.2539</v>
+        <v>14.266</v>
       </c>
       <c r="C91" t="n">
-        <v>16.5285</v>
+        <v>16.5249</v>
       </c>
       <c r="D91" t="n">
-        <v>60.6833</v>
+        <v>60.6839</v>
       </c>
       <c r="E91" t="n">
-        <v>14.6498</v>
+        <v>14.6424</v>
       </c>
       <c r="F91" t="n">
-        <v>51.9667</v>
+        <v>51.682</v>
       </c>
     </row>
     <row r="92">
@@ -6880,19 +6880,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>14.003</v>
+        <v>13.9486</v>
       </c>
       <c r="C92" t="n">
-        <v>16.442</v>
+        <v>16.4539</v>
       </c>
       <c r="D92" t="n">
-        <v>60.962</v>
+        <v>61.0428</v>
       </c>
       <c r="E92" t="n">
-        <v>20.2426</v>
+        <v>18.2336</v>
       </c>
       <c r="F92" t="n">
-        <v>55.9464</v>
+        <v>55.9651</v>
       </c>
     </row>
     <row r="93">
@@ -6900,19 +6900,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>13.6168</v>
+        <v>13.6059</v>
       </c>
       <c r="C93" t="n">
-        <v>16.3756</v>
+        <v>16.3925</v>
       </c>
       <c r="D93" t="n">
-        <v>61.2383</v>
+        <v>60.7887</v>
       </c>
       <c r="E93" t="n">
-        <v>20.6794</v>
+        <v>17.7019</v>
       </c>
       <c r="F93" t="n">
-        <v>55.7391</v>
+        <v>55.716</v>
       </c>
     </row>
     <row r="94">
@@ -6920,19 +6920,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>13.197</v>
+        <v>13.1887</v>
       </c>
       <c r="C94" t="n">
-        <v>17.8457</v>
+        <v>17.8202</v>
       </c>
       <c r="D94" t="n">
-        <v>61.291</v>
+        <v>60.8757</v>
       </c>
       <c r="E94" t="n">
-        <v>18.3686</v>
+        <v>17.3878</v>
       </c>
       <c r="F94" t="n">
-        <v>55.5435</v>
+        <v>55.2738</v>
       </c>
     </row>
     <row r="95">
@@ -6940,19 +6940,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>17.6917</v>
+        <v>17.7133</v>
       </c>
       <c r="C95" t="n">
-        <v>17.6654</v>
+        <v>17.6543</v>
       </c>
       <c r="D95" t="n">
-        <v>60.8036</v>
+        <v>60.8157</v>
       </c>
       <c r="E95" t="n">
-        <v>17.4138</v>
+        <v>17.0494</v>
       </c>
       <c r="F95" t="n">
-        <v>55.2558</v>
+        <v>54.9087</v>
       </c>
     </row>
     <row r="96">
@@ -6960,19 +6960,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>17.3989</v>
+        <v>17.4059</v>
       </c>
       <c r="C96" t="n">
-        <v>17.5065</v>
+        <v>17.4997</v>
       </c>
       <c r="D96" t="n">
-        <v>60.6928</v>
+        <v>60.6767</v>
       </c>
       <c r="E96" t="n">
-        <v>17.0513</v>
+        <v>16.8128</v>
       </c>
       <c r="F96" t="n">
-        <v>54.6701</v>
+        <v>54.8467</v>
       </c>
     </row>
     <row r="97">
@@ -6980,19 +6980,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>17.0665</v>
+        <v>17.0829</v>
       </c>
       <c r="C97" t="n">
-        <v>17.3625</v>
+        <v>17.3572</v>
       </c>
       <c r="D97" t="n">
-        <v>60.7511</v>
+        <v>60.816</v>
       </c>
       <c r="E97" t="n">
-        <v>16.5652</v>
+        <v>16.5518</v>
       </c>
       <c r="F97" t="n">
-        <v>54.4805</v>
+        <v>54.4691</v>
       </c>
     </row>
     <row r="98">
@@ -7000,19 +7000,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>16.7011</v>
+        <v>16.7118</v>
       </c>
       <c r="C98" t="n">
-        <v>17.21</v>
+        <v>17.2352</v>
       </c>
       <c r="D98" t="n">
-        <v>60.8591</v>
+        <v>60.583</v>
       </c>
       <c r="E98" t="n">
-        <v>16.4985</v>
+        <v>16.2971</v>
       </c>
       <c r="F98" t="n">
-        <v>54.2799</v>
+        <v>54.0676</v>
       </c>
     </row>
     <row r="99">
@@ -7020,19 +7020,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>16.3422</v>
+        <v>16.3431</v>
       </c>
       <c r="C99" t="n">
-        <v>17.1001</v>
+        <v>17.1071</v>
       </c>
       <c r="D99" t="n">
-        <v>60.9286</v>
+        <v>60.6779</v>
       </c>
       <c r="E99" t="n">
-        <v>16.1877</v>
+        <v>16.0744</v>
       </c>
       <c r="F99" t="n">
-        <v>53.9087</v>
+        <v>53.9253</v>
       </c>
     </row>
     <row r="100">
@@ -7040,19 +7040,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>15.9665</v>
+        <v>15.9685</v>
       </c>
       <c r="C100" t="n">
-        <v>17.0085</v>
+        <v>17.0032</v>
       </c>
       <c r="D100" t="n">
-        <v>60.6865</v>
+        <v>60.4404</v>
       </c>
       <c r="E100" t="n">
-        <v>15.843</v>
+        <v>15.8395</v>
       </c>
       <c r="F100" t="n">
-        <v>53.3628</v>
+        <v>53.523</v>
       </c>
     </row>
     <row r="101">
@@ -7060,19 +7060,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>15.6051</v>
+        <v>15.6045</v>
       </c>
       <c r="C101" t="n">
-        <v>16.8864</v>
+        <v>16.8799</v>
       </c>
       <c r="D101" t="n">
-        <v>60.5511</v>
+        <v>60.4214</v>
       </c>
       <c r="E101" t="n">
-        <v>15.6115</v>
+        <v>15.6409</v>
       </c>
       <c r="F101" t="n">
-        <v>53.2102</v>
+        <v>53.1324</v>
       </c>
     </row>
     <row r="102">
@@ -7080,19 +7080,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>15.2618</v>
+        <v>15.2544</v>
       </c>
       <c r="C102" t="n">
-        <v>16.7957</v>
+        <v>16.805</v>
       </c>
       <c r="D102" t="n">
-        <v>60.6266</v>
+        <v>60.4919</v>
       </c>
       <c r="E102" t="n">
-        <v>15.4203</v>
+        <v>15.3967</v>
       </c>
       <c r="F102" t="n">
-        <v>52.9865</v>
+        <v>52.9328</v>
       </c>
     </row>
     <row r="103">
@@ -7100,19 +7100,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>14.9246</v>
+        <v>14.9385</v>
       </c>
       <c r="C103" t="n">
-        <v>16.7021</v>
+        <v>16.6987</v>
       </c>
       <c r="D103" t="n">
-        <v>60.5957</v>
+        <v>60.3516</v>
       </c>
       <c r="E103" t="n">
-        <v>15.1765</v>
+        <v>15.1464</v>
       </c>
       <c r="F103" t="n">
-        <v>52.6945</v>
+        <v>52.545</v>
       </c>
     </row>
     <row r="104">
@@ -7120,19 +7120,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>14.6251</v>
+        <v>14.6212</v>
       </c>
       <c r="C104" t="n">
-        <v>16.6204</v>
+        <v>16.6101</v>
       </c>
       <c r="D104" t="n">
-        <v>60.5179</v>
+        <v>60.2775</v>
       </c>
       <c r="E104" t="n">
-        <v>14.9116</v>
+        <v>14.9314</v>
       </c>
       <c r="F104" t="n">
-        <v>52.4584</v>
+        <v>52.2983</v>
       </c>
     </row>
     <row r="105">
@@ -7140,19 +7140,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>14.3151</v>
+        <v>14.3237</v>
       </c>
       <c r="C105" t="n">
-        <v>16.5305</v>
+        <v>16.5573</v>
       </c>
       <c r="D105" t="n">
-        <v>60.357</v>
+        <v>60.3411</v>
       </c>
       <c r="E105" t="n">
-        <v>14.7009</v>
+        <v>14.7017</v>
       </c>
       <c r="F105" t="n">
-        <v>51.7684</v>
+        <v>52.0394</v>
       </c>
     </row>
     <row r="106">
@@ -7160,19 +7160,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>13.9969</v>
+        <v>14.0078</v>
       </c>
       <c r="C106" t="n">
-        <v>16.4574</v>
+        <v>16.4663</v>
       </c>
       <c r="D106" t="n">
-        <v>60.315</v>
+        <v>60.2101</v>
       </c>
       <c r="E106" t="n">
-        <v>14.4381</v>
+        <v>14.4465</v>
       </c>
       <c r="F106" t="n">
-        <v>51.7776</v>
+        <v>51.6148</v>
       </c>
     </row>
     <row r="107">
@@ -7180,19 +7180,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>13.6527</v>
+        <v>13.6567</v>
       </c>
       <c r="C107" t="n">
-        <v>16.3725</v>
+        <v>16.4031</v>
       </c>
       <c r="D107" t="n">
-        <v>59.3668</v>
+        <v>59.1759</v>
       </c>
       <c r="E107" t="n">
-        <v>19.6779</v>
+        <v>18.0072</v>
       </c>
       <c r="F107" t="n">
-        <v>55.7943</v>
+        <v>55.6086</v>
       </c>
     </row>
     <row r="108">
@@ -7200,19 +7200,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>13.2427</v>
+        <v>13.2803</v>
       </c>
       <c r="C108" t="n">
-        <v>17.8695</v>
+        <v>17.8481</v>
       </c>
       <c r="D108" t="n">
-        <v>59.5172</v>
+        <v>59.1593</v>
       </c>
       <c r="E108" t="n">
-        <v>17.9274</v>
+        <v>17.4508</v>
       </c>
       <c r="F108" t="n">
-        <v>55.5262</v>
+        <v>55.5592</v>
       </c>
     </row>
     <row r="109">
@@ -7220,19 +7220,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>12.7671</v>
+        <v>12.7476</v>
       </c>
       <c r="C109" t="n">
-        <v>17.6825</v>
+        <v>17.7114</v>
       </c>
       <c r="D109" t="n">
-        <v>59.4397</v>
+        <v>59.2915</v>
       </c>
       <c r="E109" t="n">
-        <v>17.2041</v>
+        <v>17.147</v>
       </c>
       <c r="F109" t="n">
-        <v>55.0523</v>
+        <v>55.2367</v>
       </c>
     </row>
     <row r="110">
@@ -7240,19 +7240,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>17.4678</v>
+        <v>17.4821</v>
       </c>
       <c r="C110" t="n">
-        <v>17.518</v>
+        <v>17.5223</v>
       </c>
       <c r="D110" t="n">
-        <v>59.3139</v>
+        <v>59.4168</v>
       </c>
       <c r="E110" t="n">
-        <v>18.3156</v>
+        <v>16.8929</v>
       </c>
       <c r="F110" t="n">
-        <v>54.9519</v>
+        <v>54.6803</v>
       </c>
     </row>
     <row r="111">
@@ -7260,19 +7260,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>17.1399</v>
+        <v>17.1414</v>
       </c>
       <c r="C111" t="n">
-        <v>17.3706</v>
+        <v>17.393</v>
       </c>
       <c r="D111" t="n">
-        <v>59.5312</v>
+        <v>59.4233</v>
       </c>
       <c r="E111" t="n">
-        <v>17.8331</v>
+        <v>16.6317</v>
       </c>
       <c r="F111" t="n">
-        <v>54.599</v>
+        <v>54.3256</v>
       </c>
     </row>
     <row r="112">
@@ -7280,19 +7280,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>16.7911</v>
+        <v>16.7876</v>
       </c>
       <c r="C112" t="n">
-        <v>17.251</v>
+        <v>17.2598</v>
       </c>
       <c r="D112" t="n">
-        <v>59.6644</v>
+        <v>59.342</v>
       </c>
       <c r="E112" t="n">
-        <v>17.2713</v>
+        <v>16.3628</v>
       </c>
       <c r="F112" t="n">
-        <v>54.4319</v>
+        <v>54.2005</v>
       </c>
     </row>
     <row r="113">
@@ -7300,19 +7300,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>16.4215</v>
+        <v>16.4197</v>
       </c>
       <c r="C113" t="n">
-        <v>17.1274</v>
+        <v>17.1184</v>
       </c>
       <c r="D113" t="n">
-        <v>59.5957</v>
+        <v>59.3833</v>
       </c>
       <c r="E113" t="n">
-        <v>16.2084</v>
+        <v>16.1045</v>
       </c>
       <c r="F113" t="n">
-        <v>53.9128</v>
+        <v>53.8965</v>
       </c>
     </row>
     <row r="114">
@@ -7320,19 +7320,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>16.035</v>
+        <v>16.0506</v>
       </c>
       <c r="C114" t="n">
-        <v>16.9997</v>
+        <v>17.0065</v>
       </c>
       <c r="D114" t="n">
-        <v>59.5091</v>
+        <v>59.4785</v>
       </c>
       <c r="E114" t="n">
-        <v>16.0863</v>
+        <v>15.8846</v>
       </c>
       <c r="F114" t="n">
-        <v>53.5735</v>
+        <v>53.3575</v>
       </c>
     </row>
     <row r="115">
@@ -7340,19 +7340,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>15.6696</v>
+        <v>15.6792</v>
       </c>
       <c r="C115" t="n">
-        <v>16.8919</v>
+        <v>16.9111</v>
       </c>
       <c r="D115" t="n">
-        <v>59.5729</v>
+        <v>59.4069</v>
       </c>
       <c r="E115" t="n">
-        <v>15.6828</v>
+        <v>15.6661</v>
       </c>
       <c r="F115" t="n">
-        <v>53.3453</v>
+        <v>53.1414</v>
       </c>
     </row>
     <row r="116">
@@ -7360,19 +7360,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>15.3106</v>
+        <v>15.3242</v>
       </c>
       <c r="C116" t="n">
-        <v>16.7799</v>
+        <v>16.8062</v>
       </c>
       <c r="D116" t="n">
-        <v>59.5211</v>
+        <v>59.5765</v>
       </c>
       <c r="E116" t="n">
-        <v>15.694</v>
+        <v>15.437</v>
       </c>
       <c r="F116" t="n">
-        <v>53.1106</v>
+        <v>52.7524</v>
       </c>
     </row>
     <row r="117">
@@ -7380,19 +7380,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>15.0072</v>
+        <v>15.0024</v>
       </c>
       <c r="C117" t="n">
-        <v>16.6975</v>
+        <v>16.7094</v>
       </c>
       <c r="D117" t="n">
-        <v>59.5496</v>
+        <v>59.4864</v>
       </c>
       <c r="E117" t="n">
-        <v>15.2179</v>
+        <v>15.2126</v>
       </c>
       <c r="F117" t="n">
-        <v>52.5971</v>
+        <v>52.4544</v>
       </c>
     </row>
     <row r="118">
@@ -7400,19 +7400,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>14.6763</v>
+        <v>14.6803</v>
       </c>
       <c r="C118" t="n">
-        <v>16.617</v>
+        <v>16.609</v>
       </c>
       <c r="D118" t="n">
-        <v>59.6331</v>
+        <v>59.6947</v>
       </c>
       <c r="E118" t="n">
-        <v>14.9748</v>
+        <v>14.9662</v>
       </c>
       <c r="F118" t="n">
-        <v>52.2282</v>
+        <v>52.2782</v>
       </c>
     </row>
     <row r="119">
@@ -7420,19 +7420,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>14.3597</v>
+        <v>14.3817</v>
       </c>
       <c r="C119" t="n">
-        <v>16.536</v>
+        <v>16.5506</v>
       </c>
       <c r="D119" t="n">
-        <v>59.617</v>
+        <v>59.5204</v>
       </c>
       <c r="E119" t="n">
-        <v>14.7294</v>
+        <v>14.7497</v>
       </c>
       <c r="F119" t="n">
-        <v>52.0821</v>
+        <v>51.8554</v>
       </c>
     </row>
     <row r="120">
@@ -7440,19 +7440,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>14.0732</v>
+        <v>14.0598</v>
       </c>
       <c r="C120" t="n">
-        <v>16.4645</v>
+        <v>16.4801</v>
       </c>
       <c r="D120" t="n">
-        <v>59.6687</v>
+        <v>59.5125</v>
       </c>
       <c r="E120" t="n">
-        <v>15.2133</v>
+        <v>14.4898</v>
       </c>
       <c r="F120" t="n">
-        <v>51.6319</v>
+        <v>51.5256</v>
       </c>
     </row>
     <row r="121">
@@ -7460,19 +7460,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>13.7339</v>
+        <v>13.7302</v>
       </c>
       <c r="C121" t="n">
-        <v>16.4204</v>
+        <v>16.398</v>
       </c>
       <c r="D121" t="n">
-        <v>61.7389</v>
+        <v>61.5402</v>
       </c>
       <c r="E121" t="n">
-        <v>19.086</v>
+        <v>18.1664</v>
       </c>
       <c r="F121" t="n">
-        <v>55.5135</v>
+        <v>55.6291</v>
       </c>
     </row>
     <row r="122">
@@ -7480,19 +7480,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>13.3912</v>
+        <v>13.3232</v>
       </c>
       <c r="C122" t="n">
-        <v>17.8871</v>
+        <v>17.8787</v>
       </c>
       <c r="D122" t="n">
-        <v>61.4593</v>
+        <v>61.3672</v>
       </c>
       <c r="E122" t="n">
-        <v>18.2615</v>
+        <v>19.1967</v>
       </c>
       <c r="F122" t="n">
-        <v>55.2433</v>
+        <v>55.348</v>
       </c>
     </row>
     <row r="123">
@@ -7500,19 +7500,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>12.8714</v>
+        <v>12.8314</v>
       </c>
       <c r="C123" t="n">
-        <v>17.7145</v>
+        <v>17.7107</v>
       </c>
       <c r="D123" t="n">
-        <v>61.5998</v>
+        <v>61.3849</v>
       </c>
       <c r="E123" t="n">
-        <v>18.0481</v>
+        <v>17.4319</v>
       </c>
       <c r="F123" t="n">
-        <v>55.027</v>
+        <v>55.0906</v>
       </c>
     </row>
     <row r="124">
@@ -7520,19 +7520,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>17.538</v>
+        <v>17.5257</v>
       </c>
       <c r="C124" t="n">
-        <v>17.5365</v>
+        <v>17.5462</v>
       </c>
       <c r="D124" t="n">
-        <v>61.2665</v>
+        <v>61.2699</v>
       </c>
       <c r="E124" t="n">
-        <v>17.8825</v>
+        <v>17.0811</v>
       </c>
       <c r="F124" t="n">
-        <v>55.0842</v>
+        <v>54.5325</v>
       </c>
     </row>
     <row r="125">
@@ -7540,19 +7540,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>17.2062</v>
+        <v>17.2191</v>
       </c>
       <c r="C125" t="n">
-        <v>17.3874</v>
+        <v>17.4017</v>
       </c>
       <c r="D125" t="n">
-        <v>61.4218</v>
+        <v>61.1693</v>
       </c>
       <c r="E125" t="n">
-        <v>17.7798</v>
+        <v>16.75</v>
       </c>
       <c r="F125" t="n">
-        <v>54.387</v>
+        <v>54.2607</v>
       </c>
     </row>
     <row r="126">
@@ -7560,19 +7560,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>16.8742</v>
+        <v>16.8552</v>
       </c>
       <c r="C126" t="n">
-        <v>17.2591</v>
+        <v>17.2586</v>
       </c>
       <c r="D126" t="n">
-        <v>61.2411</v>
+        <v>61.1453</v>
       </c>
       <c r="E126" t="n">
-        <v>17.1537</v>
+        <v>16.5962</v>
       </c>
       <c r="F126" t="n">
-        <v>53.9881</v>
+        <v>54.094</v>
       </c>
     </row>
     <row r="127">
@@ -7580,19 +7580,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>16.4911</v>
+        <v>16.4902</v>
       </c>
       <c r="C127" t="n">
-        <v>17.1364</v>
+        <v>17.1225</v>
       </c>
       <c r="D127" t="n">
-        <v>61.1949</v>
+        <v>61.1344</v>
       </c>
       <c r="E127" t="n">
-        <v>16.9464</v>
+        <v>16.1852</v>
       </c>
       <c r="F127" t="n">
-        <v>53.7416</v>
+        <v>53.7088</v>
       </c>
     </row>
     <row r="128">
@@ -7600,19 +7600,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>16.1081</v>
+        <v>16.1326</v>
       </c>
       <c r="C128" t="n">
-        <v>17.0059</v>
+        <v>17.0148</v>
       </c>
       <c r="D128" t="n">
-        <v>61.1689</v>
+        <v>60.9771</v>
       </c>
       <c r="E128" t="n">
-        <v>16.1071</v>
+        <v>15.9509</v>
       </c>
       <c r="F128" t="n">
-        <v>53.5558</v>
+        <v>53.0313</v>
       </c>
     </row>
     <row r="129">
@@ -7620,19 +7620,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>15.7332</v>
+        <v>15.755</v>
       </c>
       <c r="C129" t="n">
-        <v>16.9019</v>
+        <v>16.9063</v>
       </c>
       <c r="D129" t="n">
-        <v>61.0144</v>
+        <v>60.9593</v>
       </c>
       <c r="E129" t="n">
-        <v>16.6126</v>
+        <v>15.7427</v>
       </c>
       <c r="F129" t="n">
-        <v>53.1788</v>
+        <v>53.0183</v>
       </c>
     </row>
     <row r="130">
@@ -7640,19 +7640,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>15.3974</v>
+        <v>15.3852</v>
       </c>
       <c r="C130" t="n">
-        <v>16.8022</v>
+        <v>16.8074</v>
       </c>
       <c r="D130" t="n">
-        <v>60.9263</v>
+        <v>60.8698</v>
       </c>
       <c r="E130" t="n">
-        <v>15.5386</v>
+        <v>15.5124</v>
       </c>
       <c r="F130" t="n">
-        <v>52.7481</v>
+        <v>52.5445</v>
       </c>
     </row>
     <row r="131">
@@ -7660,19 +7660,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>15.063</v>
+        <v>15.0486</v>
       </c>
       <c r="C131" t="n">
-        <v>16.715</v>
+        <v>16.6989</v>
       </c>
       <c r="D131" t="n">
-        <v>60.7671</v>
+        <v>60.7233</v>
       </c>
       <c r="E131" t="n">
-        <v>15.2863</v>
+        <v>15.2931</v>
       </c>
       <c r="F131" t="n">
-        <v>52.4012</v>
+        <v>52.4278</v>
       </c>
     </row>
     <row r="132">
@@ -7680,19 +7680,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>14.7468</v>
+        <v>14.7334</v>
       </c>
       <c r="C132" t="n">
-        <v>16.6282</v>
+        <v>16.6321</v>
       </c>
       <c r="D132" t="n">
-        <v>60.7892</v>
+        <v>60.6929</v>
       </c>
       <c r="E132" t="n">
-        <v>15.0343</v>
+        <v>15.0467</v>
       </c>
       <c r="F132" t="n">
-        <v>52.1591</v>
+        <v>52.0637</v>
       </c>
     </row>
     <row r="133">
@@ -7700,19 +7700,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>14.4315</v>
+        <v>14.4309</v>
       </c>
       <c r="C133" t="n">
-        <v>16.5482</v>
+        <v>16.5404</v>
       </c>
       <c r="D133" t="n">
-        <v>60.718</v>
+        <v>60.6841</v>
       </c>
       <c r="E133" t="n">
-        <v>14.7941</v>
+        <v>14.7853</v>
       </c>
       <c r="F133" t="n">
-        <v>51.8833</v>
+        <v>51.7322</v>
       </c>
     </row>
     <row r="134">
@@ -7720,19 +7720,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.138</v>
+        <v>14.1127</v>
       </c>
       <c r="C134" t="n">
-        <v>16.4826</v>
+        <v>16.456</v>
       </c>
       <c r="D134" t="n">
-        <v>60.6902</v>
+        <v>60.6029</v>
       </c>
       <c r="E134" t="n">
-        <v>14.5679</v>
+        <v>14.5439</v>
       </c>
       <c r="F134" t="n">
-        <v>51.5035</v>
+        <v>51.4843</v>
       </c>
     </row>
     <row r="135">
@@ -7740,19 +7740,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>13.7738</v>
+        <v>13.8188</v>
       </c>
       <c r="C135" t="n">
-        <v>16.3994</v>
+        <v>16.4151</v>
       </c>
       <c r="D135" t="n">
-        <v>62.1486</v>
+        <v>62.0636</v>
       </c>
       <c r="E135" t="n">
-        <v>20.8787</v>
+        <v>18.4572</v>
       </c>
       <c r="F135" t="n">
-        <v>55.5496</v>
+        <v>55.8021</v>
       </c>
     </row>
     <row r="136">
@@ -7760,19 +7760,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>13.4721</v>
+        <v>13.4026</v>
       </c>
       <c r="C136" t="n">
-        <v>17.8992</v>
+        <v>17.896</v>
       </c>
       <c r="D136" t="n">
-        <v>61.8856</v>
+        <v>61.8873</v>
       </c>
       <c r="E136" t="n">
-        <v>20.3903</v>
+        <v>17.988</v>
       </c>
       <c r="F136" t="n">
-        <v>55.1765</v>
+        <v>55.1394</v>
       </c>
     </row>
     <row r="137">
@@ -7780,19 +7780,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>12.927</v>
+        <v>12.9312</v>
       </c>
       <c r="C137" t="n">
-        <v>17.712</v>
+        <v>17.7318</v>
       </c>
       <c r="D137" t="n">
-        <v>61.8337</v>
+        <v>61.7333</v>
       </c>
       <c r="E137" t="n">
-        <v>19.8377</v>
+        <v>18.2298</v>
       </c>
       <c r="F137" t="n">
-        <v>54.7085</v>
+        <v>54.9421</v>
       </c>
     </row>
     <row r="138">
@@ -7800,19 +7800,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>17.6137</v>
+        <v>17.588</v>
       </c>
       <c r="C138" t="n">
-        <v>17.5755</v>
+        <v>17.5574</v>
       </c>
       <c r="D138" t="n">
-        <v>61.8146</v>
+        <v>61.5884</v>
       </c>
       <c r="E138" t="n">
-        <v>18.2999</v>
+        <v>17.2293</v>
       </c>
       <c r="F138" t="n">
-        <v>54.6818</v>
+        <v>54.3572</v>
       </c>
     </row>
     <row r="139">
@@ -7820,19 +7820,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>17.2802</v>
+        <v>17.3058</v>
       </c>
       <c r="C139" t="n">
-        <v>17.4217</v>
+        <v>17.4146</v>
       </c>
       <c r="D139" t="n">
-        <v>61.6344</v>
+        <v>61.5962</v>
       </c>
       <c r="E139" t="n">
-        <v>18.8725</v>
+        <v>16.7604</v>
       </c>
       <c r="F139" t="n">
-        <v>54.1201</v>
+        <v>53.9666</v>
       </c>
     </row>
     <row r="140">
@@ -7840,19 +7840,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>16.94</v>
+        <v>16.9415</v>
       </c>
       <c r="C140" t="n">
-        <v>17.2618</v>
+        <v>17.2807</v>
       </c>
       <c r="D140" t="n">
-        <v>61.5797</v>
+        <v>61.4913</v>
       </c>
       <c r="E140" t="n">
-        <v>17.3583</v>
+        <v>16.4627</v>
       </c>
       <c r="F140" t="n">
-        <v>54.0434</v>
+        <v>54.0451</v>
       </c>
     </row>
     <row r="141">
@@ -7860,19 +7860,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>16.572</v>
+        <v>16.5714</v>
       </c>
       <c r="C141" t="n">
-        <v>17.1352</v>
+        <v>17.1562</v>
       </c>
       <c r="D141" t="n">
-        <v>61.6253</v>
+        <v>61.3903</v>
       </c>
       <c r="E141" t="n">
-        <v>16.5137</v>
+        <v>16.249</v>
       </c>
       <c r="F141" t="n">
-        <v>53.4831</v>
+        <v>53.394</v>
       </c>
     </row>
     <row r="142">
@@ -7880,19 +7880,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>16.1982</v>
+        <v>16.2105</v>
       </c>
       <c r="C142" t="n">
-        <v>17.0361</v>
+        <v>17.0268</v>
       </c>
       <c r="D142" t="n">
-        <v>61.3581</v>
+        <v>61.2643</v>
       </c>
       <c r="E142" t="n">
-        <v>16.4881</v>
+        <v>16.0281</v>
       </c>
       <c r="F142" t="n">
-        <v>53.0532</v>
+        <v>53.1698</v>
       </c>
     </row>
     <row r="143">
@@ -7900,19 +7900,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>15.8515</v>
+        <v>15.8226</v>
       </c>
       <c r="C143" t="n">
-        <v>16.914</v>
+        <v>16.9208</v>
       </c>
       <c r="D143" t="n">
-        <v>61.2597</v>
+        <v>61.2632</v>
       </c>
       <c r="E143" t="n">
-        <v>16.721</v>
+        <v>15.8435</v>
       </c>
       <c r="F143" t="n">
-        <v>52.7332</v>
+        <v>52.8274</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Running erasure.xlsx
+++ b/vs-x64/Running erasure.xlsx
@@ -5080,19 +5080,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>14.4896</v>
+        <v>14.7355</v>
       </c>
       <c r="C2" t="n">
-        <v>14.9681</v>
+        <v>14.9282</v>
       </c>
       <c r="D2" t="n">
-        <v>41.7763</v>
+        <v>41.8979</v>
       </c>
       <c r="E2" t="n">
-        <v>14.2164</v>
+        <v>14.2972</v>
       </c>
       <c r="F2" t="n">
-        <v>35.4526</v>
+        <v>35.4062</v>
       </c>
     </row>
     <row r="3">
@@ -5100,19 +5100,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>14.2366</v>
+        <v>14.2168</v>
       </c>
       <c r="C3" t="n">
-        <v>15.0114</v>
+        <v>15.0506</v>
       </c>
       <c r="D3" t="n">
-        <v>41.8693</v>
+        <v>41.852</v>
       </c>
       <c r="E3" t="n">
-        <v>14.1502</v>
+        <v>14.0177</v>
       </c>
       <c r="F3" t="n">
-        <v>35.0973</v>
+        <v>35.2301</v>
       </c>
     </row>
     <row r="4">
@@ -5120,19 +5120,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>13.9325</v>
+        <v>13.9254</v>
       </c>
       <c r="C4" t="n">
-        <v>15.2027</v>
+        <v>15.1639</v>
       </c>
       <c r="D4" t="n">
-        <v>41.92</v>
+        <v>42.068</v>
       </c>
       <c r="E4" t="n">
-        <v>13.8629</v>
+        <v>13.8317</v>
       </c>
       <c r="F4" t="n">
-        <v>34.5077</v>
+        <v>34.8066</v>
       </c>
     </row>
     <row r="5">
@@ -5140,19 +5140,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>13.8633</v>
+        <v>13.7244</v>
       </c>
       <c r="C5" t="n">
-        <v>15.1526</v>
+        <v>15.0757</v>
       </c>
       <c r="D5" t="n">
-        <v>41.7884</v>
+        <v>41.8604</v>
       </c>
       <c r="E5" t="n">
-        <v>13.6838</v>
+        <v>20.3483</v>
       </c>
       <c r="F5" t="n">
-        <v>34.6108</v>
+        <v>38.9113</v>
       </c>
     </row>
     <row r="6">
@@ -5160,19 +5160,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>13.4194</v>
+        <v>13.4378</v>
       </c>
       <c r="C6" t="n">
-        <v>15.1535</v>
+        <v>15.1631</v>
       </c>
       <c r="D6" t="n">
-        <v>41.8788</v>
+        <v>41.8051</v>
       </c>
       <c r="E6" t="n">
-        <v>13.5548</v>
+        <v>20.7367</v>
       </c>
       <c r="F6" t="n">
-        <v>34.5053</v>
+        <v>38.6134</v>
       </c>
     </row>
     <row r="7">
@@ -5180,19 +5180,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>13.1498</v>
+        <v>13.1703</v>
       </c>
       <c r="C7" t="n">
-        <v>15.1642</v>
+        <v>15.1779</v>
       </c>
       <c r="D7" t="n">
-        <v>42.575</v>
+        <v>42.5518</v>
       </c>
       <c r="E7" t="n">
-        <v>16.8169</v>
+        <v>16.7753</v>
       </c>
       <c r="F7" t="n">
-        <v>38.3208</v>
+        <v>38.3622</v>
       </c>
     </row>
     <row r="8">
@@ -5200,19 +5200,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>12.719</v>
+        <v>12.8881</v>
       </c>
       <c r="C8" t="n">
-        <v>16.9338</v>
+        <v>17.0294</v>
       </c>
       <c r="D8" t="n">
-        <v>42.6441</v>
+        <v>42.7293</v>
       </c>
       <c r="E8" t="n">
-        <v>16.5475</v>
+        <v>16.391</v>
       </c>
       <c r="F8" t="n">
-        <v>38.115</v>
+        <v>38.0787</v>
       </c>
     </row>
     <row r="9">
@@ -5220,19 +5220,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>12.3714</v>
+        <v>12.309</v>
       </c>
       <c r="C9" t="n">
-        <v>16.9496</v>
+        <v>16.9485</v>
       </c>
       <c r="D9" t="n">
-        <v>42.7578</v>
+        <v>42.7773</v>
       </c>
       <c r="E9" t="n">
-        <v>16.4188</v>
+        <v>19.515</v>
       </c>
       <c r="F9" t="n">
-        <v>37.8796</v>
+        <v>37.9002</v>
       </c>
     </row>
     <row r="10">
@@ -5240,19 +5240,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>17.2002</v>
+        <v>17.1044</v>
       </c>
       <c r="C10" t="n">
-        <v>16.7602</v>
+        <v>16.7389</v>
       </c>
       <c r="D10" t="n">
-        <v>42.6282</v>
+        <v>42.7024</v>
       </c>
       <c r="E10" t="n">
-        <v>16.2762</v>
+        <v>16.2293</v>
       </c>
       <c r="F10" t="n">
-        <v>37.8271</v>
+        <v>37.5649</v>
       </c>
     </row>
     <row r="11">
@@ -5260,19 +5260,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>16.8827</v>
+        <v>16.9157</v>
       </c>
       <c r="C11" t="n">
-        <v>16.6774</v>
+        <v>16.7213</v>
       </c>
       <c r="D11" t="n">
-        <v>42.6089</v>
+        <v>42.6393</v>
       </c>
       <c r="E11" t="n">
-        <v>15.9754</v>
+        <v>15.931</v>
       </c>
       <c r="F11" t="n">
-        <v>37.2241</v>
+        <v>37.4723</v>
       </c>
     </row>
     <row r="12">
@@ -5280,19 +5280,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>16.6076</v>
+        <v>16.4879</v>
       </c>
       <c r="C12" t="n">
-        <v>16.6572</v>
+        <v>16.6489</v>
       </c>
       <c r="D12" t="n">
-        <v>42.6349</v>
+        <v>42.6603</v>
       </c>
       <c r="E12" t="n">
-        <v>15.7261</v>
+        <v>15.7148</v>
       </c>
       <c r="F12" t="n">
-        <v>36.8937</v>
+        <v>37.0201</v>
       </c>
     </row>
     <row r="13">
@@ -5300,19 +5300,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>16.1755</v>
+        <v>16.138</v>
       </c>
       <c r="C13" t="n">
-        <v>16.5521</v>
+        <v>16.547</v>
       </c>
       <c r="D13" t="n">
-        <v>42.5207</v>
+        <v>42.6279</v>
       </c>
       <c r="E13" t="n">
-        <v>15.5257</v>
+        <v>15.5452</v>
       </c>
       <c r="F13" t="n">
-        <v>36.6262</v>
+        <v>36.7439</v>
       </c>
     </row>
     <row r="14">
@@ -5320,19 +5320,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>15.9356</v>
+        <v>15.842</v>
       </c>
       <c r="C14" t="n">
-        <v>16.4492</v>
+        <v>16.5381</v>
       </c>
       <c r="D14" t="n">
-        <v>42.5984</v>
+        <v>42.6934</v>
       </c>
       <c r="E14" t="n">
-        <v>15.3783</v>
+        <v>15.3384</v>
       </c>
       <c r="F14" t="n">
-        <v>36.3601</v>
+        <v>36.3362</v>
       </c>
     </row>
     <row r="15">
@@ -5340,19 +5340,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>15.5821</v>
+        <v>15.6977</v>
       </c>
       <c r="C15" t="n">
-        <v>16.3849</v>
+        <v>16.3868</v>
       </c>
       <c r="D15" t="n">
-        <v>42.5794</v>
+        <v>42.6322</v>
       </c>
       <c r="E15" t="n">
-        <v>15.1119</v>
+        <v>15.1664</v>
       </c>
       <c r="F15" t="n">
-        <v>36.1313</v>
+        <v>36.2735</v>
       </c>
     </row>
     <row r="16">
@@ -5360,19 +5360,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>15.2678</v>
+        <v>15.2122</v>
       </c>
       <c r="C16" t="n">
-        <v>16.3393</v>
+        <v>16.369</v>
       </c>
       <c r="D16" t="n">
-        <v>42.4986</v>
+        <v>42.5089</v>
       </c>
       <c r="E16" t="n">
-        <v>14.9258</v>
+        <v>14.9899</v>
       </c>
       <c r="F16" t="n">
-        <v>35.8597</v>
+        <v>35.8598</v>
       </c>
     </row>
     <row r="17">
@@ -5380,19 +5380,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>15.0279</v>
+        <v>14.8685</v>
       </c>
       <c r="C17" t="n">
-        <v>16.1511</v>
+        <v>16.182</v>
       </c>
       <c r="D17" t="n">
-        <v>42.4607</v>
+        <v>42.4303</v>
       </c>
       <c r="E17" t="n">
-        <v>14.6949</v>
+        <v>15.4733</v>
       </c>
       <c r="F17" t="n">
-        <v>35.4375</v>
+        <v>35.6047</v>
       </c>
     </row>
     <row r="18">
@@ -5400,19 +5400,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>14.78</v>
+        <v>14.6417</v>
       </c>
       <c r="C18" t="n">
-        <v>16.1339</v>
+        <v>16.1565</v>
       </c>
       <c r="D18" t="n">
-        <v>42.4371</v>
+        <v>42.5049</v>
       </c>
       <c r="E18" t="n">
-        <v>14.5018</v>
+        <v>14.5258</v>
       </c>
       <c r="F18" t="n">
-        <v>35.3494</v>
+        <v>35.4268</v>
       </c>
     </row>
     <row r="19">
@@ -5420,19 +5420,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>14.3521</v>
+        <v>14.2435</v>
       </c>
       <c r="C19" t="n">
-        <v>16.0357</v>
+        <v>16.0808</v>
       </c>
       <c r="D19" t="n">
-        <v>42.4825</v>
+        <v>42.4559</v>
       </c>
       <c r="E19" t="n">
-        <v>14.2851</v>
+        <v>14.2664</v>
       </c>
       <c r="F19" t="n">
-        <v>35.0447</v>
+        <v>35.247</v>
       </c>
     </row>
     <row r="20">
@@ -5440,19 +5440,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>14.0101</v>
+        <v>14.0272</v>
       </c>
       <c r="C20" t="n">
-        <v>16.0773</v>
+        <v>16.0808</v>
       </c>
       <c r="D20" t="n">
-        <v>42.4342</v>
+        <v>42.537</v>
       </c>
       <c r="E20" t="n">
-        <v>14.0674</v>
+        <v>17.4612</v>
       </c>
       <c r="F20" t="n">
-        <v>34.6252</v>
+        <v>39.1379</v>
       </c>
     </row>
     <row r="21">
@@ -5460,19 +5460,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>13.675</v>
+        <v>13.6967</v>
       </c>
       <c r="C21" t="n">
-        <v>15.9096</v>
+        <v>15.9461</v>
       </c>
       <c r="D21" t="n">
-        <v>43.24</v>
+        <v>43.2904</v>
       </c>
       <c r="E21" t="n">
-        <v>17.2037</v>
+        <v>17.1657</v>
       </c>
       <c r="F21" t="n">
-        <v>38.7654</v>
+        <v>38.8356</v>
       </c>
     </row>
     <row r="22">
@@ -5480,19 +5480,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>13.3467</v>
+        <v>13.2641</v>
       </c>
       <c r="C22" t="n">
-        <v>17.6317</v>
+        <v>17.6479</v>
       </c>
       <c r="D22" t="n">
-        <v>43.309</v>
+        <v>43.1568</v>
       </c>
       <c r="E22" t="n">
-        <v>16.97</v>
+        <v>16.9977</v>
       </c>
       <c r="F22" t="n">
-        <v>38.4794</v>
+        <v>38.7242</v>
       </c>
     </row>
     <row r="23">
@@ -5500,19 +5500,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.7668</v>
+        <v>12.8917</v>
       </c>
       <c r="C23" t="n">
-        <v>17.4922</v>
+        <v>17.5043</v>
       </c>
       <c r="D23" t="n">
-        <v>43.225</v>
+        <v>43.2473</v>
       </c>
       <c r="E23" t="n">
-        <v>16.5987</v>
+        <v>16.7154</v>
       </c>
       <c r="F23" t="n">
-        <v>38.1943</v>
+        <v>38.2386</v>
       </c>
     </row>
     <row r="24">
@@ -5520,19 +5520,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>17.4641</v>
+        <v>17.4632</v>
       </c>
       <c r="C24" t="n">
-        <v>17.324</v>
+        <v>17.3609</v>
       </c>
       <c r="D24" t="n">
-        <v>43.1791</v>
+        <v>43.0987</v>
       </c>
       <c r="E24" t="n">
-        <v>16.4032</v>
+        <v>16.3736</v>
       </c>
       <c r="F24" t="n">
-        <v>37.7571</v>
+        <v>37.8639</v>
       </c>
     </row>
     <row r="25">
@@ -5540,19 +5540,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>17.1834</v>
+        <v>17.1674</v>
       </c>
       <c r="C25" t="n">
-        <v>17.1831</v>
+        <v>17.2325</v>
       </c>
       <c r="D25" t="n">
-        <v>43.0896</v>
+        <v>43.1403</v>
       </c>
       <c r="E25" t="n">
-        <v>16.1911</v>
+        <v>16.214</v>
       </c>
       <c r="F25" t="n">
-        <v>37.4512</v>
+        <v>37.689</v>
       </c>
     </row>
     <row r="26">
@@ -5560,19 +5560,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>16.8399</v>
+        <v>16.8524</v>
       </c>
       <c r="C26" t="n">
-        <v>17.0996</v>
+        <v>17.1033</v>
       </c>
       <c r="D26" t="n">
-        <v>43.0842</v>
+        <v>43.0923</v>
       </c>
       <c r="E26" t="n">
-        <v>15.9662</v>
+        <v>15.9269</v>
       </c>
       <c r="F26" t="n">
-        <v>37.3886</v>
+        <v>37.3133</v>
       </c>
     </row>
     <row r="27">
@@ -5580,19 +5580,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>16.483</v>
+        <v>16.4837</v>
       </c>
       <c r="C27" t="n">
-        <v>16.9605</v>
+        <v>16.9786</v>
       </c>
       <c r="D27" t="n">
-        <v>43.1547</v>
+        <v>43.046</v>
       </c>
       <c r="E27" t="n">
-        <v>15.659</v>
+        <v>15.7626</v>
       </c>
       <c r="F27" t="n">
-        <v>37.1146</v>
+        <v>37.0969</v>
       </c>
     </row>
     <row r="28">
@@ -5600,19 +5600,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>16.1276</v>
+        <v>16.1358</v>
       </c>
       <c r="C28" t="n">
-        <v>16.8503</v>
+        <v>16.8633</v>
       </c>
       <c r="D28" t="n">
-        <v>43.0853</v>
+        <v>43.0366</v>
       </c>
       <c r="E28" t="n">
-        <v>15.556</v>
+        <v>15.5436</v>
       </c>
       <c r="F28" t="n">
-        <v>36.9174</v>
+        <v>36.5555</v>
       </c>
     </row>
     <row r="29">
@@ -5620,19 +5620,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>15.7689</v>
+        <v>15.7927</v>
       </c>
       <c r="C29" t="n">
-        <v>16.7306</v>
+        <v>16.7135</v>
       </c>
       <c r="D29" t="n">
-        <v>43.1932</v>
+        <v>43.0388</v>
       </c>
       <c r="E29" t="n">
-        <v>15.3519</v>
+        <v>15.4505</v>
       </c>
       <c r="F29" t="n">
-        <v>36.6441</v>
+        <v>36.4592</v>
       </c>
     </row>
     <row r="30">
@@ -5640,19 +5640,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>15.4543</v>
+        <v>15.4683</v>
       </c>
       <c r="C30" t="n">
-        <v>16.6853</v>
+        <v>16.6581</v>
       </c>
       <c r="D30" t="n">
-        <v>43.1342</v>
+        <v>42.9482</v>
       </c>
       <c r="E30" t="n">
-        <v>15.1755</v>
+        <v>15.1817</v>
       </c>
       <c r="F30" t="n">
-        <v>36.34</v>
+        <v>36.2276</v>
       </c>
     </row>
     <row r="31">
@@ -5660,19 +5660,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>15.1241</v>
+        <v>15.1053</v>
       </c>
       <c r="C31" t="n">
-        <v>16.5645</v>
+        <v>16.5908</v>
       </c>
       <c r="D31" t="n">
-        <v>43.0055</v>
+        <v>42.8189</v>
       </c>
       <c r="E31" t="n">
-        <v>14.9525</v>
+        <v>14.9685</v>
       </c>
       <c r="F31" t="n">
-        <v>36.1923</v>
+        <v>35.9022</v>
       </c>
     </row>
     <row r="32">
@@ -5680,19 +5680,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>14.8378</v>
+        <v>14.8422</v>
       </c>
       <c r="C32" t="n">
-        <v>16.5382</v>
+        <v>16.5709</v>
       </c>
       <c r="D32" t="n">
-        <v>43.0229</v>
+        <v>42.7401</v>
       </c>
       <c r="E32" t="n">
-        <v>14.7963</v>
+        <v>14.8254</v>
       </c>
       <c r="F32" t="n">
-        <v>35.77</v>
+        <v>35.7404</v>
       </c>
     </row>
     <row r="33">
@@ -5700,19 +5700,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>14.5429</v>
+        <v>14.5474</v>
       </c>
       <c r="C33" t="n">
-        <v>16.4173</v>
+        <v>16.4297</v>
       </c>
       <c r="D33" t="n">
-        <v>42.9263</v>
+        <v>42.7998</v>
       </c>
       <c r="E33" t="n">
-        <v>14.5425</v>
+        <v>14.52</v>
       </c>
       <c r="F33" t="n">
-        <v>35.4789</v>
+        <v>35.4063</v>
       </c>
     </row>
     <row r="34">
@@ -5720,19 +5720,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>14.2495</v>
+        <v>14.257</v>
       </c>
       <c r="C34" t="n">
-        <v>16.3671</v>
+        <v>16.3561</v>
       </c>
       <c r="D34" t="n">
-        <v>42.8679</v>
+        <v>42.7937</v>
       </c>
       <c r="E34" t="n">
-        <v>14.3405</v>
+        <v>18.1</v>
       </c>
       <c r="F34" t="n">
-        <v>35.3687</v>
+        <v>39.4784</v>
       </c>
     </row>
     <row r="35">
@@ -5740,19 +5740,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>13.9561</v>
+        <v>13.9407</v>
       </c>
       <c r="C35" t="n">
-        <v>16.3112</v>
+        <v>16.3184</v>
       </c>
       <c r="D35" t="n">
-        <v>43.8373</v>
+        <v>43.8</v>
       </c>
       <c r="E35" t="n">
-        <v>17.754</v>
+        <v>17.7981</v>
       </c>
       <c r="F35" t="n">
-        <v>39.3138</v>
+        <v>39.3098</v>
       </c>
     </row>
     <row r="36">
@@ -5760,19 +5760,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>13.6548</v>
+        <v>13.61</v>
       </c>
       <c r="C36" t="n">
-        <v>16.203</v>
+        <v>16.2278</v>
       </c>
       <c r="D36" t="n">
-        <v>43.8191</v>
+        <v>43.7177</v>
       </c>
       <c r="E36" t="n">
-        <v>17.4129</v>
+        <v>17.4392</v>
       </c>
       <c r="F36" t="n">
-        <v>38.9517</v>
+        <v>38.9825</v>
       </c>
     </row>
     <row r="37">
@@ -5780,19 +5780,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.1978</v>
+        <v>13.1968</v>
       </c>
       <c r="C37" t="n">
-        <v>17.7603</v>
+        <v>17.7959</v>
       </c>
       <c r="D37" t="n">
-        <v>43.8446</v>
+        <v>43.7145</v>
       </c>
       <c r="E37" t="n">
-        <v>17.0576</v>
+        <v>17.0849</v>
       </c>
       <c r="F37" t="n">
-        <v>38.823</v>
+        <v>38.7793</v>
       </c>
     </row>
     <row r="38">
@@ -5800,19 +5800,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>17.622</v>
+        <v>17.6411</v>
       </c>
       <c r="C38" t="n">
-        <v>17.606</v>
+        <v>17.6056</v>
       </c>
       <c r="D38" t="n">
-        <v>43.693</v>
+        <v>43.5104</v>
       </c>
       <c r="E38" t="n">
-        <v>16.838</v>
+        <v>16.7803</v>
       </c>
       <c r="F38" t="n">
-        <v>38.4074</v>
+        <v>38.3725</v>
       </c>
     </row>
     <row r="39">
@@ -5820,19 +5820,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>17.3389</v>
+        <v>17.349</v>
       </c>
       <c r="C39" t="n">
-        <v>17.5091</v>
+        <v>17.497</v>
       </c>
       <c r="D39" t="n">
-        <v>43.6127</v>
+        <v>43.5918</v>
       </c>
       <c r="E39" t="n">
-        <v>16.4826</v>
+        <v>16.5082</v>
       </c>
       <c r="F39" t="n">
-        <v>37.9601</v>
+        <v>38.1677</v>
       </c>
     </row>
     <row r="40">
@@ -5840,19 +5840,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>17.0316</v>
+        <v>17.038</v>
       </c>
       <c r="C40" t="n">
-        <v>17.3797</v>
+        <v>17.3619</v>
       </c>
       <c r="D40" t="n">
-        <v>43.5852</v>
+        <v>43.5334</v>
       </c>
       <c r="E40" t="n">
-        <v>16.2742</v>
+        <v>16.2758</v>
       </c>
       <c r="F40" t="n">
-        <v>37.7392</v>
+        <v>37.7544</v>
       </c>
     </row>
     <row r="41">
@@ -5860,19 +5860,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>16.6804</v>
+        <v>16.6898</v>
       </c>
       <c r="C41" t="n">
-        <v>17.1981</v>
+        <v>17.2058</v>
       </c>
       <c r="D41" t="n">
-        <v>43.484</v>
+        <v>43.4997</v>
       </c>
       <c r="E41" t="n">
-        <v>15.9886</v>
+        <v>15.9946</v>
       </c>
       <c r="F41" t="n">
-        <v>37.4061</v>
+        <v>37.5493</v>
       </c>
     </row>
     <row r="42">
@@ -5880,19 +5880,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>16.3457</v>
+        <v>16.3379</v>
       </c>
       <c r="C42" t="n">
-        <v>17.0274</v>
+        <v>17.0292</v>
       </c>
       <c r="D42" t="n">
-        <v>43.5669</v>
+        <v>43.4267</v>
       </c>
       <c r="E42" t="n">
-        <v>15.77</v>
+        <v>15.7807</v>
       </c>
       <c r="F42" t="n">
-        <v>37.0107</v>
+        <v>37.0936</v>
       </c>
     </row>
     <row r="43">
@@ -5900,19 +5900,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>15.9749</v>
+        <v>15.9878</v>
       </c>
       <c r="C43" t="n">
-        <v>16.9143</v>
+        <v>16.9186</v>
       </c>
       <c r="D43" t="n">
-        <v>43.291</v>
+        <v>43.3816</v>
       </c>
       <c r="E43" t="n">
-        <v>15.6249</v>
+        <v>15.5984</v>
       </c>
       <c r="F43" t="n">
-        <v>36.9579</v>
+        <v>36.8641</v>
       </c>
     </row>
     <row r="44">
@@ -5920,19 +5920,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>15.5973</v>
+        <v>15.6073</v>
       </c>
       <c r="C44" t="n">
-        <v>16.8179</v>
+        <v>16.831</v>
       </c>
       <c r="D44" t="n">
-        <v>43.398</v>
+        <v>43.3876</v>
       </c>
       <c r="E44" t="n">
-        <v>15.4075</v>
+        <v>15.4274</v>
       </c>
       <c r="F44" t="n">
-        <v>36.4585</v>
+        <v>36.6298</v>
       </c>
     </row>
     <row r="45">
@@ -5940,19 +5940,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>15.2638</v>
+        <v>15.2724</v>
       </c>
       <c r="C45" t="n">
-        <v>16.7198</v>
+        <v>16.725</v>
       </c>
       <c r="D45" t="n">
-        <v>43.2733</v>
+        <v>43.1293</v>
       </c>
       <c r="E45" t="n">
-        <v>15.2613</v>
+        <v>15.2323</v>
       </c>
       <c r="F45" t="n">
-        <v>36.3256</v>
+        <v>36.1645</v>
       </c>
     </row>
     <row r="46">
@@ -5960,19 +5960,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>14.9412</v>
+        <v>14.9457</v>
       </c>
       <c r="C46" t="n">
-        <v>16.6284</v>
+        <v>16.6141</v>
       </c>
       <c r="D46" t="n">
-        <v>43.2341</v>
+        <v>43.2981</v>
       </c>
       <c r="E46" t="n">
-        <v>15.03</v>
+        <v>15.0419</v>
       </c>
       <c r="F46" t="n">
-        <v>35.946</v>
+        <v>35.9731</v>
       </c>
     </row>
     <row r="47">
@@ -5980,19 +5980,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>14.6332</v>
+        <v>14.6642</v>
       </c>
       <c r="C47" t="n">
-        <v>16.5462</v>
+        <v>16.5417</v>
       </c>
       <c r="D47" t="n">
-        <v>43.1067</v>
+        <v>43.0959</v>
       </c>
       <c r="E47" t="n">
-        <v>14.8403</v>
+        <v>14.8008</v>
       </c>
       <c r="F47" t="n">
-        <v>35.7547</v>
+        <v>35.7515</v>
       </c>
     </row>
     <row r="48">
@@ -6000,19 +6000,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>14.3541</v>
+        <v>14.4127</v>
       </c>
       <c r="C48" t="n">
-        <v>16.4802</v>
+        <v>16.4785</v>
       </c>
       <c r="D48" t="n">
-        <v>43.1438</v>
+        <v>43.1414</v>
       </c>
       <c r="E48" t="n">
-        <v>14.5868</v>
+        <v>18.3569</v>
       </c>
       <c r="F48" t="n">
-        <v>35.6274</v>
+        <v>40.0384</v>
       </c>
     </row>
     <row r="49">
@@ -6020,19 +6020,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>14.0822</v>
+        <v>14.0772</v>
       </c>
       <c r="C49" t="n">
-        <v>16.4045</v>
+        <v>16.398</v>
       </c>
       <c r="D49" t="n">
-        <v>43.2062</v>
+        <v>42.9561</v>
       </c>
       <c r="E49" t="n">
-        <v>14.366</v>
+        <v>17.9854</v>
       </c>
       <c r="F49" t="n">
-        <v>35.0424</v>
+        <v>39.7088</v>
       </c>
     </row>
     <row r="50">
@@ -6040,19 +6040,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>13.7137</v>
+        <v>13.756</v>
       </c>
       <c r="C50" t="n">
-        <v>16.3315</v>
+        <v>16.3329</v>
       </c>
       <c r="D50" t="n">
-        <v>44.1207</v>
+        <v>44.047</v>
       </c>
       <c r="E50" t="n">
-        <v>17.5694</v>
+        <v>17.5868</v>
       </c>
       <c r="F50" t="n">
-        <v>39.4401</v>
+        <v>39.4045</v>
       </c>
     </row>
     <row r="51">
@@ -6060,19 +6060,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>13.3498</v>
+        <v>13.3413</v>
       </c>
       <c r="C51" t="n">
-        <v>17.8656</v>
+        <v>17.8539</v>
       </c>
       <c r="D51" t="n">
-        <v>44.0869</v>
+        <v>44.0111</v>
       </c>
       <c r="E51" t="n">
-        <v>17.2188</v>
+        <v>17.2695</v>
       </c>
       <c r="F51" t="n">
-        <v>39.1854</v>
+        <v>38.9751</v>
       </c>
     </row>
     <row r="52">
@@ -6080,19 +6080,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>12.8062</v>
+        <v>12.8317</v>
       </c>
       <c r="C52" t="n">
-        <v>17.6707</v>
+        <v>17.6741</v>
       </c>
       <c r="D52" t="n">
-        <v>44.0653</v>
+        <v>43.9698</v>
       </c>
       <c r="E52" t="n">
-        <v>16.9603</v>
+        <v>17.1022</v>
       </c>
       <c r="F52" t="n">
-        <v>38.7367</v>
+        <v>38.7012</v>
       </c>
     </row>
     <row r="53">
@@ -6100,19 +6100,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>17.4139</v>
+        <v>17.4026</v>
       </c>
       <c r="C53" t="n">
-        <v>17.4912</v>
+        <v>17.5063</v>
       </c>
       <c r="D53" t="n">
-        <v>43.9065</v>
+        <v>43.8864</v>
       </c>
       <c r="E53" t="n">
-        <v>16.7047</v>
+        <v>16.7316</v>
       </c>
       <c r="F53" t="n">
-        <v>38.3237</v>
+        <v>38.2847</v>
       </c>
     </row>
     <row r="54">
@@ -6120,19 +6120,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>17.1131</v>
+        <v>17.0908</v>
       </c>
       <c r="C54" t="n">
-        <v>17.3972</v>
+        <v>17.3952</v>
       </c>
       <c r="D54" t="n">
-        <v>43.8299</v>
+        <v>43.7949</v>
       </c>
       <c r="E54" t="n">
-        <v>16.46</v>
+        <v>16.4879</v>
       </c>
       <c r="F54" t="n">
-        <v>38.4367</v>
+        <v>38.2551</v>
       </c>
     </row>
     <row r="55">
@@ -6140,19 +6140,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>16.7893</v>
+        <v>16.7718</v>
       </c>
       <c r="C55" t="n">
-        <v>17.256</v>
+        <v>17.2707</v>
       </c>
       <c r="D55" t="n">
-        <v>43.8821</v>
+        <v>43.9343</v>
       </c>
       <c r="E55" t="n">
-        <v>16.2371</v>
+        <v>16.2356</v>
       </c>
       <c r="F55" t="n">
-        <v>38.5304</v>
+        <v>37.7616</v>
       </c>
     </row>
     <row r="56">
@@ -6160,19 +6160,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>16.4193</v>
+        <v>16.4376</v>
       </c>
       <c r="C56" t="n">
-        <v>17.125</v>
+        <v>17.1124</v>
       </c>
       <c r="D56" t="n">
-        <v>43.8387</v>
+        <v>43.684</v>
       </c>
       <c r="E56" t="n">
-        <v>16.0062</v>
+        <v>15.9867</v>
       </c>
       <c r="F56" t="n">
-        <v>38.109</v>
+        <v>39.0198</v>
       </c>
     </row>
     <row r="57">
@@ -6180,19 +6180,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>16.045</v>
+        <v>16.0454</v>
       </c>
       <c r="C57" t="n">
-        <v>17.0385</v>
+        <v>17.0269</v>
       </c>
       <c r="D57" t="n">
-        <v>43.8481</v>
+        <v>43.8049</v>
       </c>
       <c r="E57" t="n">
-        <v>15.7788</v>
+        <v>15.7985</v>
       </c>
       <c r="F57" t="n">
-        <v>38.4622</v>
+        <v>37.4171</v>
       </c>
     </row>
     <row r="58">
@@ -6200,19 +6200,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>15.6931</v>
+        <v>15.6903</v>
       </c>
       <c r="C58" t="n">
-        <v>16.8784</v>
+        <v>16.8921</v>
       </c>
       <c r="D58" t="n">
-        <v>43.9193</v>
+        <v>43.8662</v>
       </c>
       <c r="E58" t="n">
-        <v>15.557</v>
+        <v>15.5397</v>
       </c>
       <c r="F58" t="n">
-        <v>37.8449</v>
+        <v>37.7416</v>
       </c>
     </row>
     <row r="59">
@@ -6220,19 +6220,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>15.3429</v>
+        <v>15.3605</v>
       </c>
       <c r="C59" t="n">
-        <v>16.783</v>
+        <v>16.7938</v>
       </c>
       <c r="D59" t="n">
-        <v>43.8117</v>
+        <v>43.6988</v>
       </c>
       <c r="E59" t="n">
-        <v>15.3318</v>
+        <v>15.3382</v>
       </c>
       <c r="F59" t="n">
-        <v>37.8862</v>
+        <v>37.9488</v>
       </c>
     </row>
     <row r="60">
@@ -6240,19 +6240,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>15.0142</v>
+        <v>15.0253</v>
       </c>
       <c r="C60" t="n">
-        <v>16.6983</v>
+        <v>16.6857</v>
       </c>
       <c r="D60" t="n">
-        <v>44.4636</v>
+        <v>44.6861</v>
       </c>
       <c r="E60" t="n">
-        <v>15.1691</v>
+        <v>15.1917</v>
       </c>
       <c r="F60" t="n">
-        <v>37.7404</v>
+        <v>38.0639</v>
       </c>
     </row>
     <row r="61">
@@ -6260,19 +6260,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>14.717</v>
+        <v>14.7367</v>
       </c>
       <c r="C61" t="n">
-        <v>16.6209</v>
+        <v>16.6135</v>
       </c>
       <c r="D61" t="n">
-        <v>44.474</v>
+        <v>43.8993</v>
       </c>
       <c r="E61" t="n">
-        <v>14.9502</v>
+        <v>14.9204</v>
       </c>
       <c r="F61" t="n">
-        <v>37.4624</v>
+        <v>37.0546</v>
       </c>
     </row>
     <row r="62">
@@ -6280,19 +6280,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>14.4596</v>
+        <v>14.4542</v>
       </c>
       <c r="C62" t="n">
-        <v>16.57</v>
+        <v>16.5458</v>
       </c>
       <c r="D62" t="n">
-        <v>44.7118</v>
+        <v>44.8308</v>
       </c>
       <c r="E62" t="n">
-        <v>14.7112</v>
+        <v>14.691</v>
       </c>
       <c r="F62" t="n">
-        <v>38.3028</v>
+        <v>37.5191</v>
       </c>
     </row>
     <row r="63">
@@ -6300,19 +6300,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>14.137</v>
+        <v>14.1805</v>
       </c>
       <c r="C63" t="n">
-        <v>16.4927</v>
+        <v>16.4844</v>
       </c>
       <c r="D63" t="n">
-        <v>45.6514</v>
+        <v>45.3643</v>
       </c>
       <c r="E63" t="n">
-        <v>14.4811</v>
+        <v>18.2729</v>
       </c>
       <c r="F63" t="n">
-        <v>38.3544</v>
+        <v>46.7283</v>
       </c>
     </row>
     <row r="64">
@@ -6320,19 +6320,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>13.8308</v>
+        <v>13.8376</v>
       </c>
       <c r="C64" t="n">
-        <v>16.4211</v>
+        <v>16.3864</v>
       </c>
       <c r="D64" t="n">
-        <v>50.7006</v>
+        <v>50.5406</v>
       </c>
       <c r="E64" t="n">
-        <v>17.8589</v>
+        <v>17.8624</v>
       </c>
       <c r="F64" t="n">
-        <v>47.1284</v>
+        <v>47.0566</v>
       </c>
     </row>
     <row r="65">
@@ -6340,19 +6340,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>13.4365</v>
+        <v>13.4355</v>
       </c>
       <c r="C65" t="n">
-        <v>17.8899</v>
+        <v>17.8914</v>
       </c>
       <c r="D65" t="n">
-        <v>51.0246</v>
+        <v>50.9851</v>
       </c>
       <c r="E65" t="n">
-        <v>17.505</v>
+        <v>17.5828</v>
       </c>
       <c r="F65" t="n">
-        <v>47.3773</v>
+        <v>47.3828</v>
       </c>
     </row>
     <row r="66">
@@ -6360,19 +6360,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>13.0074</v>
+        <v>12.9472</v>
       </c>
       <c r="C66" t="n">
-        <v>17.7162</v>
+        <v>17.7242</v>
       </c>
       <c r="D66" t="n">
-        <v>51.4464</v>
+        <v>51.6004</v>
       </c>
       <c r="E66" t="n">
-        <v>17.1835</v>
+        <v>17.3966</v>
       </c>
       <c r="F66" t="n">
-        <v>47.7953</v>
+        <v>47.3493</v>
       </c>
     </row>
     <row r="67">
@@ -6380,19 +6380,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>17.5543</v>
+        <v>17.542</v>
       </c>
       <c r="C67" t="n">
-        <v>17.569</v>
+        <v>17.5756</v>
       </c>
       <c r="D67" t="n">
-        <v>52.2852</v>
+        <v>52.0708</v>
       </c>
       <c r="E67" t="n">
-        <v>16.9225</v>
+        <v>16.9101</v>
       </c>
       <c r="F67" t="n">
-        <v>48.1404</v>
+        <v>48.1134</v>
       </c>
     </row>
     <row r="68">
@@ -6400,19 +6400,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>17.2465</v>
+        <v>17.2342</v>
       </c>
       <c r="C68" t="n">
-        <v>17.4093</v>
+        <v>17.4068</v>
       </c>
       <c r="D68" t="n">
-        <v>52.552</v>
+        <v>52.3421</v>
       </c>
       <c r="E68" t="n">
-        <v>16.7</v>
+        <v>16.6357</v>
       </c>
       <c r="F68" t="n">
-        <v>48.2877</v>
+        <v>48.3961</v>
       </c>
     </row>
     <row r="69">
@@ -6420,19 +6420,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>16.8887</v>
+        <v>16.8997</v>
       </c>
       <c r="C69" t="n">
-        <v>17.3061</v>
+        <v>17.2823</v>
       </c>
       <c r="D69" t="n">
-        <v>52.9807</v>
+        <v>52.7054</v>
       </c>
       <c r="E69" t="n">
-        <v>16.4238</v>
+        <v>16.3869</v>
       </c>
       <c r="F69" t="n">
-        <v>48.2993</v>
+        <v>48.2517</v>
       </c>
     </row>
     <row r="70">
@@ -6440,19 +6440,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>16.5332</v>
+        <v>16.5262</v>
       </c>
       <c r="C70" t="n">
-        <v>17.1752</v>
+        <v>17.189</v>
       </c>
       <c r="D70" t="n">
-        <v>53.1585</v>
+        <v>53.2749</v>
       </c>
       <c r="E70" t="n">
-        <v>16.1605</v>
+        <v>16.1656</v>
       </c>
       <c r="F70" t="n">
-        <v>48.1454</v>
+        <v>48.2397</v>
       </c>
     </row>
     <row r="71">
@@ -6460,19 +6460,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>16.1493</v>
+        <v>16.1347</v>
       </c>
       <c r="C71" t="n">
-        <v>17.0377</v>
+        <v>17.0492</v>
       </c>
       <c r="D71" t="n">
-        <v>53.3423</v>
+        <v>53.3522</v>
       </c>
       <c r="E71" t="n">
-        <v>15.933</v>
+        <v>15.9517</v>
       </c>
       <c r="F71" t="n">
-        <v>47.9162</v>
+        <v>48.0789</v>
       </c>
     </row>
     <row r="72">
@@ -6480,19 +6480,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>15.7863</v>
+        <v>15.7715</v>
       </c>
       <c r="C72" t="n">
-        <v>16.9533</v>
+        <v>16.9416</v>
       </c>
       <c r="D72" t="n">
-        <v>53.6159</v>
+        <v>53.7234</v>
       </c>
       <c r="E72" t="n">
-        <v>15.7106</v>
+        <v>15.7244</v>
       </c>
       <c r="F72" t="n">
-        <v>47.7342</v>
+        <v>47.9301</v>
       </c>
     </row>
     <row r="73">
@@ -6500,19 +6500,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>15.4372</v>
+        <v>15.4173</v>
       </c>
       <c r="C73" t="n">
-        <v>16.8496</v>
+        <v>16.8604</v>
       </c>
       <c r="D73" t="n">
-        <v>53.8561</v>
+        <v>53.7996</v>
       </c>
       <c r="E73" t="n">
-        <v>15.5205</v>
+        <v>15.4988</v>
       </c>
       <c r="F73" t="n">
-        <v>47.7337</v>
+        <v>47.6847</v>
       </c>
     </row>
     <row r="74">
@@ -6520,19 +6520,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>15.1059</v>
+        <v>15.0927</v>
       </c>
       <c r="C74" t="n">
-        <v>16.747</v>
+        <v>16.7542</v>
       </c>
       <c r="D74" t="n">
-        <v>54.0378</v>
+        <v>54.1378</v>
       </c>
       <c r="E74" t="n">
-        <v>15.3058</v>
+        <v>15.2757</v>
       </c>
       <c r="F74" t="n">
-        <v>47.5312</v>
+        <v>47.4961</v>
       </c>
     </row>
     <row r="75">
@@ -6540,19 +6540,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>14.7993</v>
+        <v>14.7863</v>
       </c>
       <c r="C75" t="n">
-        <v>16.6778</v>
+        <v>16.6574</v>
       </c>
       <c r="D75" t="n">
-        <v>54.2983</v>
+        <v>54.3822</v>
       </c>
       <c r="E75" t="n">
-        <v>15.0578</v>
+        <v>15.0908</v>
       </c>
       <c r="F75" t="n">
-        <v>47.2881</v>
+        <v>47.2918</v>
       </c>
     </row>
     <row r="76">
@@ -6560,19 +6560,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>14.4876</v>
+        <v>14.4947</v>
       </c>
       <c r="C76" t="n">
-        <v>16.5939</v>
+        <v>16.5953</v>
       </c>
       <c r="D76" t="n">
-        <v>54.5247</v>
+        <v>54.2686</v>
       </c>
       <c r="E76" t="n">
-        <v>14.8412</v>
+        <v>14.818</v>
       </c>
       <c r="F76" t="n">
-        <v>47.0291</v>
+        <v>46.8596</v>
       </c>
     </row>
     <row r="77">
@@ -6580,19 +6580,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>14.2275</v>
+        <v>14.2152</v>
       </c>
       <c r="C77" t="n">
-        <v>16.5166</v>
+        <v>16.5158</v>
       </c>
       <c r="D77" t="n">
-        <v>54.5211</v>
+        <v>54.5859</v>
       </c>
       <c r="E77" t="n">
-        <v>14.6117</v>
+        <v>18.8541</v>
       </c>
       <c r="F77" t="n">
-        <v>46.7806</v>
+        <v>51.3378</v>
       </c>
     </row>
     <row r="78">
@@ -6600,19 +6600,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>13.878</v>
+        <v>13.8836</v>
       </c>
       <c r="C78" t="n">
-        <v>16.4326</v>
+        <v>16.4459</v>
       </c>
       <c r="D78" t="n">
-        <v>57.4647</v>
+        <v>57.3971</v>
       </c>
       <c r="E78" t="n">
-        <v>17.9401</v>
+        <v>18.3992</v>
       </c>
       <c r="F78" t="n">
-        <v>50.939</v>
+        <v>51.0677</v>
       </c>
     </row>
     <row r="79">
@@ -6620,19 +6620,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>13.5554</v>
+        <v>13.5187</v>
       </c>
       <c r="C79" t="n">
-        <v>17.9893</v>
+        <v>17.9854</v>
       </c>
       <c r="D79" t="n">
-        <v>57.4901</v>
+        <v>57.3803</v>
       </c>
       <c r="E79" t="n">
-        <v>17.6669</v>
+        <v>18.6627</v>
       </c>
       <c r="F79" t="n">
-        <v>50.615</v>
+        <v>50.8359</v>
       </c>
     </row>
     <row r="80">
@@ -6640,19 +6640,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>13.1261</v>
+        <v>13.0915</v>
       </c>
       <c r="C80" t="n">
-        <v>17.7893</v>
+        <v>17.8094</v>
       </c>
       <c r="D80" t="n">
-        <v>57.2599</v>
+        <v>57.3783</v>
       </c>
       <c r="E80" t="n">
-        <v>17.282</v>
+        <v>17.9287</v>
       </c>
       <c r="F80" t="n">
-        <v>50.3227</v>
+        <v>50.4381</v>
       </c>
     </row>
     <row r="81">
@@ -6660,19 +6660,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>17.6636</v>
+        <v>17.6414</v>
       </c>
       <c r="C81" t="n">
-        <v>17.64</v>
+        <v>17.6072</v>
       </c>
       <c r="D81" t="n">
-        <v>57.3005</v>
+        <v>57.2956</v>
       </c>
       <c r="E81" t="n">
-        <v>16.9628</v>
+        <v>17.3909</v>
       </c>
       <c r="F81" t="n">
-        <v>50.036</v>
+        <v>50.1475</v>
       </c>
     </row>
     <row r="82">
@@ -6680,19 +6680,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>17.3545</v>
+        <v>17.354</v>
       </c>
       <c r="C82" t="n">
-        <v>17.4935</v>
+        <v>17.4932</v>
       </c>
       <c r="D82" t="n">
-        <v>57.2923</v>
+        <v>57.3084</v>
       </c>
       <c r="E82" t="n">
-        <v>16.7844</v>
+        <v>16.898</v>
       </c>
       <c r="F82" t="n">
-        <v>49.7747</v>
+        <v>49.6557</v>
       </c>
     </row>
     <row r="83">
@@ -6700,19 +6700,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>17.0076</v>
+        <v>16.9953</v>
       </c>
       <c r="C83" t="n">
-        <v>17.3404</v>
+        <v>17.3454</v>
       </c>
       <c r="D83" t="n">
-        <v>57.4042</v>
+        <v>57.4226</v>
       </c>
       <c r="E83" t="n">
-        <v>16.5476</v>
+        <v>16.5176</v>
       </c>
       <c r="F83" t="n">
-        <v>49.3419</v>
+        <v>49.4734</v>
       </c>
     </row>
     <row r="84">
@@ -6720,19 +6720,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>16.6576</v>
+        <v>16.6296</v>
       </c>
       <c r="C84" t="n">
-        <v>17.2337</v>
+        <v>17.2151</v>
       </c>
       <c r="D84" t="n">
-        <v>60.8584</v>
+        <v>60.8665</v>
       </c>
       <c r="E84" t="n">
-        <v>16.2283</v>
+        <v>16.2352</v>
       </c>
       <c r="F84" t="n">
-        <v>53.8967</v>
+        <v>53.7508</v>
       </c>
     </row>
     <row r="85">
@@ -6740,19 +6740,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>16.2613</v>
+        <v>16.2529</v>
       </c>
       <c r="C85" t="n">
-        <v>17.102</v>
+        <v>17.1085</v>
       </c>
       <c r="D85" t="n">
-        <v>60.6628</v>
+        <v>60.8251</v>
       </c>
       <c r="E85" t="n">
-        <v>16.0368</v>
+        <v>16.016</v>
       </c>
       <c r="F85" t="n">
-        <v>53.6046</v>
+        <v>53.6932</v>
       </c>
     </row>
     <row r="86">
@@ -6760,19 +6760,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>15.8853</v>
+        <v>15.8827</v>
       </c>
       <c r="C86" t="n">
-        <v>16.9965</v>
+        <v>16.9766</v>
       </c>
       <c r="D86" t="n">
-        <v>60.8131</v>
+        <v>60.7671</v>
       </c>
       <c r="E86" t="n">
-        <v>15.7732</v>
+        <v>15.8988</v>
       </c>
       <c r="F86" t="n">
-        <v>53.5903</v>
+        <v>53.4776</v>
       </c>
     </row>
     <row r="87">
@@ -6780,19 +6780,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>15.5315</v>
+        <v>15.5249</v>
       </c>
       <c r="C87" t="n">
-        <v>16.8852</v>
+        <v>16.879</v>
       </c>
       <c r="D87" t="n">
-        <v>60.8223</v>
+        <v>60.7724</v>
       </c>
       <c r="E87" t="n">
-        <v>15.5638</v>
+        <v>15.5738</v>
       </c>
       <c r="F87" t="n">
-        <v>53.1424</v>
+        <v>53.2347</v>
       </c>
     </row>
     <row r="88">
@@ -6800,19 +6800,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>15.1965</v>
+        <v>15.1979</v>
       </c>
       <c r="C88" t="n">
-        <v>16.7958</v>
+        <v>16.7698</v>
       </c>
       <c r="D88" t="n">
-        <v>60.8997</v>
+        <v>60.7594</v>
       </c>
       <c r="E88" t="n">
-        <v>15.3478</v>
+        <v>15.3376</v>
       </c>
       <c r="F88" t="n">
-        <v>52.7695</v>
+        <v>52.7834</v>
       </c>
     </row>
     <row r="89">
@@ -6820,19 +6820,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>14.8742</v>
+        <v>14.874</v>
       </c>
       <c r="C89" t="n">
-        <v>16.6917</v>
+        <v>16.7026</v>
       </c>
       <c r="D89" t="n">
-        <v>60.7298</v>
+        <v>60.8924</v>
       </c>
       <c r="E89" t="n">
-        <v>15.1136</v>
+        <v>15.1314</v>
       </c>
       <c r="F89" t="n">
-        <v>52.4342</v>
+        <v>52.5724</v>
       </c>
     </row>
     <row r="90">
@@ -6840,19 +6840,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>14.5612</v>
+        <v>14.5661</v>
       </c>
       <c r="C90" t="n">
-        <v>16.6043</v>
+        <v>16.6145</v>
       </c>
       <c r="D90" t="n">
-        <v>60.7765</v>
+        <v>60.6603</v>
       </c>
       <c r="E90" t="n">
-        <v>14.8857</v>
+        <v>14.8967</v>
       </c>
       <c r="F90" t="n">
-        <v>52.1736</v>
+        <v>52.5197</v>
       </c>
     </row>
     <row r="91">
@@ -6860,19 +6860,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>14.266</v>
+        <v>14.2542</v>
       </c>
       <c r="C91" t="n">
-        <v>16.5249</v>
+        <v>16.5156</v>
       </c>
       <c r="D91" t="n">
-        <v>60.6839</v>
+        <v>60.7246</v>
       </c>
       <c r="E91" t="n">
-        <v>14.6424</v>
+        <v>19.2869</v>
       </c>
       <c r="F91" t="n">
-        <v>51.682</v>
+        <v>56.4228</v>
       </c>
     </row>
     <row r="92">
@@ -6880,19 +6880,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>13.9486</v>
+        <v>13.9203</v>
       </c>
       <c r="C92" t="n">
-        <v>16.4539</v>
+        <v>16.4457</v>
       </c>
       <c r="D92" t="n">
-        <v>61.0428</v>
+        <v>60.9626</v>
       </c>
       <c r="E92" t="n">
-        <v>18.2336</v>
+        <v>19.7095</v>
       </c>
       <c r="F92" t="n">
-        <v>55.9651</v>
+        <v>56.0993</v>
       </c>
     </row>
     <row r="93">
@@ -6900,19 +6900,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>13.6059</v>
+        <v>13.5853</v>
       </c>
       <c r="C93" t="n">
-        <v>16.3925</v>
+        <v>16.3766</v>
       </c>
       <c r="D93" t="n">
-        <v>60.7887</v>
+        <v>61.0451</v>
       </c>
       <c r="E93" t="n">
-        <v>17.7019</v>
+        <v>19.158</v>
       </c>
       <c r="F93" t="n">
-        <v>55.716</v>
+        <v>56.0175</v>
       </c>
     </row>
     <row r="94">
@@ -6920,19 +6920,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>13.1887</v>
+        <v>13.1377</v>
       </c>
       <c r="C94" t="n">
-        <v>17.8202</v>
+        <v>17.8372</v>
       </c>
       <c r="D94" t="n">
-        <v>60.8757</v>
+        <v>60.86</v>
       </c>
       <c r="E94" t="n">
-        <v>17.3878</v>
+        <v>17.7342</v>
       </c>
       <c r="F94" t="n">
-        <v>55.2738</v>
+        <v>55.4205</v>
       </c>
     </row>
     <row r="95">
@@ -6940,19 +6940,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>17.7133</v>
+        <v>17.7025</v>
       </c>
       <c r="C95" t="n">
-        <v>17.6543</v>
+        <v>17.6668</v>
       </c>
       <c r="D95" t="n">
-        <v>60.8157</v>
+        <v>60.7337</v>
       </c>
       <c r="E95" t="n">
-        <v>17.0494</v>
+        <v>17.2311</v>
       </c>
       <c r="F95" t="n">
-        <v>54.9087</v>
+        <v>55.1166</v>
       </c>
     </row>
     <row r="96">
@@ -6960,19 +6960,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>17.4059</v>
+        <v>17.4014</v>
       </c>
       <c r="C96" t="n">
-        <v>17.4997</v>
+        <v>17.5121</v>
       </c>
       <c r="D96" t="n">
-        <v>60.6767</v>
+        <v>60.8041</v>
       </c>
       <c r="E96" t="n">
-        <v>16.8128</v>
+        <v>16.9482</v>
       </c>
       <c r="F96" t="n">
-        <v>54.8467</v>
+        <v>54.6617</v>
       </c>
     </row>
     <row r="97">
@@ -6980,19 +6980,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>17.0829</v>
+        <v>17.0678</v>
       </c>
       <c r="C97" t="n">
-        <v>17.3572</v>
+        <v>17.3451</v>
       </c>
       <c r="D97" t="n">
-        <v>60.816</v>
+        <v>60.6119</v>
       </c>
       <c r="E97" t="n">
-        <v>16.5518</v>
+        <v>17.0863</v>
       </c>
       <c r="F97" t="n">
-        <v>54.4691</v>
+        <v>54.382</v>
       </c>
     </row>
     <row r="98">
@@ -7000,19 +7000,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>16.7118</v>
+        <v>16.703</v>
       </c>
       <c r="C98" t="n">
-        <v>17.2352</v>
+        <v>17.2322</v>
       </c>
       <c r="D98" t="n">
-        <v>60.583</v>
+        <v>60.7018</v>
       </c>
       <c r="E98" t="n">
-        <v>16.2971</v>
+        <v>16.2924</v>
       </c>
       <c r="F98" t="n">
-        <v>54.0676</v>
+        <v>54.1229</v>
       </c>
     </row>
     <row r="99">
@@ -7020,19 +7020,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>16.3431</v>
+        <v>16.3331</v>
       </c>
       <c r="C99" t="n">
-        <v>17.1071</v>
+        <v>17.1145</v>
       </c>
       <c r="D99" t="n">
-        <v>60.6779</v>
+        <v>60.4744</v>
       </c>
       <c r="E99" t="n">
-        <v>16.0744</v>
+        <v>16.0837</v>
       </c>
       <c r="F99" t="n">
-        <v>53.9253</v>
+        <v>53.793</v>
       </c>
     </row>
     <row r="100">
@@ -7040,19 +7040,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>15.9685</v>
+        <v>15.9533</v>
       </c>
       <c r="C100" t="n">
-        <v>17.0032</v>
+        <v>16.9971</v>
       </c>
       <c r="D100" t="n">
-        <v>60.4404</v>
+        <v>60.4983</v>
       </c>
       <c r="E100" t="n">
-        <v>15.8395</v>
+        <v>15.8671</v>
       </c>
       <c r="F100" t="n">
-        <v>53.523</v>
+        <v>53.3255</v>
       </c>
     </row>
     <row r="101">
@@ -7060,19 +7060,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>15.6045</v>
+        <v>15.5829</v>
       </c>
       <c r="C101" t="n">
-        <v>16.8799</v>
+        <v>16.8798</v>
       </c>
       <c r="D101" t="n">
-        <v>60.4214</v>
+        <v>60.3997</v>
       </c>
       <c r="E101" t="n">
-        <v>15.6409</v>
+        <v>15.6513</v>
       </c>
       <c r="F101" t="n">
-        <v>53.1324</v>
+        <v>53.272</v>
       </c>
     </row>
     <row r="102">
@@ -7080,19 +7080,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>15.2544</v>
+        <v>15.2535</v>
       </c>
       <c r="C102" t="n">
-        <v>16.805</v>
+        <v>16.7892</v>
       </c>
       <c r="D102" t="n">
-        <v>60.4919</v>
+        <v>60.4678</v>
       </c>
       <c r="E102" t="n">
-        <v>15.3967</v>
+        <v>15.3987</v>
       </c>
       <c r="F102" t="n">
-        <v>52.9328</v>
+        <v>52.9232</v>
       </c>
     </row>
     <row r="103">
@@ -7100,19 +7100,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>14.9385</v>
+        <v>14.9269</v>
       </c>
       <c r="C103" t="n">
-        <v>16.6987</v>
+        <v>16.7207</v>
       </c>
       <c r="D103" t="n">
-        <v>60.3516</v>
+        <v>60.4461</v>
       </c>
       <c r="E103" t="n">
-        <v>15.1464</v>
+        <v>15.1533</v>
       </c>
       <c r="F103" t="n">
-        <v>52.545</v>
+        <v>52.7555</v>
       </c>
     </row>
     <row r="104">
@@ -7120,19 +7120,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>14.6212</v>
+        <v>14.6145</v>
       </c>
       <c r="C104" t="n">
-        <v>16.6101</v>
+        <v>16.6042</v>
       </c>
       <c r="D104" t="n">
-        <v>60.2775</v>
+        <v>60.4311</v>
       </c>
       <c r="E104" t="n">
-        <v>14.9314</v>
+        <v>14.9259</v>
       </c>
       <c r="F104" t="n">
-        <v>52.2983</v>
+        <v>52.5324</v>
       </c>
     </row>
     <row r="105">
@@ -7140,19 +7140,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>14.3237</v>
+        <v>14.3118</v>
       </c>
       <c r="C105" t="n">
-        <v>16.5573</v>
+        <v>16.5391</v>
       </c>
       <c r="D105" t="n">
-        <v>60.3411</v>
+        <v>60.3356</v>
       </c>
       <c r="E105" t="n">
-        <v>14.7017</v>
+        <v>21.864</v>
       </c>
       <c r="F105" t="n">
-        <v>52.0394</v>
+        <v>56.4613</v>
       </c>
     </row>
     <row r="106">
@@ -7160,19 +7160,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>14.0078</v>
+        <v>14.0036</v>
       </c>
       <c r="C106" t="n">
-        <v>16.4663</v>
+        <v>16.4469</v>
       </c>
       <c r="D106" t="n">
-        <v>60.2101</v>
+        <v>60.2666</v>
       </c>
       <c r="E106" t="n">
-        <v>14.4465</v>
+        <v>20.0416</v>
       </c>
       <c r="F106" t="n">
-        <v>51.6148</v>
+        <v>56.3112</v>
       </c>
     </row>
     <row r="107">
@@ -7180,19 +7180,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>13.6567</v>
+        <v>13.6673</v>
       </c>
       <c r="C107" t="n">
-        <v>16.4031</v>
+        <v>16.383</v>
       </c>
       <c r="D107" t="n">
-        <v>59.1759</v>
+        <v>59.1737</v>
       </c>
       <c r="E107" t="n">
-        <v>18.0072</v>
+        <v>18.4966</v>
       </c>
       <c r="F107" t="n">
-        <v>55.6086</v>
+        <v>55.9325</v>
       </c>
     </row>
     <row r="108">
@@ -7200,19 +7200,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>13.2803</v>
+        <v>13.2876</v>
       </c>
       <c r="C108" t="n">
-        <v>17.8481</v>
+        <v>17.8792</v>
       </c>
       <c r="D108" t="n">
-        <v>59.1593</v>
+        <v>59.241</v>
       </c>
       <c r="E108" t="n">
-        <v>17.4508</v>
+        <v>17.6912</v>
       </c>
       <c r="F108" t="n">
-        <v>55.5592</v>
+        <v>55.5661</v>
       </c>
     </row>
     <row r="109">
@@ -7220,19 +7220,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>12.7476</v>
+        <v>12.7175</v>
       </c>
       <c r="C109" t="n">
-        <v>17.7114</v>
+        <v>17.6973</v>
       </c>
       <c r="D109" t="n">
-        <v>59.2915</v>
+        <v>59.2367</v>
       </c>
       <c r="E109" t="n">
-        <v>17.147</v>
+        <v>18.5789</v>
       </c>
       <c r="F109" t="n">
-        <v>55.2367</v>
+        <v>55.1126</v>
       </c>
     </row>
     <row r="110">
@@ -7240,19 +7240,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>17.4821</v>
+        <v>17.4692</v>
       </c>
       <c r="C110" t="n">
-        <v>17.5223</v>
+        <v>17.5191</v>
       </c>
       <c r="D110" t="n">
-        <v>59.4168</v>
+        <v>59.5776</v>
       </c>
       <c r="E110" t="n">
-        <v>16.8929</v>
+        <v>18.3346</v>
       </c>
       <c r="F110" t="n">
-        <v>54.6803</v>
+        <v>55.0376</v>
       </c>
     </row>
     <row r="111">
@@ -7260,19 +7260,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>17.1414</v>
+        <v>17.1351</v>
       </c>
       <c r="C111" t="n">
-        <v>17.393</v>
+        <v>17.3918</v>
       </c>
       <c r="D111" t="n">
-        <v>59.4233</v>
+        <v>59.4531</v>
       </c>
       <c r="E111" t="n">
-        <v>16.6317</v>
+        <v>17.4175</v>
       </c>
       <c r="F111" t="n">
-        <v>54.3256</v>
+        <v>54.3895</v>
       </c>
     </row>
     <row r="112">
@@ -7280,19 +7280,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>16.7876</v>
+        <v>16.7763</v>
       </c>
       <c r="C112" t="n">
-        <v>17.2598</v>
+        <v>17.2633</v>
       </c>
       <c r="D112" t="n">
-        <v>59.342</v>
+        <v>59.4397</v>
       </c>
       <c r="E112" t="n">
-        <v>16.3628</v>
+        <v>16.9787</v>
       </c>
       <c r="F112" t="n">
-        <v>54.2005</v>
+        <v>54.3634</v>
       </c>
     </row>
     <row r="113">
@@ -7300,19 +7300,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>16.4197</v>
+        <v>16.4121</v>
       </c>
       <c r="C113" t="n">
-        <v>17.1184</v>
+        <v>17.1215</v>
       </c>
       <c r="D113" t="n">
-        <v>59.3833</v>
+        <v>59.57</v>
       </c>
       <c r="E113" t="n">
-        <v>16.1045</v>
+        <v>16.2391</v>
       </c>
       <c r="F113" t="n">
-        <v>53.8965</v>
+        <v>53.9556</v>
       </c>
     </row>
     <row r="114">
@@ -7320,19 +7320,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>16.0506</v>
+        <v>16.0321</v>
       </c>
       <c r="C114" t="n">
-        <v>17.0065</v>
+        <v>16.9936</v>
       </c>
       <c r="D114" t="n">
-        <v>59.4785</v>
+        <v>59.464</v>
       </c>
       <c r="E114" t="n">
-        <v>15.8846</v>
+        <v>15.9928</v>
       </c>
       <c r="F114" t="n">
-        <v>53.3575</v>
+        <v>53.5973</v>
       </c>
     </row>
     <row r="115">
@@ -7340,19 +7340,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>15.6792</v>
+        <v>15.6698</v>
       </c>
       <c r="C115" t="n">
-        <v>16.9111</v>
+        <v>16.8847</v>
       </c>
       <c r="D115" t="n">
-        <v>59.4069</v>
+        <v>59.6467</v>
       </c>
       <c r="E115" t="n">
-        <v>15.6661</v>
+        <v>15.6544</v>
       </c>
       <c r="F115" t="n">
-        <v>53.1414</v>
+        <v>53.192</v>
       </c>
     </row>
     <row r="116">
@@ -7360,19 +7360,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>15.3242</v>
+        <v>15.3169</v>
       </c>
       <c r="C116" t="n">
-        <v>16.8062</v>
+        <v>16.794</v>
       </c>
       <c r="D116" t="n">
-        <v>59.5765</v>
+        <v>59.6343</v>
       </c>
       <c r="E116" t="n">
-        <v>15.437</v>
+        <v>15.4479</v>
       </c>
       <c r="F116" t="n">
-        <v>52.7524</v>
+        <v>52.8301</v>
       </c>
     </row>
     <row r="117">
@@ -7380,19 +7380,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>15.0024</v>
+        <v>14.9861</v>
       </c>
       <c r="C117" t="n">
-        <v>16.7094</v>
+        <v>16.7135</v>
       </c>
       <c r="D117" t="n">
-        <v>59.4864</v>
+        <v>59.5384</v>
       </c>
       <c r="E117" t="n">
-        <v>15.2126</v>
+        <v>15.2256</v>
       </c>
       <c r="F117" t="n">
-        <v>52.4544</v>
+        <v>52.5364</v>
       </c>
     </row>
     <row r="118">
@@ -7400,19 +7400,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>14.6803</v>
+        <v>14.6908</v>
       </c>
       <c r="C118" t="n">
-        <v>16.609</v>
+        <v>16.6139</v>
       </c>
       <c r="D118" t="n">
-        <v>59.6947</v>
+        <v>59.5018</v>
       </c>
       <c r="E118" t="n">
-        <v>14.9662</v>
+        <v>15.0012</v>
       </c>
       <c r="F118" t="n">
-        <v>52.2782</v>
+        <v>52.2882</v>
       </c>
     </row>
     <row r="119">
@@ -7420,19 +7420,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>14.3817</v>
+        <v>14.3645</v>
       </c>
       <c r="C119" t="n">
-        <v>16.5506</v>
+        <v>16.5392</v>
       </c>
       <c r="D119" t="n">
-        <v>59.5204</v>
+        <v>59.6179</v>
       </c>
       <c r="E119" t="n">
-        <v>14.7497</v>
+        <v>22.1022</v>
       </c>
       <c r="F119" t="n">
-        <v>51.8554</v>
+        <v>56.5416</v>
       </c>
     </row>
     <row r="120">
@@ -7440,19 +7440,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>14.0598</v>
+        <v>14.0512</v>
       </c>
       <c r="C120" t="n">
         <v>16.4801</v>
       </c>
       <c r="D120" t="n">
-        <v>59.5125</v>
+        <v>59.6129</v>
       </c>
       <c r="E120" t="n">
-        <v>14.4898</v>
+        <v>21.3392</v>
       </c>
       <c r="F120" t="n">
-        <v>51.5256</v>
+        <v>56.0789</v>
       </c>
     </row>
     <row r="121">
@@ -7460,19 +7460,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>13.7302</v>
+        <v>13.7211</v>
       </c>
       <c r="C121" t="n">
-        <v>16.398</v>
+        <v>16.4032</v>
       </c>
       <c r="D121" t="n">
-        <v>61.5402</v>
+        <v>61.6465</v>
       </c>
       <c r="E121" t="n">
-        <v>18.1664</v>
+        <v>20.2431</v>
       </c>
       <c r="F121" t="n">
-        <v>55.6291</v>
+        <v>55.9769</v>
       </c>
     </row>
     <row r="122">
@@ -7480,19 +7480,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>13.3232</v>
+        <v>13.3723</v>
       </c>
       <c r="C122" t="n">
-        <v>17.8787</v>
+        <v>17.8657</v>
       </c>
       <c r="D122" t="n">
-        <v>61.3672</v>
+        <v>61.4461</v>
       </c>
       <c r="E122" t="n">
-        <v>19.1967</v>
+        <v>19.3867</v>
       </c>
       <c r="F122" t="n">
-        <v>55.348</v>
+        <v>55.5689</v>
       </c>
     </row>
     <row r="123">
@@ -7500,19 +7500,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>12.8314</v>
+        <v>12.8157</v>
       </c>
       <c r="C123" t="n">
-        <v>17.7107</v>
+        <v>17.7061</v>
       </c>
       <c r="D123" t="n">
-        <v>61.3849</v>
+        <v>61.3317</v>
       </c>
       <c r="E123" t="n">
-        <v>17.4319</v>
+        <v>19.0943</v>
       </c>
       <c r="F123" t="n">
-        <v>55.0906</v>
+        <v>55.1109</v>
       </c>
     </row>
     <row r="124">
@@ -7520,19 +7520,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>17.5257</v>
+        <v>17.532</v>
       </c>
       <c r="C124" t="n">
-        <v>17.5462</v>
+        <v>17.5526</v>
       </c>
       <c r="D124" t="n">
-        <v>61.2699</v>
+        <v>61.27</v>
       </c>
       <c r="E124" t="n">
-        <v>17.0811</v>
+        <v>17.5873</v>
       </c>
       <c r="F124" t="n">
-        <v>54.5325</v>
+        <v>54.9004</v>
       </c>
     </row>
     <row r="125">
@@ -7540,19 +7540,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>17.2191</v>
+        <v>17.2138</v>
       </c>
       <c r="C125" t="n">
-        <v>17.4017</v>
+        <v>17.3881</v>
       </c>
       <c r="D125" t="n">
-        <v>61.1693</v>
+        <v>61.2744</v>
       </c>
       <c r="E125" t="n">
-        <v>16.75</v>
+        <v>17.0553</v>
       </c>
       <c r="F125" t="n">
-        <v>54.2607</v>
+        <v>54.3437</v>
       </c>
     </row>
     <row r="126">
@@ -7560,19 +7560,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>16.8552</v>
+        <v>16.867</v>
       </c>
       <c r="C126" t="n">
-        <v>17.2586</v>
+        <v>17.2558</v>
       </c>
       <c r="D126" t="n">
-        <v>61.1453</v>
+        <v>61.1834</v>
       </c>
       <c r="E126" t="n">
-        <v>16.5962</v>
+        <v>16.5703</v>
       </c>
       <c r="F126" t="n">
-        <v>54.094</v>
+        <v>54.0549</v>
       </c>
     </row>
     <row r="127">
@@ -7580,19 +7580,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>16.4902</v>
+        <v>16.5074</v>
       </c>
       <c r="C127" t="n">
-        <v>17.1225</v>
+        <v>17.1524</v>
       </c>
       <c r="D127" t="n">
-        <v>61.1344</v>
+        <v>61.1209</v>
       </c>
       <c r="E127" t="n">
-        <v>16.1852</v>
+        <v>16.5426</v>
       </c>
       <c r="F127" t="n">
-        <v>53.7088</v>
+        <v>53.7114</v>
       </c>
     </row>
     <row r="128">
@@ -7600,19 +7600,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>16.1326</v>
+        <v>16.1115</v>
       </c>
       <c r="C128" t="n">
-        <v>17.0148</v>
+        <v>17.0093</v>
       </c>
       <c r="D128" t="n">
-        <v>60.9771</v>
+        <v>61.0583</v>
       </c>
       <c r="E128" t="n">
-        <v>15.9509</v>
+        <v>16.4538</v>
       </c>
       <c r="F128" t="n">
-        <v>53.0313</v>
+        <v>53.1891</v>
       </c>
     </row>
     <row r="129">
@@ -7620,19 +7620,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>15.755</v>
+        <v>15.7522</v>
       </c>
       <c r="C129" t="n">
-        <v>16.9063</v>
+        <v>16.933</v>
       </c>
       <c r="D129" t="n">
-        <v>60.9593</v>
+        <v>61.055</v>
       </c>
       <c r="E129" t="n">
-        <v>15.7427</v>
+        <v>15.7652</v>
       </c>
       <c r="F129" t="n">
-        <v>53.0183</v>
+        <v>53.1347</v>
       </c>
     </row>
     <row r="130">
@@ -7640,19 +7640,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>15.3852</v>
+        <v>15.4069</v>
       </c>
       <c r="C130" t="n">
-        <v>16.8074</v>
+        <v>16.8241</v>
       </c>
       <c r="D130" t="n">
-        <v>60.8698</v>
+        <v>60.8876</v>
       </c>
       <c r="E130" t="n">
-        <v>15.5124</v>
+        <v>15.544</v>
       </c>
       <c r="F130" t="n">
-        <v>52.5445</v>
+        <v>52.5639</v>
       </c>
     </row>
     <row r="131">
@@ -7660,19 +7660,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>15.0486</v>
+        <v>15.0589</v>
       </c>
       <c r="C131" t="n">
-        <v>16.6989</v>
+        <v>16.7179</v>
       </c>
       <c r="D131" t="n">
-        <v>60.7233</v>
+        <v>60.7586</v>
       </c>
       <c r="E131" t="n">
-        <v>15.2931</v>
+        <v>15.2709</v>
       </c>
       <c r="F131" t="n">
-        <v>52.4278</v>
+        <v>52.5693</v>
       </c>
     </row>
     <row r="132">
@@ -7680,19 +7680,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>14.7334</v>
+        <v>14.7364</v>
       </c>
       <c r="C132" t="n">
-        <v>16.6321</v>
+        <v>16.6543</v>
       </c>
       <c r="D132" t="n">
-        <v>60.6929</v>
+        <v>60.7432</v>
       </c>
       <c r="E132" t="n">
-        <v>15.0467</v>
+        <v>15.0207</v>
       </c>
       <c r="F132" t="n">
-        <v>52.0637</v>
+        <v>52.1602</v>
       </c>
     </row>
     <row r="133">
@@ -7700,19 +7700,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>14.4309</v>
+        <v>14.4231</v>
       </c>
       <c r="C133" t="n">
-        <v>16.5404</v>
+        <v>16.5434</v>
       </c>
       <c r="D133" t="n">
-        <v>60.6841</v>
+        <v>60.6807</v>
       </c>
       <c r="E133" t="n">
-        <v>14.7853</v>
+        <v>14.8036</v>
       </c>
       <c r="F133" t="n">
-        <v>51.7322</v>
+        <v>52.0732</v>
       </c>
     </row>
     <row r="134">
@@ -7720,19 +7720,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.1127</v>
+        <v>14.1103</v>
       </c>
       <c r="C134" t="n">
-        <v>16.456</v>
+        <v>16.4693</v>
       </c>
       <c r="D134" t="n">
-        <v>60.6029</v>
+        <v>60.6875</v>
       </c>
       <c r="E134" t="n">
-        <v>14.5439</v>
+        <v>21.6124</v>
       </c>
       <c r="F134" t="n">
-        <v>51.4843</v>
+        <v>56.0394</v>
       </c>
     </row>
     <row r="135">
@@ -7740,19 +7740,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>13.8188</v>
+        <v>13.7898</v>
       </c>
       <c r="C135" t="n">
-        <v>16.4151</v>
+        <v>16.4121</v>
       </c>
       <c r="D135" t="n">
-        <v>62.0636</v>
+        <v>62.1823</v>
       </c>
       <c r="E135" t="n">
-        <v>18.4572</v>
+        <v>20.6456</v>
       </c>
       <c r="F135" t="n">
-        <v>55.8021</v>
+        <v>55.6848</v>
       </c>
     </row>
     <row r="136">
@@ -7760,19 +7760,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>13.4026</v>
+        <v>13.4419</v>
       </c>
       <c r="C136" t="n">
-        <v>17.896</v>
+        <v>17.9109</v>
       </c>
       <c r="D136" t="n">
-        <v>61.8873</v>
+        <v>61.9857</v>
       </c>
       <c r="E136" t="n">
-        <v>17.988</v>
+        <v>20.5321</v>
       </c>
       <c r="F136" t="n">
-        <v>55.1394</v>
+        <v>55.3341</v>
       </c>
     </row>
     <row r="137">
@@ -7780,19 +7780,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>12.9312</v>
+        <v>12.9271</v>
       </c>
       <c r="C137" t="n">
-        <v>17.7318</v>
+        <v>17.7393</v>
       </c>
       <c r="D137" t="n">
-        <v>61.7333</v>
+        <v>61.7364</v>
       </c>
       <c r="E137" t="n">
-        <v>18.2298</v>
+        <v>18.7197</v>
       </c>
       <c r="F137" t="n">
-        <v>54.9421</v>
+        <v>55.197</v>
       </c>
     </row>
     <row r="138">
@@ -7800,19 +7800,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>17.588</v>
+        <v>17.6207</v>
       </c>
       <c r="C138" t="n">
-        <v>17.5574</v>
+        <v>17.5831</v>
       </c>
       <c r="D138" t="n">
-        <v>61.5884</v>
+        <v>61.6127</v>
       </c>
       <c r="E138" t="n">
-        <v>17.2293</v>
+        <v>18.8887</v>
       </c>
       <c r="F138" t="n">
-        <v>54.3572</v>
+        <v>54.4228</v>
       </c>
     </row>
     <row r="139">
@@ -7820,19 +7820,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>17.3058</v>
+        <v>17.2723</v>
       </c>
       <c r="C139" t="n">
-        <v>17.4146</v>
+        <v>17.431</v>
       </c>
       <c r="D139" t="n">
-        <v>61.5962</v>
+        <v>61.5456</v>
       </c>
       <c r="E139" t="n">
-        <v>16.7604</v>
+        <v>17.476</v>
       </c>
       <c r="F139" t="n">
-        <v>53.9666</v>
+        <v>54.094</v>
       </c>
     </row>
     <row r="140">
@@ -7840,19 +7840,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>16.9415</v>
+        <v>16.9273</v>
       </c>
       <c r="C140" t="n">
-        <v>17.2807</v>
+        <v>17.2964</v>
       </c>
       <c r="D140" t="n">
-        <v>61.4913</v>
+        <v>61.4534</v>
       </c>
       <c r="E140" t="n">
-        <v>16.4627</v>
+        <v>17.5837</v>
       </c>
       <c r="F140" t="n">
-        <v>54.0451</v>
+        <v>53.9205</v>
       </c>
     </row>
     <row r="141">
@@ -7860,19 +7860,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>16.5714</v>
+        <v>16.5711</v>
       </c>
       <c r="C141" t="n">
-        <v>17.1562</v>
+        <v>17.1458</v>
       </c>
       <c r="D141" t="n">
-        <v>61.3903</v>
+        <v>61.3739</v>
       </c>
       <c r="E141" t="n">
-        <v>16.249</v>
+        <v>16.8677</v>
       </c>
       <c r="F141" t="n">
-        <v>53.394</v>
+        <v>53.5919</v>
       </c>
     </row>
     <row r="142">
@@ -7880,19 +7880,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>16.2105</v>
+        <v>16.1862</v>
       </c>
       <c r="C142" t="n">
-        <v>17.0268</v>
+        <v>17.0161</v>
       </c>
       <c r="D142" t="n">
-        <v>61.2643</v>
+        <v>61.2963</v>
       </c>
       <c r="E142" t="n">
-        <v>16.0281</v>
+        <v>17.1194</v>
       </c>
       <c r="F142" t="n">
-        <v>53.1698</v>
+        <v>53.0587</v>
       </c>
     </row>
     <row r="143">
@@ -7900,19 +7900,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>15.8226</v>
+        <v>15.8115</v>
       </c>
       <c r="C143" t="n">
-        <v>16.9208</v>
+        <v>16.9109</v>
       </c>
       <c r="D143" t="n">
-        <v>61.2632</v>
+        <v>61.265</v>
       </c>
       <c r="E143" t="n">
-        <v>15.8435</v>
+        <v>15.9641</v>
       </c>
       <c r="F143" t="n">
-        <v>52.8274</v>
+        <v>53.1579</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Running erasure.xlsx
+++ b/vs-x64/Running erasure.xlsx
@@ -5080,19 +5080,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>14.7355</v>
+        <v>14.4659</v>
       </c>
       <c r="C2" t="n">
-        <v>14.9282</v>
+        <v>14.965</v>
       </c>
       <c r="D2" t="n">
-        <v>41.8979</v>
+        <v>41.9022</v>
       </c>
       <c r="E2" t="n">
-        <v>14.2972</v>
+        <v>14.206</v>
       </c>
       <c r="F2" t="n">
-        <v>35.4062</v>
+        <v>35.4925</v>
       </c>
     </row>
     <row r="3">
@@ -5100,19 +5100,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>14.2168</v>
+        <v>14.2069</v>
       </c>
       <c r="C3" t="n">
-        <v>15.0506</v>
+        <v>15.0842</v>
       </c>
       <c r="D3" t="n">
-        <v>41.852</v>
+        <v>41.8772</v>
       </c>
       <c r="E3" t="n">
-        <v>14.0177</v>
+        <v>14.1933</v>
       </c>
       <c r="F3" t="n">
-        <v>35.2301</v>
+        <v>35.2062</v>
       </c>
     </row>
     <row r="4">
@@ -5120,19 +5120,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>13.9254</v>
+        <v>13.9149</v>
       </c>
       <c r="C4" t="n">
-        <v>15.1639</v>
+        <v>15.2279</v>
       </c>
       <c r="D4" t="n">
-        <v>42.068</v>
+        <v>41.9761</v>
       </c>
       <c r="E4" t="n">
-        <v>13.8317</v>
+        <v>13.7872</v>
       </c>
       <c r="F4" t="n">
-        <v>34.8066</v>
+        <v>34.7132</v>
       </c>
     </row>
     <row r="5">
@@ -5140,19 +5140,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>13.7244</v>
+        <v>13.8436</v>
       </c>
       <c r="C5" t="n">
-        <v>15.0757</v>
+        <v>15.1516</v>
       </c>
       <c r="D5" t="n">
-        <v>41.8604</v>
+        <v>41.8558</v>
       </c>
       <c r="E5" t="n">
-        <v>20.3483</v>
+        <v>17.1391</v>
       </c>
       <c r="F5" t="n">
-        <v>38.9113</v>
+        <v>38.7587</v>
       </c>
     </row>
     <row r="6">
@@ -5160,19 +5160,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>13.4378</v>
+        <v>13.6487</v>
       </c>
       <c r="C6" t="n">
-        <v>15.1631</v>
+        <v>15.1823</v>
       </c>
       <c r="D6" t="n">
-        <v>41.8051</v>
+        <v>41.7723</v>
       </c>
       <c r="E6" t="n">
-        <v>20.7367</v>
+        <v>18.2444</v>
       </c>
       <c r="F6" t="n">
-        <v>38.6134</v>
+        <v>38.6594</v>
       </c>
     </row>
     <row r="7">
@@ -5180,19 +5180,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>13.1703</v>
+        <v>13.1501</v>
       </c>
       <c r="C7" t="n">
-        <v>15.1779</v>
+        <v>15.1471</v>
       </c>
       <c r="D7" t="n">
-        <v>42.5518</v>
+        <v>42.6817</v>
       </c>
       <c r="E7" t="n">
-        <v>16.7753</v>
+        <v>20.8631</v>
       </c>
       <c r="F7" t="n">
-        <v>38.3622</v>
+        <v>38.5999</v>
       </c>
     </row>
     <row r="8">
@@ -5200,19 +5200,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>12.8881</v>
+        <v>12.746</v>
       </c>
       <c r="C8" t="n">
-        <v>17.0294</v>
+        <v>17.0098</v>
       </c>
       <c r="D8" t="n">
-        <v>42.7293</v>
+        <v>42.7704</v>
       </c>
       <c r="E8" t="n">
-        <v>16.391</v>
+        <v>20.1757</v>
       </c>
       <c r="F8" t="n">
-        <v>38.0787</v>
+        <v>38.0241</v>
       </c>
     </row>
     <row r="9">
@@ -5220,19 +5220,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>12.309</v>
+        <v>12.466</v>
       </c>
       <c r="C9" t="n">
-        <v>16.9485</v>
+        <v>16.8808</v>
       </c>
       <c r="D9" t="n">
-        <v>42.7773</v>
+        <v>42.7327</v>
       </c>
       <c r="E9" t="n">
-        <v>19.515</v>
+        <v>16.4007</v>
       </c>
       <c r="F9" t="n">
-        <v>37.9002</v>
+        <v>38.0336</v>
       </c>
     </row>
     <row r="10">
@@ -5240,19 +5240,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>17.1044</v>
+        <v>17.2087</v>
       </c>
       <c r="C10" t="n">
-        <v>16.7389</v>
+        <v>16.7283</v>
       </c>
       <c r="D10" t="n">
-        <v>42.7024</v>
+        <v>42.6679</v>
       </c>
       <c r="E10" t="n">
-        <v>16.2293</v>
+        <v>16.1671</v>
       </c>
       <c r="F10" t="n">
-        <v>37.5649</v>
+        <v>37.7541</v>
       </c>
     </row>
     <row r="11">
@@ -5260,19 +5260,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>16.9157</v>
+        <v>16.9668</v>
       </c>
       <c r="C11" t="n">
-        <v>16.7213</v>
+        <v>16.7216</v>
       </c>
       <c r="D11" t="n">
-        <v>42.6393</v>
+        <v>42.6282</v>
       </c>
       <c r="E11" t="n">
-        <v>15.931</v>
+        <v>15.9581</v>
       </c>
       <c r="F11" t="n">
-        <v>37.4723</v>
+        <v>37.489</v>
       </c>
     </row>
     <row r="12">
@@ -5280,19 +5280,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>16.4879</v>
+        <v>16.5975</v>
       </c>
       <c r="C12" t="n">
-        <v>16.6489</v>
+        <v>16.686</v>
       </c>
       <c r="D12" t="n">
-        <v>42.6603</v>
+        <v>42.6182</v>
       </c>
       <c r="E12" t="n">
-        <v>15.7148</v>
+        <v>15.7488</v>
       </c>
       <c r="F12" t="n">
-        <v>37.0201</v>
+        <v>36.9015</v>
       </c>
     </row>
     <row r="13">
@@ -5300,19 +5300,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>16.138</v>
+        <v>16.3083</v>
       </c>
       <c r="C13" t="n">
-        <v>16.547</v>
+        <v>16.5262</v>
       </c>
       <c r="D13" t="n">
-        <v>42.6279</v>
+        <v>42.6156</v>
       </c>
       <c r="E13" t="n">
-        <v>15.5452</v>
+        <v>15.541</v>
       </c>
       <c r="F13" t="n">
-        <v>36.7439</v>
+        <v>36.8016</v>
       </c>
     </row>
     <row r="14">
@@ -5320,19 +5320,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>15.842</v>
+        <v>15.92</v>
       </c>
       <c r="C14" t="n">
-        <v>16.5381</v>
+        <v>16.4987</v>
       </c>
       <c r="D14" t="n">
-        <v>42.6934</v>
+        <v>42.6644</v>
       </c>
       <c r="E14" t="n">
-        <v>15.3384</v>
+        <v>15.3554</v>
       </c>
       <c r="F14" t="n">
-        <v>36.3362</v>
+        <v>36.7308</v>
       </c>
     </row>
     <row r="15">
@@ -5340,19 +5340,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>15.6977</v>
+        <v>15.6269</v>
       </c>
       <c r="C15" t="n">
-        <v>16.3868</v>
+        <v>16.3931</v>
       </c>
       <c r="D15" t="n">
-        <v>42.6322</v>
+        <v>42.6132</v>
       </c>
       <c r="E15" t="n">
-        <v>15.1664</v>
+        <v>15.1684</v>
       </c>
       <c r="F15" t="n">
-        <v>36.2735</v>
+        <v>36.2953</v>
       </c>
     </row>
     <row r="16">
@@ -5360,19 +5360,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>15.2122</v>
+        <v>15.2871</v>
       </c>
       <c r="C16" t="n">
-        <v>16.369</v>
+        <v>16.3855</v>
       </c>
       <c r="D16" t="n">
-        <v>42.5089</v>
+        <v>42.6589</v>
       </c>
       <c r="E16" t="n">
-        <v>14.9899</v>
+        <v>14.8915</v>
       </c>
       <c r="F16" t="n">
-        <v>35.8598</v>
+        <v>36.0453</v>
       </c>
     </row>
     <row r="17">
@@ -5380,19 +5380,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>14.8685</v>
+        <v>15.0721</v>
       </c>
       <c r="C17" t="n">
-        <v>16.182</v>
+        <v>16.1891</v>
       </c>
       <c r="D17" t="n">
-        <v>42.4303</v>
+        <v>42.5132</v>
       </c>
       <c r="E17" t="n">
-        <v>15.4733</v>
+        <v>14.7284</v>
       </c>
       <c r="F17" t="n">
-        <v>35.6047</v>
+        <v>35.8858</v>
       </c>
     </row>
     <row r="18">
@@ -5400,19 +5400,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>14.6417</v>
+        <v>14.6493</v>
       </c>
       <c r="C18" t="n">
-        <v>16.1565</v>
+        <v>16.1354</v>
       </c>
       <c r="D18" t="n">
-        <v>42.5049</v>
+        <v>42.4572</v>
       </c>
       <c r="E18" t="n">
-        <v>14.5258</v>
+        <v>14.5836</v>
       </c>
       <c r="F18" t="n">
-        <v>35.4268</v>
+        <v>35.4344</v>
       </c>
     </row>
     <row r="19">
@@ -5420,19 +5420,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>14.2435</v>
+        <v>14.3393</v>
       </c>
       <c r="C19" t="n">
-        <v>16.0808</v>
+        <v>16.1085</v>
       </c>
       <c r="D19" t="n">
-        <v>42.4559</v>
+        <v>42.6252</v>
       </c>
       <c r="E19" t="n">
-        <v>14.2664</v>
+        <v>14.2965</v>
       </c>
       <c r="F19" t="n">
-        <v>35.247</v>
+        <v>35.1211</v>
       </c>
     </row>
     <row r="20">
@@ -5440,19 +5440,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>14.0272</v>
+        <v>14.0636</v>
       </c>
       <c r="C20" t="n">
-        <v>16.0808</v>
+        <v>16.0621</v>
       </c>
       <c r="D20" t="n">
-        <v>42.537</v>
+        <v>42.5345</v>
       </c>
       <c r="E20" t="n">
-        <v>17.4612</v>
+        <v>17.4508</v>
       </c>
       <c r="F20" t="n">
-        <v>39.1379</v>
+        <v>39.2403</v>
       </c>
     </row>
     <row r="21">
@@ -5460,19 +5460,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>13.6967</v>
+        <v>13.6669</v>
       </c>
       <c r="C21" t="n">
-        <v>15.9461</v>
+        <v>15.8953</v>
       </c>
       <c r="D21" t="n">
-        <v>43.2904</v>
+        <v>43.4307</v>
       </c>
       <c r="E21" t="n">
-        <v>17.1657</v>
+        <v>17.0646</v>
       </c>
       <c r="F21" t="n">
-        <v>38.8356</v>
+        <v>38.9628</v>
       </c>
     </row>
     <row r="22">
@@ -5480,19 +5480,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>13.2641</v>
+        <v>13.3503</v>
       </c>
       <c r="C22" t="n">
-        <v>17.6479</v>
+        <v>17.6407</v>
       </c>
       <c r="D22" t="n">
-        <v>43.1568</v>
+        <v>43.5361</v>
       </c>
       <c r="E22" t="n">
-        <v>16.9977</v>
+        <v>16.999</v>
       </c>
       <c r="F22" t="n">
-        <v>38.7242</v>
+        <v>38.6097</v>
       </c>
     </row>
     <row r="23">
@@ -5500,19 +5500,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.8917</v>
+        <v>12.8041</v>
       </c>
       <c r="C23" t="n">
-        <v>17.5043</v>
+        <v>17.4722</v>
       </c>
       <c r="D23" t="n">
-        <v>43.2473</v>
+        <v>43.3691</v>
       </c>
       <c r="E23" t="n">
-        <v>16.7154</v>
+        <v>16.6915</v>
       </c>
       <c r="F23" t="n">
-        <v>38.2386</v>
+        <v>38.2777</v>
       </c>
     </row>
     <row r="24">
@@ -5520,19 +5520,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>17.4632</v>
+        <v>17.4881</v>
       </c>
       <c r="C24" t="n">
-        <v>17.3609</v>
+        <v>17.3016</v>
       </c>
       <c r="D24" t="n">
-        <v>43.0987</v>
+        <v>43.2773</v>
       </c>
       <c r="E24" t="n">
-        <v>16.3736</v>
+        <v>16.4115</v>
       </c>
       <c r="F24" t="n">
-        <v>37.8639</v>
+        <v>38.0553</v>
       </c>
     </row>
     <row r="25">
@@ -5540,19 +5540,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>17.1674</v>
+        <v>17.1722</v>
       </c>
       <c r="C25" t="n">
-        <v>17.2325</v>
+        <v>17.2097</v>
       </c>
       <c r="D25" t="n">
-        <v>43.1403</v>
+        <v>43.168</v>
       </c>
       <c r="E25" t="n">
-        <v>16.214</v>
+        <v>16.1952</v>
       </c>
       <c r="F25" t="n">
-        <v>37.689</v>
+        <v>38.1478</v>
       </c>
     </row>
     <row r="26">
@@ -5560,19 +5560,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>16.8524</v>
+        <v>16.827</v>
       </c>
       <c r="C26" t="n">
-        <v>17.1033</v>
+        <v>17.067</v>
       </c>
       <c r="D26" t="n">
-        <v>43.0923</v>
+        <v>43.2093</v>
       </c>
       <c r="E26" t="n">
-        <v>15.9269</v>
+        <v>15.9374</v>
       </c>
       <c r="F26" t="n">
-        <v>37.3133</v>
+        <v>37.5455</v>
       </c>
     </row>
     <row r="27">
@@ -5580,19 +5580,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>16.4837</v>
+        <v>16.4727</v>
       </c>
       <c r="C27" t="n">
-        <v>16.9786</v>
+        <v>16.9598</v>
       </c>
       <c r="D27" t="n">
-        <v>43.046</v>
+        <v>43.1044</v>
       </c>
       <c r="E27" t="n">
-        <v>15.7626</v>
+        <v>15.7456</v>
       </c>
       <c r="F27" t="n">
-        <v>37.0969</v>
+        <v>37.2142</v>
       </c>
     </row>
     <row r="28">
@@ -5600,19 +5600,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>16.1358</v>
+        <v>16.1229</v>
       </c>
       <c r="C28" t="n">
-        <v>16.8633</v>
+        <v>16.8414</v>
       </c>
       <c r="D28" t="n">
-        <v>43.0366</v>
+        <v>43.226</v>
       </c>
       <c r="E28" t="n">
-        <v>15.5436</v>
+        <v>15.5887</v>
       </c>
       <c r="F28" t="n">
-        <v>36.5555</v>
+        <v>37.1351</v>
       </c>
     </row>
     <row r="29">
@@ -5620,19 +5620,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>15.7927</v>
+        <v>15.7774</v>
       </c>
       <c r="C29" t="n">
-        <v>16.7135</v>
+        <v>16.7164</v>
       </c>
       <c r="D29" t="n">
-        <v>43.0388</v>
+        <v>43.0768</v>
       </c>
       <c r="E29" t="n">
-        <v>15.4505</v>
+        <v>15.4091</v>
       </c>
       <c r="F29" t="n">
-        <v>36.4592</v>
+        <v>36.6958</v>
       </c>
     </row>
     <row r="30">
@@ -5640,19 +5640,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>15.4683</v>
+        <v>15.4339</v>
       </c>
       <c r="C30" t="n">
-        <v>16.6581</v>
+        <v>16.6648</v>
       </c>
       <c r="D30" t="n">
-        <v>42.9482</v>
+        <v>43.1042</v>
       </c>
       <c r="E30" t="n">
-        <v>15.1817</v>
+        <v>15.1704</v>
       </c>
       <c r="F30" t="n">
-        <v>36.2276</v>
+        <v>36.3374</v>
       </c>
     </row>
     <row r="31">
@@ -5660,19 +5660,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>15.1053</v>
+        <v>15.1395</v>
       </c>
       <c r="C31" t="n">
-        <v>16.5908</v>
+        <v>16.572</v>
       </c>
       <c r="D31" t="n">
-        <v>42.8189</v>
+        <v>42.9298</v>
       </c>
       <c r="E31" t="n">
-        <v>14.9685</v>
+        <v>14.9768</v>
       </c>
       <c r="F31" t="n">
-        <v>35.9022</v>
+        <v>36.0205</v>
       </c>
     </row>
     <row r="32">
@@ -5680,19 +5680,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>14.8422</v>
+        <v>14.8007</v>
       </c>
       <c r="C32" t="n">
-        <v>16.5709</v>
+        <v>16.5408</v>
       </c>
       <c r="D32" t="n">
-        <v>42.7401</v>
+        <v>42.9661</v>
       </c>
       <c r="E32" t="n">
-        <v>14.8254</v>
+        <v>14.7973</v>
       </c>
       <c r="F32" t="n">
-        <v>35.7404</v>
+        <v>35.8517</v>
       </c>
     </row>
     <row r="33">
@@ -5700,19 +5700,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>14.5474</v>
+        <v>14.5362</v>
       </c>
       <c r="C33" t="n">
-        <v>16.4297</v>
+        <v>16.4125</v>
       </c>
       <c r="D33" t="n">
-        <v>42.7998</v>
+        <v>42.8684</v>
       </c>
       <c r="E33" t="n">
-        <v>14.52</v>
+        <v>14.552</v>
       </c>
       <c r="F33" t="n">
-        <v>35.4063</v>
+        <v>35.6193</v>
       </c>
     </row>
     <row r="34">
@@ -5720,19 +5720,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>14.257</v>
+        <v>14.2523</v>
       </c>
       <c r="C34" t="n">
-        <v>16.3561</v>
+        <v>16.3586</v>
       </c>
       <c r="D34" t="n">
-        <v>42.7937</v>
+        <v>42.8503</v>
       </c>
       <c r="E34" t="n">
-        <v>18.1</v>
+        <v>18.1611</v>
       </c>
       <c r="F34" t="n">
-        <v>39.4784</v>
+        <v>39.8052</v>
       </c>
     </row>
     <row r="35">
@@ -5740,19 +5740,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>13.9407</v>
+        <v>13.9282</v>
       </c>
       <c r="C35" t="n">
-        <v>16.3184</v>
+        <v>16.2932</v>
       </c>
       <c r="D35" t="n">
-        <v>43.8</v>
+        <v>43.8584</v>
       </c>
       <c r="E35" t="n">
-        <v>17.7981</v>
+        <v>17.753</v>
       </c>
       <c r="F35" t="n">
-        <v>39.3098</v>
+        <v>39.6633</v>
       </c>
     </row>
     <row r="36">
@@ -5760,19 +5760,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>13.61</v>
+        <v>13.6003</v>
       </c>
       <c r="C36" t="n">
-        <v>16.2278</v>
+        <v>16.2121</v>
       </c>
       <c r="D36" t="n">
-        <v>43.7177</v>
+        <v>43.7752</v>
       </c>
       <c r="E36" t="n">
-        <v>17.4392</v>
+        <v>17.4646</v>
       </c>
       <c r="F36" t="n">
-        <v>38.9825</v>
+        <v>39.0185</v>
       </c>
     </row>
     <row r="37">
@@ -5780,19 +5780,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.1968</v>
+        <v>13.1977</v>
       </c>
       <c r="C37" t="n">
-        <v>17.7959</v>
+        <v>17.7407</v>
       </c>
       <c r="D37" t="n">
-        <v>43.7145</v>
+        <v>43.8489</v>
       </c>
       <c r="E37" t="n">
-        <v>17.0849</v>
+        <v>17.0966</v>
       </c>
       <c r="F37" t="n">
-        <v>38.7793</v>
+        <v>38.9816</v>
       </c>
     </row>
     <row r="38">
@@ -5800,19 +5800,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>17.6411</v>
+        <v>17.6101</v>
       </c>
       <c r="C38" t="n">
-        <v>17.6056</v>
+        <v>17.5786</v>
       </c>
       <c r="D38" t="n">
-        <v>43.5104</v>
+        <v>43.6775</v>
       </c>
       <c r="E38" t="n">
-        <v>16.7803</v>
+        <v>16.7392</v>
       </c>
       <c r="F38" t="n">
-        <v>38.3725</v>
+        <v>38.4977</v>
       </c>
     </row>
     <row r="39">
@@ -5820,19 +5820,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>17.349</v>
+        <v>17.3278</v>
       </c>
       <c r="C39" t="n">
-        <v>17.497</v>
+        <v>17.4475</v>
       </c>
       <c r="D39" t="n">
-        <v>43.5918</v>
+        <v>43.6618</v>
       </c>
       <c r="E39" t="n">
-        <v>16.5082</v>
+        <v>16.4968</v>
       </c>
       <c r="F39" t="n">
-        <v>38.1677</v>
+        <v>37.9104</v>
       </c>
     </row>
     <row r="40">
@@ -5840,19 +5840,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>17.038</v>
+        <v>17.017</v>
       </c>
       <c r="C40" t="n">
-        <v>17.3619</v>
+        <v>17.3337</v>
       </c>
       <c r="D40" t="n">
-        <v>43.5334</v>
+        <v>43.6694</v>
       </c>
       <c r="E40" t="n">
-        <v>16.2758</v>
+        <v>16.2887</v>
       </c>
       <c r="F40" t="n">
-        <v>37.7544</v>
+        <v>37.6119</v>
       </c>
     </row>
     <row r="41">
@@ -5860,19 +5860,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>16.6898</v>
+        <v>16.6871</v>
       </c>
       <c r="C41" t="n">
-        <v>17.2058</v>
+        <v>17.1528</v>
       </c>
       <c r="D41" t="n">
-        <v>43.4997</v>
+        <v>43.6143</v>
       </c>
       <c r="E41" t="n">
-        <v>15.9946</v>
+        <v>16.0162</v>
       </c>
       <c r="F41" t="n">
-        <v>37.5493</v>
+        <v>37.4924</v>
       </c>
     </row>
     <row r="42">
@@ -5880,19 +5880,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>16.3379</v>
+        <v>16.333</v>
       </c>
       <c r="C42" t="n">
-        <v>17.0292</v>
+        <v>17.0035</v>
       </c>
       <c r="D42" t="n">
-        <v>43.4267</v>
+        <v>43.499</v>
       </c>
       <c r="E42" t="n">
-        <v>15.7807</v>
+        <v>15.7854</v>
       </c>
       <c r="F42" t="n">
-        <v>37.0936</v>
+        <v>37.8148</v>
       </c>
     </row>
     <row r="43">
@@ -5900,19 +5900,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>15.9878</v>
+        <v>15.9786</v>
       </c>
       <c r="C43" t="n">
-        <v>16.9186</v>
+        <v>16.9102</v>
       </c>
       <c r="D43" t="n">
-        <v>43.3816</v>
+        <v>43.5976</v>
       </c>
       <c r="E43" t="n">
-        <v>15.5984</v>
+        <v>15.6373</v>
       </c>
       <c r="F43" t="n">
-        <v>36.8641</v>
+        <v>36.9825</v>
       </c>
     </row>
     <row r="44">
@@ -5920,19 +5920,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>15.6073</v>
+        <v>15.6045</v>
       </c>
       <c r="C44" t="n">
-        <v>16.831</v>
+        <v>16.8133</v>
       </c>
       <c r="D44" t="n">
-        <v>43.3876</v>
+        <v>43.4917</v>
       </c>
       <c r="E44" t="n">
-        <v>15.4274</v>
+        <v>15.4583</v>
       </c>
       <c r="F44" t="n">
-        <v>36.6298</v>
+        <v>36.7213</v>
       </c>
     </row>
     <row r="45">
@@ -5940,19 +5940,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>15.2724</v>
+        <v>15.2646</v>
       </c>
       <c r="C45" t="n">
-        <v>16.725</v>
+        <v>16.7053</v>
       </c>
       <c r="D45" t="n">
-        <v>43.1293</v>
+        <v>43.3788</v>
       </c>
       <c r="E45" t="n">
-        <v>15.2323</v>
+        <v>15.2706</v>
       </c>
       <c r="F45" t="n">
-        <v>36.1645</v>
+        <v>36.6544</v>
       </c>
     </row>
     <row r="46">
@@ -5960,19 +5960,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>14.9457</v>
+        <v>14.9547</v>
       </c>
       <c r="C46" t="n">
-        <v>16.6141</v>
+        <v>16.6071</v>
       </c>
       <c r="D46" t="n">
-        <v>43.2981</v>
+        <v>43.2488</v>
       </c>
       <c r="E46" t="n">
-        <v>15.0419</v>
+        <v>15.0173</v>
       </c>
       <c r="F46" t="n">
-        <v>35.9731</v>
+        <v>36.1252</v>
       </c>
     </row>
     <row r="47">
@@ -5980,19 +5980,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>14.6642</v>
+        <v>14.6286</v>
       </c>
       <c r="C47" t="n">
-        <v>16.5417</v>
+        <v>16.5601</v>
       </c>
       <c r="D47" t="n">
-        <v>43.0959</v>
+        <v>43.1992</v>
       </c>
       <c r="E47" t="n">
-        <v>14.8008</v>
+        <v>14.8447</v>
       </c>
       <c r="F47" t="n">
-        <v>35.7515</v>
+        <v>35.6584</v>
       </c>
     </row>
     <row r="48">
@@ -6000,19 +6000,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>14.4127</v>
+        <v>14.3669</v>
       </c>
       <c r="C48" t="n">
-        <v>16.4785</v>
+        <v>16.4807</v>
       </c>
       <c r="D48" t="n">
-        <v>43.1414</v>
+        <v>43.1435</v>
       </c>
       <c r="E48" t="n">
-        <v>18.3569</v>
+        <v>18.4067</v>
       </c>
       <c r="F48" t="n">
-        <v>40.0384</v>
+        <v>39.9456</v>
       </c>
     </row>
     <row r="49">
@@ -6020,19 +6020,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>14.0772</v>
+        <v>14.0613</v>
       </c>
       <c r="C49" t="n">
-        <v>16.398</v>
+        <v>16.3888</v>
       </c>
       <c r="D49" t="n">
-        <v>42.9561</v>
+        <v>43.1122</v>
       </c>
       <c r="E49" t="n">
-        <v>17.9854</v>
+        <v>17.9532</v>
       </c>
       <c r="F49" t="n">
-        <v>39.7088</v>
+        <v>39.5621</v>
       </c>
     </row>
     <row r="50">
@@ -6040,19 +6040,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>13.756</v>
+        <v>13.7331</v>
       </c>
       <c r="C50" t="n">
-        <v>16.3329</v>
+        <v>16.3566</v>
       </c>
       <c r="D50" t="n">
-        <v>44.047</v>
+        <v>44.1334</v>
       </c>
       <c r="E50" t="n">
-        <v>17.5868</v>
+        <v>17.63</v>
       </c>
       <c r="F50" t="n">
-        <v>39.4045</v>
+        <v>39.4424</v>
       </c>
     </row>
     <row r="51">
@@ -6060,19 +6060,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>13.3413</v>
+        <v>13.3434</v>
       </c>
       <c r="C51" t="n">
-        <v>17.8539</v>
+        <v>17.8436</v>
       </c>
       <c r="D51" t="n">
-        <v>44.0111</v>
+        <v>44.0669</v>
       </c>
       <c r="E51" t="n">
-        <v>17.2695</v>
+        <v>17.2722</v>
       </c>
       <c r="F51" t="n">
-        <v>38.9751</v>
+        <v>39.2715</v>
       </c>
     </row>
     <row r="52">
@@ -6080,19 +6080,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>12.8317</v>
+        <v>12.8256</v>
       </c>
       <c r="C52" t="n">
-        <v>17.6741</v>
+        <v>17.6771</v>
       </c>
       <c r="D52" t="n">
-        <v>43.9698</v>
+        <v>44.0552</v>
       </c>
       <c r="E52" t="n">
-        <v>17.1022</v>
+        <v>16.9895</v>
       </c>
       <c r="F52" t="n">
-        <v>38.7012</v>
+        <v>38.6116</v>
       </c>
     </row>
     <row r="53">
@@ -6100,19 +6100,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>17.4026</v>
+        <v>17.4107</v>
       </c>
       <c r="C53" t="n">
-        <v>17.5063</v>
+        <v>17.4864</v>
       </c>
       <c r="D53" t="n">
-        <v>43.8864</v>
+        <v>43.9431</v>
       </c>
       <c r="E53" t="n">
-        <v>16.7316</v>
+        <v>16.7116</v>
       </c>
       <c r="F53" t="n">
-        <v>38.2847</v>
+        <v>38.5483</v>
       </c>
     </row>
     <row r="54">
@@ -6120,19 +6120,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>17.0908</v>
+        <v>17.1137</v>
       </c>
       <c r="C54" t="n">
-        <v>17.3952</v>
+        <v>17.3633</v>
       </c>
       <c r="D54" t="n">
-        <v>43.7949</v>
+        <v>43.8332</v>
       </c>
       <c r="E54" t="n">
-        <v>16.4879</v>
+        <v>16.462</v>
       </c>
       <c r="F54" t="n">
-        <v>38.2551</v>
+        <v>38.2121</v>
       </c>
     </row>
     <row r="55">
@@ -6140,19 +6140,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>16.7718</v>
+        <v>16.7748</v>
       </c>
       <c r="C55" t="n">
-        <v>17.2707</v>
+        <v>17.2589</v>
       </c>
       <c r="D55" t="n">
-        <v>43.9343</v>
+        <v>43.8298</v>
       </c>
       <c r="E55" t="n">
-        <v>16.2356</v>
+        <v>16.2255</v>
       </c>
       <c r="F55" t="n">
-        <v>37.7616</v>
+        <v>37.8028</v>
       </c>
     </row>
     <row r="56">
@@ -6160,19 +6160,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>16.4376</v>
+        <v>16.4207</v>
       </c>
       <c r="C56" t="n">
-        <v>17.1124</v>
+        <v>17.0899</v>
       </c>
       <c r="D56" t="n">
-        <v>43.684</v>
+        <v>43.7276</v>
       </c>
       <c r="E56" t="n">
-        <v>15.9867</v>
+        <v>15.9918</v>
       </c>
       <c r="F56" t="n">
-        <v>39.0198</v>
+        <v>38.6301</v>
       </c>
     </row>
     <row r="57">
@@ -6180,19 +6180,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>16.0454</v>
+        <v>16.0508</v>
       </c>
       <c r="C57" t="n">
-        <v>17.0269</v>
+        <v>17.0093</v>
       </c>
       <c r="D57" t="n">
-        <v>43.8049</v>
+        <v>44.0155</v>
       </c>
       <c r="E57" t="n">
-        <v>15.7985</v>
+        <v>15.7855</v>
       </c>
       <c r="F57" t="n">
-        <v>37.4171</v>
+        <v>38.1388</v>
       </c>
     </row>
     <row r="58">
@@ -6200,19 +6200,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>15.6903</v>
+        <v>15.6971</v>
       </c>
       <c r="C58" t="n">
-        <v>16.8921</v>
+        <v>16.8703</v>
       </c>
       <c r="D58" t="n">
-        <v>43.8662</v>
+        <v>43.7424</v>
       </c>
       <c r="E58" t="n">
-        <v>15.5397</v>
+        <v>15.5398</v>
       </c>
       <c r="F58" t="n">
-        <v>37.7416</v>
+        <v>38.3535</v>
       </c>
     </row>
     <row r="59">
@@ -6220,19 +6220,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>15.3605</v>
+        <v>15.34</v>
       </c>
       <c r="C59" t="n">
-        <v>16.7938</v>
+        <v>16.7766</v>
       </c>
       <c r="D59" t="n">
-        <v>43.6988</v>
+        <v>44.497</v>
       </c>
       <c r="E59" t="n">
-        <v>15.3382</v>
+        <v>15.3561</v>
       </c>
       <c r="F59" t="n">
-        <v>37.9488</v>
+        <v>37.6277</v>
       </c>
     </row>
     <row r="60">
@@ -6240,19 +6240,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>15.0253</v>
+        <v>15.0322</v>
       </c>
       <c r="C60" t="n">
-        <v>16.6857</v>
+        <v>16.6945</v>
       </c>
       <c r="D60" t="n">
-        <v>44.6861</v>
+        <v>44.375</v>
       </c>
       <c r="E60" t="n">
-        <v>15.1917</v>
+        <v>15.2367</v>
       </c>
       <c r="F60" t="n">
-        <v>38.0639</v>
+        <v>37.1763</v>
       </c>
     </row>
     <row r="61">
@@ -6260,19 +6260,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>14.7367</v>
+        <v>14.7317</v>
       </c>
       <c r="C61" t="n">
-        <v>16.6135</v>
+        <v>16.6029</v>
       </c>
       <c r="D61" t="n">
-        <v>43.8993</v>
+        <v>44.4467</v>
       </c>
       <c r="E61" t="n">
-        <v>14.9204</v>
+        <v>14.9702</v>
       </c>
       <c r="F61" t="n">
-        <v>37.0546</v>
+        <v>37.6119</v>
       </c>
     </row>
     <row r="62">
@@ -6280,19 +6280,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>14.4542</v>
+        <v>14.4742</v>
       </c>
       <c r="C62" t="n">
-        <v>16.5458</v>
+        <v>16.5565</v>
       </c>
       <c r="D62" t="n">
-        <v>44.8308</v>
+        <v>44.8122</v>
       </c>
       <c r="E62" t="n">
-        <v>14.691</v>
+        <v>14.6966</v>
       </c>
       <c r="F62" t="n">
-        <v>37.5191</v>
+        <v>37.5713</v>
       </c>
     </row>
     <row r="63">
@@ -6300,19 +6300,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>14.1805</v>
+        <v>14.1456</v>
       </c>
       <c r="C63" t="n">
-        <v>16.4844</v>
+        <v>16.4888</v>
       </c>
       <c r="D63" t="n">
-        <v>45.3643</v>
+        <v>44.8872</v>
       </c>
       <c r="E63" t="n">
-        <v>18.2729</v>
+        <v>18.2386</v>
       </c>
       <c r="F63" t="n">
-        <v>46.7283</v>
+        <v>46.1628</v>
       </c>
     </row>
     <row r="64">
@@ -6320,19 +6320,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>13.8376</v>
+        <v>13.8442</v>
       </c>
       <c r="C64" t="n">
-        <v>16.3864</v>
+        <v>16.4087</v>
       </c>
       <c r="D64" t="n">
-        <v>50.5406</v>
+        <v>49.7851</v>
       </c>
       <c r="E64" t="n">
-        <v>17.8624</v>
+        <v>17.8593</v>
       </c>
       <c r="F64" t="n">
-        <v>47.0566</v>
+        <v>46.2104</v>
       </c>
     </row>
     <row r="65">
@@ -6340,19 +6340,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>13.4355</v>
+        <v>13.4498</v>
       </c>
       <c r="C65" t="n">
-        <v>17.8914</v>
+        <v>17.8774</v>
       </c>
       <c r="D65" t="n">
-        <v>50.9851</v>
+        <v>50.85</v>
       </c>
       <c r="E65" t="n">
-        <v>17.5828</v>
+        <v>17.9831</v>
       </c>
       <c r="F65" t="n">
-        <v>47.3828</v>
+        <v>46.9122</v>
       </c>
     </row>
     <row r="66">
@@ -6360,19 +6360,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>12.9472</v>
+        <v>12.9911</v>
       </c>
       <c r="C66" t="n">
-        <v>17.7242</v>
+        <v>17.698</v>
       </c>
       <c r="D66" t="n">
-        <v>51.6004</v>
+        <v>51.3087</v>
       </c>
       <c r="E66" t="n">
-        <v>17.3966</v>
+        <v>17.1831</v>
       </c>
       <c r="F66" t="n">
-        <v>47.3493</v>
+        <v>47.5795</v>
       </c>
     </row>
     <row r="67">
@@ -6380,19 +6380,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>17.542</v>
+        <v>17.5493</v>
       </c>
       <c r="C67" t="n">
-        <v>17.5756</v>
+        <v>17.5436</v>
       </c>
       <c r="D67" t="n">
-        <v>52.0708</v>
+        <v>52.0085</v>
       </c>
       <c r="E67" t="n">
-        <v>16.9101</v>
+        <v>16.9462</v>
       </c>
       <c r="F67" t="n">
-        <v>48.1134</v>
+        <v>47.8106</v>
       </c>
     </row>
     <row r="68">
@@ -6400,19 +6400,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>17.2342</v>
+        <v>17.2357</v>
       </c>
       <c r="C68" t="n">
-        <v>17.4068</v>
+        <v>17.4024</v>
       </c>
       <c r="D68" t="n">
-        <v>52.3421</v>
+        <v>52.3264</v>
       </c>
       <c r="E68" t="n">
-        <v>16.6357</v>
+        <v>16.6963</v>
       </c>
       <c r="F68" t="n">
-        <v>48.3961</v>
+        <v>48.2157</v>
       </c>
     </row>
     <row r="69">
@@ -6420,19 +6420,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>16.8997</v>
+        <v>16.902</v>
       </c>
       <c r="C69" t="n">
-        <v>17.2823</v>
+        <v>17.2928</v>
       </c>
       <c r="D69" t="n">
-        <v>52.7054</v>
+        <v>52.8449</v>
       </c>
       <c r="E69" t="n">
-        <v>16.3869</v>
+        <v>16.4375</v>
       </c>
       <c r="F69" t="n">
-        <v>48.2517</v>
+        <v>48.1946</v>
       </c>
     </row>
     <row r="70">
@@ -6440,19 +6440,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>16.5262</v>
+        <v>16.5306</v>
       </c>
       <c r="C70" t="n">
-        <v>17.189</v>
+        <v>17.1619</v>
       </c>
       <c r="D70" t="n">
-        <v>53.2749</v>
+        <v>52.9038</v>
       </c>
       <c r="E70" t="n">
-        <v>16.1656</v>
+        <v>16.1809</v>
       </c>
       <c r="F70" t="n">
-        <v>48.2397</v>
+        <v>48.3388</v>
       </c>
     </row>
     <row r="71">
@@ -6460,19 +6460,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>16.1347</v>
+        <v>16.1614</v>
       </c>
       <c r="C71" t="n">
-        <v>17.0492</v>
+        <v>17.0488</v>
       </c>
       <c r="D71" t="n">
-        <v>53.3522</v>
+        <v>53.5046</v>
       </c>
       <c r="E71" t="n">
-        <v>15.9517</v>
+        <v>15.933</v>
       </c>
       <c r="F71" t="n">
-        <v>48.0789</v>
+        <v>48.1802</v>
       </c>
     </row>
     <row r="72">
@@ -6480,19 +6480,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>15.7715</v>
+        <v>15.785</v>
       </c>
       <c r="C72" t="n">
-        <v>16.9416</v>
+        <v>16.9311</v>
       </c>
       <c r="D72" t="n">
-        <v>53.7234</v>
+        <v>53.2633</v>
       </c>
       <c r="E72" t="n">
-        <v>15.7244</v>
+        <v>15.7656</v>
       </c>
       <c r="F72" t="n">
-        <v>47.9301</v>
+        <v>47.8712</v>
       </c>
     </row>
     <row r="73">
@@ -6500,19 +6500,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>15.4173</v>
+        <v>15.4333</v>
       </c>
       <c r="C73" t="n">
-        <v>16.8604</v>
+        <v>16.844</v>
       </c>
       <c r="D73" t="n">
-        <v>53.7996</v>
+        <v>53.8714</v>
       </c>
       <c r="E73" t="n">
-        <v>15.4988</v>
+        <v>15.5171</v>
       </c>
       <c r="F73" t="n">
-        <v>47.6847</v>
+        <v>47.7985</v>
       </c>
     </row>
     <row r="74">
@@ -6520,19 +6520,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>15.0927</v>
+        <v>15.1013</v>
       </c>
       <c r="C74" t="n">
-        <v>16.7542</v>
+        <v>16.7396</v>
       </c>
       <c r="D74" t="n">
-        <v>54.1378</v>
+        <v>53.9402</v>
       </c>
       <c r="E74" t="n">
-        <v>15.2757</v>
+        <v>15.2793</v>
       </c>
       <c r="F74" t="n">
-        <v>47.4961</v>
+        <v>47.5395</v>
       </c>
     </row>
     <row r="75">
@@ -6540,19 +6540,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>14.7863</v>
+        <v>14.79</v>
       </c>
       <c r="C75" t="n">
-        <v>16.6574</v>
+        <v>16.6701</v>
       </c>
       <c r="D75" t="n">
-        <v>54.3822</v>
+        <v>54.2162</v>
       </c>
       <c r="E75" t="n">
-        <v>15.0908</v>
+        <v>15.0702</v>
       </c>
       <c r="F75" t="n">
-        <v>47.2918</v>
+        <v>47.5063</v>
       </c>
     </row>
     <row r="76">
@@ -6560,19 +6560,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>14.4947</v>
+        <v>14.4978</v>
       </c>
       <c r="C76" t="n">
-        <v>16.5953</v>
+        <v>16.5796</v>
       </c>
       <c r="D76" t="n">
-        <v>54.2686</v>
+        <v>54.2414</v>
       </c>
       <c r="E76" t="n">
-        <v>14.818</v>
+        <v>14.8192</v>
       </c>
       <c r="F76" t="n">
-        <v>46.8596</v>
+        <v>47.0102</v>
       </c>
     </row>
     <row r="77">
@@ -6580,19 +6580,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>14.2152</v>
+        <v>14.1958</v>
       </c>
       <c r="C77" t="n">
-        <v>16.5158</v>
+        <v>16.5199</v>
       </c>
       <c r="D77" t="n">
-        <v>54.5859</v>
+        <v>54.601</v>
       </c>
       <c r="E77" t="n">
-        <v>18.8541</v>
+        <v>19.8348</v>
       </c>
       <c r="F77" t="n">
-        <v>51.3378</v>
+        <v>51.286</v>
       </c>
     </row>
     <row r="78">
@@ -6600,19 +6600,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>13.8836</v>
+        <v>13.866</v>
       </c>
       <c r="C78" t="n">
-        <v>16.4459</v>
+        <v>16.4251</v>
       </c>
       <c r="D78" t="n">
-        <v>57.3971</v>
+        <v>57.5006</v>
       </c>
       <c r="E78" t="n">
-        <v>18.3992</v>
+        <v>18.8821</v>
       </c>
       <c r="F78" t="n">
-        <v>51.0677</v>
+        <v>51.2259</v>
       </c>
     </row>
     <row r="79">
@@ -6620,19 +6620,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>13.5187</v>
+        <v>13.5463</v>
       </c>
       <c r="C79" t="n">
-        <v>17.9854</v>
+        <v>17.9648</v>
       </c>
       <c r="D79" t="n">
-        <v>57.3803</v>
+        <v>57.2601</v>
       </c>
       <c r="E79" t="n">
-        <v>18.6627</v>
+        <v>17.8726</v>
       </c>
       <c r="F79" t="n">
-        <v>50.8359</v>
+        <v>50.7227</v>
       </c>
     </row>
     <row r="80">
@@ -6640,19 +6640,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>13.0915</v>
+        <v>13.1314</v>
       </c>
       <c r="C80" t="n">
-        <v>17.8094</v>
+        <v>17.769</v>
       </c>
       <c r="D80" t="n">
-        <v>57.3783</v>
+        <v>57.4485</v>
       </c>
       <c r="E80" t="n">
-        <v>17.9287</v>
+        <v>17.4398</v>
       </c>
       <c r="F80" t="n">
-        <v>50.4381</v>
+        <v>50.3519</v>
       </c>
     </row>
     <row r="81">
@@ -6660,19 +6660,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>17.6414</v>
+        <v>17.6634</v>
       </c>
       <c r="C81" t="n">
-        <v>17.6072</v>
+        <v>17.6177</v>
       </c>
       <c r="D81" t="n">
-        <v>57.2956</v>
+        <v>57.2397</v>
       </c>
       <c r="E81" t="n">
-        <v>17.3909</v>
+        <v>17.0754</v>
       </c>
       <c r="F81" t="n">
-        <v>50.1475</v>
+        <v>50.0645</v>
       </c>
     </row>
     <row r="82">
@@ -6680,19 +6680,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>17.354</v>
+        <v>17.3459</v>
       </c>
       <c r="C82" t="n">
-        <v>17.4932</v>
+        <v>17.4645</v>
       </c>
       <c r="D82" t="n">
-        <v>57.3084</v>
+        <v>57.371</v>
       </c>
       <c r="E82" t="n">
-        <v>16.898</v>
+        <v>16.8426</v>
       </c>
       <c r="F82" t="n">
-        <v>49.6557</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="83">
@@ -6700,19 +6700,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>16.9953</v>
+        <v>17.0017</v>
       </c>
       <c r="C83" t="n">
-        <v>17.3454</v>
+        <v>17.3394</v>
       </c>
       <c r="D83" t="n">
-        <v>57.4226</v>
+        <v>57.3333</v>
       </c>
       <c r="E83" t="n">
-        <v>16.5176</v>
+        <v>16.5047</v>
       </c>
       <c r="F83" t="n">
-        <v>49.4734</v>
+        <v>49.5362</v>
       </c>
     </row>
     <row r="84">
@@ -6720,19 +6720,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>16.6296</v>
+        <v>16.6289</v>
       </c>
       <c r="C84" t="n">
-        <v>17.2151</v>
+        <v>17.2104</v>
       </c>
       <c r="D84" t="n">
-        <v>60.8665</v>
+        <v>60.8434</v>
       </c>
       <c r="E84" t="n">
-        <v>16.2352</v>
+        <v>16.2774</v>
       </c>
       <c r="F84" t="n">
-        <v>53.7508</v>
+        <v>53.934</v>
       </c>
     </row>
     <row r="85">
@@ -6740,19 +6740,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>16.2529</v>
+        <v>16.2713</v>
       </c>
       <c r="C85" t="n">
-        <v>17.1085</v>
+        <v>17.0786</v>
       </c>
       <c r="D85" t="n">
-        <v>60.8251</v>
+        <v>60.7889</v>
       </c>
       <c r="E85" t="n">
-        <v>16.016</v>
+        <v>16.0244</v>
       </c>
       <c r="F85" t="n">
-        <v>53.6932</v>
+        <v>53.7502</v>
       </c>
     </row>
     <row r="86">
@@ -6760,19 +6760,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>15.8827</v>
+        <v>15.901</v>
       </c>
       <c r="C86" t="n">
-        <v>16.9766</v>
+        <v>16.9752</v>
       </c>
       <c r="D86" t="n">
-        <v>60.7671</v>
+        <v>61.0762</v>
       </c>
       <c r="E86" t="n">
-        <v>15.8988</v>
+        <v>15.7957</v>
       </c>
       <c r="F86" t="n">
-        <v>53.4776</v>
+        <v>53.4819</v>
       </c>
     </row>
     <row r="87">
@@ -6780,19 +6780,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>15.5249</v>
+        <v>15.5351</v>
       </c>
       <c r="C87" t="n">
-        <v>16.879</v>
+        <v>16.8899</v>
       </c>
       <c r="D87" t="n">
-        <v>60.7724</v>
+        <v>60.8725</v>
       </c>
       <c r="E87" t="n">
-        <v>15.5738</v>
+        <v>15.5513</v>
       </c>
       <c r="F87" t="n">
-        <v>53.2347</v>
+        <v>53.0716</v>
       </c>
     </row>
     <row r="88">
@@ -6800,19 +6800,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>15.1979</v>
+        <v>15.1957</v>
       </c>
       <c r="C88" t="n">
-        <v>16.7698</v>
+        <v>16.7737</v>
       </c>
       <c r="D88" t="n">
-        <v>60.7594</v>
+        <v>60.8224</v>
       </c>
       <c r="E88" t="n">
-        <v>15.3376</v>
+        <v>15.3452</v>
       </c>
       <c r="F88" t="n">
-        <v>52.7834</v>
+        <v>53.0163</v>
       </c>
     </row>
     <row r="89">
@@ -6820,19 +6820,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>14.874</v>
+        <v>14.8707</v>
       </c>
       <c r="C89" t="n">
-        <v>16.7026</v>
+        <v>16.6788</v>
       </c>
       <c r="D89" t="n">
-        <v>60.8924</v>
+        <v>60.9644</v>
       </c>
       <c r="E89" t="n">
-        <v>15.1314</v>
+        <v>15.1085</v>
       </c>
       <c r="F89" t="n">
-        <v>52.5724</v>
+        <v>52.5048</v>
       </c>
     </row>
     <row r="90">
@@ -6840,19 +6840,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>14.5661</v>
+        <v>14.5663</v>
       </c>
       <c r="C90" t="n">
-        <v>16.6145</v>
+        <v>16.5936</v>
       </c>
       <c r="D90" t="n">
-        <v>60.6603</v>
+        <v>60.792</v>
       </c>
       <c r="E90" t="n">
-        <v>14.8967</v>
+        <v>14.9071</v>
       </c>
       <c r="F90" t="n">
-        <v>52.5197</v>
+        <v>52.3044</v>
       </c>
     </row>
     <row r="91">
@@ -6860,19 +6860,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>14.2542</v>
+        <v>14.2486</v>
       </c>
       <c r="C91" t="n">
-        <v>16.5156</v>
+        <v>16.5054</v>
       </c>
       <c r="D91" t="n">
-        <v>60.7246</v>
+        <v>60.9437</v>
       </c>
       <c r="E91" t="n">
-        <v>19.2869</v>
+        <v>21.2862</v>
       </c>
       <c r="F91" t="n">
-        <v>56.4228</v>
+        <v>56.2023</v>
       </c>
     </row>
     <row r="92">
@@ -6880,19 +6880,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>13.9203</v>
+        <v>13.9899</v>
       </c>
       <c r="C92" t="n">
-        <v>16.4457</v>
+        <v>16.4284</v>
       </c>
       <c r="D92" t="n">
-        <v>60.9626</v>
+        <v>60.9285</v>
       </c>
       <c r="E92" t="n">
-        <v>19.7095</v>
+        <v>19.8649</v>
       </c>
       <c r="F92" t="n">
-        <v>56.0993</v>
+        <v>55.9386</v>
       </c>
     </row>
     <row r="93">
@@ -6900,19 +6900,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>13.5853</v>
+        <v>13.5742</v>
       </c>
       <c r="C93" t="n">
-        <v>16.3766</v>
+        <v>16.3786</v>
       </c>
       <c r="D93" t="n">
-        <v>61.0451</v>
+        <v>60.7256</v>
       </c>
       <c r="E93" t="n">
-        <v>19.158</v>
+        <v>20.5603</v>
       </c>
       <c r="F93" t="n">
-        <v>56.0175</v>
+        <v>55.9991</v>
       </c>
     </row>
     <row r="94">
@@ -6920,19 +6920,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>13.1377</v>
+        <v>13.1742</v>
       </c>
       <c r="C94" t="n">
-        <v>17.8372</v>
+        <v>17.8094</v>
       </c>
       <c r="D94" t="n">
-        <v>60.86</v>
+        <v>61.0642</v>
       </c>
       <c r="E94" t="n">
-        <v>17.7342</v>
+        <v>19.2432</v>
       </c>
       <c r="F94" t="n">
-        <v>55.4205</v>
+        <v>55.5897</v>
       </c>
     </row>
     <row r="95">
@@ -6940,19 +6940,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>17.7025</v>
+        <v>17.725</v>
       </c>
       <c r="C95" t="n">
-        <v>17.6668</v>
+        <v>17.6486</v>
       </c>
       <c r="D95" t="n">
-        <v>60.7337</v>
+        <v>60.9573</v>
       </c>
       <c r="E95" t="n">
-        <v>17.2311</v>
+        <v>17.8295</v>
       </c>
       <c r="F95" t="n">
-        <v>55.1166</v>
+        <v>55.2563</v>
       </c>
     </row>
     <row r="96">
@@ -6960,19 +6960,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>17.4014</v>
+        <v>17.4028</v>
       </c>
       <c r="C96" t="n">
-        <v>17.5121</v>
+        <v>17.5009</v>
       </c>
       <c r="D96" t="n">
-        <v>60.8041</v>
+        <v>60.7378</v>
       </c>
       <c r="E96" t="n">
-        <v>16.9482</v>
+        <v>17.6385</v>
       </c>
       <c r="F96" t="n">
-        <v>54.6617</v>
+        <v>54.9767</v>
       </c>
     </row>
     <row r="97">
@@ -6980,19 +6980,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>17.0678</v>
+        <v>17.064</v>
       </c>
       <c r="C97" t="n">
-        <v>17.3451</v>
+        <v>17.3569</v>
       </c>
       <c r="D97" t="n">
-        <v>60.6119</v>
+        <v>60.6052</v>
       </c>
       <c r="E97" t="n">
-        <v>17.0863</v>
+        <v>16.595</v>
       </c>
       <c r="F97" t="n">
-        <v>54.382</v>
+        <v>54.4092</v>
       </c>
     </row>
     <row r="98">
@@ -7000,19 +7000,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>16.703</v>
+        <v>16.712</v>
       </c>
       <c r="C98" t="n">
-        <v>17.2322</v>
+        <v>17.2507</v>
       </c>
       <c r="D98" t="n">
-        <v>60.7018</v>
+        <v>60.5393</v>
       </c>
       <c r="E98" t="n">
-        <v>16.2924</v>
+        <v>16.7284</v>
       </c>
       <c r="F98" t="n">
-        <v>54.1229</v>
+        <v>54.1404</v>
       </c>
     </row>
     <row r="99">
@@ -7020,19 +7020,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>16.3331</v>
+        <v>16.3434</v>
       </c>
       <c r="C99" t="n">
-        <v>17.1145</v>
+        <v>17.0942</v>
       </c>
       <c r="D99" t="n">
-        <v>60.4744</v>
+        <v>60.6513</v>
       </c>
       <c r="E99" t="n">
-        <v>16.0837</v>
+        <v>16.0978</v>
       </c>
       <c r="F99" t="n">
-        <v>53.793</v>
+        <v>53.9667</v>
       </c>
     </row>
     <row r="100">
@@ -7040,19 +7040,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>15.9533</v>
+        <v>15.9634</v>
       </c>
       <c r="C100" t="n">
-        <v>16.9971</v>
+        <v>16.9972</v>
       </c>
       <c r="D100" t="n">
-        <v>60.4983</v>
+        <v>60.511</v>
       </c>
       <c r="E100" t="n">
-        <v>15.8671</v>
+        <v>15.8556</v>
       </c>
       <c r="F100" t="n">
-        <v>53.3255</v>
+        <v>53.6678</v>
       </c>
     </row>
     <row r="101">
@@ -7060,19 +7060,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>15.5829</v>
+        <v>15.5988</v>
       </c>
       <c r="C101" t="n">
-        <v>16.8798</v>
+        <v>16.871</v>
       </c>
       <c r="D101" t="n">
-        <v>60.3997</v>
+        <v>60.4951</v>
       </c>
       <c r="E101" t="n">
-        <v>15.6513</v>
+        <v>15.5969</v>
       </c>
       <c r="F101" t="n">
-        <v>53.272</v>
+        <v>53.2358</v>
       </c>
     </row>
     <row r="102">
@@ -7080,19 +7080,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>15.2535</v>
+        <v>15.2469</v>
       </c>
       <c r="C102" t="n">
-        <v>16.7892</v>
+        <v>16.7752</v>
       </c>
       <c r="D102" t="n">
-        <v>60.4678</v>
+        <v>60.4879</v>
       </c>
       <c r="E102" t="n">
-        <v>15.3987</v>
+        <v>15.4185</v>
       </c>
       <c r="F102" t="n">
-        <v>52.9232</v>
+        <v>52.9078</v>
       </c>
     </row>
     <row r="103">
@@ -7100,19 +7100,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>14.9269</v>
+        <v>14.9163</v>
       </c>
       <c r="C103" t="n">
-        <v>16.7207</v>
+        <v>16.695</v>
       </c>
       <c r="D103" t="n">
-        <v>60.4461</v>
+        <v>60.4612</v>
       </c>
       <c r="E103" t="n">
-        <v>15.1533</v>
+        <v>15.1378</v>
       </c>
       <c r="F103" t="n">
-        <v>52.7555</v>
+        <v>52.7462</v>
       </c>
     </row>
     <row r="104">
@@ -7120,19 +7120,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>14.6145</v>
+        <v>14.616</v>
       </c>
       <c r="C104" t="n">
-        <v>16.6042</v>
+        <v>16.6137</v>
       </c>
       <c r="D104" t="n">
-        <v>60.4311</v>
+        <v>60.4717</v>
       </c>
       <c r="E104" t="n">
-        <v>14.9259</v>
+        <v>14.9198</v>
       </c>
       <c r="F104" t="n">
-        <v>52.5324</v>
+        <v>52.4724</v>
       </c>
     </row>
     <row r="105">
@@ -7140,19 +7140,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>14.3118</v>
+        <v>14.3167</v>
       </c>
       <c r="C105" t="n">
-        <v>16.5391</v>
+        <v>16.5362</v>
       </c>
       <c r="D105" t="n">
-        <v>60.3356</v>
+        <v>60.4042</v>
       </c>
       <c r="E105" t="n">
-        <v>21.864</v>
+        <v>21.931</v>
       </c>
       <c r="F105" t="n">
-        <v>56.4613</v>
+        <v>56.351</v>
       </c>
     </row>
     <row r="106">
@@ -7160,19 +7160,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>14.0036</v>
+        <v>14.0124</v>
       </c>
       <c r="C106" t="n">
-        <v>16.4469</v>
+        <v>16.46</v>
       </c>
       <c r="D106" t="n">
-        <v>60.2666</v>
+        <v>60.417</v>
       </c>
       <c r="E106" t="n">
-        <v>20.0416</v>
+        <v>21.5265</v>
       </c>
       <c r="F106" t="n">
-        <v>56.3112</v>
+        <v>56.1426</v>
       </c>
     </row>
     <row r="107">
@@ -7180,19 +7180,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>13.6673</v>
+        <v>13.6749</v>
       </c>
       <c r="C107" t="n">
-        <v>16.383</v>
+        <v>16.3831</v>
       </c>
       <c r="D107" t="n">
-        <v>59.1737</v>
+        <v>59.1002</v>
       </c>
       <c r="E107" t="n">
-        <v>18.4966</v>
+        <v>20.5863</v>
       </c>
       <c r="F107" t="n">
-        <v>55.9325</v>
+        <v>55.7781</v>
       </c>
     </row>
     <row r="108">
@@ -7200,19 +7200,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>13.2876</v>
+        <v>13.282</v>
       </c>
       <c r="C108" t="n">
-        <v>17.8792</v>
+        <v>17.8265</v>
       </c>
       <c r="D108" t="n">
-        <v>59.241</v>
+        <v>59.2633</v>
       </c>
       <c r="E108" t="n">
-        <v>17.6912</v>
+        <v>20.4335</v>
       </c>
       <c r="F108" t="n">
-        <v>55.5661</v>
+        <v>55.87</v>
       </c>
     </row>
     <row r="109">
@@ -7220,19 +7220,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>12.7175</v>
+        <v>12.7171</v>
       </c>
       <c r="C109" t="n">
-        <v>17.6973</v>
+        <v>17.6748</v>
       </c>
       <c r="D109" t="n">
-        <v>59.2367</v>
+        <v>59.2501</v>
       </c>
       <c r="E109" t="n">
-        <v>18.5789</v>
+        <v>19.8212</v>
       </c>
       <c r="F109" t="n">
-        <v>55.1126</v>
+        <v>55.2585</v>
       </c>
     </row>
     <row r="110">
@@ -7240,19 +7240,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>17.4692</v>
+        <v>17.464</v>
       </c>
       <c r="C110" t="n">
-        <v>17.5191</v>
+        <v>17.5176</v>
       </c>
       <c r="D110" t="n">
-        <v>59.5776</v>
+        <v>59.3827</v>
       </c>
       <c r="E110" t="n">
-        <v>18.3346</v>
+        <v>17.9074</v>
       </c>
       <c r="F110" t="n">
-        <v>55.0376</v>
+        <v>54.8752</v>
       </c>
     </row>
     <row r="111">
@@ -7260,19 +7260,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>17.1351</v>
+        <v>17.1522</v>
       </c>
       <c r="C111" t="n">
-        <v>17.3918</v>
+        <v>17.3696</v>
       </c>
       <c r="D111" t="n">
-        <v>59.4531</v>
+        <v>59.541</v>
       </c>
       <c r="E111" t="n">
-        <v>17.4175</v>
+        <v>18.0785</v>
       </c>
       <c r="F111" t="n">
-        <v>54.3895</v>
+        <v>54.2428</v>
       </c>
     </row>
     <row r="112">
@@ -7280,19 +7280,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>16.7763</v>
+        <v>16.7964</v>
       </c>
       <c r="C112" t="n">
-        <v>17.2633</v>
+        <v>17.239</v>
       </c>
       <c r="D112" t="n">
-        <v>59.4397</v>
+        <v>59.4302</v>
       </c>
       <c r="E112" t="n">
-        <v>16.9787</v>
+        <v>17.2629</v>
       </c>
       <c r="F112" t="n">
-        <v>54.3634</v>
+        <v>54.3059</v>
       </c>
     </row>
     <row r="113">
@@ -7300,19 +7300,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>16.4121</v>
+        <v>16.4204</v>
       </c>
       <c r="C113" t="n">
-        <v>17.1215</v>
+        <v>17.1076</v>
       </c>
       <c r="D113" t="n">
-        <v>59.57</v>
+        <v>59.5539</v>
       </c>
       <c r="E113" t="n">
-        <v>16.2391</v>
+        <v>17.7172</v>
       </c>
       <c r="F113" t="n">
-        <v>53.9556</v>
+        <v>53.985</v>
       </c>
     </row>
     <row r="114">
@@ -7320,19 +7320,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>16.0321</v>
+        <v>16.0324</v>
       </c>
       <c r="C114" t="n">
-        <v>16.9936</v>
+        <v>16.99</v>
       </c>
       <c r="D114" t="n">
-        <v>59.464</v>
+        <v>60.2128</v>
       </c>
       <c r="E114" t="n">
-        <v>15.9928</v>
+        <v>16.0572</v>
       </c>
       <c r="F114" t="n">
-        <v>53.5973</v>
+        <v>53.6821</v>
       </c>
     </row>
     <row r="115">
@@ -7340,19 +7340,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>15.6698</v>
+        <v>15.671</v>
       </c>
       <c r="C115" t="n">
-        <v>16.8847</v>
+        <v>16.8762</v>
       </c>
       <c r="D115" t="n">
-        <v>59.6467</v>
+        <v>59.5144</v>
       </c>
       <c r="E115" t="n">
-        <v>15.6544</v>
+        <v>16.6478</v>
       </c>
       <c r="F115" t="n">
-        <v>53.192</v>
+        <v>53.0912</v>
       </c>
     </row>
     <row r="116">
@@ -7360,19 +7360,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>15.3169</v>
+        <v>15.3162</v>
       </c>
       <c r="C116" t="n">
-        <v>16.794</v>
+        <v>16.7942</v>
       </c>
       <c r="D116" t="n">
-        <v>59.6343</v>
+        <v>59.5319</v>
       </c>
       <c r="E116" t="n">
-        <v>15.4479</v>
+        <v>15.4335</v>
       </c>
       <c r="F116" t="n">
-        <v>52.8301</v>
+        <v>52.8332</v>
       </c>
     </row>
     <row r="117">
@@ -7380,19 +7380,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>14.9861</v>
+        <v>14.9862</v>
       </c>
       <c r="C117" t="n">
-        <v>16.7135</v>
+        <v>16.7016</v>
       </c>
       <c r="D117" t="n">
-        <v>59.5384</v>
+        <v>59.6279</v>
       </c>
       <c r="E117" t="n">
-        <v>15.2256</v>
+        <v>15.2178</v>
       </c>
       <c r="F117" t="n">
-        <v>52.5364</v>
+        <v>52.5648</v>
       </c>
     </row>
     <row r="118">
@@ -7400,19 +7400,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>14.6908</v>
+        <v>14.677</v>
       </c>
       <c r="C118" t="n">
-        <v>16.6139</v>
+        <v>16.5997</v>
       </c>
       <c r="D118" t="n">
-        <v>59.5018</v>
+        <v>59.6468</v>
       </c>
       <c r="E118" t="n">
-        <v>15.0012</v>
+        <v>14.9736</v>
       </c>
       <c r="F118" t="n">
-        <v>52.2882</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="119">
@@ -7420,19 +7420,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>14.3645</v>
+        <v>14.3742</v>
       </c>
       <c r="C119" t="n">
-        <v>16.5392</v>
+        <v>16.5292</v>
       </c>
       <c r="D119" t="n">
-        <v>59.6179</v>
+        <v>59.5884</v>
       </c>
       <c r="E119" t="n">
-        <v>22.1022</v>
+        <v>21.5949</v>
       </c>
       <c r="F119" t="n">
-        <v>56.5416</v>
+        <v>56.5616</v>
       </c>
     </row>
     <row r="120">
@@ -7440,19 +7440,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>14.0512</v>
+        <v>14.07</v>
       </c>
       <c r="C120" t="n">
-        <v>16.4801</v>
+        <v>16.4459</v>
       </c>
       <c r="D120" t="n">
-        <v>59.6129</v>
+        <v>59.5675</v>
       </c>
       <c r="E120" t="n">
-        <v>21.3392</v>
+        <v>21.7389</v>
       </c>
       <c r="F120" t="n">
-        <v>56.0789</v>
+        <v>56.1632</v>
       </c>
     </row>
     <row r="121">
@@ -7460,19 +7460,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>13.7211</v>
+        <v>13.7259</v>
       </c>
       <c r="C121" t="n">
-        <v>16.4032</v>
+        <v>16.3882</v>
       </c>
       <c r="D121" t="n">
-        <v>61.6465</v>
+        <v>61.6818</v>
       </c>
       <c r="E121" t="n">
-        <v>20.2431</v>
+        <v>21.225</v>
       </c>
       <c r="F121" t="n">
-        <v>55.9769</v>
+        <v>55.9706</v>
       </c>
     </row>
     <row r="122">
@@ -7480,19 +7480,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>13.3723</v>
+        <v>13.3195</v>
       </c>
       <c r="C122" t="n">
-        <v>17.8657</v>
+        <v>17.8503</v>
       </c>
       <c r="D122" t="n">
-        <v>61.4461</v>
+        <v>61.398</v>
       </c>
       <c r="E122" t="n">
-        <v>19.3867</v>
+        <v>20.3105</v>
       </c>
       <c r="F122" t="n">
-        <v>55.5689</v>
+        <v>55.3493</v>
       </c>
     </row>
     <row r="123">
@@ -7500,19 +7500,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>12.8157</v>
+        <v>12.8368</v>
       </c>
       <c r="C123" t="n">
-        <v>17.7061</v>
+        <v>17.6872</v>
       </c>
       <c r="D123" t="n">
-        <v>61.3317</v>
+        <v>61.425</v>
       </c>
       <c r="E123" t="n">
-        <v>19.0943</v>
+        <v>19.5877</v>
       </c>
       <c r="F123" t="n">
-        <v>55.1109</v>
+        <v>54.9904</v>
       </c>
     </row>
     <row r="124">
@@ -7520,19 +7520,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>17.532</v>
+        <v>17.5189</v>
       </c>
       <c r="C124" t="n">
-        <v>17.5526</v>
+        <v>17.5327</v>
       </c>
       <c r="D124" t="n">
-        <v>61.27</v>
+        <v>61.2718</v>
       </c>
       <c r="E124" t="n">
-        <v>17.5873</v>
+        <v>19.2668</v>
       </c>
       <c r="F124" t="n">
-        <v>54.9004</v>
+        <v>54.6465</v>
       </c>
     </row>
     <row r="125">
@@ -7540,19 +7540,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>17.2138</v>
+        <v>17.2108</v>
       </c>
       <c r="C125" t="n">
-        <v>17.3881</v>
+        <v>17.3927</v>
       </c>
       <c r="D125" t="n">
-        <v>61.2744</v>
+        <v>61.2364</v>
       </c>
       <c r="E125" t="n">
-        <v>17.0553</v>
+        <v>17.6856</v>
       </c>
       <c r="F125" t="n">
-        <v>54.3437</v>
+        <v>54.3941</v>
       </c>
     </row>
     <row r="126">
@@ -7560,19 +7560,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>16.867</v>
+        <v>16.8556</v>
       </c>
       <c r="C126" t="n">
-        <v>17.2558</v>
+        <v>17.2503</v>
       </c>
       <c r="D126" t="n">
-        <v>61.1834</v>
+        <v>61.1898</v>
       </c>
       <c r="E126" t="n">
-        <v>16.5703</v>
+        <v>16.7604</v>
       </c>
       <c r="F126" t="n">
-        <v>54.0549</v>
+        <v>54.1749</v>
       </c>
     </row>
     <row r="127">
@@ -7580,19 +7580,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>16.5074</v>
+        <v>16.4949</v>
       </c>
       <c r="C127" t="n">
-        <v>17.1524</v>
+        <v>17.1164</v>
       </c>
       <c r="D127" t="n">
-        <v>61.1209</v>
+        <v>61.0295</v>
       </c>
       <c r="E127" t="n">
-        <v>16.5426</v>
+        <v>17.6601</v>
       </c>
       <c r="F127" t="n">
-        <v>53.7114</v>
+        <v>53.6883</v>
       </c>
     </row>
     <row r="128">
@@ -7600,19 +7600,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>16.1115</v>
+        <v>16.1211</v>
       </c>
       <c r="C128" t="n">
-        <v>17.0093</v>
+        <v>16.994</v>
       </c>
       <c r="D128" t="n">
-        <v>61.0583</v>
+        <v>61.0044</v>
       </c>
       <c r="E128" t="n">
-        <v>16.4538</v>
+        <v>16.0332</v>
       </c>
       <c r="F128" t="n">
-        <v>53.1891</v>
+        <v>53.6509</v>
       </c>
     </row>
     <row r="129">
@@ -7620,19 +7620,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>15.7522</v>
+        <v>15.7479</v>
       </c>
       <c r="C129" t="n">
-        <v>16.933</v>
+        <v>16.8797</v>
       </c>
       <c r="D129" t="n">
-        <v>61.055</v>
+        <v>60.9678</v>
       </c>
       <c r="E129" t="n">
-        <v>15.7652</v>
+        <v>15.88</v>
       </c>
       <c r="F129" t="n">
-        <v>53.1347</v>
+        <v>53.1454</v>
       </c>
     </row>
     <row r="130">
@@ -7640,19 +7640,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>15.4069</v>
+        <v>15.4011</v>
       </c>
       <c r="C130" t="n">
-        <v>16.8241</v>
+        <v>16.7882</v>
       </c>
       <c r="D130" t="n">
-        <v>60.8876</v>
+        <v>60.9951</v>
       </c>
       <c r="E130" t="n">
-        <v>15.544</v>
+        <v>15.7717</v>
       </c>
       <c r="F130" t="n">
-        <v>52.5639</v>
+        <v>52.6914</v>
       </c>
     </row>
     <row r="131">
@@ -7660,19 +7660,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>15.0589</v>
+        <v>15.0675</v>
       </c>
       <c r="C131" t="n">
-        <v>16.7179</v>
+        <v>16.6952</v>
       </c>
       <c r="D131" t="n">
-        <v>60.7586</v>
+        <v>60.8436</v>
       </c>
       <c r="E131" t="n">
-        <v>15.2709</v>
+        <v>15.4405</v>
       </c>
       <c r="F131" t="n">
-        <v>52.5693</v>
+        <v>52.406</v>
       </c>
     </row>
     <row r="132">
@@ -7680,19 +7680,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>14.7364</v>
+        <v>14.734</v>
       </c>
       <c r="C132" t="n">
-        <v>16.6543</v>
+        <v>16.6159</v>
       </c>
       <c r="D132" t="n">
-        <v>60.7432</v>
+        <v>60.7773</v>
       </c>
       <c r="E132" t="n">
-        <v>15.0207</v>
+        <v>15.0423</v>
       </c>
       <c r="F132" t="n">
-        <v>52.1602</v>
+        <v>52.032</v>
       </c>
     </row>
     <row r="133">
@@ -7700,19 +7700,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>14.4231</v>
+        <v>14.433</v>
       </c>
       <c r="C133" t="n">
-        <v>16.5434</v>
+        <v>16.5488</v>
       </c>
       <c r="D133" t="n">
-        <v>60.6807</v>
+        <v>60.7882</v>
       </c>
       <c r="E133" t="n">
-        <v>14.8036</v>
+        <v>14.803</v>
       </c>
       <c r="F133" t="n">
-        <v>52.0732</v>
+        <v>51.6347</v>
       </c>
     </row>
     <row r="134">
@@ -7720,19 +7720,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.1103</v>
+        <v>14.1328</v>
       </c>
       <c r="C134" t="n">
-        <v>16.4693</v>
+        <v>16.4611</v>
       </c>
       <c r="D134" t="n">
-        <v>60.6875</v>
+        <v>60.715</v>
       </c>
       <c r="E134" t="n">
-        <v>21.6124</v>
+        <v>21.3874</v>
       </c>
       <c r="F134" t="n">
-        <v>56.0394</v>
+        <v>55.9479</v>
       </c>
     </row>
     <row r="135">
@@ -7740,19 +7740,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>13.7898</v>
+        <v>13.7984</v>
       </c>
       <c r="C135" t="n">
-        <v>16.4121</v>
+        <v>16.4</v>
       </c>
       <c r="D135" t="n">
-        <v>62.1823</v>
+        <v>62.1114</v>
       </c>
       <c r="E135" t="n">
-        <v>20.6456</v>
+        <v>20.5895</v>
       </c>
       <c r="F135" t="n">
-        <v>55.6848</v>
+        <v>55.6008</v>
       </c>
     </row>
     <row r="136">
@@ -7760,19 +7760,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>13.4419</v>
+        <v>13.3952</v>
       </c>
       <c r="C136" t="n">
-        <v>17.9109</v>
+        <v>17.8824</v>
       </c>
       <c r="D136" t="n">
-        <v>61.9857</v>
+        <v>61.8408</v>
       </c>
       <c r="E136" t="n">
-        <v>20.5321</v>
+        <v>20.4967</v>
       </c>
       <c r="F136" t="n">
-        <v>55.3341</v>
+        <v>55.0615</v>
       </c>
     </row>
     <row r="137">
@@ -7780,19 +7780,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>12.9271</v>
+        <v>12.9428</v>
       </c>
       <c r="C137" t="n">
-        <v>17.7393</v>
+        <v>17.7131</v>
       </c>
       <c r="D137" t="n">
-        <v>61.7364</v>
+        <v>61.8438</v>
       </c>
       <c r="E137" t="n">
-        <v>18.7197</v>
+        <v>18.7735</v>
       </c>
       <c r="F137" t="n">
-        <v>55.197</v>
+        <v>54.9698</v>
       </c>
     </row>
     <row r="138">
@@ -7800,19 +7800,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>17.6207</v>
+        <v>17.5879</v>
       </c>
       <c r="C138" t="n">
-        <v>17.5831</v>
+        <v>17.5414</v>
       </c>
       <c r="D138" t="n">
-        <v>61.6127</v>
+        <v>61.7175</v>
       </c>
       <c r="E138" t="n">
-        <v>18.8887</v>
+        <v>18.2967</v>
       </c>
       <c r="F138" t="n">
-        <v>54.4228</v>
+        <v>54.7192</v>
       </c>
     </row>
     <row r="139">
@@ -7820,19 +7820,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>17.2723</v>
+        <v>17.295</v>
       </c>
       <c r="C139" t="n">
-        <v>17.431</v>
+        <v>17.385</v>
       </c>
       <c r="D139" t="n">
-        <v>61.5456</v>
+        <v>61.6483</v>
       </c>
       <c r="E139" t="n">
-        <v>17.476</v>
+        <v>19.118</v>
       </c>
       <c r="F139" t="n">
-        <v>54.094</v>
+        <v>54.095</v>
       </c>
     </row>
     <row r="140">
@@ -7840,19 +7840,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>16.9273</v>
+        <v>16.9442</v>
       </c>
       <c r="C140" t="n">
-        <v>17.2964</v>
+        <v>17.2615</v>
       </c>
       <c r="D140" t="n">
-        <v>61.4534</v>
+        <v>61.4937</v>
       </c>
       <c r="E140" t="n">
-        <v>17.5837</v>
+        <v>18.4088</v>
       </c>
       <c r="F140" t="n">
-        <v>53.9205</v>
+        <v>53.9673</v>
       </c>
     </row>
     <row r="141">
@@ -7860,19 +7860,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>16.5711</v>
+        <v>16.5618</v>
       </c>
       <c r="C141" t="n">
-        <v>17.1458</v>
+        <v>17.1528</v>
       </c>
       <c r="D141" t="n">
-        <v>61.3739</v>
+        <v>61.4567</v>
       </c>
       <c r="E141" t="n">
-        <v>16.8677</v>
+        <v>16.6181</v>
       </c>
       <c r="F141" t="n">
-        <v>53.5919</v>
+        <v>53.6217</v>
       </c>
     </row>
     <row r="142">
@@ -7880,19 +7880,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>16.1862</v>
+        <v>16.1932</v>
       </c>
       <c r="C142" t="n">
-        <v>17.0161</v>
+        <v>17.0174</v>
       </c>
       <c r="D142" t="n">
-        <v>61.2963</v>
+        <v>61.3418</v>
       </c>
       <c r="E142" t="n">
-        <v>17.1194</v>
+        <v>16.7215</v>
       </c>
       <c r="F142" t="n">
-        <v>53.0587</v>
+        <v>53.1247</v>
       </c>
     </row>
     <row r="143">
@@ -7900,19 +7900,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>15.8115</v>
+        <v>15.8258</v>
       </c>
       <c r="C143" t="n">
-        <v>16.9109</v>
+        <v>16.9085</v>
       </c>
       <c r="D143" t="n">
-        <v>61.265</v>
+        <v>61.2578</v>
       </c>
       <c r="E143" t="n">
-        <v>15.9641</v>
+        <v>15.9913</v>
       </c>
       <c r="F143" t="n">
-        <v>53.1579</v>
+        <v>52.8958</v>
       </c>
     </row>
   </sheetData>
